--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA85A58-F18D-441D-BE3D-F6532E314643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B75252AA-B726-4E45-9B7F-E12568D27168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30816" yWindow="-4356" windowWidth="19236" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C-9-12" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="132">
   <si>
     <t>PUNTO DE ACTA DE CONTRATO</t>
   </si>
@@ -502,6 +502,9 @@
   </si>
   <si>
     <t>CONDICIONES ESPECIALES</t>
+  </si>
+  <si>
+    <t>{{LIDER}}</t>
   </si>
 </sst>
 </file>
@@ -1894,321 +1897,354 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2224,8 +2260,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2234,6 +2271,152 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2248,6 +2431,12 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2255,221 +2444,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2942,19 +2945,19 @@
       <c r="C3" s="48"/>
       <c r="D3" s="49"/>
       <c r="E3" s="48"/>
-      <c r="F3" s="228" t="s">
+      <c r="F3" s="203" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="187"/>
       <c r="K3" s="52"/>
-      <c r="L3" s="228" t="s">
+      <c r="L3" s="203" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="172"/>
-      <c r="N3" s="172"/>
+      <c r="M3" s="187"/>
+      <c r="N3" s="187"/>
       <c r="O3" s="53"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="48"/>
@@ -2971,11 +2974,11 @@
       <c r="I4" s="51"/>
       <c r="J4" s="52"/>
       <c r="K4" s="52"/>
-      <c r="L4" s="263" t="s">
+      <c r="L4" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="156"/>
-      <c r="N4" s="156"/>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
       <c r="O4" s="53"/>
       <c r="P4" s="52"/>
       <c r="Q4" s="48"/>
@@ -2986,19 +2989,19 @@
       <c r="C5" s="48"/>
       <c r="D5" s="49"/>
       <c r="E5" s="48"/>
-      <c r="F5" s="245" t="s">
+      <c r="F5" s="171" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="246"/>
-      <c r="H5" s="242" t="s">
+      <c r="G5" s="172"/>
+      <c r="H5" s="173" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="243"/>
-      <c r="J5" s="243"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="174"/>
       <c r="K5" s="52"/>
-      <c r="L5" s="156"/>
-      <c r="M5" s="156"/>
-      <c r="N5" s="156"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
+      <c r="N5" s="119"/>
       <c r="O5" s="53"/>
       <c r="P5" s="52"/>
       <c r="Q5" s="48"/>
@@ -3010,23 +3013,23 @@
       <c r="C6" s="48"/>
       <c r="D6" s="49"/>
       <c r="E6" s="48"/>
-      <c r="F6" s="225" t="s">
+      <c r="F6" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="172"/>
-      <c r="H6" s="242" t="s">
+      <c r="G6" s="187"/>
+      <c r="H6" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="243"/>
-      <c r="J6" s="243"/>
+      <c r="I6" s="174"/>
+      <c r="J6" s="174"/>
       <c r="K6" s="52"/>
-      <c r="L6" s="254" t="s">
+      <c r="L6" s="186" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="255" t="s">
+      <c r="M6" s="192" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="256"/>
+      <c r="N6" s="193"/>
       <c r="O6" s="53"/>
       <c r="P6" s="52"/>
       <c r="Q6" s="48"/>
@@ -3043,9 +3046,9 @@
       <c r="I7" s="57"/>
       <c r="J7" s="58"/>
       <c r="K7" s="52"/>
-      <c r="L7" s="172"/>
-      <c r="M7" s="257"/>
-      <c r="N7" s="257"/>
+      <c r="L7" s="187"/>
+      <c r="M7" s="194"/>
+      <c r="N7" s="194"/>
       <c r="O7" s="53"/>
       <c r="P7" s="52"/>
       <c r="Q7" s="48"/>
@@ -3056,19 +3059,19 @@
       <c r="C8" s="48"/>
       <c r="D8" s="49"/>
       <c r="E8" s="48"/>
-      <c r="F8" s="239" t="s">
+      <c r="F8" s="218" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="172"/>
-      <c r="H8" s="240" t="s">
+      <c r="G8" s="187"/>
+      <c r="H8" s="219" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="241"/>
-      <c r="J8" s="241"/>
+      <c r="I8" s="220"/>
+      <c r="J8" s="220"/>
       <c r="K8" s="52"/>
-      <c r="L8" s="172"/>
-      <c r="M8" s="258"/>
-      <c r="N8" s="258"/>
+      <c r="L8" s="187"/>
+      <c r="M8" s="195"/>
+      <c r="N8" s="195"/>
       <c r="O8" s="52"/>
       <c r="P8" s="52"/>
       <c r="Q8" s="48"/>
@@ -3135,24 +3138,24 @@
     <row r="12" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="59"/>
       <c r="C12" s="59"/>
-      <c r="D12" s="249" t="s">
+      <c r="D12" s="179" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="250"/>
-      <c r="F12" s="247" t="s">
+      <c r="E12" s="180"/>
+      <c r="F12" s="177" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="248"/>
-      <c r="H12" s="248"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="248"/>
+      <c r="G12" s="178"/>
+      <c r="H12" s="178"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="178"/>
       <c r="K12" s="65"/>
-      <c r="L12" s="261" t="s">
+      <c r="L12" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="172"/>
-      <c r="N12" s="172"/>
-      <c r="O12" s="262"/>
+      <c r="M12" s="187"/>
+      <c r="N12" s="187"/>
+      <c r="O12" s="200"/>
       <c r="P12" s="98" t="s">
         <v>14</v>
       </c>
@@ -3162,24 +3165,24 @@
     <row r="13" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
-      <c r="D13" s="226" t="s">
+      <c r="D13" s="154" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="227"/>
-      <c r="F13" s="237" t="s">
+      <c r="E13" s="155"/>
+      <c r="F13" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="176"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="176"/>
       <c r="K13" s="66"/>
-      <c r="L13" s="265" t="s">
+      <c r="L13" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="266"/>
-      <c r="N13" s="266"/>
-      <c r="O13" s="266"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="129"/>
+      <c r="O13" s="129"/>
       <c r="P13" s="6" t="s">
         <v>18</v>
       </c>
@@ -3189,24 +3192,24 @@
     <row r="14" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
-      <c r="D14" s="226" t="s">
+      <c r="D14" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="227"/>
-      <c r="F14" s="237" t="s">
+      <c r="E14" s="155"/>
+      <c r="F14" s="175" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="238"/>
-      <c r="H14" s="238"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="238"/>
+      <c r="G14" s="176"/>
+      <c r="H14" s="176"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="176"/>
       <c r="K14" s="67"/>
-      <c r="L14" s="259" t="s">
+      <c r="L14" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="260"/>
-      <c r="N14" s="260"/>
-      <c r="O14" s="260"/>
+      <c r="M14" s="131"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="131"/>
       <c r="P14" s="6" t="s">
         <v>22</v>
       </c>
@@ -3216,24 +3219,24 @@
     <row r="15" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
-      <c r="D15" s="226" t="s">
+      <c r="D15" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="227"/>
-      <c r="F15" s="237" t="s">
+      <c r="E15" s="155"/>
+      <c r="F15" s="175" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="238"/>
-      <c r="H15" s="238"/>
-      <c r="I15" s="238"/>
-      <c r="J15" s="238"/>
+      <c r="G15" s="176"/>
+      <c r="H15" s="176"/>
+      <c r="I15" s="176"/>
+      <c r="J15" s="176"/>
       <c r="K15" s="55"/>
-      <c r="L15" s="259" t="s">
+      <c r="L15" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="260"/>
-      <c r="N15" s="260"/>
-      <c r="O15" s="260"/>
+      <c r="M15" s="131"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="131"/>
       <c r="P15" s="6" t="s">
         <v>26</v>
       </c>
@@ -3243,24 +3246,24 @@
     <row r="16" spans="2:21" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
-      <c r="D16" s="264" t="s">
+      <c r="D16" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="235"/>
-      <c r="F16" s="253" t="s">
+      <c r="E16" s="127"/>
+      <c r="F16" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
-      <c r="I16" s="238"/>
-      <c r="J16" s="238"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="176"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="176"/>
       <c r="K16" s="65"/>
-      <c r="L16" s="259" t="s">
+      <c r="L16" s="130" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="260"/>
-      <c r="N16" s="260"/>
-      <c r="O16" s="260"/>
+      <c r="M16" s="131"/>
+      <c r="N16" s="131"/>
+      <c r="O16" s="131"/>
       <c r="P16" s="6" t="s">
         <v>30</v>
       </c>
@@ -3274,8 +3277,8 @@
       <c r="E17" s="62"/>
       <c r="F17" s="63"/>
       <c r="G17" s="63"/>
-      <c r="H17" s="194"/>
-      <c r="I17" s="154"/>
+      <c r="H17" s="224"/>
+      <c r="I17" s="207"/>
       <c r="J17" s="64"/>
       <c r="K17" s="66"/>
       <c r="L17" s="55"/>
@@ -3288,23 +3291,23 @@
     <row r="18" spans="2:19" s="7" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="75"/>
       <c r="C18" s="75"/>
-      <c r="D18" s="252" t="s">
+      <c r="D18" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="187"/>
-      <c r="F18" s="187"/>
-      <c r="G18" s="187"/>
-      <c r="H18" s="187"/>
-      <c r="I18" s="187"/>
-      <c r="J18" s="188"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="125"/>
       <c r="K18" s="73"/>
-      <c r="L18" s="214" t="s">
+      <c r="L18" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="M18" s="187"/>
-      <c r="N18" s="187"/>
-      <c r="O18" s="187"/>
-      <c r="P18" s="188"/>
+      <c r="M18" s="124"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="125"/>
       <c r="Q18" s="55"/>
       <c r="R18" s="55"/>
       <c r="S18" s="1"/>
@@ -3312,24 +3315,24 @@
     <row r="19" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="74"/>
       <c r="C19" s="74"/>
-      <c r="D19" s="173" t="s">
+      <c r="D19" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="174"/>
-      <c r="F19" s="174"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="175"/>
-      <c r="I19" s="182" t="s">
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="208" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="174"/>
+      <c r="J19" s="121"/>
       <c r="K19" s="55"/>
-      <c r="L19" s="186" t="s">
+      <c r="L19" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="187"/>
-      <c r="N19" s="187"/>
-      <c r="O19" s="188"/>
+      <c r="M19" s="124"/>
+      <c r="N19" s="124"/>
+      <c r="O19" s="125"/>
       <c r="P19" s="84" t="s">
         <v>35</v>
       </c>
@@ -3339,24 +3342,24 @@
     <row r="20" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
-      <c r="D20" s="207" t="s">
+      <c r="D20" s="183" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="174"/>
-      <c r="F20" s="174"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="175"/>
-      <c r="I20" s="197" t="s">
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="189" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="174"/>
+      <c r="J20" s="121"/>
       <c r="K20" s="55"/>
-      <c r="L20" s="212" t="s">
+      <c r="L20" s="234" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="187"/>
-      <c r="N20" s="187"/>
-      <c r="O20" s="188"/>
+      <c r="M20" s="124"/>
+      <c r="N20" s="124"/>
+      <c r="O20" s="125"/>
       <c r="P20" s="85" t="s">
         <v>37</v>
       </c>
@@ -3366,24 +3369,24 @@
     <row r="21" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
-      <c r="D21" s="173" t="s">
+      <c r="D21" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="174"/>
-      <c r="F21" s="174"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="175"/>
-      <c r="I21" s="182" t="s">
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="122"/>
+      <c r="I21" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="174"/>
+      <c r="J21" s="121"/>
       <c r="K21" s="55"/>
-      <c r="L21" s="186" t="s">
+      <c r="L21" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="187"/>
-      <c r="N21" s="187"/>
-      <c r="O21" s="188"/>
+      <c r="M21" s="124"/>
+      <c r="N21" s="124"/>
+      <c r="O21" s="125"/>
       <c r="P21" s="84" t="s">
         <v>37</v>
       </c>
@@ -3393,24 +3396,24 @@
     <row r="22" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
-      <c r="D22" s="207" t="s">
+      <c r="D22" s="183" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="174"/>
-      <c r="F22" s="174"/>
-      <c r="G22" s="174"/>
-      <c r="H22" s="175"/>
-      <c r="I22" s="197" t="s">
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="122"/>
+      <c r="I22" s="189" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="174"/>
+      <c r="J22" s="121"/>
       <c r="K22" s="55"/>
-      <c r="L22" s="231" t="s">
+      <c r="L22" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="232"/>
-      <c r="N22" s="232"/>
-      <c r="O22" s="233"/>
+      <c r="M22" s="215"/>
+      <c r="N22" s="215"/>
+      <c r="O22" s="216"/>
       <c r="P22" s="86" t="s">
         <v>41</v>
       </c>
@@ -3420,17 +3423,17 @@
     <row r="23" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
-      <c r="D23" s="173" t="s">
+      <c r="D23" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="174"/>
-      <c r="F23" s="174"/>
-      <c r="G23" s="174"/>
-      <c r="H23" s="175"/>
-      <c r="I23" s="182" t="s">
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="121"/>
+      <c r="H23" s="122"/>
+      <c r="I23" s="208" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="174"/>
+      <c r="J23" s="121"/>
       <c r="K23" s="55"/>
       <c r="L23" s="82"/>
       <c r="M23" s="82"/>
@@ -3443,49 +3446,49 @@
     <row r="24" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
-      <c r="D24" s="207" t="s">
+      <c r="D24" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="174"/>
-      <c r="F24" s="174"/>
-      <c r="G24" s="174"/>
-      <c r="H24" s="175"/>
-      <c r="I24" s="197" t="s">
+      <c r="E24" s="121"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="121"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="174"/>
+      <c r="J24" s="121"/>
       <c r="K24" s="55"/>
-      <c r="L24" s="214" t="s">
+      <c r="L24" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="187"/>
-      <c r="N24" s="187"/>
-      <c r="O24" s="187"/>
-      <c r="P24" s="188"/>
+      <c r="M24" s="124"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="124"/>
+      <c r="P24" s="125"/>
       <c r="Q24" s="55"/>
       <c r="R24" s="55"/>
     </row>
     <row r="25" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="173" t="s">
+      <c r="D25" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="174"/>
-      <c r="F25" s="174"/>
-      <c r="G25" s="174"/>
-      <c r="H25" s="175"/>
-      <c r="I25" s="182" t="s">
+      <c r="E25" s="121"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="121"/>
+      <c r="H25" s="122"/>
+      <c r="I25" s="208" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="174"/>
+      <c r="J25" s="121"/>
       <c r="K25" s="55"/>
-      <c r="L25" s="186" t="s">
+      <c r="L25" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="M25" s="187"/>
-      <c r="N25" s="187"/>
-      <c r="O25" s="188"/>
+      <c r="M25" s="124"/>
+      <c r="N25" s="124"/>
+      <c r="O25" s="125"/>
       <c r="P25" s="84" t="s">
         <v>49</v>
       </c>
@@ -3495,22 +3498,22 @@
     <row r="26" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
-      <c r="D26" s="192" t="s">
+      <c r="D26" s="249" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="187"/>
-      <c r="F26" s="187"/>
-      <c r="G26" s="187"/>
-      <c r="H26" s="187"/>
-      <c r="I26" s="187"/>
-      <c r="J26" s="187"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="124"/>
       <c r="K26" s="55"/>
-      <c r="L26" s="212" t="s">
+      <c r="L26" s="234" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="187"/>
-      <c r="N26" s="187"/>
-      <c r="O26" s="188"/>
+      <c r="M26" s="124"/>
+      <c r="N26" s="124"/>
+      <c r="O26" s="125"/>
       <c r="P26" s="85" t="s">
         <v>52</v>
       </c>
@@ -3520,20 +3523,20 @@
     <row r="27" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
-      <c r="D27" s="204"/>
-      <c r="E27" s="205"/>
-      <c r="F27" s="205"/>
-      <c r="G27" s="205"/>
-      <c r="H27" s="205"/>
-      <c r="I27" s="205"/>
-      <c r="J27" s="205"/>
+      <c r="D27" s="228"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="229"/>
+      <c r="I27" s="229"/>
+      <c r="J27" s="229"/>
       <c r="K27" s="55"/>
-      <c r="L27" s="186" t="s">
+      <c r="L27" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="M27" s="187"/>
-      <c r="N27" s="187"/>
-      <c r="O27" s="188"/>
+      <c r="M27" s="124"/>
+      <c r="N27" s="124"/>
+      <c r="O27" s="125"/>
       <c r="P27" s="84" t="s">
         <v>49</v>
       </c>
@@ -3562,49 +3565,49 @@
     <row r="29" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
-      <c r="D29" s="236" t="s">
+      <c r="D29" s="188" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="172"/>
-      <c r="F29" s="172"/>
-      <c r="G29" s="172"/>
-      <c r="H29" s="172"/>
-      <c r="I29" s="172"/>
+      <c r="E29" s="187"/>
+      <c r="F29" s="187"/>
+      <c r="G29" s="187"/>
+      <c r="H29" s="187"/>
+      <c r="I29" s="187"/>
       <c r="J29" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K29" s="55"/>
-      <c r="L29" s="234" t="s">
+      <c r="L29" s="217" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="235"/>
-      <c r="N29" s="235"/>
-      <c r="O29" s="235"/>
-      <c r="P29" s="235"/>
+      <c r="M29" s="127"/>
+      <c r="N29" s="127"/>
+      <c r="O29" s="127"/>
+      <c r="P29" s="127"/>
       <c r="Q29" s="55"/>
       <c r="R29" s="55"/>
     </row>
     <row r="30" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
-      <c r="D30" s="201" t="s">
+      <c r="D30" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="202"/>
-      <c r="F30" s="202"/>
-      <c r="G30" s="202"/>
-      <c r="H30" s="202"/>
-      <c r="I30" s="203"/>
+      <c r="E30" s="197"/>
+      <c r="F30" s="197"/>
+      <c r="G30" s="197"/>
+      <c r="H30" s="197"/>
+      <c r="I30" s="198"/>
       <c r="J30" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K30" s="55"/>
-      <c r="L30" s="206" t="s">
+      <c r="L30" s="204" t="s">
         <v>59</v>
       </c>
-      <c r="M30" s="174"/>
-      <c r="N30" s="174"/>
-      <c r="O30" s="178"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="205"/>
       <c r="P30" s="9" t="s">
         <v>60</v>
       </c>
@@ -3614,24 +3617,24 @@
     <row r="31" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
-      <c r="D31" s="168" t="s">
+      <c r="D31" s="156" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="169"/>
-      <c r="F31" s="169"/>
-      <c r="G31" s="169"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="170"/>
+      <c r="E31" s="157"/>
+      <c r="F31" s="157"/>
+      <c r="G31" s="157"/>
+      <c r="H31" s="157"/>
+      <c r="I31" s="158"/>
       <c r="J31" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K31" s="55"/>
-      <c r="L31" s="177" t="s">
+      <c r="L31" s="241" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="174"/>
-      <c r="N31" s="174"/>
-      <c r="O31" s="178"/>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="205"/>
       <c r="P31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3641,24 +3644,24 @@
     <row r="32" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
-      <c r="D32" s="195" t="s">
+      <c r="D32" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="169"/>
-      <c r="F32" s="169"/>
-      <c r="G32" s="169"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="170"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="157"/>
+      <c r="H32" s="157"/>
+      <c r="I32" s="158"/>
       <c r="J32" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K32" s="55"/>
-      <c r="L32" s="206" t="s">
+      <c r="L32" s="204" t="s">
         <v>65</v>
       </c>
-      <c r="M32" s="174"/>
-      <c r="N32" s="174"/>
-      <c r="O32" s="178"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="205"/>
       <c r="P32" s="9" t="s">
         <v>66</v>
       </c>
@@ -3668,24 +3671,24 @@
     <row r="33" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74"/>
       <c r="C33" s="74"/>
-      <c r="D33" s="168" t="s">
+      <c r="D33" s="156" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="169"/>
-      <c r="F33" s="169"/>
-      <c r="G33" s="169"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="170"/>
+      <c r="E33" s="157"/>
+      <c r="F33" s="157"/>
+      <c r="G33" s="157"/>
+      <c r="H33" s="157"/>
+      <c r="I33" s="158"/>
       <c r="J33" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K33" s="55"/>
-      <c r="L33" s="230" t="s">
+      <c r="L33" s="211" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="180"/>
-      <c r="N33" s="180"/>
-      <c r="O33" s="181"/>
+      <c r="M33" s="212"/>
+      <c r="N33" s="212"/>
+      <c r="O33" s="213"/>
       <c r="P33" s="11" t="s">
         <v>63</v>
       </c>
@@ -3695,14 +3698,14 @@
     <row r="34" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
-      <c r="D34" s="195" t="s">
+      <c r="D34" s="170" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="169"/>
-      <c r="F34" s="169"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="169"/>
-      <c r="I34" s="170"/>
+      <c r="E34" s="157"/>
+      <c r="F34" s="157"/>
+      <c r="G34" s="157"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="158"/>
       <c r="J34" s="14" t="s">
         <v>58</v>
       </c>
@@ -3718,25 +3721,25 @@
     <row r="35" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="198" t="s">
+      <c r="D35" s="227" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="199"/>
-      <c r="F35" s="199"/>
-      <c r="G35" s="199"/>
-      <c r="H35" s="199"/>
-      <c r="I35" s="200"/>
+      <c r="E35" s="222"/>
+      <c r="F35" s="222"/>
+      <c r="G35" s="222"/>
+      <c r="H35" s="222"/>
+      <c r="I35" s="223"/>
       <c r="J35" s="18" t="s">
         <v>58</v>
       </c>
       <c r="K35" s="55"/>
-      <c r="L35" s="211" t="s">
+      <c r="L35" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="M35" s="172"/>
-      <c r="N35" s="172"/>
-      <c r="O35" s="172"/>
-      <c r="P35" s="172"/>
+      <c r="M35" s="187"/>
+      <c r="N35" s="187"/>
+      <c r="O35" s="187"/>
+      <c r="P35" s="187"/>
       <c r="Q35" s="55"/>
       <c r="R35" s="55"/>
     </row>
@@ -3751,12 +3754,12 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="55"/>
-      <c r="L36" s="189" t="s">
+      <c r="L36" s="246" t="s">
         <v>72</v>
       </c>
-      <c r="M36" s="190"/>
-      <c r="N36" s="190"/>
-      <c r="O36" s="191"/>
+      <c r="M36" s="247"/>
+      <c r="N36" s="247"/>
+      <c r="O36" s="248"/>
       <c r="P36" s="20" t="s">
         <v>73</v>
       </c>
@@ -3766,24 +3769,24 @@
     <row r="37" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="74"/>
       <c r="C37" s="74"/>
-      <c r="D37" s="236" t="s">
+      <c r="D37" s="188" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="172"/>
-      <c r="F37" s="172"/>
-      <c r="G37" s="172"/>
-      <c r="H37" s="172"/>
-      <c r="I37" s="172"/>
+      <c r="E37" s="187"/>
+      <c r="F37" s="187"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="187"/>
+      <c r="I37" s="187"/>
       <c r="J37" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="55"/>
-      <c r="L37" s="207" t="s">
+      <c r="L37" s="183" t="s">
         <v>75</v>
       </c>
-      <c r="M37" s="174"/>
-      <c r="N37" s="174"/>
-      <c r="O37" s="175"/>
+      <c r="M37" s="121"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="122"/>
       <c r="P37" s="10" t="s">
         <v>73</v>
       </c>
@@ -3793,24 +3796,24 @@
     <row r="38" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
-      <c r="D38" s="201" t="s">
+      <c r="D38" s="196" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="202"/>
-      <c r="F38" s="202"/>
-      <c r="G38" s="202"/>
-      <c r="H38" s="202"/>
-      <c r="I38" s="203"/>
+      <c r="E38" s="197"/>
+      <c r="F38" s="197"/>
+      <c r="G38" s="197"/>
+      <c r="H38" s="197"/>
+      <c r="I38" s="198"/>
       <c r="J38" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="55"/>
-      <c r="L38" s="173" t="s">
+      <c r="L38" s="120" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="174"/>
-      <c r="N38" s="174"/>
-      <c r="O38" s="175"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="122"/>
       <c r="P38" s="9" t="s">
         <v>73</v>
       </c>
@@ -3820,24 +3823,24 @@
     <row r="39" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
-      <c r="D39" s="168" t="s">
+      <c r="D39" s="156" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="169"/>
-      <c r="F39" s="169"/>
-      <c r="G39" s="169"/>
-      <c r="H39" s="169"/>
-      <c r="I39" s="170"/>
+      <c r="E39" s="157"/>
+      <c r="F39" s="157"/>
+      <c r="G39" s="157"/>
+      <c r="H39" s="157"/>
+      <c r="I39" s="158"/>
       <c r="J39" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K39" s="55"/>
-      <c r="L39" s="207" t="s">
+      <c r="L39" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="M39" s="174"/>
-      <c r="N39" s="174"/>
-      <c r="O39" s="175"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="122"/>
       <c r="P39" s="10" t="s">
         <v>73</v>
       </c>
@@ -3847,24 +3850,24 @@
     <row r="40" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
-      <c r="D40" s="195" t="s">
+      <c r="D40" s="170" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="169"/>
-      <c r="F40" s="169"/>
-      <c r="G40" s="169"/>
-      <c r="H40" s="169"/>
-      <c r="I40" s="170"/>
+      <c r="E40" s="157"/>
+      <c r="F40" s="157"/>
+      <c r="G40" s="157"/>
+      <c r="H40" s="157"/>
+      <c r="I40" s="158"/>
       <c r="J40" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K40" s="55"/>
-      <c r="L40" s="179" t="s">
+      <c r="L40" s="242" t="s">
         <v>81</v>
       </c>
-      <c r="M40" s="180"/>
-      <c r="N40" s="180"/>
-      <c r="O40" s="181"/>
+      <c r="M40" s="212"/>
+      <c r="N40" s="212"/>
+      <c r="O40" s="213"/>
       <c r="P40" s="21" t="s">
         <v>73</v>
       </c>
@@ -3874,14 +3877,14 @@
     <row r="41" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
-      <c r="D41" s="168" t="s">
+      <c r="D41" s="156" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="169"/>
-      <c r="F41" s="169"/>
-      <c r="G41" s="169"/>
-      <c r="H41" s="169"/>
-      <c r="I41" s="170"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="157"/>
+      <c r="H41" s="157"/>
+      <c r="I41" s="158"/>
       <c r="J41" s="13" t="s">
         <v>58</v>
       </c>
@@ -3897,14 +3900,14 @@
     <row r="42" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
-      <c r="D42" s="195" t="s">
+      <c r="D42" s="170" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="169"/>
-      <c r="F42" s="169"/>
-      <c r="G42" s="169"/>
-      <c r="H42" s="169"/>
-      <c r="I42" s="170"/>
+      <c r="E42" s="157"/>
+      <c r="F42" s="157"/>
+      <c r="G42" s="157"/>
+      <c r="H42" s="157"/>
+      <c r="I42" s="158"/>
       <c r="J42" s="14" t="s">
         <v>58</v>
       </c>
@@ -3920,14 +3923,14 @@
     <row r="43" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
-      <c r="D43" s="168" t="s">
+      <c r="D43" s="156" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="169"/>
-      <c r="F43" s="169"/>
-      <c r="G43" s="169"/>
-      <c r="H43" s="169"/>
-      <c r="I43" s="170"/>
+      <c r="E43" s="157"/>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="158"/>
       <c r="J43" s="13" t="s">
         <v>58</v>
       </c>
@@ -3943,14 +3946,14 @@
     <row r="44" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
-      <c r="D44" s="201" t="s">
+      <c r="D44" s="196" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="202"/>
-      <c r="F44" s="202"/>
-      <c r="G44" s="202"/>
-      <c r="H44" s="202"/>
-      <c r="I44" s="203"/>
+      <c r="E44" s="197"/>
+      <c r="F44" s="197"/>
+      <c r="G44" s="197"/>
+      <c r="H44" s="197"/>
+      <c r="I44" s="198"/>
       <c r="J44" s="12" t="s">
         <v>58</v>
       </c>
@@ -3966,14 +3969,14 @@
     <row r="45" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
-      <c r="D45" s="168" t="s">
+      <c r="D45" s="156" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="169"/>
-      <c r="F45" s="169"/>
-      <c r="G45" s="169"/>
-      <c r="H45" s="169"/>
-      <c r="I45" s="170"/>
+      <c r="E45" s="157"/>
+      <c r="F45" s="157"/>
+      <c r="G45" s="157"/>
+      <c r="H45" s="157"/>
+      <c r="I45" s="158"/>
       <c r="J45" s="13" t="s">
         <v>58</v>
       </c>
@@ -3989,25 +3992,25 @@
     <row r="46" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
-      <c r="D46" s="244" t="s">
+      <c r="D46" s="221" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="199"/>
-      <c r="F46" s="199"/>
-      <c r="G46" s="199"/>
-      <c r="H46" s="199"/>
-      <c r="I46" s="200"/>
+      <c r="E46" s="222"/>
+      <c r="F46" s="222"/>
+      <c r="G46" s="222"/>
+      <c r="H46" s="222"/>
+      <c r="I46" s="223"/>
       <c r="J46" s="22" t="s">
         <v>58</v>
       </c>
       <c r="K46" s="55"/>
-      <c r="L46" s="171" t="s">
+      <c r="L46" s="240" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="172"/>
-      <c r="N46" s="172"/>
-      <c r="O46" s="172"/>
-      <c r="P46" s="172"/>
+      <c r="M46" s="187"/>
+      <c r="N46" s="187"/>
+      <c r="O46" s="187"/>
+      <c r="P46" s="187"/>
       <c r="Q46" s="55"/>
       <c r="R46" s="55"/>
     </row>
@@ -4033,21 +4036,21 @@
     <row r="48" spans="2:20" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B48" s="74"/>
       <c r="C48" s="76"/>
-      <c r="D48" s="208" t="s">
+      <c r="D48" s="230" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="209"/>
-      <c r="F48" s="209"/>
-      <c r="G48" s="209"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="209"/>
-      <c r="J48" s="209"/>
-      <c r="K48" s="209"/>
-      <c r="L48" s="209"/>
-      <c r="M48" s="209"/>
-      <c r="N48" s="209"/>
-      <c r="O48" s="209"/>
-      <c r="P48" s="210"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="231"/>
+      <c r="L48" s="231"/>
+      <c r="M48" s="231"/>
+      <c r="N48" s="231"/>
+      <c r="O48" s="231"/>
+      <c r="P48" s="232"/>
       <c r="Q48" s="55"/>
       <c r="R48" s="55"/>
       <c r="T48" s="97" t="s">
@@ -4060,14 +4063,14 @@
       <c r="D49" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="115" t="s">
+      <c r="E49" s="167" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="144"/>
-      <c r="G49" s="144"/>
-      <c r="H49" s="144"/>
-      <c r="I49" s="144"/>
-      <c r="J49" s="144"/>
+      <c r="F49" s="168"/>
+      <c r="G49" s="168"/>
+      <c r="H49" s="168"/>
+      <c r="I49" s="168"/>
+      <c r="J49" s="168"/>
       <c r="K49" s="91" t="s">
         <v>93</v>
       </c>
@@ -4077,10 +4080,10 @@
       <c r="M49" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="N49" s="115" t="s">
+      <c r="N49" s="167" t="s">
         <v>96</v>
       </c>
-      <c r="O49" s="144"/>
+      <c r="O49" s="168"/>
       <c r="P49" s="91" t="s">
         <v>97</v>
       </c>
@@ -4092,101 +4095,101 @@
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
       <c r="D50" s="25"/>
-      <c r="E50" s="223"/>
-      <c r="F50" s="156"/>
-      <c r="G50" s="156"/>
-      <c r="H50" s="156"/>
-      <c r="I50" s="156"/>
-      <c r="J50" s="149"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="119"/>
+      <c r="G50" s="119"/>
+      <c r="H50" s="119"/>
+      <c r="I50" s="119"/>
+      <c r="J50" s="191"/>
       <c r="K50" s="26"/>
       <c r="L50" s="27"/>
       <c r="M50" s="28"/>
-      <c r="N50" s="152"/>
-      <c r="O50" s="149"/>
+      <c r="N50" s="243"/>
+      <c r="O50" s="191"/>
       <c r="P50" s="29"/>
     </row>
     <row r="51" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8"/>
       <c r="C51" s="23"/>
       <c r="D51" s="30"/>
-      <c r="E51" s="176"/>
-      <c r="F51" s="156"/>
-      <c r="G51" s="156"/>
-      <c r="H51" s="156"/>
-      <c r="I51" s="156"/>
-      <c r="J51" s="149"/>
+      <c r="E51" s="209"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="119"/>
+      <c r="H51" s="119"/>
+      <c r="I51" s="119"/>
+      <c r="J51" s="191"/>
       <c r="K51" s="31"/>
       <c r="L51" s="32"/>
       <c r="M51" s="33"/>
-      <c r="N51" s="148"/>
-      <c r="O51" s="149"/>
+      <c r="N51" s="236"/>
+      <c r="O51" s="191"/>
       <c r="P51" s="34"/>
     </row>
     <row r="52" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
       <c r="D52" s="25"/>
-      <c r="E52" s="223"/>
-      <c r="F52" s="156"/>
-      <c r="G52" s="156"/>
-      <c r="H52" s="156"/>
-      <c r="I52" s="156"/>
-      <c r="J52" s="149"/>
+      <c r="E52" s="190"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="119"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="191"/>
       <c r="K52" s="26"/>
       <c r="L52" s="27"/>
       <c r="M52" s="28"/>
-      <c r="N52" s="152"/>
-      <c r="O52" s="149"/>
+      <c r="N52" s="243"/>
+      <c r="O52" s="191"/>
       <c r="P52" s="29"/>
     </row>
     <row r="53" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
       <c r="D53" s="30"/>
-      <c r="E53" s="176"/>
-      <c r="F53" s="156"/>
-      <c r="G53" s="156"/>
-      <c r="H53" s="156"/>
-      <c r="I53" s="156"/>
-      <c r="J53" s="149"/>
+      <c r="E53" s="209"/>
+      <c r="F53" s="119"/>
+      <c r="G53" s="119"/>
+      <c r="H53" s="119"/>
+      <c r="I53" s="119"/>
+      <c r="J53" s="191"/>
       <c r="K53" s="31"/>
       <c r="L53" s="32"/>
       <c r="M53" s="33"/>
-      <c r="N53" s="148"/>
-      <c r="O53" s="149"/>
+      <c r="N53" s="236"/>
+      <c r="O53" s="191"/>
       <c r="P53" s="34"/>
     </row>
     <row r="54" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="D54" s="25"/>
-      <c r="E54" s="223"/>
-      <c r="F54" s="156"/>
-      <c r="G54" s="156"/>
-      <c r="H54" s="156"/>
-      <c r="I54" s="156"/>
-      <c r="J54" s="149"/>
+      <c r="E54" s="190"/>
+      <c r="F54" s="119"/>
+      <c r="G54" s="119"/>
+      <c r="H54" s="119"/>
+      <c r="I54" s="119"/>
+      <c r="J54" s="191"/>
       <c r="K54" s="26"/>
       <c r="L54" s="27"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="152"/>
-      <c r="O54" s="149"/>
+      <c r="N54" s="243"/>
+      <c r="O54" s="191"/>
       <c r="P54" s="29"/>
     </row>
     <row r="55" spans="2:23" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8"/>
       <c r="C55" s="23"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="156"/>
-      <c r="G55" s="156"/>
-      <c r="H55" s="156"/>
-      <c r="I55" s="156"/>
-      <c r="J55" s="149"/>
+      <c r="E55" s="209"/>
+      <c r="F55" s="119"/>
+      <c r="G55" s="119"/>
+      <c r="H55" s="119"/>
+      <c r="I55" s="119"/>
+      <c r="J55" s="191"/>
       <c r="K55" s="31"/>
       <c r="L55" s="32"/>
       <c r="M55" s="33"/>
-      <c r="N55" s="148"/>
-      <c r="O55" s="149"/>
+      <c r="N55" s="236"/>
+      <c r="O55" s="191"/>
       <c r="P55" s="34"/>
     </row>
     <row r="56" spans="2:23" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4204,11 +4207,11 @@
       <c r="M56" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="N56" s="221">
+      <c r="N56" s="286">
         <f>SUM(N50:N55)</f>
         <v>0</v>
       </c>
-      <c r="O56" s="222"/>
+      <c r="O56" s="287"/>
       <c r="P56" s="3"/>
     </row>
     <row r="57" spans="2:23" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4226,11 +4229,11 @@
       <c r="M57" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="N57" s="159">
+      <c r="N57" s="259">
         <f>+N56*0.12</f>
         <v>0</v>
       </c>
-      <c r="O57" s="160"/>
+      <c r="O57" s="260"/>
       <c r="P57" s="3"/>
     </row>
     <row r="58" spans="2:23" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -4248,11 +4251,11 @@
       <c r="M58" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="N58" s="293">
+      <c r="N58" s="166">
         <f>+N57+N56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="156"/>
+      <c r="O58" s="119"/>
       <c r="P58" s="3"/>
     </row>
     <row r="59" spans="2:23" s="3" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4277,48 +4280,48 @@
     <row r="60" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
-      <c r="D60" s="161" t="s">
+      <c r="D60" s="261" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="161"/>
-      <c r="F60" s="161"/>
-      <c r="G60" s="161"/>
-      <c r="H60" s="161"/>
-      <c r="I60" s="161"/>
-      <c r="J60" s="161"/>
-      <c r="K60" s="161"/>
-      <c r="L60" s="161"/>
-      <c r="M60" s="161"/>
-      <c r="N60" s="161"/>
-      <c r="O60" s="161"/>
-      <c r="P60" s="161"/>
+      <c r="E60" s="261"/>
+      <c r="F60" s="261"/>
+      <c r="G60" s="261"/>
+      <c r="H60" s="261"/>
+      <c r="I60" s="261"/>
+      <c r="J60" s="261"/>
+      <c r="K60" s="261"/>
+      <c r="L60" s="261"/>
+      <c r="M60" s="261"/>
+      <c r="N60" s="261"/>
+      <c r="O60" s="261"/>
+      <c r="P60" s="261"/>
       <c r="Q60" s="56"/>
       <c r="R60" s="56"/>
     </row>
     <row r="61" spans="2:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
-      <c r="D61" s="213" t="s">
+      <c r="D61" s="235" t="s">
         <v>102</v>
       </c>
-      <c r="E61" s="213"/>
-      <c r="F61" s="213"/>
-      <c r="G61" s="286" t="s">
+      <c r="E61" s="235"/>
+      <c r="F61" s="235"/>
+      <c r="G61" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="H61" s="286"/>
-      <c r="I61" s="286"/>
-      <c r="J61" s="287" t="s">
+      <c r="H61" s="159"/>
+      <c r="I61" s="159"/>
+      <c r="J61" s="160" t="s">
         <v>105</v>
       </c>
-      <c r="K61" s="288"/>
-      <c r="L61" s="289"/>
-      <c r="M61" s="290" t="s">
+      <c r="K61" s="161"/>
+      <c r="L61" s="162"/>
+      <c r="M61" s="163" t="s">
         <v>106</v>
       </c>
-      <c r="N61" s="291"/>
-      <c r="O61" s="291"/>
-      <c r="P61" s="292"/>
+      <c r="N61" s="164"/>
+      <c r="O61" s="164"/>
+      <c r="P61" s="165"/>
       <c r="Q61" s="56"/>
       <c r="R61" s="56"/>
       <c r="U61" s="35"/>
@@ -4328,21 +4331,21 @@
     <row r="62" spans="2:23" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
-      <c r="D62" s="217" t="s">
+      <c r="D62" s="280" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="217"/>
-      <c r="F62" s="217"/>
-      <c r="G62" s="193"/>
-      <c r="H62" s="193"/>
-      <c r="I62" s="193"/>
-      <c r="J62" s="218"/>
-      <c r="K62" s="218"/>
-      <c r="L62" s="218"/>
-      <c r="M62" s="218"/>
-      <c r="N62" s="218"/>
-      <c r="O62" s="218"/>
-      <c r="P62" s="218"/>
+      <c r="E62" s="280"/>
+      <c r="F62" s="280"/>
+      <c r="G62" s="251"/>
+      <c r="H62" s="251"/>
+      <c r="I62" s="251"/>
+      <c r="J62" s="281"/>
+      <c r="K62" s="281"/>
+      <c r="L62" s="281"/>
+      <c r="M62" s="281"/>
+      <c r="N62" s="281"/>
+      <c r="O62" s="281"/>
+      <c r="P62" s="281"/>
       <c r="Q62" s="56"/>
       <c r="R62" s="56"/>
       <c r="S62"/>
@@ -4354,19 +4357,19 @@
     <row r="63" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
-      <c r="D63" s="219"/>
-      <c r="E63" s="219"/>
-      <c r="F63" s="219"/>
-      <c r="G63" s="142"/>
-      <c r="H63" s="142"/>
-      <c r="I63" s="142"/>
-      <c r="J63" s="220"/>
-      <c r="K63" s="220"/>
-      <c r="L63" s="220"/>
-      <c r="M63" s="142"/>
-      <c r="N63" s="142"/>
-      <c r="O63" s="142"/>
-      <c r="P63" s="142"/>
+      <c r="D63" s="282"/>
+      <c r="E63" s="282"/>
+      <c r="F63" s="282"/>
+      <c r="G63" s="250"/>
+      <c r="H63" s="250"/>
+      <c r="I63" s="250"/>
+      <c r="J63" s="283"/>
+      <c r="K63" s="283"/>
+      <c r="L63" s="283"/>
+      <c r="M63" s="250"/>
+      <c r="N63" s="250"/>
+      <c r="O63" s="250"/>
+      <c r="P63" s="250"/>
       <c r="Q63" s="103"/>
       <c r="R63" s="103"/>
       <c r="S63"/>
@@ -4378,19 +4381,19 @@
     <row r="64" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
-      <c r="D64" s="193"/>
-      <c r="E64" s="193"/>
-      <c r="F64" s="193"/>
-      <c r="G64" s="141"/>
-      <c r="H64" s="141"/>
-      <c r="I64" s="141"/>
-      <c r="J64" s="294"/>
-      <c r="K64" s="294"/>
-      <c r="L64" s="294"/>
-      <c r="M64" s="141"/>
-      <c r="N64" s="141"/>
-      <c r="O64" s="141"/>
-      <c r="P64" s="141"/>
+      <c r="D64" s="251"/>
+      <c r="E64" s="251"/>
+      <c r="F64" s="251"/>
+      <c r="G64" s="169"/>
+      <c r="H64" s="169"/>
+      <c r="I64" s="169"/>
+      <c r="J64" s="117"/>
+      <c r="K64" s="117"/>
+      <c r="L64" s="117"/>
+      <c r="M64" s="169"/>
+      <c r="N64" s="169"/>
+      <c r="O64" s="169"/>
+      <c r="P64" s="169"/>
       <c r="Q64" s="56"/>
       <c r="R64" s="56"/>
       <c r="S64"/>
@@ -4402,19 +4405,19 @@
     <row r="65" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="74"/>
       <c r="C65" s="74"/>
-      <c r="D65" s="162"/>
-      <c r="E65" s="163"/>
-      <c r="F65" s="164"/>
-      <c r="G65" s="162"/>
-      <c r="H65" s="163"/>
-      <c r="I65" s="164"/>
-      <c r="J65" s="162"/>
-      <c r="K65" s="163"/>
-      <c r="L65" s="164"/>
-      <c r="M65" s="162"/>
-      <c r="N65" s="163"/>
-      <c r="O65" s="163"/>
-      <c r="P65" s="164"/>
+      <c r="D65" s="262"/>
+      <c r="E65" s="263"/>
+      <c r="F65" s="264"/>
+      <c r="G65" s="262"/>
+      <c r="H65" s="263"/>
+      <c r="I65" s="264"/>
+      <c r="J65" s="262"/>
+      <c r="K65" s="263"/>
+      <c r="L65" s="264"/>
+      <c r="M65" s="262"/>
+      <c r="N65" s="263"/>
+      <c r="O65" s="263"/>
+      <c r="P65" s="264"/>
       <c r="Q65" s="56"/>
       <c r="R65" s="56"/>
       <c r="S65"/>
@@ -4423,19 +4426,19 @@
     <row r="66" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="74"/>
       <c r="C66" s="74"/>
-      <c r="D66" s="141"/>
-      <c r="E66" s="141"/>
-      <c r="F66" s="141"/>
-      <c r="G66" s="141"/>
-      <c r="H66" s="141"/>
-      <c r="I66" s="141"/>
-      <c r="J66" s="141"/>
-      <c r="K66" s="141"/>
-      <c r="L66" s="141"/>
-      <c r="M66" s="141"/>
-      <c r="N66" s="141"/>
-      <c r="O66" s="141"/>
-      <c r="P66" s="141"/>
+      <c r="D66" s="169"/>
+      <c r="E66" s="169"/>
+      <c r="F66" s="169"/>
+      <c r="G66" s="169"/>
+      <c r="H66" s="169"/>
+      <c r="I66" s="169"/>
+      <c r="J66" s="169"/>
+      <c r="K66" s="169"/>
+      <c r="L66" s="169"/>
+      <c r="M66" s="169"/>
+      <c r="N66" s="169"/>
+      <c r="O66" s="169"/>
+      <c r="P66" s="169"/>
       <c r="Q66" s="56"/>
       <c r="R66" s="56"/>
     </row>
@@ -4464,20 +4467,20 @@
       <c r="D68" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="E68" s="273" t="s">
+      <c r="E68" s="141" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="274"/>
-      <c r="G68" s="274"/>
-      <c r="H68" s="274"/>
-      <c r="I68" s="274"/>
-      <c r="J68" s="274"/>
-      <c r="K68" s="274"/>
-      <c r="L68" s="274"/>
-      <c r="M68" s="274"/>
-      <c r="N68" s="274"/>
-      <c r="O68" s="274"/>
-      <c r="P68" s="275"/>
+      <c r="F68" s="142"/>
+      <c r="G68" s="142"/>
+      <c r="H68" s="142"/>
+      <c r="I68" s="142"/>
+      <c r="J68" s="142"/>
+      <c r="K68" s="142"/>
+      <c r="L68" s="142"/>
+      <c r="M68" s="142"/>
+      <c r="N68" s="142"/>
+      <c r="O68" s="142"/>
+      <c r="P68" s="143"/>
       <c r="Q68" s="55"/>
       <c r="R68" s="55"/>
     </row>
@@ -4487,20 +4490,20 @@
       <c r="D69" s="110">
         <v>1</v>
       </c>
-      <c r="E69" s="276" t="s">
+      <c r="E69" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="F69" s="277"/>
-      <c r="G69" s="277"/>
-      <c r="H69" s="277"/>
-      <c r="I69" s="277"/>
-      <c r="J69" s="277"/>
-      <c r="K69" s="277"/>
-      <c r="L69" s="277"/>
-      <c r="M69" s="277"/>
-      <c r="N69" s="277"/>
-      <c r="O69" s="277"/>
-      <c r="P69" s="278"/>
+      <c r="F69" s="145"/>
+      <c r="G69" s="145"/>
+      <c r="H69" s="145"/>
+      <c r="I69" s="145"/>
+      <c r="J69" s="145"/>
+      <c r="K69" s="145"/>
+      <c r="L69" s="145"/>
+      <c r="M69" s="145"/>
+      <c r="N69" s="145"/>
+      <c r="O69" s="145"/>
+      <c r="P69" s="146"/>
       <c r="Q69" s="99"/>
       <c r="R69" s="99"/>
     </row>
@@ -4510,18 +4513,18 @@
       <c r="D70" s="112">
         <v>2</v>
       </c>
-      <c r="E70" s="215"/>
-      <c r="F70" s="216"/>
-      <c r="G70" s="216"/>
-      <c r="H70" s="216"/>
-      <c r="I70" s="216"/>
-      <c r="J70" s="216"/>
-      <c r="K70" s="216"/>
-      <c r="L70" s="216"/>
-      <c r="M70" s="216"/>
-      <c r="N70" s="216"/>
-      <c r="O70" s="216"/>
-      <c r="P70" s="216"/>
+      <c r="E70" s="237"/>
+      <c r="F70" s="238"/>
+      <c r="G70" s="238"/>
+      <c r="H70" s="238"/>
+      <c r="I70" s="238"/>
+      <c r="J70" s="238"/>
+      <c r="K70" s="238"/>
+      <c r="L70" s="238"/>
+      <c r="M70" s="238"/>
+      <c r="N70" s="238"/>
+      <c r="O70" s="238"/>
+      <c r="P70" s="238"/>
       <c r="Q70" s="55"/>
       <c r="R70" s="55"/>
     </row>
@@ -4531,18 +4534,18 @@
       <c r="D71" s="110">
         <v>3</v>
       </c>
-      <c r="E71" s="224"/>
-      <c r="F71" s="151"/>
-      <c r="G71" s="151"/>
-      <c r="H71" s="151"/>
-      <c r="I71" s="151"/>
-      <c r="J71" s="151"/>
-      <c r="K71" s="151"/>
-      <c r="L71" s="151"/>
-      <c r="M71" s="151"/>
-      <c r="N71" s="151"/>
-      <c r="O71" s="151"/>
-      <c r="P71" s="151"/>
+      <c r="E71" s="201"/>
+      <c r="F71" s="182"/>
+      <c r="G71" s="182"/>
+      <c r="H71" s="182"/>
+      <c r="I71" s="182"/>
+      <c r="J71" s="182"/>
+      <c r="K71" s="182"/>
+      <c r="L71" s="182"/>
+      <c r="M71" s="182"/>
+      <c r="N71" s="182"/>
+      <c r="O71" s="182"/>
+      <c r="P71" s="182"/>
     </row>
     <row r="72" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="8"/>
@@ -4550,18 +4553,18 @@
       <c r="D72" s="112">
         <v>4</v>
       </c>
-      <c r="E72" s="196"/>
-      <c r="F72" s="185"/>
-      <c r="G72" s="185"/>
-      <c r="H72" s="185"/>
-      <c r="I72" s="185"/>
-      <c r="J72" s="185"/>
-      <c r="K72" s="185"/>
-      <c r="L72" s="185"/>
-      <c r="M72" s="185"/>
-      <c r="N72" s="185"/>
-      <c r="O72" s="185"/>
-      <c r="P72" s="185"/>
+      <c r="E72" s="225"/>
+      <c r="F72" s="226"/>
+      <c r="G72" s="226"/>
+      <c r="H72" s="226"/>
+      <c r="I72" s="226"/>
+      <c r="J72" s="226"/>
+      <c r="K72" s="226"/>
+      <c r="L72" s="226"/>
+      <c r="M72" s="226"/>
+      <c r="N72" s="226"/>
+      <c r="O72" s="226"/>
+      <c r="P72" s="226"/>
     </row>
     <row r="73" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="8"/>
@@ -4569,18 +4572,18 @@
       <c r="D73" s="110">
         <v>5</v>
       </c>
-      <c r="E73" s="251"/>
-      <c r="F73" s="151"/>
-      <c r="G73" s="151"/>
-      <c r="H73" s="151"/>
-      <c r="I73" s="151"/>
-      <c r="J73" s="151"/>
-      <c r="K73" s="151"/>
-      <c r="L73" s="151"/>
-      <c r="M73" s="151"/>
-      <c r="N73" s="151"/>
-      <c r="O73" s="151"/>
-      <c r="P73" s="151"/>
+      <c r="E73" s="181"/>
+      <c r="F73" s="182"/>
+      <c r="G73" s="182"/>
+      <c r="H73" s="182"/>
+      <c r="I73" s="182"/>
+      <c r="J73" s="182"/>
+      <c r="K73" s="182"/>
+      <c r="L73" s="182"/>
+      <c r="M73" s="182"/>
+      <c r="N73" s="182"/>
+      <c r="O73" s="182"/>
+      <c r="P73" s="182"/>
     </row>
     <row r="74" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="8"/>
@@ -4605,20 +4608,20 @@
       <c r="D75" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E75" s="157" t="s">
+      <c r="E75" s="257" t="s">
         <v>109</v>
       </c>
-      <c r="F75" s="158"/>
-      <c r="G75" s="158"/>
-      <c r="H75" s="158"/>
-      <c r="I75" s="158"/>
-      <c r="J75" s="158"/>
-      <c r="K75" s="158"/>
-      <c r="L75" s="158"/>
-      <c r="M75" s="158"/>
-      <c r="N75" s="158"/>
-      <c r="O75" s="158"/>
-      <c r="P75" s="158"/>
+      <c r="F75" s="258"/>
+      <c r="G75" s="258"/>
+      <c r="H75" s="258"/>
+      <c r="I75" s="258"/>
+      <c r="J75" s="258"/>
+      <c r="K75" s="258"/>
+      <c r="L75" s="258"/>
+      <c r="M75" s="258"/>
+      <c r="N75" s="258"/>
+      <c r="O75" s="258"/>
+      <c r="P75" s="258"/>
       <c r="Q75" s="55"/>
       <c r="R75" s="55"/>
     </row>
@@ -4628,20 +4631,20 @@
       <c r="D76" s="110">
         <v>1</v>
       </c>
-      <c r="E76" s="279" t="s">
+      <c r="E76" s="147" t="s">
         <v>110</v>
       </c>
-      <c r="F76" s="279"/>
-      <c r="G76" s="279"/>
-      <c r="H76" s="279"/>
-      <c r="I76" s="279"/>
-      <c r="J76" s="279"/>
-      <c r="K76" s="279"/>
-      <c r="L76" s="279"/>
-      <c r="M76" s="279"/>
-      <c r="N76" s="279"/>
-      <c r="O76" s="279"/>
-      <c r="P76" s="279"/>
+      <c r="F76" s="147"/>
+      <c r="G76" s="147"/>
+      <c r="H76" s="147"/>
+      <c r="I76" s="147"/>
+      <c r="J76" s="147"/>
+      <c r="K76" s="147"/>
+      <c r="L76" s="147"/>
+      <c r="M76" s="147"/>
+      <c r="N76" s="147"/>
+      <c r="O76" s="147"/>
+      <c r="P76" s="147"/>
       <c r="Q76" s="55"/>
       <c r="R76" s="55"/>
     </row>
@@ -4651,18 +4654,18 @@
       <c r="D77" s="112">
         <v>2</v>
       </c>
-      <c r="E77" s="280"/>
-      <c r="F77" s="281"/>
-      <c r="G77" s="281"/>
-      <c r="H77" s="281"/>
-      <c r="I77" s="281"/>
-      <c r="J77" s="281"/>
-      <c r="K77" s="281"/>
-      <c r="L77" s="281"/>
-      <c r="M77" s="281"/>
-      <c r="N77" s="281"/>
-      <c r="O77" s="281"/>
-      <c r="P77" s="282"/>
+      <c r="E77" s="148"/>
+      <c r="F77" s="149"/>
+      <c r="G77" s="149"/>
+      <c r="H77" s="149"/>
+      <c r="I77" s="149"/>
+      <c r="J77" s="149"/>
+      <c r="K77" s="149"/>
+      <c r="L77" s="149"/>
+      <c r="M77" s="149"/>
+      <c r="N77" s="149"/>
+      <c r="O77" s="149"/>
+      <c r="P77" s="150"/>
       <c r="Q77" s="55"/>
       <c r="R77" s="55"/>
     </row>
@@ -4672,18 +4675,18 @@
       <c r="D78" s="110">
         <v>3</v>
       </c>
-      <c r="E78" s="283"/>
-      <c r="F78" s="284"/>
-      <c r="G78" s="284"/>
-      <c r="H78" s="284"/>
-      <c r="I78" s="284"/>
-      <c r="J78" s="284"/>
-      <c r="K78" s="284"/>
-      <c r="L78" s="284"/>
-      <c r="M78" s="284"/>
-      <c r="N78" s="284"/>
-      <c r="O78" s="284"/>
-      <c r="P78" s="285"/>
+      <c r="E78" s="151"/>
+      <c r="F78" s="152"/>
+      <c r="G78" s="152"/>
+      <c r="H78" s="152"/>
+      <c r="I78" s="152"/>
+      <c r="J78" s="152"/>
+      <c r="K78" s="152"/>
+      <c r="L78" s="152"/>
+      <c r="M78" s="152"/>
+      <c r="N78" s="152"/>
+      <c r="O78" s="152"/>
+      <c r="P78" s="153"/>
       <c r="Q78" s="55"/>
       <c r="R78" s="55"/>
     </row>
@@ -4693,18 +4696,18 @@
       <c r="D79" s="112">
         <v>4</v>
       </c>
-      <c r="E79" s="184"/>
-      <c r="F79" s="185"/>
-      <c r="G79" s="185"/>
-      <c r="H79" s="185"/>
-      <c r="I79" s="185"/>
-      <c r="J79" s="185"/>
-      <c r="K79" s="185"/>
-      <c r="L79" s="185"/>
-      <c r="M79" s="185"/>
-      <c r="N79" s="185"/>
-      <c r="O79" s="185"/>
-      <c r="P79" s="185"/>
+      <c r="E79" s="245"/>
+      <c r="F79" s="226"/>
+      <c r="G79" s="226"/>
+      <c r="H79" s="226"/>
+      <c r="I79" s="226"/>
+      <c r="J79" s="226"/>
+      <c r="K79" s="226"/>
+      <c r="L79" s="226"/>
+      <c r="M79" s="226"/>
+      <c r="N79" s="226"/>
+      <c r="O79" s="226"/>
+      <c r="P79" s="226"/>
     </row>
     <row r="80" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="8"/>
@@ -4712,35 +4715,35 @@
       <c r="D80" s="110">
         <v>5</v>
       </c>
-      <c r="E80" s="150"/>
-      <c r="F80" s="151"/>
-      <c r="G80" s="151"/>
-      <c r="H80" s="151"/>
-      <c r="I80" s="151"/>
-      <c r="J80" s="151"/>
-      <c r="K80" s="151"/>
-      <c r="L80" s="151"/>
-      <c r="M80" s="151"/>
-      <c r="N80" s="151"/>
-      <c r="O80" s="151"/>
-      <c r="P80" s="151"/>
+      <c r="E80" s="254"/>
+      <c r="F80" s="182"/>
+      <c r="G80" s="182"/>
+      <c r="H80" s="182"/>
+      <c r="I80" s="182"/>
+      <c r="J80" s="182"/>
+      <c r="K80" s="182"/>
+      <c r="L80" s="182"/>
+      <c r="M80" s="182"/>
+      <c r="N80" s="182"/>
+      <c r="O80" s="182"/>
+      <c r="P80" s="182"/>
     </row>
     <row r="81" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="101"/>
-      <c r="E81" s="155"/>
-      <c r="F81" s="156"/>
-      <c r="G81" s="156"/>
-      <c r="H81" s="156"/>
-      <c r="I81" s="156"/>
-      <c r="J81" s="156"/>
-      <c r="K81" s="156"/>
-      <c r="L81" s="156"/>
-      <c r="M81" s="156"/>
-      <c r="N81" s="156"/>
-      <c r="O81" s="156"/>
-      <c r="P81" s="156"/>
+      <c r="E81" s="256"/>
+      <c r="F81" s="119"/>
+      <c r="G81" s="119"/>
+      <c r="H81" s="119"/>
+      <c r="I81" s="119"/>
+      <c r="J81" s="119"/>
+      <c r="K81" s="119"/>
+      <c r="L81" s="119"/>
+      <c r="M81" s="119"/>
+      <c r="N81" s="119"/>
+      <c r="O81" s="119"/>
+      <c r="P81" s="119"/>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B82" s="74"/>
@@ -4767,40 +4770,40 @@
       <c r="D83" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="E83" s="165" t="s">
+      <c r="E83" s="265" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="165"/>
-      <c r="G83" s="165"/>
-      <c r="H83" s="165"/>
-      <c r="I83" s="165"/>
-      <c r="J83" s="165"/>
-      <c r="K83" s="165"/>
-      <c r="L83" s="165"/>
-      <c r="M83" s="165"/>
-      <c r="N83" s="165"/>
-      <c r="O83" s="165"/>
-      <c r="P83" s="165"/>
+      <c r="F83" s="265"/>
+      <c r="G83" s="265"/>
+      <c r="H83" s="265"/>
+      <c r="I83" s="265"/>
+      <c r="J83" s="265"/>
+      <c r="K83" s="265"/>
+      <c r="L83" s="265"/>
+      <c r="M83" s="265"/>
+      <c r="N83" s="265"/>
+      <c r="O83" s="265"/>
+      <c r="P83" s="265"/>
       <c r="Q83" s="72"/>
       <c r="R83" s="72"/>
     </row>
     <row r="84" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="124">
+      <c r="D84" s="139">
         <v>1</v>
       </c>
-      <c r="E84" s="267" t="s">
+      <c r="E84" s="133" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="268"/>
-      <c r="G84" s="268"/>
-      <c r="H84" s="268"/>
-      <c r="I84" s="268"/>
-      <c r="J84" s="268"/>
-      <c r="K84" s="268"/>
-      <c r="L84" s="268"/>
-      <c r="M84" s="269"/>
+      <c r="F84" s="134"/>
+      <c r="G84" s="134"/>
+      <c r="H84" s="134"/>
+      <c r="I84" s="134"/>
+      <c r="J84" s="134"/>
+      <c r="K84" s="134"/>
+      <c r="L84" s="134"/>
+      <c r="M84" s="135"/>
       <c r="N84" s="47"/>
       <c r="O84" s="47"/>
       <c r="P84" s="47"/>
@@ -4810,44 +4813,44 @@
     <row r="85" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="125"/>
-      <c r="E85" s="270"/>
-      <c r="F85" s="271"/>
-      <c r="G85" s="271"/>
-      <c r="H85" s="271"/>
-      <c r="I85" s="271"/>
-      <c r="J85" s="271"/>
-      <c r="K85" s="271"/>
-      <c r="L85" s="271"/>
-      <c r="M85" s="272"/>
+      <c r="D85" s="140"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="137"/>
+      <c r="G85" s="137"/>
+      <c r="H85" s="137"/>
+      <c r="I85" s="137"/>
+      <c r="J85" s="137"/>
+      <c r="K85" s="137"/>
+      <c r="L85" s="137"/>
+      <c r="M85" s="138"/>
       <c r="N85" s="46"/>
-      <c r="O85" s="115" t="s">
+      <c r="O85" s="167" t="s">
         <v>113</v>
       </c>
-      <c r="P85" s="115"/>
+      <c r="P85" s="167"/>
       <c r="Q85" s="72"/>
       <c r="R85" s="72"/>
     </row>
     <row r="86" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="126">
+      <c r="D86" s="284">
         <v>2</v>
       </c>
-      <c r="E86" s="128"/>
-      <c r="F86" s="129"/>
-      <c r="G86" s="129"/>
-      <c r="H86" s="129"/>
-      <c r="I86" s="129"/>
-      <c r="J86" s="129"/>
-      <c r="K86" s="129"/>
-      <c r="L86" s="129"/>
-      <c r="M86" s="130"/>
+      <c r="E86" s="267"/>
+      <c r="F86" s="268"/>
+      <c r="G86" s="268"/>
+      <c r="H86" s="268"/>
+      <c r="I86" s="268"/>
+      <c r="J86" s="268"/>
+      <c r="K86" s="268"/>
+      <c r="L86" s="268"/>
+      <c r="M86" s="269"/>
       <c r="N86" s="4"/>
-      <c r="O86" s="116" t="s">
+      <c r="O86" s="295" t="s">
         <v>115</v>
       </c>
-      <c r="P86" s="116"/>
+      <c r="P86" s="295"/>
       <c r="Q86" s="44"/>
       <c r="R86" s="44"/>
       <c r="T86" s="97" t="s">
@@ -4857,77 +4860,77 @@
     <row r="87" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="127"/>
-      <c r="E87" s="131"/>
-      <c r="F87" s="132"/>
-      <c r="G87" s="132"/>
-      <c r="H87" s="132"/>
-      <c r="I87" s="132"/>
-      <c r="J87" s="132"/>
-      <c r="K87" s="132"/>
-      <c r="L87" s="132"/>
-      <c r="M87" s="133"/>
+      <c r="D87" s="285"/>
+      <c r="E87" s="270"/>
+      <c r="F87" s="271"/>
+      <c r="G87" s="271"/>
+      <c r="H87" s="271"/>
+      <c r="I87" s="271"/>
+      <c r="J87" s="271"/>
+      <c r="K87" s="271"/>
+      <c r="L87" s="271"/>
+      <c r="M87" s="272"/>
       <c r="N87" s="5"/>
-      <c r="O87" s="116"/>
-      <c r="P87" s="116"/>
+      <c r="O87" s="295"/>
+      <c r="P87" s="295"/>
       <c r="Q87" s="44"/>
       <c r="R87" s="44"/>
     </row>
     <row r="88" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="124">
+      <c r="D88" s="139">
         <v>3</v>
       </c>
-      <c r="E88" s="118"/>
-      <c r="F88" s="119"/>
-      <c r="G88" s="119"/>
-      <c r="H88" s="119"/>
-      <c r="I88" s="119"/>
-      <c r="J88" s="119"/>
-      <c r="K88" s="119"/>
-      <c r="L88" s="119"/>
-      <c r="M88" s="120"/>
+      <c r="E88" s="274"/>
+      <c r="F88" s="275"/>
+      <c r="G88" s="275"/>
+      <c r="H88" s="275"/>
+      <c r="I88" s="275"/>
+      <c r="J88" s="275"/>
+      <c r="K88" s="275"/>
+      <c r="L88" s="275"/>
+      <c r="M88" s="276"/>
       <c r="N88" s="5"/>
-      <c r="O88" s="116"/>
-      <c r="P88" s="116"/>
+      <c r="O88" s="295"/>
+      <c r="P88" s="295"/>
       <c r="Q88" s="44"/>
       <c r="R88" s="44"/>
     </row>
     <row r="89" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="125"/>
-      <c r="E89" s="121"/>
-      <c r="F89" s="122"/>
-      <c r="G89" s="122"/>
-      <c r="H89" s="122"/>
-      <c r="I89" s="122"/>
-      <c r="J89" s="122"/>
-      <c r="K89" s="122"/>
-      <c r="L89" s="122"/>
-      <c r="M89" s="123"/>
+      <c r="D89" s="140"/>
+      <c r="E89" s="277"/>
+      <c r="F89" s="278"/>
+      <c r="G89" s="278"/>
+      <c r="H89" s="278"/>
+      <c r="I89" s="278"/>
+      <c r="J89" s="278"/>
+      <c r="K89" s="278"/>
+      <c r="L89" s="278"/>
+      <c r="M89" s="279"/>
       <c r="N89" s="5"/>
-      <c r="O89" s="117"/>
-      <c r="P89" s="117"/>
+      <c r="O89" s="296"/>
+      <c r="P89" s="296"/>
       <c r="Q89" s="44"/>
       <c r="R89" s="44"/>
     </row>
     <row r="90" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="126">
+      <c r="D90" s="284">
         <v>4</v>
       </c>
-      <c r="E90" s="128"/>
-      <c r="F90" s="129"/>
-      <c r="G90" s="129"/>
-      <c r="H90" s="129"/>
-      <c r="I90" s="129"/>
-      <c r="J90" s="129"/>
-      <c r="K90" s="129"/>
-      <c r="L90" s="129"/>
-      <c r="M90" s="130"/>
+      <c r="E90" s="267"/>
+      <c r="F90" s="268"/>
+      <c r="G90" s="268"/>
+      <c r="H90" s="268"/>
+      <c r="I90" s="268"/>
+      <c r="J90" s="268"/>
+      <c r="K90" s="268"/>
+      <c r="L90" s="268"/>
+      <c r="M90" s="269"/>
       <c r="N90" s="5"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -4937,39 +4940,39 @@
     <row r="91" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="127"/>
-      <c r="E91" s="131"/>
-      <c r="F91" s="132"/>
-      <c r="G91" s="132"/>
-      <c r="H91" s="132"/>
-      <c r="I91" s="132"/>
-      <c r="J91" s="132"/>
-      <c r="K91" s="132"/>
-      <c r="L91" s="132"/>
-      <c r="M91" s="133"/>
+      <c r="D91" s="285"/>
+      <c r="E91" s="270"/>
+      <c r="F91" s="271"/>
+      <c r="G91" s="271"/>
+      <c r="H91" s="271"/>
+      <c r="I91" s="271"/>
+      <c r="J91" s="271"/>
+      <c r="K91" s="271"/>
+      <c r="L91" s="271"/>
+      <c r="M91" s="272"/>
       <c r="N91" s="5"/>
-      <c r="O91" s="115" t="s">
+      <c r="O91" s="167" t="s">
         <v>116</v>
       </c>
-      <c r="P91" s="115"/>
+      <c r="P91" s="167"/>
       <c r="Q91" s="44"/>
       <c r="R91" s="44"/>
     </row>
     <row r="92" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="124">
+      <c r="D92" s="139">
         <v>5</v>
       </c>
-      <c r="E92" s="118"/>
-      <c r="F92" s="119"/>
-      <c r="G92" s="119"/>
-      <c r="H92" s="119"/>
-      <c r="I92" s="119"/>
-      <c r="J92" s="119"/>
-      <c r="K92" s="119"/>
-      <c r="L92" s="119"/>
-      <c r="M92" s="120"/>
+      <c r="E92" s="274"/>
+      <c r="F92" s="275"/>
+      <c r="G92" s="275"/>
+      <c r="H92" s="275"/>
+      <c r="I92" s="275"/>
+      <c r="J92" s="275"/>
+      <c r="K92" s="275"/>
+      <c r="L92" s="275"/>
+      <c r="M92" s="276"/>
       <c r="N92" s="5"/>
       <c r="O92" s="91"/>
       <c r="P92" s="91"/>
@@ -4979,119 +4982,119 @@
     <row r="93" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="125"/>
-      <c r="E93" s="121"/>
-      <c r="F93" s="122"/>
-      <c r="G93" s="122"/>
-      <c r="H93" s="122"/>
-      <c r="I93" s="122"/>
-      <c r="J93" s="122"/>
-      <c r="K93" s="122"/>
-      <c r="L93" s="122"/>
-      <c r="M93" s="123"/>
+      <c r="D93" s="140"/>
+      <c r="E93" s="277"/>
+      <c r="F93" s="278"/>
+      <c r="G93" s="278"/>
+      <c r="H93" s="278"/>
+      <c r="I93" s="278"/>
+      <c r="J93" s="278"/>
+      <c r="K93" s="278"/>
+      <c r="L93" s="278"/>
+      <c r="M93" s="279"/>
       <c r="N93" s="5"/>
-      <c r="O93" s="116" t="s">
+      <c r="O93" s="295" t="s">
         <v>117</v>
       </c>
-      <c r="P93" s="116"/>
+      <c r="P93" s="295"/>
       <c r="Q93" s="44"/>
       <c r="R93" s="44"/>
     </row>
     <row r="94" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="126">
+      <c r="D94" s="284">
         <v>6</v>
       </c>
-      <c r="E94" s="128"/>
-      <c r="F94" s="129"/>
-      <c r="G94" s="129"/>
-      <c r="H94" s="129"/>
-      <c r="I94" s="129"/>
-      <c r="J94" s="129"/>
-      <c r="K94" s="129"/>
-      <c r="L94" s="129"/>
-      <c r="M94" s="130"/>
+      <c r="E94" s="267"/>
+      <c r="F94" s="268"/>
+      <c r="G94" s="268"/>
+      <c r="H94" s="268"/>
+      <c r="I94" s="268"/>
+      <c r="J94" s="268"/>
+      <c r="K94" s="268"/>
+      <c r="L94" s="268"/>
+      <c r="M94" s="269"/>
       <c r="N94" s="5"/>
-      <c r="O94" s="116"/>
-      <c r="P94" s="116"/>
+      <c r="O94" s="295"/>
+      <c r="P94" s="295"/>
       <c r="Q94" s="44"/>
       <c r="R94" s="44"/>
     </row>
     <row r="95" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="127"/>
-      <c r="E95" s="131"/>
-      <c r="F95" s="132"/>
-      <c r="G95" s="132"/>
-      <c r="H95" s="132"/>
-      <c r="I95" s="132"/>
-      <c r="J95" s="132"/>
-      <c r="K95" s="132"/>
-      <c r="L95" s="132"/>
-      <c r="M95" s="133"/>
+      <c r="D95" s="285"/>
+      <c r="E95" s="270"/>
+      <c r="F95" s="271"/>
+      <c r="G95" s="271"/>
+      <c r="H95" s="271"/>
+      <c r="I95" s="271"/>
+      <c r="J95" s="271"/>
+      <c r="K95" s="271"/>
+      <c r="L95" s="271"/>
+      <c r="M95" s="272"/>
       <c r="N95" s="5"/>
-      <c r="O95" s="116"/>
-      <c r="P95" s="116"/>
+      <c r="O95" s="295"/>
+      <c r="P95" s="295"/>
       <c r="Q95" s="44"/>
       <c r="R95" s="44"/>
     </row>
     <row r="96" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="124">
+      <c r="D96" s="139">
         <v>7</v>
       </c>
-      <c r="E96" s="118"/>
-      <c r="F96" s="119"/>
-      <c r="G96" s="119"/>
-      <c r="H96" s="119"/>
-      <c r="I96" s="119"/>
-      <c r="J96" s="119"/>
-      <c r="K96" s="119"/>
-      <c r="L96" s="119"/>
-      <c r="M96" s="120"/>
+      <c r="E96" s="274"/>
+      <c r="F96" s="275"/>
+      <c r="G96" s="275"/>
+      <c r="H96" s="275"/>
+      <c r="I96" s="275"/>
+      <c r="J96" s="275"/>
+      <c r="K96" s="275"/>
+      <c r="L96" s="275"/>
+      <c r="M96" s="276"/>
       <c r="N96" s="5"/>
-      <c r="O96" s="116"/>
-      <c r="P96" s="116"/>
+      <c r="O96" s="295"/>
+      <c r="P96" s="295"/>
       <c r="Q96" s="44"/>
       <c r="R96" s="44"/>
     </row>
     <row r="97" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="125"/>
-      <c r="E97" s="121"/>
-      <c r="F97" s="122"/>
-      <c r="G97" s="122"/>
-      <c r="H97" s="122"/>
-      <c r="I97" s="122"/>
-      <c r="J97" s="122"/>
-      <c r="K97" s="122"/>
-      <c r="L97" s="122"/>
-      <c r="M97" s="123"/>
+      <c r="D97" s="140"/>
+      <c r="E97" s="277"/>
+      <c r="F97" s="278"/>
+      <c r="G97" s="278"/>
+      <c r="H97" s="278"/>
+      <c r="I97" s="278"/>
+      <c r="J97" s="278"/>
+      <c r="K97" s="278"/>
+      <c r="L97" s="278"/>
+      <c r="M97" s="279"/>
       <c r="N97" s="5"/>
-      <c r="O97" s="117"/>
-      <c r="P97" s="117"/>
+      <c r="O97" s="296"/>
+      <c r="P97" s="296"/>
       <c r="Q97" s="44"/>
       <c r="R97" s="44"/>
     </row>
     <row r="98" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="126">
+      <c r="D98" s="284">
         <v>8</v>
       </c>
-      <c r="E98" s="128"/>
-      <c r="F98" s="129"/>
-      <c r="G98" s="129"/>
-      <c r="H98" s="129"/>
-      <c r="I98" s="129"/>
-      <c r="J98" s="129"/>
-      <c r="K98" s="129"/>
-      <c r="L98" s="129"/>
-      <c r="M98" s="130"/>
+      <c r="E98" s="267"/>
+      <c r="F98" s="268"/>
+      <c r="G98" s="268"/>
+      <c r="H98" s="268"/>
+      <c r="I98" s="268"/>
+      <c r="J98" s="268"/>
+      <c r="K98" s="268"/>
+      <c r="L98" s="268"/>
+      <c r="M98" s="269"/>
       <c r="N98" s="5"/>
       <c r="O98" s="114"/>
       <c r="P98" s="114"/>
@@ -5101,284 +5104,284 @@
     <row r="99" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="127"/>
-      <c r="E99" s="131"/>
-      <c r="F99" s="132"/>
-      <c r="G99" s="132"/>
-      <c r="H99" s="132"/>
-      <c r="I99" s="132"/>
-      <c r="J99" s="132"/>
-      <c r="K99" s="132"/>
-      <c r="L99" s="132"/>
-      <c r="M99" s="133"/>
+      <c r="D99" s="285"/>
+      <c r="E99" s="270"/>
+      <c r="F99" s="271"/>
+      <c r="G99" s="271"/>
+      <c r="H99" s="271"/>
+      <c r="I99" s="271"/>
+      <c r="J99" s="271"/>
+      <c r="K99" s="271"/>
+      <c r="L99" s="271"/>
+      <c r="M99" s="272"/>
       <c r="N99" s="5"/>
-      <c r="O99" s="115" t="s">
+      <c r="O99" s="167" t="s">
         <v>118</v>
       </c>
-      <c r="P99" s="115"/>
+      <c r="P99" s="167"/>
       <c r="Q99" s="44"/>
       <c r="R99" s="44"/>
     </row>
     <row r="100" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="124">
+      <c r="D100" s="139">
         <v>9</v>
       </c>
-      <c r="E100" s="118"/>
-      <c r="F100" s="119"/>
-      <c r="G100" s="119"/>
-      <c r="H100" s="119"/>
-      <c r="I100" s="119"/>
-      <c r="J100" s="119"/>
-      <c r="K100" s="119"/>
-      <c r="L100" s="119"/>
-      <c r="M100" s="120"/>
+      <c r="E100" s="274"/>
+      <c r="F100" s="275"/>
+      <c r="G100" s="275"/>
+      <c r="H100" s="275"/>
+      <c r="I100" s="275"/>
+      <c r="J100" s="275"/>
+      <c r="K100" s="275"/>
+      <c r="L100" s="275"/>
+      <c r="M100" s="276"/>
       <c r="N100" s="5"/>
-      <c r="O100" s="116" t="s">
+      <c r="O100" s="295" t="s">
         <v>119</v>
       </c>
-      <c r="P100" s="116"/>
+      <c r="P100" s="295"/>
       <c r="Q100" s="44"/>
       <c r="R100" s="44"/>
     </row>
     <row r="101" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="125"/>
-      <c r="E101" s="121"/>
-      <c r="F101" s="122"/>
-      <c r="G101" s="122"/>
-      <c r="H101" s="122"/>
-      <c r="I101" s="122"/>
-      <c r="J101" s="122"/>
-      <c r="K101" s="122"/>
-      <c r="L101" s="122"/>
-      <c r="M101" s="123"/>
+      <c r="D101" s="140"/>
+      <c r="E101" s="277"/>
+      <c r="F101" s="278"/>
+      <c r="G101" s="278"/>
+      <c r="H101" s="278"/>
+      <c r="I101" s="278"/>
+      <c r="J101" s="278"/>
+      <c r="K101" s="278"/>
+      <c r="L101" s="278"/>
+      <c r="M101" s="279"/>
       <c r="N101" s="5"/>
-      <c r="O101" s="116"/>
-      <c r="P101" s="116"/>
+      <c r="O101" s="295"/>
+      <c r="P101" s="295"/>
       <c r="Q101" s="44"/>
       <c r="R101" s="44"/>
     </row>
     <row r="102" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
-      <c r="D102" s="126">
+      <c r="D102" s="284">
         <v>10</v>
       </c>
-      <c r="E102" s="128"/>
-      <c r="F102" s="129"/>
-      <c r="G102" s="129"/>
-      <c r="H102" s="129"/>
-      <c r="I102" s="129"/>
-      <c r="J102" s="129"/>
-      <c r="K102" s="129"/>
-      <c r="L102" s="129"/>
-      <c r="M102" s="130"/>
+      <c r="E102" s="267"/>
+      <c r="F102" s="268"/>
+      <c r="G102" s="268"/>
+      <c r="H102" s="268"/>
+      <c r="I102" s="268"/>
+      <c r="J102" s="268"/>
+      <c r="K102" s="268"/>
+      <c r="L102" s="268"/>
+      <c r="M102" s="269"/>
       <c r="N102" s="5"/>
-      <c r="O102" s="116"/>
-      <c r="P102" s="116"/>
+      <c r="O102" s="295"/>
+      <c r="P102" s="295"/>
       <c r="Q102" s="44"/>
       <c r="R102" s="44"/>
     </row>
     <row r="103" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="127"/>
-      <c r="E103" s="131"/>
-      <c r="F103" s="132"/>
-      <c r="G103" s="132"/>
-      <c r="H103" s="132"/>
-      <c r="I103" s="132"/>
-      <c r="J103" s="132"/>
-      <c r="K103" s="132"/>
-      <c r="L103" s="132"/>
-      <c r="M103" s="133"/>
+      <c r="D103" s="285"/>
+      <c r="E103" s="270"/>
+      <c r="F103" s="271"/>
+      <c r="G103" s="271"/>
+      <c r="H103" s="271"/>
+      <c r="I103" s="271"/>
+      <c r="J103" s="271"/>
+      <c r="K103" s="271"/>
+      <c r="L103" s="271"/>
+      <c r="M103" s="272"/>
       <c r="N103" s="5"/>
-      <c r="O103" s="116"/>
-      <c r="P103" s="116"/>
+      <c r="O103" s="295"/>
+      <c r="P103" s="295"/>
       <c r="Q103" s="44"/>
       <c r="R103" s="44"/>
     </row>
     <row r="104" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="124">
+      <c r="D104" s="139">
         <v>11</v>
       </c>
-      <c r="E104" s="118"/>
-      <c r="F104" s="119"/>
-      <c r="G104" s="119"/>
-      <c r="H104" s="119"/>
-      <c r="I104" s="119"/>
-      <c r="J104" s="119"/>
-      <c r="K104" s="119"/>
-      <c r="L104" s="119"/>
-      <c r="M104" s="120"/>
+      <c r="E104" s="274"/>
+      <c r="F104" s="275"/>
+      <c r="G104" s="275"/>
+      <c r="H104" s="275"/>
+      <c r="I104" s="275"/>
+      <c r="J104" s="275"/>
+      <c r="K104" s="275"/>
+      <c r="L104" s="275"/>
+      <c r="M104" s="276"/>
       <c r="N104" s="5"/>
-      <c r="O104" s="116"/>
-      <c r="P104" s="116"/>
+      <c r="O104" s="295"/>
+      <c r="P104" s="295"/>
       <c r="Q104" s="44"/>
       <c r="R104" s="44"/>
     </row>
     <row r="105" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="125"/>
-      <c r="E105" s="121"/>
-      <c r="F105" s="122"/>
-      <c r="G105" s="122"/>
-      <c r="H105" s="122"/>
-      <c r="I105" s="122"/>
-      <c r="J105" s="122"/>
-      <c r="K105" s="122"/>
-      <c r="L105" s="122"/>
-      <c r="M105" s="123"/>
+      <c r="D105" s="140"/>
+      <c r="E105" s="277"/>
+      <c r="F105" s="278"/>
+      <c r="G105" s="278"/>
+      <c r="H105" s="278"/>
+      <c r="I105" s="278"/>
+      <c r="J105" s="278"/>
+      <c r="K105" s="278"/>
+      <c r="L105" s="278"/>
+      <c r="M105" s="279"/>
       <c r="N105" s="5"/>
-      <c r="O105" s="117"/>
-      <c r="P105" s="117"/>
+      <c r="O105" s="296"/>
+      <c r="P105" s="296"/>
       <c r="Q105" s="44"/>
       <c r="R105" s="44"/>
     </row>
     <row r="106" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="126">
+      <c r="D106" s="284">
         <v>12</v>
       </c>
-      <c r="E106" s="128"/>
-      <c r="F106" s="129"/>
-      <c r="G106" s="129"/>
-      <c r="H106" s="129"/>
-      <c r="I106" s="129"/>
-      <c r="J106" s="129"/>
-      <c r="K106" s="129"/>
-      <c r="L106" s="129"/>
-      <c r="M106" s="130"/>
+      <c r="E106" s="267"/>
+      <c r="F106" s="268"/>
+      <c r="G106" s="268"/>
+      <c r="H106" s="268"/>
+      <c r="I106" s="268"/>
+      <c r="J106" s="268"/>
+      <c r="K106" s="268"/>
+      <c r="L106" s="268"/>
+      <c r="M106" s="269"/>
       <c r="N106" s="5"/>
-      <c r="O106" s="135"/>
-      <c r="P106" s="135"/>
+      <c r="O106" s="289"/>
+      <c r="P106" s="289"/>
       <c r="Q106" s="44"/>
       <c r="R106" s="44"/>
     </row>
     <row r="107" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="127"/>
-      <c r="E107" s="131"/>
-      <c r="F107" s="132"/>
-      <c r="G107" s="132"/>
-      <c r="H107" s="132"/>
-      <c r="I107" s="132"/>
-      <c r="J107" s="132"/>
-      <c r="K107" s="132"/>
-      <c r="L107" s="132"/>
-      <c r="M107" s="133"/>
+      <c r="D107" s="285"/>
+      <c r="E107" s="270"/>
+      <c r="F107" s="271"/>
+      <c r="G107" s="271"/>
+      <c r="H107" s="271"/>
+      <c r="I107" s="271"/>
+      <c r="J107" s="271"/>
+      <c r="K107" s="271"/>
+      <c r="L107" s="271"/>
+      <c r="M107" s="272"/>
       <c r="N107" s="5"/>
-      <c r="O107" s="136"/>
-      <c r="P107" s="136"/>
+      <c r="O107" s="290"/>
+      <c r="P107" s="290"/>
       <c r="Q107" s="44"/>
       <c r="R107" s="44"/>
     </row>
     <row r="108" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="124">
+      <c r="D108" s="139">
         <v>13</v>
       </c>
-      <c r="E108" s="118"/>
-      <c r="F108" s="119"/>
-      <c r="G108" s="119"/>
-      <c r="H108" s="119"/>
-      <c r="I108" s="119"/>
-      <c r="J108" s="119"/>
-      <c r="K108" s="119"/>
-      <c r="L108" s="119"/>
-      <c r="M108" s="120"/>
+      <c r="E108" s="274"/>
+      <c r="F108" s="275"/>
+      <c r="G108" s="275"/>
+      <c r="H108" s="275"/>
+      <c r="I108" s="275"/>
+      <c r="J108" s="275"/>
+      <c r="K108" s="275"/>
+      <c r="L108" s="275"/>
+      <c r="M108" s="276"/>
       <c r="N108" s="5"/>
-      <c r="O108" s="136"/>
-      <c r="P108" s="136"/>
+      <c r="O108" s="290"/>
+      <c r="P108" s="290"/>
       <c r="Q108" s="44"/>
       <c r="R108" s="44"/>
     </row>
     <row r="109" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="125"/>
-      <c r="E109" s="121"/>
-      <c r="F109" s="122"/>
-      <c r="G109" s="122"/>
-      <c r="H109" s="122"/>
-      <c r="I109" s="122"/>
-      <c r="J109" s="122"/>
-      <c r="K109" s="122"/>
-      <c r="L109" s="122"/>
-      <c r="M109" s="123"/>
+      <c r="D109" s="140"/>
+      <c r="E109" s="277"/>
+      <c r="F109" s="278"/>
+      <c r="G109" s="278"/>
+      <c r="H109" s="278"/>
+      <c r="I109" s="278"/>
+      <c r="J109" s="278"/>
+      <c r="K109" s="278"/>
+      <c r="L109" s="278"/>
+      <c r="M109" s="279"/>
       <c r="N109" s="5"/>
-      <c r="O109" s="136"/>
-      <c r="P109" s="136"/>
+      <c r="O109" s="290"/>
+      <c r="P109" s="290"/>
       <c r="Q109" s="44"/>
       <c r="R109" s="44"/>
     </row>
     <row r="110" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
-      <c r="D110" s="126">
+      <c r="D110" s="284">
         <v>14</v>
       </c>
-      <c r="E110" s="128"/>
-      <c r="F110" s="129"/>
-      <c r="G110" s="129"/>
-      <c r="H110" s="129"/>
-      <c r="I110" s="129"/>
-      <c r="J110" s="129"/>
-      <c r="K110" s="129"/>
-      <c r="L110" s="129"/>
-      <c r="M110" s="130"/>
+      <c r="E110" s="267"/>
+      <c r="F110" s="268"/>
+      <c r="G110" s="268"/>
+      <c r="H110" s="268"/>
+      <c r="I110" s="268"/>
+      <c r="J110" s="268"/>
+      <c r="K110" s="268"/>
+      <c r="L110" s="268"/>
+      <c r="M110" s="269"/>
       <c r="N110" s="5"/>
-      <c r="O110" s="136"/>
-      <c r="P110" s="136"/>
+      <c r="O110" s="290"/>
+      <c r="P110" s="290"/>
       <c r="Q110" s="44"/>
       <c r="R110" s="44"/>
     </row>
     <row r="111" spans="2:18" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="127"/>
-      <c r="E111" s="131"/>
-      <c r="F111" s="132"/>
-      <c r="G111" s="132"/>
-      <c r="H111" s="132"/>
-      <c r="I111" s="132"/>
-      <c r="J111" s="132"/>
-      <c r="K111" s="132"/>
-      <c r="L111" s="132"/>
-      <c r="M111" s="133"/>
+      <c r="D111" s="285"/>
+      <c r="E111" s="270"/>
+      <c r="F111" s="271"/>
+      <c r="G111" s="271"/>
+      <c r="H111" s="271"/>
+      <c r="I111" s="271"/>
+      <c r="J111" s="271"/>
+      <c r="K111" s="271"/>
+      <c r="L111" s="271"/>
+      <c r="M111" s="272"/>
       <c r="N111" s="5"/>
-      <c r="O111" s="137"/>
-      <c r="P111" s="137"/>
+      <c r="O111" s="291"/>
+      <c r="P111" s="291"/>
       <c r="Q111" s="46"/>
       <c r="R111" s="46"/>
     </row>
     <row r="112" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
-      <c r="D112" s="295"/>
-      <c r="E112" s="296"/>
-      <c r="F112" s="296"/>
-      <c r="G112" s="296"/>
-      <c r="H112" s="296"/>
-      <c r="I112" s="296"/>
-      <c r="J112" s="296"/>
-      <c r="K112" s="296"/>
-      <c r="L112" s="296"/>
-      <c r="M112" s="296"/>
+      <c r="D112" s="115"/>
+      <c r="E112" s="116"/>
+      <c r="F112" s="116"/>
+      <c r="G112" s="116"/>
+      <c r="H112" s="116"/>
+      <c r="I112" s="116"/>
+      <c r="J112" s="116"/>
+      <c r="K112" s="116"/>
+      <c r="L112" s="116"/>
+      <c r="M112" s="116"/>
       <c r="N112" s="5"/>
-      <c r="O112" s="134" t="s">
+      <c r="O112" s="288" t="s">
         <v>88</v>
       </c>
-      <c r="P112" s="134"/>
+      <c r="P112" s="288"/>
       <c r="Q112" s="46"/>
       <c r="R112" s="46"/>
     </row>
@@ -5407,20 +5410,20 @@
       <c r="D114" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="E114" s="138" t="s">
+      <c r="E114" s="292" t="s">
         <v>130</v>
       </c>
-      <c r="F114" s="139"/>
-      <c r="G114" s="139"/>
-      <c r="H114" s="139"/>
-      <c r="I114" s="139"/>
-      <c r="J114" s="139"/>
-      <c r="K114" s="139"/>
-      <c r="L114" s="139"/>
-      <c r="M114" s="139"/>
-      <c r="N114" s="139"/>
-      <c r="O114" s="139"/>
-      <c r="P114" s="139"/>
+      <c r="F114" s="293"/>
+      <c r="G114" s="293"/>
+      <c r="H114" s="293"/>
+      <c r="I114" s="293"/>
+      <c r="J114" s="293"/>
+      <c r="K114" s="293"/>
+      <c r="L114" s="293"/>
+      <c r="M114" s="293"/>
+      <c r="N114" s="293"/>
+      <c r="O114" s="293"/>
+      <c r="P114" s="293"/>
       <c r="Q114" s="44"/>
       <c r="R114" s="44"/>
     </row>
@@ -5430,20 +5433,20 @@
       <c r="D115" s="108">
         <v>1</v>
       </c>
-      <c r="E115" s="140" t="s">
+      <c r="E115" s="294" t="s">
         <v>120</v>
       </c>
-      <c r="F115" s="140"/>
-      <c r="G115" s="140"/>
-      <c r="H115" s="140"/>
-      <c r="I115" s="140"/>
-      <c r="J115" s="140"/>
-      <c r="K115" s="140"/>
-      <c r="L115" s="140"/>
-      <c r="M115" s="140"/>
-      <c r="N115" s="140"/>
-      <c r="O115" s="140"/>
-      <c r="P115" s="140"/>
+      <c r="F115" s="294"/>
+      <c r="G115" s="294"/>
+      <c r="H115" s="294"/>
+      <c r="I115" s="294"/>
+      <c r="J115" s="294"/>
+      <c r="K115" s="294"/>
+      <c r="L115" s="294"/>
+      <c r="M115" s="294"/>
+      <c r="N115" s="294"/>
+      <c r="O115" s="294"/>
+      <c r="P115" s="294"/>
       <c r="Q115" s="55"/>
       <c r="R115" s="55"/>
     </row>
@@ -5453,18 +5456,18 @@
       <c r="D116" s="113">
         <v>2</v>
       </c>
-      <c r="E116" s="142"/>
-      <c r="F116" s="142"/>
-      <c r="G116" s="142"/>
-      <c r="H116" s="142"/>
-      <c r="I116" s="142"/>
-      <c r="J116" s="142"/>
-      <c r="K116" s="142"/>
-      <c r="L116" s="142"/>
-      <c r="M116" s="142"/>
-      <c r="N116" s="142"/>
-      <c r="O116" s="142"/>
-      <c r="P116" s="142"/>
+      <c r="E116" s="250"/>
+      <c r="F116" s="250"/>
+      <c r="G116" s="250"/>
+      <c r="H116" s="250"/>
+      <c r="I116" s="250"/>
+      <c r="J116" s="250"/>
+      <c r="K116" s="250"/>
+      <c r="L116" s="250"/>
+      <c r="M116" s="250"/>
+      <c r="N116" s="250"/>
+      <c r="O116" s="250"/>
+      <c r="P116" s="250"/>
       <c r="Q116" s="55"/>
       <c r="R116" s="55"/>
     </row>
@@ -5474,18 +5477,18 @@
       <c r="D117" s="108">
         <v>3</v>
       </c>
-      <c r="E117" s="141"/>
-      <c r="F117" s="141"/>
-      <c r="G117" s="141"/>
-      <c r="H117" s="141"/>
-      <c r="I117" s="141"/>
-      <c r="J117" s="141"/>
-      <c r="K117" s="141"/>
-      <c r="L117" s="141"/>
-      <c r="M117" s="141"/>
-      <c r="N117" s="141"/>
-      <c r="O117" s="141"/>
-      <c r="P117" s="141"/>
+      <c r="E117" s="169"/>
+      <c r="F117" s="169"/>
+      <c r="G117" s="169"/>
+      <c r="H117" s="169"/>
+      <c r="I117" s="169"/>
+      <c r="J117" s="169"/>
+      <c r="K117" s="169"/>
+      <c r="L117" s="169"/>
+      <c r="M117" s="169"/>
+      <c r="N117" s="169"/>
+      <c r="O117" s="169"/>
+      <c r="P117" s="169"/>
       <c r="Q117" s="55"/>
       <c r="R117" s="55"/>
     </row>
@@ -5495,18 +5498,18 @@
       <c r="D118" s="113">
         <v>4</v>
       </c>
-      <c r="E118" s="142"/>
-      <c r="F118" s="142"/>
-      <c r="G118" s="142"/>
-      <c r="H118" s="142"/>
-      <c r="I118" s="142"/>
-      <c r="J118" s="142"/>
-      <c r="K118" s="142"/>
-      <c r="L118" s="142"/>
-      <c r="M118" s="142"/>
-      <c r="N118" s="142"/>
-      <c r="O118" s="142"/>
-      <c r="P118" s="142"/>
+      <c r="E118" s="250"/>
+      <c r="F118" s="250"/>
+      <c r="G118" s="250"/>
+      <c r="H118" s="250"/>
+      <c r="I118" s="250"/>
+      <c r="J118" s="250"/>
+      <c r="K118" s="250"/>
+      <c r="L118" s="250"/>
+      <c r="M118" s="250"/>
+      <c r="N118" s="250"/>
+      <c r="O118" s="250"/>
+      <c r="P118" s="250"/>
     </row>
     <row r="119" spans="2:18" ht="24" x14ac:dyDescent="0.3">
       <c r="B119" s="3"/>
@@ -5514,18 +5517,18 @@
       <c r="D119" s="108">
         <v>5</v>
       </c>
-      <c r="E119" s="143"/>
-      <c r="F119" s="143"/>
-      <c r="G119" s="143"/>
-      <c r="H119" s="143"/>
-      <c r="I119" s="143"/>
-      <c r="J119" s="143"/>
-      <c r="K119" s="143"/>
-      <c r="L119" s="143"/>
-      <c r="M119" s="143"/>
-      <c r="N119" s="143"/>
-      <c r="O119" s="143"/>
-      <c r="P119" s="143"/>
+      <c r="E119" s="273"/>
+      <c r="F119" s="273"/>
+      <c r="G119" s="273"/>
+      <c r="H119" s="273"/>
+      <c r="I119" s="273"/>
+      <c r="J119" s="273"/>
+      <c r="K119" s="273"/>
+      <c r="L119" s="273"/>
+      <c r="M119" s="273"/>
+      <c r="N119" s="273"/>
+      <c r="O119" s="273"/>
+      <c r="P119" s="273"/>
     </row>
     <row r="120" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="8"/>
@@ -5533,18 +5536,18 @@
       <c r="D120" s="113">
         <v>6</v>
       </c>
-      <c r="E120" s="142"/>
-      <c r="F120" s="142"/>
-      <c r="G120" s="142"/>
-      <c r="H120" s="142"/>
-      <c r="I120" s="142"/>
-      <c r="J120" s="142"/>
-      <c r="K120" s="142"/>
-      <c r="L120" s="142"/>
-      <c r="M120" s="142"/>
-      <c r="N120" s="142"/>
-      <c r="O120" s="142"/>
-      <c r="P120" s="142"/>
+      <c r="E120" s="250"/>
+      <c r="F120" s="250"/>
+      <c r="G120" s="250"/>
+      <c r="H120" s="250"/>
+      <c r="I120" s="250"/>
+      <c r="J120" s="250"/>
+      <c r="K120" s="250"/>
+      <c r="L120" s="250"/>
+      <c r="M120" s="250"/>
+      <c r="N120" s="250"/>
+      <c r="O120" s="250"/>
+      <c r="P120" s="250"/>
       <c r="Q120" s="55"/>
       <c r="R120" s="55"/>
     </row>
@@ -5554,18 +5557,18 @@
       <c r="D121" s="108">
         <v>7</v>
       </c>
-      <c r="E121" s="141"/>
-      <c r="F121" s="141"/>
-      <c r="G121" s="141"/>
-      <c r="H121" s="141"/>
-      <c r="I121" s="141"/>
-      <c r="J121" s="141"/>
-      <c r="K121" s="141"/>
-      <c r="L121" s="141"/>
-      <c r="M121" s="141"/>
-      <c r="N121" s="141"/>
-      <c r="O121" s="141"/>
-      <c r="P121" s="141"/>
+      <c r="E121" s="169"/>
+      <c r="F121" s="169"/>
+      <c r="G121" s="169"/>
+      <c r="H121" s="169"/>
+      <c r="I121" s="169"/>
+      <c r="J121" s="169"/>
+      <c r="K121" s="169"/>
+      <c r="L121" s="169"/>
+      <c r="M121" s="169"/>
+      <c r="N121" s="169"/>
+      <c r="O121" s="169"/>
+      <c r="P121" s="169"/>
       <c r="Q121" s="55"/>
       <c r="R121" s="55"/>
     </row>
@@ -5575,58 +5578,58 @@
       <c r="D122" s="113">
         <v>8</v>
       </c>
-      <c r="E122" s="142"/>
-      <c r="F122" s="142"/>
-      <c r="G122" s="142"/>
-      <c r="H122" s="142"/>
-      <c r="I122" s="142"/>
-      <c r="J122" s="142"/>
-      <c r="K122" s="142"/>
-      <c r="L122" s="142"/>
-      <c r="M122" s="142"/>
-      <c r="N122" s="142"/>
-      <c r="O122" s="142"/>
-      <c r="P122" s="142"/>
+      <c r="E122" s="250"/>
+      <c r="F122" s="250"/>
+      <c r="G122" s="250"/>
+      <c r="H122" s="250"/>
+      <c r="I122" s="250"/>
+      <c r="J122" s="250"/>
+      <c r="K122" s="250"/>
+      <c r="L122" s="250"/>
+      <c r="M122" s="250"/>
+      <c r="N122" s="250"/>
+      <c r="O122" s="250"/>
+      <c r="P122" s="250"/>
       <c r="Q122" s="55"/>
       <c r="R122" s="55"/>
     </row>
     <row r="123" spans="2:18" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="74"/>
       <c r="C123" s="74"/>
-      <c r="D123" s="166"/>
-      <c r="E123" s="166"/>
-      <c r="F123" s="166"/>
-      <c r="G123" s="166"/>
-      <c r="H123" s="166"/>
-      <c r="I123" s="166"/>
-      <c r="J123" s="166"/>
-      <c r="K123" s="166"/>
-      <c r="L123" s="166"/>
-      <c r="M123" s="166"/>
-      <c r="N123" s="166"/>
-      <c r="O123" s="166"/>
-      <c r="P123" s="166"/>
+      <c r="D123" s="266"/>
+      <c r="E123" s="266"/>
+      <c r="F123" s="266"/>
+      <c r="G123" s="266"/>
+      <c r="H123" s="266"/>
+      <c r="I123" s="266"/>
+      <c r="J123" s="266"/>
+      <c r="K123" s="266"/>
+      <c r="L123" s="266"/>
+      <c r="M123" s="266"/>
+      <c r="N123" s="266"/>
+      <c r="O123" s="266"/>
+      <c r="P123" s="266"/>
       <c r="Q123" s="55"/>
       <c r="R123" s="55"/>
     </row>
     <row r="124" spans="2:18" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="74"/>
       <c r="C124" s="74"/>
-      <c r="D124" s="183" t="s">
+      <c r="D124" s="244" t="s">
         <v>121</v>
       </c>
-      <c r="E124" s="183"/>
-      <c r="F124" s="183"/>
-      <c r="G124" s="183"/>
-      <c r="H124" s="183"/>
-      <c r="I124" s="183"/>
-      <c r="J124" s="183"/>
-      <c r="K124" s="183"/>
-      <c r="L124" s="183"/>
-      <c r="M124" s="183"/>
-      <c r="N124" s="183"/>
-      <c r="O124" s="183"/>
-      <c r="P124" s="183"/>
+      <c r="E124" s="244"/>
+      <c r="F124" s="244"/>
+      <c r="G124" s="244"/>
+      <c r="H124" s="244"/>
+      <c r="I124" s="244"/>
+      <c r="J124" s="244"/>
+      <c r="K124" s="244"/>
+      <c r="L124" s="244"/>
+      <c r="M124" s="244"/>
+      <c r="N124" s="244"/>
+      <c r="O124" s="244"/>
+      <c r="P124" s="244"/>
       <c r="Q124" s="55"/>
       <c r="R124" s="55"/>
     </row>
@@ -5652,27 +5655,27 @@
     <row r="126" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="74"/>
       <c r="C126" s="74"/>
-      <c r="D126" s="147" t="s">
+      <c r="D126" s="210" t="s">
         <v>122</v>
       </c>
-      <c r="E126" s="147"/>
-      <c r="F126" s="147"/>
+      <c r="E126" s="210"/>
+      <c r="F126" s="210"/>
       <c r="G126" s="55"/>
-      <c r="H126" s="147" t="s">
+      <c r="H126" s="210" t="s">
         <v>122</v>
       </c>
-      <c r="I126" s="147"/>
-      <c r="J126" s="147"/>
+      <c r="I126" s="210"/>
+      <c r="J126" s="210"/>
       <c r="K126" s="55"/>
-      <c r="L126" s="147" t="s">
+      <c r="L126" s="210" t="s">
         <v>122</v>
       </c>
-      <c r="M126" s="147"/>
+      <c r="M126" s="210"/>
       <c r="N126" s="55"/>
-      <c r="O126" s="147" t="s">
+      <c r="O126" s="210" t="s">
         <v>123</v>
       </c>
-      <c r="P126" s="147"/>
+      <c r="P126" s="210"/>
       <c r="Q126" s="55"/>
       <c r="R126" s="55"/>
     </row>
@@ -5774,54 +5777,54 @@
     <row r="132" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="74"/>
       <c r="C132" s="74"/>
-      <c r="D132" s="229" t="s">
+      <c r="D132" s="206" t="s">
         <v>124</v>
       </c>
-      <c r="E132" s="154"/>
-      <c r="F132" s="154"/>
+      <c r="E132" s="207"/>
+      <c r="F132" s="207"/>
       <c r="G132" s="94"/>
-      <c r="H132" s="153" t="s">
+      <c r="H132" s="255" t="s">
         <v>125</v>
       </c>
-      <c r="I132" s="154"/>
-      <c r="J132" s="154"/>
+      <c r="I132" s="207"/>
+      <c r="J132" s="207"/>
       <c r="K132" s="94"/>
-      <c r="L132" s="145" t="s">
+      <c r="L132" s="252" t="s">
         <v>126</v>
       </c>
-      <c r="M132" s="146"/>
+      <c r="M132" s="253"/>
       <c r="N132" s="94"/>
-      <c r="O132" s="145" t="s">
+      <c r="O132" s="252" t="s">
         <v>127</v>
       </c>
-      <c r="P132" s="146"/>
+      <c r="P132" s="253"/>
       <c r="Q132" s="55"/>
       <c r="R132" s="55"/>
     </row>
     <row r="133" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B133" s="74"/>
       <c r="C133" s="74"/>
-      <c r="D133" s="167" t="s">
+      <c r="D133" s="239" t="s">
+        <v>131</v>
+      </c>
+      <c r="E133" s="119"/>
+      <c r="F133" s="119"/>
+      <c r="G133" s="90"/>
+      <c r="H133" s="239" t="s">
+        <v>128</v>
+      </c>
+      <c r="I133" s="119"/>
+      <c r="J133" s="119"/>
+      <c r="K133" s="94"/>
+      <c r="L133" s="240" t="s">
+        <v>129</v>
+      </c>
+      <c r="M133" s="207"/>
+      <c r="N133" s="94"/>
+      <c r="O133" s="239" t="s">
         <v>16</v>
       </c>
-      <c r="E133" s="156"/>
-      <c r="F133" s="156"/>
-      <c r="G133" s="90"/>
-      <c r="H133" s="167" t="s">
-        <v>128</v>
-      </c>
-      <c r="I133" s="156"/>
-      <c r="J133" s="156"/>
-      <c r="K133" s="94"/>
-      <c r="L133" s="171" t="s">
-        <v>129</v>
-      </c>
-      <c r="M133" s="154"/>
-      <c r="N133" s="94"/>
-      <c r="O133" s="167" t="s">
-        <v>128</v>
-      </c>
-      <c r="P133" s="156"/>
+      <c r="P133" s="119"/>
       <c r="Q133" s="55"/>
       <c r="R133" s="55"/>
     </row>
@@ -5869,54 +5872,132 @@
     </row>
   </sheetData>
   <mergeCells count="198">
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="L18:P18"/>
-    <mergeCell ref="E84:M85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E68:P68"/>
-    <mergeCell ref="E69:P69"/>
-    <mergeCell ref="E76:P76"/>
-    <mergeCell ref="E77:P77"/>
-    <mergeCell ref="E78:P78"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="M61:P61"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="E73:P73"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="D37:I37"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="E54:J54"/>
-    <mergeCell ref="M6:N8"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D39:I39"/>
-    <mergeCell ref="L37:O37"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="E108:M109"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="E110:M111"/>
+    <mergeCell ref="E98:M99"/>
+    <mergeCell ref="O106:P111"/>
+    <mergeCell ref="E114:P114"/>
+    <mergeCell ref="E115:P115"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:M105"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="E106:M107"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="O100:P105"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="E100:M101"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E102:M103"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="E96:M97"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="M62:P62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="E86:M87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="E88:M89"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="O86:P89"/>
+    <mergeCell ref="O91:P91"/>
+    <mergeCell ref="E94:M95"/>
+    <mergeCell ref="E121:P121"/>
+    <mergeCell ref="E122:P122"/>
+    <mergeCell ref="E116:P116"/>
+    <mergeCell ref="E117:P117"/>
+    <mergeCell ref="E118:P118"/>
+    <mergeCell ref="E119:P119"/>
+    <mergeCell ref="E120:P120"/>
+    <mergeCell ref="M64:P64"/>
+    <mergeCell ref="O112:P112"/>
+    <mergeCell ref="O93:P97"/>
+    <mergeCell ref="E92:M93"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="L132:M132"/>
+    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="L126:M126"/>
+    <mergeCell ref="E80:P80"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="H132:J132"/>
+    <mergeCell ref="O132:P132"/>
+    <mergeCell ref="E81:P81"/>
+    <mergeCell ref="E75:P75"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="D60:P60"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="J66:L66"/>
+    <mergeCell ref="M66:P66"/>
+    <mergeCell ref="M65:P65"/>
+    <mergeCell ref="J65:L65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="E83:P83"/>
+    <mergeCell ref="D123:P123"/>
+    <mergeCell ref="E90:M91"/>
+    <mergeCell ref="E70:P70"/>
+    <mergeCell ref="H133:J133"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="D45:I45"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="L38:O38"/>
+    <mergeCell ref="E51:J51"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="L40:O40"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="H126:J126"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="D124:P124"/>
+    <mergeCell ref="E79:P79"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="L133:M133"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="O133:P133"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="E72:P72"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="D48:P48"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="L35:P35"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="D32:I32"/>
     <mergeCell ref="L12:O12"/>
     <mergeCell ref="E52:J52"/>
     <mergeCell ref="E71:P71"/>
@@ -5941,132 +6022,54 @@
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D42:I42"/>
-    <mergeCell ref="E72:P72"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D44:I44"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L39:O39"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="D48:P48"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="L35:P35"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="E70:P70"/>
-    <mergeCell ref="H133:J133"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="D45:I45"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="L38:O38"/>
-    <mergeCell ref="E51:J51"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="L40:O40"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="H126:J126"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="D124:P124"/>
-    <mergeCell ref="E79:P79"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="L133:M133"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="O133:P133"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="L132:M132"/>
-    <mergeCell ref="O126:P126"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="L126:M126"/>
-    <mergeCell ref="E80:P80"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="H132:J132"/>
-    <mergeCell ref="O132:P132"/>
-    <mergeCell ref="E81:P81"/>
-    <mergeCell ref="E75:P75"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="D60:P60"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="J66:L66"/>
-    <mergeCell ref="M66:P66"/>
-    <mergeCell ref="M65:P65"/>
-    <mergeCell ref="J65:L65"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="E83:P83"/>
-    <mergeCell ref="D123:P123"/>
-    <mergeCell ref="E90:M91"/>
-    <mergeCell ref="E94:M95"/>
-    <mergeCell ref="E121:P121"/>
-    <mergeCell ref="E122:P122"/>
-    <mergeCell ref="E116:P116"/>
-    <mergeCell ref="E117:P117"/>
-    <mergeCell ref="E118:P118"/>
-    <mergeCell ref="E119:P119"/>
-    <mergeCell ref="E120:P120"/>
-    <mergeCell ref="M64:P64"/>
-    <mergeCell ref="E49:J49"/>
-    <mergeCell ref="E96:M97"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="M62:P62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="E86:M87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="E88:M89"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="O112:P112"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="E108:M109"/>
-    <mergeCell ref="D110:D111"/>
-    <mergeCell ref="E110:M111"/>
-    <mergeCell ref="E98:M99"/>
-    <mergeCell ref="O106:P111"/>
-    <mergeCell ref="E114:P114"/>
-    <mergeCell ref="E115:P115"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:M105"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="E106:M107"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="O100:P105"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="O85:P85"/>
-    <mergeCell ref="O86:P89"/>
-    <mergeCell ref="O91:P91"/>
-    <mergeCell ref="O93:P97"/>
-    <mergeCell ref="E92:M93"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="E100:M101"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="E102:M103"/>
+    <mergeCell ref="E84:M85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E68:P68"/>
+    <mergeCell ref="E69:P69"/>
+    <mergeCell ref="E76:P76"/>
+    <mergeCell ref="E77:P77"/>
+    <mergeCell ref="E78:P78"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="M61:P61"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="E73:P73"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="L4:N5"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="D37:I37"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E54:J54"/>
+    <mergeCell ref="M6:N8"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D39:I39"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="F13:J13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B75252AA-B726-4E45-9B7F-E12568D27168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8CA0C09-266D-4C4D-823A-DC4706DED39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30816" yWindow="-4356" windowWidth="19236" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1503,7 +1503,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -2473,6 +2473,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5804,11 +5812,11 @@
     <row r="133" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B133" s="74"/>
       <c r="C133" s="74"/>
-      <c r="D133" s="239" t="s">
+      <c r="D133" s="297" t="s">
         <v>131</v>
       </c>
-      <c r="E133" s="119"/>
-      <c r="F133" s="119"/>
+      <c r="E133" s="298"/>
+      <c r="F133" s="298"/>
       <c r="G133" s="90"/>
       <c r="H133" s="239" t="s">
         <v>128</v>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8CA0C09-266D-4C4D-823A-DC4706DED39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21AF3DEB-73C1-4754-9BD4-3E019929534F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30816" yWindow="-4356" windowWidth="19236" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1503,7 +1503,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -2473,14 +2473,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2985,8 +2977,8 @@
       <c r="L4" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
       <c r="O4" s="53"/>
       <c r="P4" s="52"/>
       <c r="Q4" s="48"/>
@@ -3007,9 +2999,9 @@
       <c r="I5" s="174"/>
       <c r="J5" s="174"/>
       <c r="K5" s="52"/>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
-      <c r="N5" s="119"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
       <c r="O5" s="53"/>
       <c r="P5" s="52"/>
       <c r="Q5" s="48"/>
@@ -5812,11 +5804,11 @@
     <row r="133" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B133" s="74"/>
       <c r="C133" s="74"/>
-      <c r="D133" s="297" t="s">
+      <c r="D133" s="239" t="s">
         <v>131</v>
       </c>
-      <c r="E133" s="298"/>
-      <c r="F133" s="298"/>
+      <c r="E133" s="239"/>
+      <c r="F133" s="239"/>
       <c r="G133" s="90"/>
       <c r="H133" s="239" t="s">
         <v>128</v>
@@ -5832,7 +5824,7 @@
       <c r="O133" s="239" t="s">
         <v>16</v>
       </c>
-      <c r="P133" s="119"/>
+      <c r="P133" s="239"/>
       <c r="Q133" s="55"/>
       <c r="R133" s="55"/>
     </row>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21AF3DEB-73C1-4754-9BD4-3E019929534F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11995E6-8BBC-4296-A65F-BA33BBDC81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30816" yWindow="-4356" windowWidth="19236" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -495,9 +495,6 @@
     <t>FIRMA - Contratista</t>
   </si>
   <si>
-    <t>[Instertar nombre]</t>
-  </si>
-  <si>
     <t>Arq. Melissa Alvarenga</t>
   </si>
   <si>
@@ -505,6 +502,9 @@
   </si>
   <si>
     <t>{{LIDER}}</t>
+  </si>
+  <si>
+    <t>{{GERENTE_PROYECTO}}</t>
   </si>
 </sst>
 </file>
@@ -5411,7 +5411,7 @@
         <v>91</v>
       </c>
       <c r="E114" s="292" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F114" s="293"/>
       <c r="G114" s="293"/>
@@ -5805,19 +5805,19 @@
       <c r="B133" s="74"/>
       <c r="C133" s="74"/>
       <c r="D133" s="239" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E133" s="239"/>
       <c r="F133" s="239"/>
       <c r="G133" s="90"/>
       <c r="H133" s="239" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I133" s="119"/>
       <c r="J133" s="119"/>
       <c r="K133" s="94"/>
       <c r="L133" s="240" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M133" s="207"/>
       <c r="N133" s="94"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11995E6-8BBC-4296-A65F-BA33BBDC81D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C891623F-0A8A-413B-B882-92275ECF9323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30816" yWindow="-4356" windowWidth="19236" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C-9-12" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="133">
   <si>
     <t>PUNTO DE ACTA DE CONTRATO</t>
   </si>
@@ -505,6 +505,9 @@
   </si>
   <si>
     <t>{{GERENTE_PROYECTO}}</t>
+  </si>
+  <si>
+    <t>DIAS</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="73">
     <border>
       <left/>
       <right/>
@@ -1316,45 +1319,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color theme="2" tint="-0.249977111117893"/>
       </left>
       <right/>
@@ -1498,12 +1462,151 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1901,10 +2004,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1945,6 +2044,15 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1960,15 +2068,6 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1978,34 +2077,34 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2022,18 +2121,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2347,9 +2434,23 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2359,11 +2460,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2377,22 +2476,22 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2402,18 +2501,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2427,14 +2514,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2444,7 +2527,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2453,7 +2536,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -2473,6 +2556,92 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2945,19 +3114,19 @@
       <c r="C3" s="48"/>
       <c r="D3" s="49"/>
       <c r="E3" s="48"/>
-      <c r="F3" s="203" t="s">
+      <c r="F3" s="198" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="187"/>
-      <c r="H3" s="187"/>
-      <c r="I3" s="187"/>
-      <c r="J3" s="187"/>
+      <c r="G3" s="182"/>
+      <c r="H3" s="182"/>
+      <c r="I3" s="182"/>
+      <c r="J3" s="182"/>
       <c r="K3" s="52"/>
-      <c r="L3" s="203" t="s">
+      <c r="L3" s="198" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="187"/>
-      <c r="N3" s="187"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
       <c r="O3" s="53"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="48"/>
@@ -2974,11 +3143,11 @@
       <c r="I4" s="51"/>
       <c r="J4" s="52"/>
       <c r="K4" s="52"/>
-      <c r="L4" s="118" t="s">
+      <c r="L4" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
       <c r="O4" s="53"/>
       <c r="P4" s="52"/>
       <c r="Q4" s="48"/>
@@ -2989,19 +3158,19 @@
       <c r="C5" s="48"/>
       <c r="D5" s="49"/>
       <c r="E5" s="48"/>
-      <c r="F5" s="171" t="s">
+      <c r="F5" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="172"/>
-      <c r="H5" s="173" t="s">
+      <c r="G5" s="167"/>
+      <c r="H5" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="174"/>
-      <c r="J5" s="174"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="169"/>
       <c r="K5" s="52"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
       <c r="O5" s="53"/>
       <c r="P5" s="52"/>
       <c r="Q5" s="48"/>
@@ -3013,23 +3182,23 @@
       <c r="C6" s="48"/>
       <c r="D6" s="49"/>
       <c r="E6" s="48"/>
-      <c r="F6" s="202" t="s">
+      <c r="F6" s="197" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="187"/>
-      <c r="H6" s="173" t="s">
+      <c r="G6" s="182"/>
+      <c r="H6" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="174"/>
-      <c r="J6" s="174"/>
+      <c r="I6" s="169"/>
+      <c r="J6" s="169"/>
       <c r="K6" s="52"/>
-      <c r="L6" s="186" t="s">
+      <c r="L6" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="192" t="s">
+      <c r="M6" s="187" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="193"/>
+      <c r="N6" s="188"/>
       <c r="O6" s="53"/>
       <c r="P6" s="52"/>
       <c r="Q6" s="48"/>
@@ -3046,9 +3215,9 @@
       <c r="I7" s="57"/>
       <c r="J7" s="58"/>
       <c r="K7" s="52"/>
-      <c r="L7" s="187"/>
-      <c r="M7" s="194"/>
-      <c r="N7" s="194"/>
+      <c r="L7" s="182"/>
+      <c r="M7" s="189"/>
+      <c r="N7" s="189"/>
       <c r="O7" s="53"/>
       <c r="P7" s="52"/>
       <c r="Q7" s="48"/>
@@ -3059,19 +3228,19 @@
       <c r="C8" s="48"/>
       <c r="D8" s="49"/>
       <c r="E8" s="48"/>
-      <c r="F8" s="218" t="s">
+      <c r="F8" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="187"/>
-      <c r="H8" s="219" t="s">
+      <c r="G8" s="182"/>
+      <c r="H8" s="214" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="220"/>
-      <c r="J8" s="220"/>
+      <c r="I8" s="215"/>
+      <c r="J8" s="215"/>
       <c r="K8" s="52"/>
-      <c r="L8" s="187"/>
-      <c r="M8" s="195"/>
-      <c r="N8" s="195"/>
+      <c r="L8" s="182"/>
+      <c r="M8" s="190"/>
+      <c r="N8" s="190"/>
       <c r="O8" s="52"/>
       <c r="P8" s="52"/>
       <c r="Q8" s="48"/>
@@ -3138,24 +3307,24 @@
     <row r="12" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="59"/>
       <c r="C12" s="59"/>
-      <c r="D12" s="179" t="s">
+      <c r="D12" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="180"/>
-      <c r="F12" s="177" t="s">
+      <c r="E12" s="175"/>
+      <c r="F12" s="172" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="178"/>
-      <c r="H12" s="178"/>
-      <c r="I12" s="178"/>
-      <c r="J12" s="178"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="173"/>
       <c r="K12" s="65"/>
-      <c r="L12" s="199" t="s">
+      <c r="L12" s="194" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="187"/>
-      <c r="N12" s="187"/>
-      <c r="O12" s="200"/>
+      <c r="M12" s="182"/>
+      <c r="N12" s="182"/>
+      <c r="O12" s="195"/>
       <c r="P12" s="98" t="s">
         <v>14</v>
       </c>
@@ -3165,24 +3334,24 @@
     <row r="13" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
-      <c r="D13" s="154" t="s">
+      <c r="D13" s="153" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="155"/>
-      <c r="F13" s="175" t="s">
+      <c r="E13" s="154"/>
+      <c r="F13" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="176"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="176"/>
+      <c r="G13" s="171"/>
+      <c r="H13" s="171"/>
+      <c r="I13" s="171"/>
+      <c r="J13" s="171"/>
       <c r="K13" s="66"/>
-      <c r="L13" s="128" t="s">
+      <c r="L13" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="129"/>
-      <c r="N13" s="129"/>
-      <c r="O13" s="129"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
       <c r="P13" s="6" t="s">
         <v>18</v>
       </c>
@@ -3192,24 +3361,24 @@
     <row r="14" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
-      <c r="D14" s="154" t="s">
+      <c r="D14" s="153" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="155"/>
-      <c r="F14" s="175" t="s">
+      <c r="E14" s="154"/>
+      <c r="F14" s="170" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="176"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="171"/>
+      <c r="I14" s="171"/>
+      <c r="J14" s="171"/>
       <c r="K14" s="67"/>
-      <c r="L14" s="130" t="s">
+      <c r="L14" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="131"/>
-      <c r="N14" s="131"/>
-      <c r="O14" s="131"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="130"/>
+      <c r="O14" s="130"/>
       <c r="P14" s="6" t="s">
         <v>22</v>
       </c>
@@ -3219,24 +3388,24 @@
     <row r="15" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
-      <c r="D15" s="154" t="s">
+      <c r="D15" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="155"/>
-      <c r="F15" s="175" t="s">
+      <c r="E15" s="154"/>
+      <c r="F15" s="170" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="176"/>
-      <c r="H15" s="176"/>
-      <c r="I15" s="176"/>
-      <c r="J15" s="176"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="171"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="171"/>
       <c r="K15" s="55"/>
-      <c r="L15" s="130" t="s">
+      <c r="L15" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="131"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="131"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="130"/>
+      <c r="O15" s="130"/>
       <c r="P15" s="6" t="s">
         <v>26</v>
       </c>
@@ -3246,24 +3415,24 @@
     <row r="16" spans="2:21" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
-      <c r="D16" s="126" t="s">
+      <c r="D16" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="127"/>
-      <c r="F16" s="185" t="s">
+      <c r="E16" s="126"/>
+      <c r="F16" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="176"/>
-      <c r="H16" s="176"/>
-      <c r="I16" s="176"/>
-      <c r="J16" s="176"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="171"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="171"/>
       <c r="K16" s="65"/>
-      <c r="L16" s="130" t="s">
+      <c r="L16" s="129" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="131"/>
-      <c r="N16" s="131"/>
-      <c r="O16" s="131"/>
+      <c r="M16" s="130"/>
+      <c r="N16" s="130"/>
+      <c r="O16" s="130"/>
       <c r="P16" s="6" t="s">
         <v>30</v>
       </c>
@@ -3277,8 +3446,8 @@
       <c r="E17" s="62"/>
       <c r="F17" s="63"/>
       <c r="G17" s="63"/>
-      <c r="H17" s="224"/>
-      <c r="I17" s="207"/>
+      <c r="H17" s="219"/>
+      <c r="I17" s="202"/>
       <c r="J17" s="64"/>
       <c r="K17" s="66"/>
       <c r="L17" s="55"/>
@@ -3291,23 +3460,23 @@
     <row r="18" spans="2:19" s="7" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="75"/>
       <c r="C18" s="75"/>
-      <c r="D18" s="184" t="s">
+      <c r="D18" s="179" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="124"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="124"/>
-      <c r="J18" s="125"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="123"/>
+      <c r="J18" s="124"/>
       <c r="K18" s="73"/>
-      <c r="L18" s="132" t="s">
+      <c r="L18" s="131" t="s">
         <v>32</v>
       </c>
-      <c r="M18" s="124"/>
-      <c r="N18" s="124"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="125"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="124"/>
       <c r="Q18" s="55"/>
       <c r="R18" s="55"/>
       <c r="S18" s="1"/>
@@ -3315,24 +3484,24 @@
     <row r="19" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="74"/>
       <c r="C19" s="74"/>
-      <c r="D19" s="120" t="s">
+      <c r="D19" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="208" t="s">
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="203" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="121"/>
+      <c r="J19" s="120"/>
       <c r="K19" s="55"/>
-      <c r="L19" s="123" t="s">
+      <c r="L19" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="124"/>
-      <c r="N19" s="124"/>
-      <c r="O19" s="125"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="124"/>
       <c r="P19" s="84" t="s">
         <v>35</v>
       </c>
@@ -3342,24 +3511,24 @@
     <row r="20" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
-      <c r="D20" s="183" t="s">
+      <c r="D20" s="178" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="189" t="s">
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="121"/>
+      <c r="J20" s="120"/>
       <c r="K20" s="55"/>
-      <c r="L20" s="234" t="s">
+      <c r="L20" s="229" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="124"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="125"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="124"/>
       <c r="P20" s="85" t="s">
         <v>37</v>
       </c>
@@ -3369,24 +3538,24 @@
     <row r="21" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="208" t="s">
+      <c r="E21" s="120"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="121"/>
+      <c r="J21" s="120"/>
       <c r="K21" s="55"/>
-      <c r="L21" s="123" t="s">
+      <c r="L21" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="124"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="125"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="124"/>
       <c r="P21" s="84" t="s">
         <v>37</v>
       </c>
@@ -3396,24 +3565,24 @@
     <row r="22" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
-      <c r="D22" s="183" t="s">
+      <c r="D22" s="178" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="189" t="s">
+      <c r="E22" s="120"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="121"/>
+      <c r="J22" s="120"/>
       <c r="K22" s="55"/>
-      <c r="L22" s="214" t="s">
+      <c r="L22" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="215"/>
-      <c r="N22" s="215"/>
-      <c r="O22" s="216"/>
+      <c r="M22" s="210"/>
+      <c r="N22" s="210"/>
+      <c r="O22" s="211"/>
       <c r="P22" s="86" t="s">
         <v>41</v>
       </c>
@@ -3423,17 +3592,17 @@
     <row r="23" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
-      <c r="D23" s="120" t="s">
+      <c r="D23" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="208" t="s">
+      <c r="E23" s="120"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="203" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="121"/>
+      <c r="J23" s="120"/>
       <c r="K23" s="55"/>
       <c r="L23" s="82"/>
       <c r="M23" s="82"/>
@@ -3446,49 +3615,49 @@
     <row r="24" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
-      <c r="D24" s="183" t="s">
+      <c r="D24" s="178" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="189" t="s">
+      <c r="E24" s="120"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="121"/>
+      <c r="J24" s="120"/>
       <c r="K24" s="55"/>
-      <c r="L24" s="132" t="s">
+      <c r="L24" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="125"/>
+      <c r="M24" s="123"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="123"/>
+      <c r="P24" s="124"/>
       <c r="Q24" s="55"/>
       <c r="R24" s="55"/>
     </row>
     <row r="25" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="120" t="s">
+      <c r="D25" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="208" t="s">
+      <c r="E25" s="120"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="121"/>
+      <c r="I25" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="121"/>
+      <c r="J25" s="120"/>
       <c r="K25" s="55"/>
-      <c r="L25" s="123" t="s">
+      <c r="L25" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="M25" s="124"/>
-      <c r="N25" s="124"/>
-      <c r="O25" s="125"/>
+      <c r="M25" s="123"/>
+      <c r="N25" s="123"/>
+      <c r="O25" s="124"/>
       <c r="P25" s="84" t="s">
         <v>49</v>
       </c>
@@ -3498,22 +3667,22 @@
     <row r="26" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
-      <c r="D26" s="249" t="s">
+      <c r="D26" s="244" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="124"/>
-      <c r="F26" s="124"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="124"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="124"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="123"/>
       <c r="K26" s="55"/>
-      <c r="L26" s="234" t="s">
+      <c r="L26" s="229" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="124"/>
-      <c r="N26" s="124"/>
-      <c r="O26" s="125"/>
+      <c r="M26" s="123"/>
+      <c r="N26" s="123"/>
+      <c r="O26" s="124"/>
       <c r="P26" s="85" t="s">
         <v>52</v>
       </c>
@@ -3523,20 +3692,20 @@
     <row r="27" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
-      <c r="D27" s="228"/>
-      <c r="E27" s="229"/>
-      <c r="F27" s="229"/>
-      <c r="G27" s="229"/>
-      <c r="H27" s="229"/>
-      <c r="I27" s="229"/>
-      <c r="J27" s="229"/>
+      <c r="D27" s="223"/>
+      <c r="E27" s="224"/>
+      <c r="F27" s="224"/>
+      <c r="G27" s="224"/>
+      <c r="H27" s="224"/>
+      <c r="I27" s="224"/>
+      <c r="J27" s="224"/>
       <c r="K27" s="55"/>
-      <c r="L27" s="123" t="s">
+      <c r="L27" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="M27" s="124"/>
-      <c r="N27" s="124"/>
-      <c r="O27" s="125"/>
+      <c r="M27" s="123"/>
+      <c r="N27" s="123"/>
+      <c r="O27" s="124"/>
       <c r="P27" s="84" t="s">
         <v>49</v>
       </c>
@@ -3565,49 +3734,49 @@
     <row r="29" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
-      <c r="D29" s="188" t="s">
+      <c r="D29" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="187"/>
-      <c r="F29" s="187"/>
-      <c r="G29" s="187"/>
-      <c r="H29" s="187"/>
-      <c r="I29" s="187"/>
+      <c r="E29" s="182"/>
+      <c r="F29" s="182"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="182"/>
+      <c r="I29" s="182"/>
       <c r="J29" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K29" s="55"/>
-      <c r="L29" s="217" t="s">
+      <c r="L29" s="212" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="127"/>
-      <c r="N29" s="127"/>
-      <c r="O29" s="127"/>
-      <c r="P29" s="127"/>
+      <c r="M29" s="126"/>
+      <c r="N29" s="126"/>
+      <c r="O29" s="126"/>
+      <c r="P29" s="126"/>
       <c r="Q29" s="55"/>
       <c r="R29" s="55"/>
     </row>
     <row r="30" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
-      <c r="D30" s="196" t="s">
+      <c r="D30" s="191" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="197"/>
-      <c r="F30" s="197"/>
-      <c r="G30" s="197"/>
-      <c r="H30" s="197"/>
-      <c r="I30" s="198"/>
+      <c r="E30" s="192"/>
+      <c r="F30" s="192"/>
+      <c r="G30" s="192"/>
+      <c r="H30" s="192"/>
+      <c r="I30" s="193"/>
       <c r="J30" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K30" s="55"/>
-      <c r="L30" s="204" t="s">
+      <c r="L30" s="199" t="s">
         <v>59</v>
       </c>
-      <c r="M30" s="121"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="205"/>
+      <c r="M30" s="120"/>
+      <c r="N30" s="120"/>
+      <c r="O30" s="200"/>
       <c r="P30" s="9" t="s">
         <v>60</v>
       </c>
@@ -3617,24 +3786,24 @@
     <row r="31" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
-      <c r="D31" s="156" t="s">
+      <c r="D31" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="157"/>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="158"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="157"/>
       <c r="J31" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K31" s="55"/>
-      <c r="L31" s="241" t="s">
+      <c r="L31" s="236" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="121"/>
-      <c r="N31" s="121"/>
-      <c r="O31" s="205"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
+      <c r="O31" s="200"/>
       <c r="P31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3644,24 +3813,24 @@
     <row r="32" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
-      <c r="D32" s="170" t="s">
+      <c r="D32" s="165" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="157"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="157"/>
-      <c r="H32" s="157"/>
-      <c r="I32" s="158"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="156"/>
+      <c r="G32" s="156"/>
+      <c r="H32" s="156"/>
+      <c r="I32" s="157"/>
       <c r="J32" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K32" s="55"/>
-      <c r="L32" s="204" t="s">
+      <c r="L32" s="199" t="s">
         <v>65</v>
       </c>
-      <c r="M32" s="121"/>
-      <c r="N32" s="121"/>
-      <c r="O32" s="205"/>
+      <c r="M32" s="120"/>
+      <c r="N32" s="120"/>
+      <c r="O32" s="200"/>
       <c r="P32" s="9" t="s">
         <v>66</v>
       </c>
@@ -3671,24 +3840,24 @@
     <row r="33" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74"/>
       <c r="C33" s="74"/>
-      <c r="D33" s="156" t="s">
+      <c r="D33" s="155" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="157"/>
-      <c r="F33" s="157"/>
-      <c r="G33" s="157"/>
-      <c r="H33" s="157"/>
-      <c r="I33" s="158"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="156"/>
+      <c r="I33" s="157"/>
       <c r="J33" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K33" s="55"/>
-      <c r="L33" s="211" t="s">
+      <c r="L33" s="206" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="212"/>
-      <c r="N33" s="212"/>
-      <c r="O33" s="213"/>
+      <c r="M33" s="207"/>
+      <c r="N33" s="207"/>
+      <c r="O33" s="208"/>
       <c r="P33" s="11" t="s">
         <v>63</v>
       </c>
@@ -3698,14 +3867,14 @@
     <row r="34" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
-      <c r="D34" s="170" t="s">
+      <c r="D34" s="165" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="157"/>
-      <c r="F34" s="157"/>
-      <c r="G34" s="157"/>
-      <c r="H34" s="157"/>
-      <c r="I34" s="158"/>
+      <c r="E34" s="156"/>
+      <c r="F34" s="156"/>
+      <c r="G34" s="156"/>
+      <c r="H34" s="156"/>
+      <c r="I34" s="157"/>
       <c r="J34" s="14" t="s">
         <v>58</v>
       </c>
@@ -3721,25 +3890,25 @@
     <row r="35" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="227" t="s">
+      <c r="D35" s="222" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="222"/>
-      <c r="I35" s="223"/>
+      <c r="E35" s="217"/>
+      <c r="F35" s="217"/>
+      <c r="G35" s="217"/>
+      <c r="H35" s="217"/>
+      <c r="I35" s="218"/>
       <c r="J35" s="18" t="s">
         <v>58</v>
       </c>
       <c r="K35" s="55"/>
-      <c r="L35" s="233" t="s">
+      <c r="L35" s="228" t="s">
         <v>71</v>
       </c>
-      <c r="M35" s="187"/>
-      <c r="N35" s="187"/>
-      <c r="O35" s="187"/>
-      <c r="P35" s="187"/>
+      <c r="M35" s="182"/>
+      <c r="N35" s="182"/>
+      <c r="O35" s="182"/>
+      <c r="P35" s="182"/>
       <c r="Q35" s="55"/>
       <c r="R35" s="55"/>
     </row>
@@ -3754,12 +3923,12 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="55"/>
-      <c r="L36" s="246" t="s">
+      <c r="L36" s="241" t="s">
         <v>72</v>
       </c>
-      <c r="M36" s="247"/>
-      <c r="N36" s="247"/>
-      <c r="O36" s="248"/>
+      <c r="M36" s="242"/>
+      <c r="N36" s="242"/>
+      <c r="O36" s="243"/>
       <c r="P36" s="20" t="s">
         <v>73</v>
       </c>
@@ -3769,24 +3938,24 @@
     <row r="37" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="74"/>
       <c r="C37" s="74"/>
-      <c r="D37" s="188" t="s">
+      <c r="D37" s="183" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="187"/>
-      <c r="F37" s="187"/>
-      <c r="G37" s="187"/>
-      <c r="H37" s="187"/>
-      <c r="I37" s="187"/>
+      <c r="E37" s="182"/>
+      <c r="F37" s="182"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="182"/>
+      <c r="I37" s="182"/>
       <c r="J37" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="55"/>
-      <c r="L37" s="183" t="s">
+      <c r="L37" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="M37" s="121"/>
-      <c r="N37" s="121"/>
-      <c r="O37" s="122"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="121"/>
       <c r="P37" s="10" t="s">
         <v>73</v>
       </c>
@@ -3796,24 +3965,24 @@
     <row r="38" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
-      <c r="D38" s="196" t="s">
+      <c r="D38" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="197"/>
-      <c r="F38" s="197"/>
-      <c r="G38" s="197"/>
-      <c r="H38" s="197"/>
-      <c r="I38" s="198"/>
+      <c r="E38" s="192"/>
+      <c r="F38" s="192"/>
+      <c r="G38" s="192"/>
+      <c r="H38" s="192"/>
+      <c r="I38" s="193"/>
       <c r="J38" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="55"/>
-      <c r="L38" s="120" t="s">
+      <c r="L38" s="119" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
-      <c r="O38" s="122"/>
+      <c r="M38" s="120"/>
+      <c r="N38" s="120"/>
+      <c r="O38" s="121"/>
       <c r="P38" s="9" t="s">
         <v>73</v>
       </c>
@@ -3823,24 +3992,24 @@
     <row r="39" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
-      <c r="D39" s="156" t="s">
+      <c r="D39" s="155" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="157"/>
-      <c r="F39" s="157"/>
-      <c r="G39" s="157"/>
-      <c r="H39" s="157"/>
-      <c r="I39" s="158"/>
+      <c r="E39" s="156"/>
+      <c r="F39" s="156"/>
+      <c r="G39" s="156"/>
+      <c r="H39" s="156"/>
+      <c r="I39" s="157"/>
       <c r="J39" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K39" s="55"/>
-      <c r="L39" s="183" t="s">
+      <c r="L39" s="178" t="s">
         <v>79</v>
       </c>
-      <c r="M39" s="121"/>
-      <c r="N39" s="121"/>
-      <c r="O39" s="122"/>
+      <c r="M39" s="120"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="121"/>
       <c r="P39" s="10" t="s">
         <v>73</v>
       </c>
@@ -3850,24 +4019,24 @@
     <row r="40" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
-      <c r="D40" s="170" t="s">
+      <c r="D40" s="165" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="157"/>
-      <c r="F40" s="157"/>
-      <c r="G40" s="157"/>
-      <c r="H40" s="157"/>
-      <c r="I40" s="158"/>
+      <c r="E40" s="156"/>
+      <c r="F40" s="156"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="157"/>
       <c r="J40" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K40" s="55"/>
-      <c r="L40" s="242" t="s">
+      <c r="L40" s="237" t="s">
         <v>81</v>
       </c>
-      <c r="M40" s="212"/>
-      <c r="N40" s="212"/>
-      <c r="O40" s="213"/>
+      <c r="M40" s="207"/>
+      <c r="N40" s="207"/>
+      <c r="O40" s="208"/>
       <c r="P40" s="21" t="s">
         <v>73</v>
       </c>
@@ -3877,14 +4046,14 @@
     <row r="41" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
-      <c r="D41" s="156" t="s">
+      <c r="D41" s="155" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="157"/>
-      <c r="F41" s="157"/>
-      <c r="G41" s="157"/>
-      <c r="H41" s="157"/>
-      <c r="I41" s="158"/>
+      <c r="E41" s="156"/>
+      <c r="F41" s="156"/>
+      <c r="G41" s="156"/>
+      <c r="H41" s="156"/>
+      <c r="I41" s="157"/>
       <c r="J41" s="13" t="s">
         <v>58</v>
       </c>
@@ -3900,14 +4069,14 @@
     <row r="42" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
-      <c r="D42" s="170" t="s">
+      <c r="D42" s="165" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="157"/>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
-      <c r="H42" s="157"/>
-      <c r="I42" s="158"/>
+      <c r="E42" s="156"/>
+      <c r="F42" s="156"/>
+      <c r="G42" s="156"/>
+      <c r="H42" s="156"/>
+      <c r="I42" s="157"/>
       <c r="J42" s="14" t="s">
         <v>58</v>
       </c>
@@ -3923,14 +4092,14 @@
     <row r="43" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
-      <c r="D43" s="156" t="s">
+      <c r="D43" s="155" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="157"/>
-      <c r="F43" s="157"/>
-      <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="158"/>
+      <c r="E43" s="156"/>
+      <c r="F43" s="156"/>
+      <c r="G43" s="156"/>
+      <c r="H43" s="156"/>
+      <c r="I43" s="157"/>
       <c r="J43" s="13" t="s">
         <v>58</v>
       </c>
@@ -3946,14 +4115,14 @@
     <row r="44" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
-      <c r="D44" s="196" t="s">
+      <c r="D44" s="191" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="197"/>
-      <c r="F44" s="197"/>
-      <c r="G44" s="197"/>
-      <c r="H44" s="197"/>
-      <c r="I44" s="198"/>
+      <c r="E44" s="192"/>
+      <c r="F44" s="192"/>
+      <c r="G44" s="192"/>
+      <c r="H44" s="192"/>
+      <c r="I44" s="193"/>
       <c r="J44" s="12" t="s">
         <v>58</v>
       </c>
@@ -3969,14 +4138,14 @@
     <row r="45" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
-      <c r="D45" s="156" t="s">
+      <c r="D45" s="155" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="157"/>
-      <c r="F45" s="157"/>
-      <c r="G45" s="157"/>
-      <c r="H45" s="157"/>
-      <c r="I45" s="158"/>
+      <c r="E45" s="156"/>
+      <c r="F45" s="156"/>
+      <c r="G45" s="156"/>
+      <c r="H45" s="156"/>
+      <c r="I45" s="157"/>
       <c r="J45" s="13" t="s">
         <v>58</v>
       </c>
@@ -3992,25 +4161,25 @@
     <row r="46" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
-      <c r="D46" s="221" t="s">
+      <c r="D46" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="222"/>
-      <c r="F46" s="222"/>
-      <c r="G46" s="222"/>
-      <c r="H46" s="222"/>
-      <c r="I46" s="223"/>
+      <c r="E46" s="217"/>
+      <c r="F46" s="217"/>
+      <c r="G46" s="217"/>
+      <c r="H46" s="217"/>
+      <c r="I46" s="218"/>
       <c r="J46" s="22" t="s">
         <v>58</v>
       </c>
       <c r="K46" s="55"/>
-      <c r="L46" s="240" t="s">
+      <c r="L46" s="235" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="187"/>
-      <c r="N46" s="187"/>
-      <c r="O46" s="187"/>
-      <c r="P46" s="187"/>
+      <c r="M46" s="182"/>
+      <c r="N46" s="182"/>
+      <c r="O46" s="182"/>
+      <c r="P46" s="182"/>
       <c r="Q46" s="55"/>
       <c r="R46" s="55"/>
     </row>
@@ -4036,21 +4205,21 @@
     <row r="48" spans="2:20" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B48" s="74"/>
       <c r="C48" s="76"/>
-      <c r="D48" s="230" t="s">
+      <c r="D48" s="225" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="231"/>
-      <c r="F48" s="231"/>
-      <c r="G48" s="231"/>
-      <c r="H48" s="231"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="231"/>
-      <c r="L48" s="231"/>
-      <c r="M48" s="231"/>
-      <c r="N48" s="231"/>
-      <c r="O48" s="231"/>
-      <c r="P48" s="232"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="226"/>
+      <c r="I48" s="226"/>
+      <c r="J48" s="226"/>
+      <c r="K48" s="226"/>
+      <c r="L48" s="226"/>
+      <c r="M48" s="226"/>
+      <c r="N48" s="226"/>
+      <c r="O48" s="226"/>
+      <c r="P48" s="227"/>
       <c r="Q48" s="55"/>
       <c r="R48" s="55"/>
       <c r="T48" s="97" t="s">
@@ -4063,14 +4232,14 @@
       <c r="D49" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="167" t="s">
+      <c r="E49" s="162" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="168"/>
-      <c r="G49" s="168"/>
-      <c r="H49" s="168"/>
-      <c r="I49" s="168"/>
-      <c r="J49" s="168"/>
+      <c r="F49" s="163"/>
+      <c r="G49" s="163"/>
+      <c r="H49" s="163"/>
+      <c r="I49" s="163"/>
+      <c r="J49" s="163"/>
       <c r="K49" s="91" t="s">
         <v>93</v>
       </c>
@@ -4080,10 +4249,10 @@
       <c r="M49" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="N49" s="167" t="s">
+      <c r="N49" s="162" t="s">
         <v>96</v>
       </c>
-      <c r="O49" s="168"/>
+      <c r="O49" s="163"/>
       <c r="P49" s="91" t="s">
         <v>97</v>
       </c>
@@ -4095,101 +4264,101 @@
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
       <c r="D50" s="25"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="119"/>
-      <c r="G50" s="119"/>
-      <c r="H50" s="119"/>
-      <c r="I50" s="119"/>
-      <c r="J50" s="191"/>
+      <c r="E50" s="185"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="118"/>
+      <c r="I50" s="118"/>
+      <c r="J50" s="186"/>
       <c r="K50" s="26"/>
       <c r="L50" s="27"/>
       <c r="M50" s="28"/>
-      <c r="N50" s="243"/>
-      <c r="O50" s="191"/>
+      <c r="N50" s="238"/>
+      <c r="O50" s="186"/>
       <c r="P50" s="29"/>
     </row>
     <row r="51" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8"/>
       <c r="C51" s="23"/>
       <c r="D51" s="30"/>
-      <c r="E51" s="209"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="119"/>
-      <c r="H51" s="119"/>
-      <c r="I51" s="119"/>
-      <c r="J51" s="191"/>
+      <c r="E51" s="204"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="118"/>
+      <c r="H51" s="118"/>
+      <c r="I51" s="118"/>
+      <c r="J51" s="186"/>
       <c r="K51" s="31"/>
       <c r="L51" s="32"/>
       <c r="M51" s="33"/>
-      <c r="N51" s="236"/>
-      <c r="O51" s="191"/>
+      <c r="N51" s="231"/>
+      <c r="O51" s="186"/>
       <c r="P51" s="34"/>
     </row>
     <row r="52" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
       <c r="D52" s="25"/>
-      <c r="E52" s="190"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="119"/>
-      <c r="H52" s="119"/>
-      <c r="I52" s="119"/>
-      <c r="J52" s="191"/>
+      <c r="E52" s="185"/>
+      <c r="F52" s="118"/>
+      <c r="G52" s="118"/>
+      <c r="H52" s="118"/>
+      <c r="I52" s="118"/>
+      <c r="J52" s="186"/>
       <c r="K52" s="26"/>
       <c r="L52" s="27"/>
       <c r="M52" s="28"/>
-      <c r="N52" s="243"/>
-      <c r="O52" s="191"/>
+      <c r="N52" s="238"/>
+      <c r="O52" s="186"/>
       <c r="P52" s="29"/>
     </row>
     <row r="53" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
       <c r="D53" s="30"/>
-      <c r="E53" s="209"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="119"/>
-      <c r="H53" s="119"/>
-      <c r="I53" s="119"/>
-      <c r="J53" s="191"/>
+      <c r="E53" s="204"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="118"/>
+      <c r="H53" s="118"/>
+      <c r="I53" s="118"/>
+      <c r="J53" s="186"/>
       <c r="K53" s="31"/>
       <c r="L53" s="32"/>
       <c r="M53" s="33"/>
-      <c r="N53" s="236"/>
-      <c r="O53" s="191"/>
+      <c r="N53" s="231"/>
+      <c r="O53" s="186"/>
       <c r="P53" s="34"/>
     </row>
     <row r="54" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="D54" s="25"/>
-      <c r="E54" s="190"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="119"/>
-      <c r="H54" s="119"/>
-      <c r="I54" s="119"/>
-      <c r="J54" s="191"/>
+      <c r="E54" s="185"/>
+      <c r="F54" s="118"/>
+      <c r="G54" s="118"/>
+      <c r="H54" s="118"/>
+      <c r="I54" s="118"/>
+      <c r="J54" s="186"/>
       <c r="K54" s="26"/>
       <c r="L54" s="27"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="243"/>
-      <c r="O54" s="191"/>
+      <c r="N54" s="238"/>
+      <c r="O54" s="186"/>
       <c r="P54" s="29"/>
     </row>
     <row r="55" spans="2:23" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8"/>
       <c r="C55" s="23"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="209"/>
-      <c r="F55" s="119"/>
-      <c r="G55" s="119"/>
-      <c r="H55" s="119"/>
-      <c r="I55" s="119"/>
-      <c r="J55" s="191"/>
+      <c r="E55" s="204"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="118"/>
+      <c r="H55" s="118"/>
+      <c r="I55" s="118"/>
+      <c r="J55" s="186"/>
       <c r="K55" s="31"/>
       <c r="L55" s="32"/>
       <c r="M55" s="33"/>
-      <c r="N55" s="236"/>
-      <c r="O55" s="191"/>
+      <c r="N55" s="231"/>
+      <c r="O55" s="186"/>
       <c r="P55" s="34"/>
     </row>
     <row r="56" spans="2:23" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4207,11 +4376,11 @@
       <c r="M56" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="N56" s="286">
+      <c r="N56" s="280">
         <f>SUM(N50:N55)</f>
         <v>0</v>
       </c>
-      <c r="O56" s="287"/>
+      <c r="O56" s="281"/>
       <c r="P56" s="3"/>
     </row>
     <row r="57" spans="2:23" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4229,11 +4398,11 @@
       <c r="M57" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="N57" s="259">
+      <c r="N57" s="254">
         <f>+N56*0.12</f>
         <v>0</v>
       </c>
-      <c r="O57" s="260"/>
+      <c r="O57" s="255"/>
       <c r="P57" s="3"/>
     </row>
     <row r="58" spans="2:23" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -4251,11 +4420,11 @@
       <c r="M58" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="N58" s="166">
+      <c r="N58" s="161">
         <f>+N57+N56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="119"/>
+      <c r="O58" s="118"/>
       <c r="P58" s="3"/>
     </row>
     <row r="59" spans="2:23" s="3" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4280,48 +4449,50 @@
     <row r="60" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
-      <c r="D60" s="261" t="s">
+      <c r="D60" s="256" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="261"/>
-      <c r="F60" s="261"/>
-      <c r="G60" s="261"/>
-      <c r="H60" s="261"/>
-      <c r="I60" s="261"/>
-      <c r="J60" s="261"/>
-      <c r="K60" s="261"/>
-      <c r="L60" s="261"/>
-      <c r="M60" s="261"/>
-      <c r="N60" s="261"/>
-      <c r="O60" s="261"/>
-      <c r="P60" s="261"/>
+      <c r="E60" s="256"/>
+      <c r="F60" s="256"/>
+      <c r="G60" s="256"/>
+      <c r="H60" s="256"/>
+      <c r="I60" s="256"/>
+      <c r="J60" s="256"/>
+      <c r="K60" s="256"/>
+      <c r="L60" s="256"/>
+      <c r="M60" s="256"/>
+      <c r="N60" s="256"/>
+      <c r="O60" s="256"/>
+      <c r="P60" s="256"/>
       <c r="Q60" s="56"/>
       <c r="R60" s="56"/>
     </row>
     <row r="61" spans="2:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
-      <c r="D61" s="235" t="s">
+      <c r="D61" s="230" t="s">
         <v>102</v>
       </c>
-      <c r="E61" s="235"/>
-      <c r="F61" s="235"/>
-      <c r="G61" s="159" t="s">
+      <c r="E61" s="230"/>
+      <c r="F61" s="230"/>
+      <c r="G61" s="294" t="s">
         <v>103</v>
       </c>
-      <c r="H61" s="159"/>
-      <c r="I61" s="159"/>
-      <c r="J61" s="160" t="s">
+      <c r="H61" s="295"/>
+      <c r="I61" s="305" t="s">
         <v>105</v>
       </c>
-      <c r="K61" s="161"/>
-      <c r="L61" s="162"/>
-      <c r="M61" s="163" t="s">
+      <c r="J61" s="305"/>
+      <c r="K61" s="158" t="s">
+        <v>132</v>
+      </c>
+      <c r="L61" s="160"/>
+      <c r="M61" s="158" t="s">
         <v>106</v>
       </c>
-      <c r="N61" s="164"/>
-      <c r="O61" s="164"/>
-      <c r="P61" s="165"/>
+      <c r="N61" s="159"/>
+      <c r="O61" s="159"/>
+      <c r="P61" s="160"/>
       <c r="Q61" s="56"/>
       <c r="R61" s="56"/>
       <c r="U61" s="35"/>
@@ -4331,21 +4502,21 @@
     <row r="62" spans="2:23" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
-      <c r="D62" s="280" t="s">
+      <c r="D62" s="275" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="280"/>
-      <c r="F62" s="280"/>
-      <c r="G62" s="251"/>
-      <c r="H62" s="251"/>
-      <c r="I62" s="251"/>
-      <c r="J62" s="281"/>
-      <c r="K62" s="281"/>
-      <c r="L62" s="281"/>
-      <c r="M62" s="281"/>
-      <c r="N62" s="281"/>
-      <c r="O62" s="281"/>
-      <c r="P62" s="281"/>
+      <c r="E62" s="275"/>
+      <c r="F62" s="275"/>
+      <c r="G62" s="296"/>
+      <c r="H62" s="297"/>
+      <c r="I62" s="312"/>
+      <c r="J62" s="313"/>
+      <c r="K62" s="306"/>
+      <c r="L62" s="307"/>
+      <c r="M62" s="304"/>
+      <c r="N62" s="276"/>
+      <c r="O62" s="276"/>
+      <c r="P62" s="276"/>
       <c r="Q62" s="56"/>
       <c r="R62" s="56"/>
       <c r="S62"/>
@@ -4357,19 +4528,19 @@
     <row r="63" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
-      <c r="D63" s="282"/>
-      <c r="E63" s="282"/>
-      <c r="F63" s="282"/>
-      <c r="G63" s="250"/>
-      <c r="H63" s="250"/>
-      <c r="I63" s="250"/>
-      <c r="J63" s="283"/>
-      <c r="K63" s="283"/>
-      <c r="L63" s="283"/>
-      <c r="M63" s="250"/>
-      <c r="N63" s="250"/>
-      <c r="O63" s="250"/>
-      <c r="P63" s="250"/>
+      <c r="D63" s="277"/>
+      <c r="E63" s="277"/>
+      <c r="F63" s="277"/>
+      <c r="G63" s="257"/>
+      <c r="H63" s="258"/>
+      <c r="I63" s="298"/>
+      <c r="J63" s="299"/>
+      <c r="K63" s="308"/>
+      <c r="L63" s="309"/>
+      <c r="M63" s="259"/>
+      <c r="N63" s="245"/>
+      <c r="O63" s="245"/>
+      <c r="P63" s="245"/>
       <c r="Q63" s="103"/>
       <c r="R63" s="103"/>
       <c r="S63"/>
@@ -4381,19 +4552,19 @@
     <row r="64" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
-      <c r="D64" s="251"/>
-      <c r="E64" s="251"/>
-      <c r="F64" s="251"/>
-      <c r="G64" s="169"/>
-      <c r="H64" s="169"/>
-      <c r="I64" s="169"/>
-      <c r="J64" s="117"/>
-      <c r="K64" s="117"/>
-      <c r="L64" s="117"/>
-      <c r="M64" s="169"/>
-      <c r="N64" s="169"/>
-      <c r="O64" s="169"/>
-      <c r="P64" s="169"/>
+      <c r="D64" s="246"/>
+      <c r="E64" s="246"/>
+      <c r="F64" s="246"/>
+      <c r="G64" s="291"/>
+      <c r="H64" s="292"/>
+      <c r="I64" s="300"/>
+      <c r="J64" s="301"/>
+      <c r="K64" s="310"/>
+      <c r="L64" s="311"/>
+      <c r="M64" s="293"/>
+      <c r="N64" s="164"/>
+      <c r="O64" s="164"/>
+      <c r="P64" s="164"/>
       <c r="Q64" s="56"/>
       <c r="R64" s="56"/>
       <c r="S64"/>
@@ -4405,19 +4576,19 @@
     <row r="65" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="74"/>
       <c r="C65" s="74"/>
-      <c r="D65" s="262"/>
-      <c r="E65" s="263"/>
-      <c r="F65" s="264"/>
-      <c r="G65" s="262"/>
-      <c r="H65" s="263"/>
-      <c r="I65" s="264"/>
-      <c r="J65" s="262"/>
-      <c r="K65" s="263"/>
-      <c r="L65" s="264"/>
-      <c r="M65" s="262"/>
-      <c r="N65" s="263"/>
-      <c r="O65" s="263"/>
-      <c r="P65" s="264"/>
+      <c r="D65" s="257"/>
+      <c r="E65" s="258"/>
+      <c r="F65" s="259"/>
+      <c r="G65" s="257"/>
+      <c r="H65" s="258"/>
+      <c r="I65" s="298"/>
+      <c r="J65" s="299"/>
+      <c r="K65" s="298"/>
+      <c r="L65" s="299"/>
+      <c r="M65" s="258"/>
+      <c r="N65" s="258"/>
+      <c r="O65" s="258"/>
+      <c r="P65" s="259"/>
       <c r="Q65" s="56"/>
       <c r="R65" s="56"/>
       <c r="S65"/>
@@ -4426,19 +4597,19 @@
     <row r="66" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="74"/>
       <c r="C66" s="74"/>
-      <c r="D66" s="169"/>
-      <c r="E66" s="169"/>
-      <c r="F66" s="169"/>
-      <c r="G66" s="169"/>
-      <c r="H66" s="169"/>
-      <c r="I66" s="169"/>
-      <c r="J66" s="169"/>
-      <c r="K66" s="169"/>
-      <c r="L66" s="169"/>
-      <c r="M66" s="169"/>
-      <c r="N66" s="169"/>
-      <c r="O66" s="169"/>
-      <c r="P66" s="169"/>
+      <c r="D66" s="164"/>
+      <c r="E66" s="164"/>
+      <c r="F66" s="164"/>
+      <c r="G66" s="291"/>
+      <c r="H66" s="292"/>
+      <c r="I66" s="302"/>
+      <c r="J66" s="303"/>
+      <c r="K66" s="302"/>
+      <c r="L66" s="303"/>
+      <c r="M66" s="293"/>
+      <c r="N66" s="164"/>
+      <c r="O66" s="164"/>
+      <c r="P66" s="164"/>
       <c r="Q66" s="56"/>
       <c r="R66" s="56"/>
     </row>
@@ -4467,20 +4638,20 @@
       <c r="D68" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="E68" s="141" t="s">
+      <c r="E68" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="142"/>
-      <c r="G68" s="142"/>
-      <c r="H68" s="142"/>
-      <c r="I68" s="142"/>
-      <c r="J68" s="142"/>
-      <c r="K68" s="142"/>
-      <c r="L68" s="142"/>
-      <c r="M68" s="142"/>
-      <c r="N68" s="142"/>
-      <c r="O68" s="142"/>
-      <c r="P68" s="143"/>
+      <c r="F68" s="141"/>
+      <c r="G68" s="141"/>
+      <c r="H68" s="141"/>
+      <c r="I68" s="141"/>
+      <c r="J68" s="141"/>
+      <c r="K68" s="141"/>
+      <c r="L68" s="141"/>
+      <c r="M68" s="141"/>
+      <c r="N68" s="141"/>
+      <c r="O68" s="141"/>
+      <c r="P68" s="142"/>
       <c r="Q68" s="55"/>
       <c r="R68" s="55"/>
     </row>
@@ -4490,20 +4661,20 @@
       <c r="D69" s="110">
         <v>1</v>
       </c>
-      <c r="E69" s="144" t="s">
+      <c r="E69" s="143" t="s">
         <v>108</v>
       </c>
-      <c r="F69" s="145"/>
-      <c r="G69" s="145"/>
-      <c r="H69" s="145"/>
-      <c r="I69" s="145"/>
-      <c r="J69" s="145"/>
-      <c r="K69" s="145"/>
-      <c r="L69" s="145"/>
-      <c r="M69" s="145"/>
-      <c r="N69" s="145"/>
-      <c r="O69" s="145"/>
-      <c r="P69" s="146"/>
+      <c r="F69" s="144"/>
+      <c r="G69" s="144"/>
+      <c r="H69" s="144"/>
+      <c r="I69" s="144"/>
+      <c r="J69" s="144"/>
+      <c r="K69" s="144"/>
+      <c r="L69" s="144"/>
+      <c r="M69" s="144"/>
+      <c r="N69" s="144"/>
+      <c r="O69" s="144"/>
+      <c r="P69" s="145"/>
       <c r="Q69" s="99"/>
       <c r="R69" s="99"/>
     </row>
@@ -4513,18 +4684,18 @@
       <c r="D70" s="112">
         <v>2</v>
       </c>
-      <c r="E70" s="237"/>
-      <c r="F70" s="238"/>
-      <c r="G70" s="238"/>
-      <c r="H70" s="238"/>
-      <c r="I70" s="238"/>
-      <c r="J70" s="238"/>
-      <c r="K70" s="238"/>
-      <c r="L70" s="238"/>
-      <c r="M70" s="238"/>
-      <c r="N70" s="238"/>
-      <c r="O70" s="238"/>
-      <c r="P70" s="238"/>
+      <c r="E70" s="232"/>
+      <c r="F70" s="233"/>
+      <c r="G70" s="233"/>
+      <c r="H70" s="233"/>
+      <c r="I70" s="233"/>
+      <c r="J70" s="233"/>
+      <c r="K70" s="233"/>
+      <c r="L70" s="233"/>
+      <c r="M70" s="233"/>
+      <c r="N70" s="233"/>
+      <c r="O70" s="233"/>
+      <c r="P70" s="233"/>
       <c r="Q70" s="55"/>
       <c r="R70" s="55"/>
     </row>
@@ -4534,18 +4705,18 @@
       <c r="D71" s="110">
         <v>3</v>
       </c>
-      <c r="E71" s="201"/>
-      <c r="F71" s="182"/>
-      <c r="G71" s="182"/>
-      <c r="H71" s="182"/>
-      <c r="I71" s="182"/>
-      <c r="J71" s="182"/>
-      <c r="K71" s="182"/>
-      <c r="L71" s="182"/>
-      <c r="M71" s="182"/>
-      <c r="N71" s="182"/>
-      <c r="O71" s="182"/>
-      <c r="P71" s="182"/>
+      <c r="E71" s="196"/>
+      <c r="F71" s="177"/>
+      <c r="G71" s="177"/>
+      <c r="H71" s="177"/>
+      <c r="I71" s="177"/>
+      <c r="J71" s="177"/>
+      <c r="K71" s="177"/>
+      <c r="L71" s="177"/>
+      <c r="M71" s="177"/>
+      <c r="N71" s="177"/>
+      <c r="O71" s="177"/>
+      <c r="P71" s="177"/>
     </row>
     <row r="72" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="8"/>
@@ -4553,18 +4724,18 @@
       <c r="D72" s="112">
         <v>4</v>
       </c>
-      <c r="E72" s="225"/>
-      <c r="F72" s="226"/>
-      <c r="G72" s="226"/>
-      <c r="H72" s="226"/>
-      <c r="I72" s="226"/>
-      <c r="J72" s="226"/>
-      <c r="K72" s="226"/>
-      <c r="L72" s="226"/>
-      <c r="M72" s="226"/>
-      <c r="N72" s="226"/>
-      <c r="O72" s="226"/>
-      <c r="P72" s="226"/>
+      <c r="E72" s="220"/>
+      <c r="F72" s="221"/>
+      <c r="G72" s="221"/>
+      <c r="H72" s="221"/>
+      <c r="I72" s="221"/>
+      <c r="J72" s="221"/>
+      <c r="K72" s="221"/>
+      <c r="L72" s="221"/>
+      <c r="M72" s="221"/>
+      <c r="N72" s="221"/>
+      <c r="O72" s="221"/>
+      <c r="P72" s="221"/>
     </row>
     <row r="73" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="8"/>
@@ -4572,18 +4743,18 @@
       <c r="D73" s="110">
         <v>5</v>
       </c>
-      <c r="E73" s="181"/>
-      <c r="F73" s="182"/>
-      <c r="G73" s="182"/>
-      <c r="H73" s="182"/>
-      <c r="I73" s="182"/>
-      <c r="J73" s="182"/>
-      <c r="K73" s="182"/>
-      <c r="L73" s="182"/>
-      <c r="M73" s="182"/>
-      <c r="N73" s="182"/>
-      <c r="O73" s="182"/>
-      <c r="P73" s="182"/>
+      <c r="E73" s="176"/>
+      <c r="F73" s="177"/>
+      <c r="G73" s="177"/>
+      <c r="H73" s="177"/>
+      <c r="I73" s="177"/>
+      <c r="J73" s="177"/>
+      <c r="K73" s="177"/>
+      <c r="L73" s="177"/>
+      <c r="M73" s="177"/>
+      <c r="N73" s="177"/>
+      <c r="O73" s="177"/>
+      <c r="P73" s="177"/>
     </row>
     <row r="74" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="8"/>
@@ -4608,20 +4779,20 @@
       <c r="D75" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E75" s="257" t="s">
+      <c r="E75" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="F75" s="258"/>
-      <c r="G75" s="258"/>
-      <c r="H75" s="258"/>
-      <c r="I75" s="258"/>
-      <c r="J75" s="258"/>
-      <c r="K75" s="258"/>
-      <c r="L75" s="258"/>
-      <c r="M75" s="258"/>
-      <c r="N75" s="258"/>
-      <c r="O75" s="258"/>
-      <c r="P75" s="258"/>
+      <c r="F75" s="253"/>
+      <c r="G75" s="253"/>
+      <c r="H75" s="253"/>
+      <c r="I75" s="253"/>
+      <c r="J75" s="253"/>
+      <c r="K75" s="253"/>
+      <c r="L75" s="253"/>
+      <c r="M75" s="253"/>
+      <c r="N75" s="253"/>
+      <c r="O75" s="253"/>
+      <c r="P75" s="253"/>
       <c r="Q75" s="55"/>
       <c r="R75" s="55"/>
     </row>
@@ -4631,20 +4802,20 @@
       <c r="D76" s="110">
         <v>1</v>
       </c>
-      <c r="E76" s="147" t="s">
+      <c r="E76" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="F76" s="147"/>
-      <c r="G76" s="147"/>
-      <c r="H76" s="147"/>
-      <c r="I76" s="147"/>
-      <c r="J76" s="147"/>
-      <c r="K76" s="147"/>
-      <c r="L76" s="147"/>
-      <c r="M76" s="147"/>
-      <c r="N76" s="147"/>
-      <c r="O76" s="147"/>
-      <c r="P76" s="147"/>
+      <c r="F76" s="146"/>
+      <c r="G76" s="146"/>
+      <c r="H76" s="146"/>
+      <c r="I76" s="146"/>
+      <c r="J76" s="146"/>
+      <c r="K76" s="146"/>
+      <c r="L76" s="146"/>
+      <c r="M76" s="146"/>
+      <c r="N76" s="146"/>
+      <c r="O76" s="146"/>
+      <c r="P76" s="146"/>
       <c r="Q76" s="55"/>
       <c r="R76" s="55"/>
     </row>
@@ -4654,18 +4825,18 @@
       <c r="D77" s="112">
         <v>2</v>
       </c>
-      <c r="E77" s="148"/>
-      <c r="F77" s="149"/>
-      <c r="G77" s="149"/>
-      <c r="H77" s="149"/>
-      <c r="I77" s="149"/>
-      <c r="J77" s="149"/>
-      <c r="K77" s="149"/>
-      <c r="L77" s="149"/>
-      <c r="M77" s="149"/>
-      <c r="N77" s="149"/>
-      <c r="O77" s="149"/>
-      <c r="P77" s="150"/>
+      <c r="E77" s="147"/>
+      <c r="F77" s="148"/>
+      <c r="G77" s="148"/>
+      <c r="H77" s="148"/>
+      <c r="I77" s="148"/>
+      <c r="J77" s="148"/>
+      <c r="K77" s="148"/>
+      <c r="L77" s="148"/>
+      <c r="M77" s="148"/>
+      <c r="N77" s="148"/>
+      <c r="O77" s="148"/>
+      <c r="P77" s="149"/>
       <c r="Q77" s="55"/>
       <c r="R77" s="55"/>
     </row>
@@ -4675,18 +4846,18 @@
       <c r="D78" s="110">
         <v>3</v>
       </c>
-      <c r="E78" s="151"/>
-      <c r="F78" s="152"/>
-      <c r="G78" s="152"/>
-      <c r="H78" s="152"/>
-      <c r="I78" s="152"/>
-      <c r="J78" s="152"/>
-      <c r="K78" s="152"/>
-      <c r="L78" s="152"/>
-      <c r="M78" s="152"/>
-      <c r="N78" s="152"/>
-      <c r="O78" s="152"/>
-      <c r="P78" s="153"/>
+      <c r="E78" s="150"/>
+      <c r="F78" s="151"/>
+      <c r="G78" s="151"/>
+      <c r="H78" s="151"/>
+      <c r="I78" s="151"/>
+      <c r="J78" s="151"/>
+      <c r="K78" s="151"/>
+      <c r="L78" s="151"/>
+      <c r="M78" s="151"/>
+      <c r="N78" s="151"/>
+      <c r="O78" s="151"/>
+      <c r="P78" s="152"/>
       <c r="Q78" s="55"/>
       <c r="R78" s="55"/>
     </row>
@@ -4696,18 +4867,18 @@
       <c r="D79" s="112">
         <v>4</v>
       </c>
-      <c r="E79" s="245"/>
-      <c r="F79" s="226"/>
-      <c r="G79" s="226"/>
-      <c r="H79" s="226"/>
-      <c r="I79" s="226"/>
-      <c r="J79" s="226"/>
-      <c r="K79" s="226"/>
-      <c r="L79" s="226"/>
-      <c r="M79" s="226"/>
-      <c r="N79" s="226"/>
-      <c r="O79" s="226"/>
-      <c r="P79" s="226"/>
+      <c r="E79" s="240"/>
+      <c r="F79" s="221"/>
+      <c r="G79" s="221"/>
+      <c r="H79" s="221"/>
+      <c r="I79" s="221"/>
+      <c r="J79" s="221"/>
+      <c r="K79" s="221"/>
+      <c r="L79" s="221"/>
+      <c r="M79" s="221"/>
+      <c r="N79" s="221"/>
+      <c r="O79" s="221"/>
+      <c r="P79" s="221"/>
     </row>
     <row r="80" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="8"/>
@@ -4715,35 +4886,35 @@
       <c r="D80" s="110">
         <v>5</v>
       </c>
-      <c r="E80" s="254"/>
-      <c r="F80" s="182"/>
-      <c r="G80" s="182"/>
-      <c r="H80" s="182"/>
-      <c r="I80" s="182"/>
-      <c r="J80" s="182"/>
-      <c r="K80" s="182"/>
-      <c r="L80" s="182"/>
-      <c r="M80" s="182"/>
-      <c r="N80" s="182"/>
-      <c r="O80" s="182"/>
-      <c r="P80" s="182"/>
+      <c r="E80" s="249"/>
+      <c r="F80" s="177"/>
+      <c r="G80" s="177"/>
+      <c r="H80" s="177"/>
+      <c r="I80" s="177"/>
+      <c r="J80" s="177"/>
+      <c r="K80" s="177"/>
+      <c r="L80" s="177"/>
+      <c r="M80" s="177"/>
+      <c r="N80" s="177"/>
+      <c r="O80" s="177"/>
+      <c r="P80" s="177"/>
     </row>
     <row r="81" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="101"/>
-      <c r="E81" s="256"/>
-      <c r="F81" s="119"/>
-      <c r="G81" s="119"/>
-      <c r="H81" s="119"/>
-      <c r="I81" s="119"/>
-      <c r="J81" s="119"/>
-      <c r="K81" s="119"/>
-      <c r="L81" s="119"/>
-      <c r="M81" s="119"/>
-      <c r="N81" s="119"/>
-      <c r="O81" s="119"/>
-      <c r="P81" s="119"/>
+      <c r="E81" s="251"/>
+      <c r="F81" s="118"/>
+      <c r="G81" s="118"/>
+      <c r="H81" s="118"/>
+      <c r="I81" s="118"/>
+      <c r="J81" s="118"/>
+      <c r="K81" s="118"/>
+      <c r="L81" s="118"/>
+      <c r="M81" s="118"/>
+      <c r="N81" s="118"/>
+      <c r="O81" s="118"/>
+      <c r="P81" s="118"/>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B82" s="74"/>
@@ -4770,40 +4941,40 @@
       <c r="D83" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="E83" s="265" t="s">
+      <c r="E83" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="265"/>
-      <c r="G83" s="265"/>
-      <c r="H83" s="265"/>
-      <c r="I83" s="265"/>
-      <c r="J83" s="265"/>
-      <c r="K83" s="265"/>
-      <c r="L83" s="265"/>
-      <c r="M83" s="265"/>
-      <c r="N83" s="265"/>
-      <c r="O83" s="265"/>
-      <c r="P83" s="265"/>
+      <c r="F83" s="260"/>
+      <c r="G83" s="260"/>
+      <c r="H83" s="260"/>
+      <c r="I83" s="260"/>
+      <c r="J83" s="260"/>
+      <c r="K83" s="260"/>
+      <c r="L83" s="260"/>
+      <c r="M83" s="260"/>
+      <c r="N83" s="260"/>
+      <c r="O83" s="260"/>
+      <c r="P83" s="260"/>
       <c r="Q83" s="72"/>
       <c r="R83" s="72"/>
     </row>
     <row r="84" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="139">
+      <c r="D84" s="138">
         <v>1</v>
       </c>
-      <c r="E84" s="133" t="s">
+      <c r="E84" s="132" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="134"/>
-      <c r="G84" s="134"/>
-      <c r="H84" s="134"/>
-      <c r="I84" s="134"/>
-      <c r="J84" s="134"/>
-      <c r="K84" s="134"/>
-      <c r="L84" s="134"/>
-      <c r="M84" s="135"/>
+      <c r="F84" s="133"/>
+      <c r="G84" s="133"/>
+      <c r="H84" s="133"/>
+      <c r="I84" s="133"/>
+      <c r="J84" s="133"/>
+      <c r="K84" s="133"/>
+      <c r="L84" s="133"/>
+      <c r="M84" s="134"/>
       <c r="N84" s="47"/>
       <c r="O84" s="47"/>
       <c r="P84" s="47"/>
@@ -4813,44 +4984,44 @@
     <row r="85" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="140"/>
-      <c r="E85" s="136"/>
-      <c r="F85" s="137"/>
-      <c r="G85" s="137"/>
-      <c r="H85" s="137"/>
-      <c r="I85" s="137"/>
-      <c r="J85" s="137"/>
-      <c r="K85" s="137"/>
-      <c r="L85" s="137"/>
-      <c r="M85" s="138"/>
+      <c r="D85" s="139"/>
+      <c r="E85" s="135"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="136"/>
+      <c r="H85" s="136"/>
+      <c r="I85" s="136"/>
+      <c r="J85" s="136"/>
+      <c r="K85" s="136"/>
+      <c r="L85" s="136"/>
+      <c r="M85" s="137"/>
       <c r="N85" s="46"/>
-      <c r="O85" s="167" t="s">
+      <c r="O85" s="162" t="s">
         <v>113</v>
       </c>
-      <c r="P85" s="167"/>
+      <c r="P85" s="162"/>
       <c r="Q85" s="72"/>
       <c r="R85" s="72"/>
     </row>
     <row r="86" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="284">
+      <c r="D86" s="278">
         <v>2</v>
       </c>
-      <c r="E86" s="267"/>
-      <c r="F86" s="268"/>
-      <c r="G86" s="268"/>
-      <c r="H86" s="268"/>
-      <c r="I86" s="268"/>
-      <c r="J86" s="268"/>
-      <c r="K86" s="268"/>
-      <c r="L86" s="268"/>
-      <c r="M86" s="269"/>
+      <c r="E86" s="262"/>
+      <c r="F86" s="263"/>
+      <c r="G86" s="263"/>
+      <c r="H86" s="263"/>
+      <c r="I86" s="263"/>
+      <c r="J86" s="263"/>
+      <c r="K86" s="263"/>
+      <c r="L86" s="263"/>
+      <c r="M86" s="264"/>
       <c r="N86" s="4"/>
-      <c r="O86" s="295" t="s">
+      <c r="O86" s="289" t="s">
         <v>115</v>
       </c>
-      <c r="P86" s="295"/>
+      <c r="P86" s="289"/>
       <c r="Q86" s="44"/>
       <c r="R86" s="44"/>
       <c r="T86" s="97" t="s">
@@ -4860,77 +5031,77 @@
     <row r="87" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="285"/>
-      <c r="E87" s="270"/>
-      <c r="F87" s="271"/>
-      <c r="G87" s="271"/>
-      <c r="H87" s="271"/>
-      <c r="I87" s="271"/>
-      <c r="J87" s="271"/>
-      <c r="K87" s="271"/>
-      <c r="L87" s="271"/>
-      <c r="M87" s="272"/>
+      <c r="D87" s="279"/>
+      <c r="E87" s="265"/>
+      <c r="F87" s="266"/>
+      <c r="G87" s="266"/>
+      <c r="H87" s="266"/>
+      <c r="I87" s="266"/>
+      <c r="J87" s="266"/>
+      <c r="K87" s="266"/>
+      <c r="L87" s="266"/>
+      <c r="M87" s="267"/>
       <c r="N87" s="5"/>
-      <c r="O87" s="295"/>
-      <c r="P87" s="295"/>
+      <c r="O87" s="289"/>
+      <c r="P87" s="289"/>
       <c r="Q87" s="44"/>
       <c r="R87" s="44"/>
     </row>
     <row r="88" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="139">
+      <c r="D88" s="138">
         <v>3</v>
       </c>
-      <c r="E88" s="274"/>
-      <c r="F88" s="275"/>
-      <c r="G88" s="275"/>
-      <c r="H88" s="275"/>
-      <c r="I88" s="275"/>
-      <c r="J88" s="275"/>
-      <c r="K88" s="275"/>
-      <c r="L88" s="275"/>
-      <c r="M88" s="276"/>
+      <c r="E88" s="269"/>
+      <c r="F88" s="270"/>
+      <c r="G88" s="270"/>
+      <c r="H88" s="270"/>
+      <c r="I88" s="270"/>
+      <c r="J88" s="270"/>
+      <c r="K88" s="270"/>
+      <c r="L88" s="270"/>
+      <c r="M88" s="271"/>
       <c r="N88" s="5"/>
-      <c r="O88" s="295"/>
-      <c r="P88" s="295"/>
+      <c r="O88" s="289"/>
+      <c r="P88" s="289"/>
       <c r="Q88" s="44"/>
       <c r="R88" s="44"/>
     </row>
     <row r="89" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="140"/>
-      <c r="E89" s="277"/>
-      <c r="F89" s="278"/>
-      <c r="G89" s="278"/>
-      <c r="H89" s="278"/>
-      <c r="I89" s="278"/>
-      <c r="J89" s="278"/>
-      <c r="K89" s="278"/>
-      <c r="L89" s="278"/>
-      <c r="M89" s="279"/>
+      <c r="D89" s="139"/>
+      <c r="E89" s="272"/>
+      <c r="F89" s="273"/>
+      <c r="G89" s="273"/>
+      <c r="H89" s="273"/>
+      <c r="I89" s="273"/>
+      <c r="J89" s="273"/>
+      <c r="K89" s="273"/>
+      <c r="L89" s="273"/>
+      <c r="M89" s="274"/>
       <c r="N89" s="5"/>
-      <c r="O89" s="296"/>
-      <c r="P89" s="296"/>
+      <c r="O89" s="290"/>
+      <c r="P89" s="290"/>
       <c r="Q89" s="44"/>
       <c r="R89" s="44"/>
     </row>
     <row r="90" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="284">
+      <c r="D90" s="278">
         <v>4</v>
       </c>
-      <c r="E90" s="267"/>
-      <c r="F90" s="268"/>
-      <c r="G90" s="268"/>
-      <c r="H90" s="268"/>
-      <c r="I90" s="268"/>
-      <c r="J90" s="268"/>
-      <c r="K90" s="268"/>
-      <c r="L90" s="268"/>
-      <c r="M90" s="269"/>
+      <c r="E90" s="262"/>
+      <c r="F90" s="263"/>
+      <c r="G90" s="263"/>
+      <c r="H90" s="263"/>
+      <c r="I90" s="263"/>
+      <c r="J90" s="263"/>
+      <c r="K90" s="263"/>
+      <c r="L90" s="263"/>
+      <c r="M90" s="264"/>
       <c r="N90" s="5"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -4940,39 +5111,39 @@
     <row r="91" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="285"/>
-      <c r="E91" s="270"/>
-      <c r="F91" s="271"/>
-      <c r="G91" s="271"/>
-      <c r="H91" s="271"/>
-      <c r="I91" s="271"/>
-      <c r="J91" s="271"/>
-      <c r="K91" s="271"/>
-      <c r="L91" s="271"/>
-      <c r="M91" s="272"/>
+      <c r="D91" s="279"/>
+      <c r="E91" s="265"/>
+      <c r="F91" s="266"/>
+      <c r="G91" s="266"/>
+      <c r="H91" s="266"/>
+      <c r="I91" s="266"/>
+      <c r="J91" s="266"/>
+      <c r="K91" s="266"/>
+      <c r="L91" s="266"/>
+      <c r="M91" s="267"/>
       <c r="N91" s="5"/>
-      <c r="O91" s="167" t="s">
+      <c r="O91" s="162" t="s">
         <v>116</v>
       </c>
-      <c r="P91" s="167"/>
+      <c r="P91" s="162"/>
       <c r="Q91" s="44"/>
       <c r="R91" s="44"/>
     </row>
     <row r="92" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="139">
+      <c r="D92" s="138">
         <v>5</v>
       </c>
-      <c r="E92" s="274"/>
-      <c r="F92" s="275"/>
-      <c r="G92" s="275"/>
-      <c r="H92" s="275"/>
-      <c r="I92" s="275"/>
-      <c r="J92" s="275"/>
-      <c r="K92" s="275"/>
-      <c r="L92" s="275"/>
-      <c r="M92" s="276"/>
+      <c r="E92" s="269"/>
+      <c r="F92" s="270"/>
+      <c r="G92" s="270"/>
+      <c r="H92" s="270"/>
+      <c r="I92" s="270"/>
+      <c r="J92" s="270"/>
+      <c r="K92" s="270"/>
+      <c r="L92" s="270"/>
+      <c r="M92" s="271"/>
       <c r="N92" s="5"/>
       <c r="O92" s="91"/>
       <c r="P92" s="91"/>
@@ -4982,119 +5153,119 @@
     <row r="93" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="140"/>
-      <c r="E93" s="277"/>
-      <c r="F93" s="278"/>
-      <c r="G93" s="278"/>
-      <c r="H93" s="278"/>
-      <c r="I93" s="278"/>
-      <c r="J93" s="278"/>
-      <c r="K93" s="278"/>
-      <c r="L93" s="278"/>
-      <c r="M93" s="279"/>
+      <c r="D93" s="139"/>
+      <c r="E93" s="272"/>
+      <c r="F93" s="273"/>
+      <c r="G93" s="273"/>
+      <c r="H93" s="273"/>
+      <c r="I93" s="273"/>
+      <c r="J93" s="273"/>
+      <c r="K93" s="273"/>
+      <c r="L93" s="273"/>
+      <c r="M93" s="274"/>
       <c r="N93" s="5"/>
-      <c r="O93" s="295" t="s">
+      <c r="O93" s="289" t="s">
         <v>117</v>
       </c>
-      <c r="P93" s="295"/>
+      <c r="P93" s="289"/>
       <c r="Q93" s="44"/>
       <c r="R93" s="44"/>
     </row>
     <row r="94" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="284">
+      <c r="D94" s="278">
         <v>6</v>
       </c>
-      <c r="E94" s="267"/>
-      <c r="F94" s="268"/>
-      <c r="G94" s="268"/>
-      <c r="H94" s="268"/>
-      <c r="I94" s="268"/>
-      <c r="J94" s="268"/>
-      <c r="K94" s="268"/>
-      <c r="L94" s="268"/>
-      <c r="M94" s="269"/>
+      <c r="E94" s="262"/>
+      <c r="F94" s="263"/>
+      <c r="G94" s="263"/>
+      <c r="H94" s="263"/>
+      <c r="I94" s="263"/>
+      <c r="J94" s="263"/>
+      <c r="K94" s="263"/>
+      <c r="L94" s="263"/>
+      <c r="M94" s="264"/>
       <c r="N94" s="5"/>
-      <c r="O94" s="295"/>
-      <c r="P94" s="295"/>
+      <c r="O94" s="289"/>
+      <c r="P94" s="289"/>
       <c r="Q94" s="44"/>
       <c r="R94" s="44"/>
     </row>
     <row r="95" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="285"/>
-      <c r="E95" s="270"/>
-      <c r="F95" s="271"/>
-      <c r="G95" s="271"/>
-      <c r="H95" s="271"/>
-      <c r="I95" s="271"/>
-      <c r="J95" s="271"/>
-      <c r="K95" s="271"/>
-      <c r="L95" s="271"/>
-      <c r="M95" s="272"/>
+      <c r="D95" s="279"/>
+      <c r="E95" s="265"/>
+      <c r="F95" s="266"/>
+      <c r="G95" s="266"/>
+      <c r="H95" s="266"/>
+      <c r="I95" s="266"/>
+      <c r="J95" s="266"/>
+      <c r="K95" s="266"/>
+      <c r="L95" s="266"/>
+      <c r="M95" s="267"/>
       <c r="N95" s="5"/>
-      <c r="O95" s="295"/>
-      <c r="P95" s="295"/>
+      <c r="O95" s="289"/>
+      <c r="P95" s="289"/>
       <c r="Q95" s="44"/>
       <c r="R95" s="44"/>
     </row>
     <row r="96" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="139">
+      <c r="D96" s="138">
         <v>7</v>
       </c>
-      <c r="E96" s="274"/>
-      <c r="F96" s="275"/>
-      <c r="G96" s="275"/>
-      <c r="H96" s="275"/>
-      <c r="I96" s="275"/>
-      <c r="J96" s="275"/>
-      <c r="K96" s="275"/>
-      <c r="L96" s="275"/>
-      <c r="M96" s="276"/>
+      <c r="E96" s="269"/>
+      <c r="F96" s="270"/>
+      <c r="G96" s="270"/>
+      <c r="H96" s="270"/>
+      <c r="I96" s="270"/>
+      <c r="J96" s="270"/>
+      <c r="K96" s="270"/>
+      <c r="L96" s="270"/>
+      <c r="M96" s="271"/>
       <c r="N96" s="5"/>
-      <c r="O96" s="295"/>
-      <c r="P96" s="295"/>
+      <c r="O96" s="289"/>
+      <c r="P96" s="289"/>
       <c r="Q96" s="44"/>
       <c r="R96" s="44"/>
     </row>
     <row r="97" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="140"/>
-      <c r="E97" s="277"/>
-      <c r="F97" s="278"/>
-      <c r="G97" s="278"/>
-      <c r="H97" s="278"/>
-      <c r="I97" s="278"/>
-      <c r="J97" s="278"/>
-      <c r="K97" s="278"/>
-      <c r="L97" s="278"/>
-      <c r="M97" s="279"/>
+      <c r="D97" s="139"/>
+      <c r="E97" s="272"/>
+      <c r="F97" s="273"/>
+      <c r="G97" s="273"/>
+      <c r="H97" s="273"/>
+      <c r="I97" s="273"/>
+      <c r="J97" s="273"/>
+      <c r="K97" s="273"/>
+      <c r="L97" s="273"/>
+      <c r="M97" s="274"/>
       <c r="N97" s="5"/>
-      <c r="O97" s="296"/>
-      <c r="P97" s="296"/>
+      <c r="O97" s="290"/>
+      <c r="P97" s="290"/>
       <c r="Q97" s="44"/>
       <c r="R97" s="44"/>
     </row>
     <row r="98" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="284">
+      <c r="D98" s="278">
         <v>8</v>
       </c>
-      <c r="E98" s="267"/>
-      <c r="F98" s="268"/>
-      <c r="G98" s="268"/>
-      <c r="H98" s="268"/>
-      <c r="I98" s="268"/>
-      <c r="J98" s="268"/>
-      <c r="K98" s="268"/>
-      <c r="L98" s="268"/>
-      <c r="M98" s="269"/>
+      <c r="E98" s="262"/>
+      <c r="F98" s="263"/>
+      <c r="G98" s="263"/>
+      <c r="H98" s="263"/>
+      <c r="I98" s="263"/>
+      <c r="J98" s="263"/>
+      <c r="K98" s="263"/>
+      <c r="L98" s="263"/>
+      <c r="M98" s="264"/>
       <c r="N98" s="5"/>
       <c r="O98" s="114"/>
       <c r="P98" s="114"/>
@@ -5104,263 +5275,263 @@
     <row r="99" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="285"/>
-      <c r="E99" s="270"/>
-      <c r="F99" s="271"/>
-      <c r="G99" s="271"/>
-      <c r="H99" s="271"/>
-      <c r="I99" s="271"/>
-      <c r="J99" s="271"/>
-      <c r="K99" s="271"/>
-      <c r="L99" s="271"/>
-      <c r="M99" s="272"/>
+      <c r="D99" s="279"/>
+      <c r="E99" s="265"/>
+      <c r="F99" s="266"/>
+      <c r="G99" s="266"/>
+      <c r="H99" s="266"/>
+      <c r="I99" s="266"/>
+      <c r="J99" s="266"/>
+      <c r="K99" s="266"/>
+      <c r="L99" s="266"/>
+      <c r="M99" s="267"/>
       <c r="N99" s="5"/>
-      <c r="O99" s="167" t="s">
+      <c r="O99" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="P99" s="167"/>
+      <c r="P99" s="162"/>
       <c r="Q99" s="44"/>
       <c r="R99" s="44"/>
     </row>
     <row r="100" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="139">
+      <c r="D100" s="138">
         <v>9</v>
       </c>
-      <c r="E100" s="274"/>
-      <c r="F100" s="275"/>
-      <c r="G100" s="275"/>
-      <c r="H100" s="275"/>
-      <c r="I100" s="275"/>
-      <c r="J100" s="275"/>
-      <c r="K100" s="275"/>
-      <c r="L100" s="275"/>
-      <c r="M100" s="276"/>
+      <c r="E100" s="269"/>
+      <c r="F100" s="270"/>
+      <c r="G100" s="270"/>
+      <c r="H100" s="270"/>
+      <c r="I100" s="270"/>
+      <c r="J100" s="270"/>
+      <c r="K100" s="270"/>
+      <c r="L100" s="270"/>
+      <c r="M100" s="271"/>
       <c r="N100" s="5"/>
-      <c r="O100" s="295" t="s">
+      <c r="O100" s="289" t="s">
         <v>119</v>
       </c>
-      <c r="P100" s="295"/>
+      <c r="P100" s="289"/>
       <c r="Q100" s="44"/>
       <c r="R100" s="44"/>
     </row>
     <row r="101" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="140"/>
-      <c r="E101" s="277"/>
-      <c r="F101" s="278"/>
-      <c r="G101" s="278"/>
-      <c r="H101" s="278"/>
-      <c r="I101" s="278"/>
-      <c r="J101" s="278"/>
-      <c r="K101" s="278"/>
-      <c r="L101" s="278"/>
-      <c r="M101" s="279"/>
+      <c r="D101" s="139"/>
+      <c r="E101" s="272"/>
+      <c r="F101" s="273"/>
+      <c r="G101" s="273"/>
+      <c r="H101" s="273"/>
+      <c r="I101" s="273"/>
+      <c r="J101" s="273"/>
+      <c r="K101" s="273"/>
+      <c r="L101" s="273"/>
+      <c r="M101" s="274"/>
       <c r="N101" s="5"/>
-      <c r="O101" s="295"/>
-      <c r="P101" s="295"/>
+      <c r="O101" s="289"/>
+      <c r="P101" s="289"/>
       <c r="Q101" s="44"/>
       <c r="R101" s="44"/>
     </row>
     <row r="102" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
-      <c r="D102" s="284">
+      <c r="D102" s="278">
         <v>10</v>
       </c>
-      <c r="E102" s="267"/>
-      <c r="F102" s="268"/>
-      <c r="G102" s="268"/>
-      <c r="H102" s="268"/>
-      <c r="I102" s="268"/>
-      <c r="J102" s="268"/>
-      <c r="K102" s="268"/>
-      <c r="L102" s="268"/>
-      <c r="M102" s="269"/>
+      <c r="E102" s="262"/>
+      <c r="F102" s="263"/>
+      <c r="G102" s="263"/>
+      <c r="H102" s="263"/>
+      <c r="I102" s="263"/>
+      <c r="J102" s="263"/>
+      <c r="K102" s="263"/>
+      <c r="L102" s="263"/>
+      <c r="M102" s="264"/>
       <c r="N102" s="5"/>
-      <c r="O102" s="295"/>
-      <c r="P102" s="295"/>
+      <c r="O102" s="289"/>
+      <c r="P102" s="289"/>
       <c r="Q102" s="44"/>
       <c r="R102" s="44"/>
     </row>
     <row r="103" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="285"/>
-      <c r="E103" s="270"/>
-      <c r="F103" s="271"/>
-      <c r="G103" s="271"/>
-      <c r="H103" s="271"/>
-      <c r="I103" s="271"/>
-      <c r="J103" s="271"/>
-      <c r="K103" s="271"/>
-      <c r="L103" s="271"/>
-      <c r="M103" s="272"/>
+      <c r="D103" s="279"/>
+      <c r="E103" s="265"/>
+      <c r="F103" s="266"/>
+      <c r="G103" s="266"/>
+      <c r="H103" s="266"/>
+      <c r="I103" s="266"/>
+      <c r="J103" s="266"/>
+      <c r="K103" s="266"/>
+      <c r="L103" s="266"/>
+      <c r="M103" s="267"/>
       <c r="N103" s="5"/>
-      <c r="O103" s="295"/>
-      <c r="P103" s="295"/>
+      <c r="O103" s="289"/>
+      <c r="P103" s="289"/>
       <c r="Q103" s="44"/>
       <c r="R103" s="44"/>
     </row>
     <row r="104" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="139">
+      <c r="D104" s="138">
         <v>11</v>
       </c>
-      <c r="E104" s="274"/>
-      <c r="F104" s="275"/>
-      <c r="G104" s="275"/>
-      <c r="H104" s="275"/>
-      <c r="I104" s="275"/>
-      <c r="J104" s="275"/>
-      <c r="K104" s="275"/>
-      <c r="L104" s="275"/>
-      <c r="M104" s="276"/>
+      <c r="E104" s="269"/>
+      <c r="F104" s="270"/>
+      <c r="G104" s="270"/>
+      <c r="H104" s="270"/>
+      <c r="I104" s="270"/>
+      <c r="J104" s="270"/>
+      <c r="K104" s="270"/>
+      <c r="L104" s="270"/>
+      <c r="M104" s="271"/>
       <c r="N104" s="5"/>
-      <c r="O104" s="295"/>
-      <c r="P104" s="295"/>
+      <c r="O104" s="289"/>
+      <c r="P104" s="289"/>
       <c r="Q104" s="44"/>
       <c r="R104" s="44"/>
     </row>
     <row r="105" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="140"/>
-      <c r="E105" s="277"/>
-      <c r="F105" s="278"/>
-      <c r="G105" s="278"/>
-      <c r="H105" s="278"/>
-      <c r="I105" s="278"/>
-      <c r="J105" s="278"/>
-      <c r="K105" s="278"/>
-      <c r="L105" s="278"/>
-      <c r="M105" s="279"/>
+      <c r="D105" s="139"/>
+      <c r="E105" s="272"/>
+      <c r="F105" s="273"/>
+      <c r="G105" s="273"/>
+      <c r="H105" s="273"/>
+      <c r="I105" s="273"/>
+      <c r="J105" s="273"/>
+      <c r="K105" s="273"/>
+      <c r="L105" s="273"/>
+      <c r="M105" s="274"/>
       <c r="N105" s="5"/>
-      <c r="O105" s="296"/>
-      <c r="P105" s="296"/>
+      <c r="O105" s="290"/>
+      <c r="P105" s="290"/>
       <c r="Q105" s="44"/>
       <c r="R105" s="44"/>
     </row>
     <row r="106" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="284">
+      <c r="D106" s="278">
         <v>12</v>
       </c>
-      <c r="E106" s="267"/>
-      <c r="F106" s="268"/>
-      <c r="G106" s="268"/>
-      <c r="H106" s="268"/>
-      <c r="I106" s="268"/>
-      <c r="J106" s="268"/>
-      <c r="K106" s="268"/>
-      <c r="L106" s="268"/>
-      <c r="M106" s="269"/>
+      <c r="E106" s="262"/>
+      <c r="F106" s="263"/>
+      <c r="G106" s="263"/>
+      <c r="H106" s="263"/>
+      <c r="I106" s="263"/>
+      <c r="J106" s="263"/>
+      <c r="K106" s="263"/>
+      <c r="L106" s="263"/>
+      <c r="M106" s="264"/>
       <c r="N106" s="5"/>
-      <c r="O106" s="289"/>
-      <c r="P106" s="289"/>
+      <c r="O106" s="283"/>
+      <c r="P106" s="283"/>
       <c r="Q106" s="44"/>
       <c r="R106" s="44"/>
     </row>
     <row r="107" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="285"/>
-      <c r="E107" s="270"/>
-      <c r="F107" s="271"/>
-      <c r="G107" s="271"/>
-      <c r="H107" s="271"/>
-      <c r="I107" s="271"/>
-      <c r="J107" s="271"/>
-      <c r="K107" s="271"/>
-      <c r="L107" s="271"/>
-      <c r="M107" s="272"/>
+      <c r="D107" s="279"/>
+      <c r="E107" s="265"/>
+      <c r="F107" s="266"/>
+      <c r="G107" s="266"/>
+      <c r="H107" s="266"/>
+      <c r="I107" s="266"/>
+      <c r="J107" s="266"/>
+      <c r="K107" s="266"/>
+      <c r="L107" s="266"/>
+      <c r="M107" s="267"/>
       <c r="N107" s="5"/>
-      <c r="O107" s="290"/>
-      <c r="P107" s="290"/>
+      <c r="O107" s="284"/>
+      <c r="P107" s="284"/>
       <c r="Q107" s="44"/>
       <c r="R107" s="44"/>
     </row>
     <row r="108" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="139">
+      <c r="D108" s="138">
         <v>13</v>
       </c>
-      <c r="E108" s="274"/>
-      <c r="F108" s="275"/>
-      <c r="G108" s="275"/>
-      <c r="H108" s="275"/>
-      <c r="I108" s="275"/>
-      <c r="J108" s="275"/>
-      <c r="K108" s="275"/>
-      <c r="L108" s="275"/>
-      <c r="M108" s="276"/>
+      <c r="E108" s="269"/>
+      <c r="F108" s="270"/>
+      <c r="G108" s="270"/>
+      <c r="H108" s="270"/>
+      <c r="I108" s="270"/>
+      <c r="J108" s="270"/>
+      <c r="K108" s="270"/>
+      <c r="L108" s="270"/>
+      <c r="M108" s="271"/>
       <c r="N108" s="5"/>
-      <c r="O108" s="290"/>
-      <c r="P108" s="290"/>
+      <c r="O108" s="284"/>
+      <c r="P108" s="284"/>
       <c r="Q108" s="44"/>
       <c r="R108" s="44"/>
     </row>
     <row r="109" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="140"/>
-      <c r="E109" s="277"/>
-      <c r="F109" s="278"/>
-      <c r="G109" s="278"/>
-      <c r="H109" s="278"/>
-      <c r="I109" s="278"/>
-      <c r="J109" s="278"/>
-      <c r="K109" s="278"/>
-      <c r="L109" s="278"/>
-      <c r="M109" s="279"/>
+      <c r="D109" s="139"/>
+      <c r="E109" s="272"/>
+      <c r="F109" s="273"/>
+      <c r="G109" s="273"/>
+      <c r="H109" s="273"/>
+      <c r="I109" s="273"/>
+      <c r="J109" s="273"/>
+      <c r="K109" s="273"/>
+      <c r="L109" s="273"/>
+      <c r="M109" s="274"/>
       <c r="N109" s="5"/>
-      <c r="O109" s="290"/>
-      <c r="P109" s="290"/>
+      <c r="O109" s="284"/>
+      <c r="P109" s="284"/>
       <c r="Q109" s="44"/>
       <c r="R109" s="44"/>
     </row>
     <row r="110" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
-      <c r="D110" s="284">
+      <c r="D110" s="278">
         <v>14</v>
       </c>
-      <c r="E110" s="267"/>
-      <c r="F110" s="268"/>
-      <c r="G110" s="268"/>
-      <c r="H110" s="268"/>
-      <c r="I110" s="268"/>
-      <c r="J110" s="268"/>
-      <c r="K110" s="268"/>
-      <c r="L110" s="268"/>
-      <c r="M110" s="269"/>
+      <c r="E110" s="262"/>
+      <c r="F110" s="263"/>
+      <c r="G110" s="263"/>
+      <c r="H110" s="263"/>
+      <c r="I110" s="263"/>
+      <c r="J110" s="263"/>
+      <c r="K110" s="263"/>
+      <c r="L110" s="263"/>
+      <c r="M110" s="264"/>
       <c r="N110" s="5"/>
-      <c r="O110" s="290"/>
-      <c r="P110" s="290"/>
+      <c r="O110" s="284"/>
+      <c r="P110" s="284"/>
       <c r="Q110" s="44"/>
       <c r="R110" s="44"/>
     </row>
     <row r="111" spans="2:18" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="285"/>
-      <c r="E111" s="270"/>
-      <c r="F111" s="271"/>
-      <c r="G111" s="271"/>
-      <c r="H111" s="271"/>
-      <c r="I111" s="271"/>
-      <c r="J111" s="271"/>
-      <c r="K111" s="271"/>
-      <c r="L111" s="271"/>
-      <c r="M111" s="272"/>
+      <c r="D111" s="279"/>
+      <c r="E111" s="265"/>
+      <c r="F111" s="266"/>
+      <c r="G111" s="266"/>
+      <c r="H111" s="266"/>
+      <c r="I111" s="266"/>
+      <c r="J111" s="266"/>
+      <c r="K111" s="266"/>
+      <c r="L111" s="266"/>
+      <c r="M111" s="267"/>
       <c r="N111" s="5"/>
-      <c r="O111" s="291"/>
-      <c r="P111" s="291"/>
+      <c r="O111" s="285"/>
+      <c r="P111" s="285"/>
       <c r="Q111" s="46"/>
       <c r="R111" s="46"/>
     </row>
@@ -5378,10 +5549,10 @@
       <c r="L112" s="116"/>
       <c r="M112" s="116"/>
       <c r="N112" s="5"/>
-      <c r="O112" s="288" t="s">
+      <c r="O112" s="282" t="s">
         <v>88</v>
       </c>
-      <c r="P112" s="288"/>
+      <c r="P112" s="282"/>
       <c r="Q112" s="46"/>
       <c r="R112" s="46"/>
     </row>
@@ -5410,20 +5581,20 @@
       <c r="D114" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="E114" s="292" t="s">
+      <c r="E114" s="286" t="s">
         <v>129</v>
       </c>
-      <c r="F114" s="293"/>
-      <c r="G114" s="293"/>
-      <c r="H114" s="293"/>
-      <c r="I114" s="293"/>
-      <c r="J114" s="293"/>
-      <c r="K114" s="293"/>
-      <c r="L114" s="293"/>
-      <c r="M114" s="293"/>
-      <c r="N114" s="293"/>
-      <c r="O114" s="293"/>
-      <c r="P114" s="293"/>
+      <c r="F114" s="287"/>
+      <c r="G114" s="287"/>
+      <c r="H114" s="287"/>
+      <c r="I114" s="287"/>
+      <c r="J114" s="287"/>
+      <c r="K114" s="287"/>
+      <c r="L114" s="287"/>
+      <c r="M114" s="287"/>
+      <c r="N114" s="287"/>
+      <c r="O114" s="287"/>
+      <c r="P114" s="287"/>
       <c r="Q114" s="44"/>
       <c r="R114" s="44"/>
     </row>
@@ -5433,20 +5604,20 @@
       <c r="D115" s="108">
         <v>1</v>
       </c>
-      <c r="E115" s="294" t="s">
+      <c r="E115" s="288" t="s">
         <v>120</v>
       </c>
-      <c r="F115" s="294"/>
-      <c r="G115" s="294"/>
-      <c r="H115" s="294"/>
-      <c r="I115" s="294"/>
-      <c r="J115" s="294"/>
-      <c r="K115" s="294"/>
-      <c r="L115" s="294"/>
-      <c r="M115" s="294"/>
-      <c r="N115" s="294"/>
-      <c r="O115" s="294"/>
-      <c r="P115" s="294"/>
+      <c r="F115" s="288"/>
+      <c r="G115" s="288"/>
+      <c r="H115" s="288"/>
+      <c r="I115" s="288"/>
+      <c r="J115" s="288"/>
+      <c r="K115" s="288"/>
+      <c r="L115" s="288"/>
+      <c r="M115" s="288"/>
+      <c r="N115" s="288"/>
+      <c r="O115" s="288"/>
+      <c r="P115" s="288"/>
       <c r="Q115" s="55"/>
       <c r="R115" s="55"/>
     </row>
@@ -5456,18 +5627,18 @@
       <c r="D116" s="113">
         <v>2</v>
       </c>
-      <c r="E116" s="250"/>
-      <c r="F116" s="250"/>
-      <c r="G116" s="250"/>
-      <c r="H116" s="250"/>
-      <c r="I116" s="250"/>
-      <c r="J116" s="250"/>
-      <c r="K116" s="250"/>
-      <c r="L116" s="250"/>
-      <c r="M116" s="250"/>
-      <c r="N116" s="250"/>
-      <c r="O116" s="250"/>
-      <c r="P116" s="250"/>
+      <c r="E116" s="245"/>
+      <c r="F116" s="245"/>
+      <c r="G116" s="245"/>
+      <c r="H116" s="245"/>
+      <c r="I116" s="245"/>
+      <c r="J116" s="245"/>
+      <c r="K116" s="245"/>
+      <c r="L116" s="245"/>
+      <c r="M116" s="245"/>
+      <c r="N116" s="245"/>
+      <c r="O116" s="245"/>
+      <c r="P116" s="245"/>
       <c r="Q116" s="55"/>
       <c r="R116" s="55"/>
     </row>
@@ -5477,18 +5648,18 @@
       <c r="D117" s="108">
         <v>3</v>
       </c>
-      <c r="E117" s="169"/>
-      <c r="F117" s="169"/>
-      <c r="G117" s="169"/>
-      <c r="H117" s="169"/>
-      <c r="I117" s="169"/>
-      <c r="J117" s="169"/>
-      <c r="K117" s="169"/>
-      <c r="L117" s="169"/>
-      <c r="M117" s="169"/>
-      <c r="N117" s="169"/>
-      <c r="O117" s="169"/>
-      <c r="P117" s="169"/>
+      <c r="E117" s="164"/>
+      <c r="F117" s="164"/>
+      <c r="G117" s="164"/>
+      <c r="H117" s="164"/>
+      <c r="I117" s="164"/>
+      <c r="J117" s="164"/>
+      <c r="K117" s="164"/>
+      <c r="L117" s="164"/>
+      <c r="M117" s="164"/>
+      <c r="N117" s="164"/>
+      <c r="O117" s="164"/>
+      <c r="P117" s="164"/>
       <c r="Q117" s="55"/>
       <c r="R117" s="55"/>
     </row>
@@ -5498,18 +5669,18 @@
       <c r="D118" s="113">
         <v>4</v>
       </c>
-      <c r="E118" s="250"/>
-      <c r="F118" s="250"/>
-      <c r="G118" s="250"/>
-      <c r="H118" s="250"/>
-      <c r="I118" s="250"/>
-      <c r="J118" s="250"/>
-      <c r="K118" s="250"/>
-      <c r="L118" s="250"/>
-      <c r="M118" s="250"/>
-      <c r="N118" s="250"/>
-      <c r="O118" s="250"/>
-      <c r="P118" s="250"/>
+      <c r="E118" s="245"/>
+      <c r="F118" s="245"/>
+      <c r="G118" s="245"/>
+      <c r="H118" s="245"/>
+      <c r="I118" s="245"/>
+      <c r="J118" s="245"/>
+      <c r="K118" s="245"/>
+      <c r="L118" s="245"/>
+      <c r="M118" s="245"/>
+      <c r="N118" s="245"/>
+      <c r="O118" s="245"/>
+      <c r="P118" s="245"/>
     </row>
     <row r="119" spans="2:18" ht="24" x14ac:dyDescent="0.3">
       <c r="B119" s="3"/>
@@ -5517,18 +5688,18 @@
       <c r="D119" s="108">
         <v>5</v>
       </c>
-      <c r="E119" s="273"/>
-      <c r="F119" s="273"/>
-      <c r="G119" s="273"/>
-      <c r="H119" s="273"/>
-      <c r="I119" s="273"/>
-      <c r="J119" s="273"/>
-      <c r="K119" s="273"/>
-      <c r="L119" s="273"/>
-      <c r="M119" s="273"/>
-      <c r="N119" s="273"/>
-      <c r="O119" s="273"/>
-      <c r="P119" s="273"/>
+      <c r="E119" s="268"/>
+      <c r="F119" s="268"/>
+      <c r="G119" s="268"/>
+      <c r="H119" s="268"/>
+      <c r="I119" s="268"/>
+      <c r="J119" s="268"/>
+      <c r="K119" s="268"/>
+      <c r="L119" s="268"/>
+      <c r="M119" s="268"/>
+      <c r="N119" s="268"/>
+      <c r="O119" s="268"/>
+      <c r="P119" s="268"/>
     </row>
     <row r="120" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="8"/>
@@ -5536,18 +5707,18 @@
       <c r="D120" s="113">
         <v>6</v>
       </c>
-      <c r="E120" s="250"/>
-      <c r="F120" s="250"/>
-      <c r="G120" s="250"/>
-      <c r="H120" s="250"/>
-      <c r="I120" s="250"/>
-      <c r="J120" s="250"/>
-      <c r="K120" s="250"/>
-      <c r="L120" s="250"/>
-      <c r="M120" s="250"/>
-      <c r="N120" s="250"/>
-      <c r="O120" s="250"/>
-      <c r="P120" s="250"/>
+      <c r="E120" s="245"/>
+      <c r="F120" s="245"/>
+      <c r="G120" s="245"/>
+      <c r="H120" s="245"/>
+      <c r="I120" s="245"/>
+      <c r="J120" s="245"/>
+      <c r="K120" s="245"/>
+      <c r="L120" s="245"/>
+      <c r="M120" s="245"/>
+      <c r="N120" s="245"/>
+      <c r="O120" s="245"/>
+      <c r="P120" s="245"/>
       <c r="Q120" s="55"/>
       <c r="R120" s="55"/>
     </row>
@@ -5557,18 +5728,18 @@
       <c r="D121" s="108">
         <v>7</v>
       </c>
-      <c r="E121" s="169"/>
-      <c r="F121" s="169"/>
-      <c r="G121" s="169"/>
-      <c r="H121" s="169"/>
-      <c r="I121" s="169"/>
-      <c r="J121" s="169"/>
-      <c r="K121" s="169"/>
-      <c r="L121" s="169"/>
-      <c r="M121" s="169"/>
-      <c r="N121" s="169"/>
-      <c r="O121" s="169"/>
-      <c r="P121" s="169"/>
+      <c r="E121" s="164"/>
+      <c r="F121" s="164"/>
+      <c r="G121" s="164"/>
+      <c r="H121" s="164"/>
+      <c r="I121" s="164"/>
+      <c r="J121" s="164"/>
+      <c r="K121" s="164"/>
+      <c r="L121" s="164"/>
+      <c r="M121" s="164"/>
+      <c r="N121" s="164"/>
+      <c r="O121" s="164"/>
+      <c r="P121" s="164"/>
       <c r="Q121" s="55"/>
       <c r="R121" s="55"/>
     </row>
@@ -5578,58 +5749,58 @@
       <c r="D122" s="113">
         <v>8</v>
       </c>
-      <c r="E122" s="250"/>
-      <c r="F122" s="250"/>
-      <c r="G122" s="250"/>
-      <c r="H122" s="250"/>
-      <c r="I122" s="250"/>
-      <c r="J122" s="250"/>
-      <c r="K122" s="250"/>
-      <c r="L122" s="250"/>
-      <c r="M122" s="250"/>
-      <c r="N122" s="250"/>
-      <c r="O122" s="250"/>
-      <c r="P122" s="250"/>
+      <c r="E122" s="245"/>
+      <c r="F122" s="245"/>
+      <c r="G122" s="245"/>
+      <c r="H122" s="245"/>
+      <c r="I122" s="245"/>
+      <c r="J122" s="245"/>
+      <c r="K122" s="245"/>
+      <c r="L122" s="245"/>
+      <c r="M122" s="245"/>
+      <c r="N122" s="245"/>
+      <c r="O122" s="245"/>
+      <c r="P122" s="245"/>
       <c r="Q122" s="55"/>
       <c r="R122" s="55"/>
     </row>
     <row r="123" spans="2:18" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="74"/>
       <c r="C123" s="74"/>
-      <c r="D123" s="266"/>
-      <c r="E123" s="266"/>
-      <c r="F123" s="266"/>
-      <c r="G123" s="266"/>
-      <c r="H123" s="266"/>
-      <c r="I123" s="266"/>
-      <c r="J123" s="266"/>
-      <c r="K123" s="266"/>
-      <c r="L123" s="266"/>
-      <c r="M123" s="266"/>
-      <c r="N123" s="266"/>
-      <c r="O123" s="266"/>
-      <c r="P123" s="266"/>
+      <c r="D123" s="261"/>
+      <c r="E123" s="261"/>
+      <c r="F123" s="261"/>
+      <c r="G123" s="261"/>
+      <c r="H123" s="261"/>
+      <c r="I123" s="261"/>
+      <c r="J123" s="261"/>
+      <c r="K123" s="261"/>
+      <c r="L123" s="261"/>
+      <c r="M123" s="261"/>
+      <c r="N123" s="261"/>
+      <c r="O123" s="261"/>
+      <c r="P123" s="261"/>
       <c r="Q123" s="55"/>
       <c r="R123" s="55"/>
     </row>
     <row r="124" spans="2:18" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="74"/>
       <c r="C124" s="74"/>
-      <c r="D124" s="244" t="s">
+      <c r="D124" s="239" t="s">
         <v>121</v>
       </c>
-      <c r="E124" s="244"/>
-      <c r="F124" s="244"/>
-      <c r="G124" s="244"/>
-      <c r="H124" s="244"/>
-      <c r="I124" s="244"/>
-      <c r="J124" s="244"/>
-      <c r="K124" s="244"/>
-      <c r="L124" s="244"/>
-      <c r="M124" s="244"/>
-      <c r="N124" s="244"/>
-      <c r="O124" s="244"/>
-      <c r="P124" s="244"/>
+      <c r="E124" s="239"/>
+      <c r="F124" s="239"/>
+      <c r="G124" s="239"/>
+      <c r="H124" s="239"/>
+      <c r="I124" s="239"/>
+      <c r="J124" s="239"/>
+      <c r="K124" s="239"/>
+      <c r="L124" s="239"/>
+      <c r="M124" s="239"/>
+      <c r="N124" s="239"/>
+      <c r="O124" s="239"/>
+      <c r="P124" s="239"/>
       <c r="Q124" s="55"/>
       <c r="R124" s="55"/>
     </row>
@@ -5655,27 +5826,27 @@
     <row r="126" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="74"/>
       <c r="C126" s="74"/>
-      <c r="D126" s="210" t="s">
+      <c r="D126" s="205" t="s">
         <v>122</v>
       </c>
-      <c r="E126" s="210"/>
-      <c r="F126" s="210"/>
+      <c r="E126" s="205"/>
+      <c r="F126" s="205"/>
       <c r="G126" s="55"/>
-      <c r="H126" s="210" t="s">
+      <c r="H126" s="205" t="s">
         <v>122</v>
       </c>
-      <c r="I126" s="210"/>
-      <c r="J126" s="210"/>
+      <c r="I126" s="205"/>
+      <c r="J126" s="205"/>
       <c r="K126" s="55"/>
-      <c r="L126" s="210" t="s">
+      <c r="L126" s="205" t="s">
         <v>122</v>
       </c>
-      <c r="M126" s="210"/>
+      <c r="M126" s="205"/>
       <c r="N126" s="55"/>
-      <c r="O126" s="210" t="s">
+      <c r="O126" s="205" t="s">
         <v>123</v>
       </c>
-      <c r="P126" s="210"/>
+      <c r="P126" s="205"/>
       <c r="Q126" s="55"/>
       <c r="R126" s="55"/>
     </row>
@@ -5777,54 +5948,54 @@
     <row r="132" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="74"/>
       <c r="C132" s="74"/>
-      <c r="D132" s="206" t="s">
+      <c r="D132" s="201" t="s">
         <v>124</v>
       </c>
-      <c r="E132" s="207"/>
-      <c r="F132" s="207"/>
+      <c r="E132" s="202"/>
+      <c r="F132" s="202"/>
       <c r="G132" s="94"/>
-      <c r="H132" s="255" t="s">
+      <c r="H132" s="250" t="s">
         <v>125</v>
       </c>
-      <c r="I132" s="207"/>
-      <c r="J132" s="207"/>
+      <c r="I132" s="202"/>
+      <c r="J132" s="202"/>
       <c r="K132" s="94"/>
-      <c r="L132" s="252" t="s">
+      <c r="L132" s="247" t="s">
         <v>126</v>
       </c>
-      <c r="M132" s="253"/>
+      <c r="M132" s="248"/>
       <c r="N132" s="94"/>
-      <c r="O132" s="252" t="s">
+      <c r="O132" s="247" t="s">
         <v>127</v>
       </c>
-      <c r="P132" s="253"/>
+      <c r="P132" s="248"/>
       <c r="Q132" s="55"/>
       <c r="R132" s="55"/>
     </row>
     <row r="133" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B133" s="74"/>
       <c r="C133" s="74"/>
-      <c r="D133" s="239" t="s">
+      <c r="D133" s="234" t="s">
         <v>130</v>
       </c>
-      <c r="E133" s="239"/>
-      <c r="F133" s="239"/>
+      <c r="E133" s="234"/>
+      <c r="F133" s="234"/>
       <c r="G133" s="90"/>
-      <c r="H133" s="239" t="s">
+      <c r="H133" s="234" t="s">
         <v>131</v>
       </c>
-      <c r="I133" s="119"/>
-      <c r="J133" s="119"/>
+      <c r="I133" s="118"/>
+      <c r="J133" s="118"/>
       <c r="K133" s="94"/>
-      <c r="L133" s="240" t="s">
+      <c r="L133" s="235" t="s">
         <v>128</v>
       </c>
-      <c r="M133" s="207"/>
+      <c r="M133" s="202"/>
       <c r="N133" s="94"/>
-      <c r="O133" s="239" t="s">
+      <c r="O133" s="234" t="s">
         <v>16</v>
       </c>
-      <c r="P133" s="239"/>
+      <c r="P133" s="234"/>
       <c r="Q133" s="55"/>
       <c r="R133" s="55"/>
     </row>
@@ -5871,7 +6042,14 @@
       <c r="R136" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="204">
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="K66:L66"/>
     <mergeCell ref="D108:D109"/>
     <mergeCell ref="E108:M109"/>
     <mergeCell ref="D110:D111"/>
@@ -5895,12 +6073,8 @@
     <mergeCell ref="O99:P99"/>
     <mergeCell ref="N52:O52"/>
     <mergeCell ref="D62:F62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="J62:L62"/>
     <mergeCell ref="M62:P62"/>
     <mergeCell ref="D63:F63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="J63:L63"/>
     <mergeCell ref="E86:M87"/>
     <mergeCell ref="D86:D87"/>
     <mergeCell ref="E88:M89"/>
@@ -5926,6 +6100,17 @@
     <mergeCell ref="O112:P112"/>
     <mergeCell ref="O93:P97"/>
     <mergeCell ref="E92:M93"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="L132:M132"/>
     <mergeCell ref="O126:P126"/>
@@ -5940,12 +6125,8 @@
     <mergeCell ref="N57:O57"/>
     <mergeCell ref="D60:P60"/>
     <mergeCell ref="D66:F66"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="J66:L66"/>
     <mergeCell ref="M66:P66"/>
     <mergeCell ref="M65:P65"/>
-    <mergeCell ref="J65:L65"/>
-    <mergeCell ref="G65:I65"/>
     <mergeCell ref="D65:F65"/>
     <mergeCell ref="E83:P83"/>
     <mergeCell ref="D123:P123"/>
@@ -6032,12 +6213,9 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="L14:O14"/>
     <mergeCell ref="D41:I41"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="J61:L61"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="N58:O58"/>
     <mergeCell ref="N49:O49"/>
-    <mergeCell ref="G64:I64"/>
     <mergeCell ref="D40:I40"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F14:J14"/>
@@ -6046,7 +6224,6 @@
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D18:J18"/>
     <mergeCell ref="F16:J16"/>
-    <mergeCell ref="J64:L64"/>
     <mergeCell ref="L4:N5"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="L21:O21"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C891623F-0A8A-413B-B882-92275ECF9323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D451670-02E8-40E6-AFFA-08CF2BF19978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,7 +793,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="73">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -1364,94 +1364,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1601,12 +1513,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="314">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -2007,11 +1934,266 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2024,269 +2206,147 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2297,6 +2357,17 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -2304,344 +2375,142 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3114,19 +2983,19 @@
       <c r="C3" s="48"/>
       <c r="D3" s="49"/>
       <c r="E3" s="48"/>
-      <c r="F3" s="198" t="s">
+      <c r="F3" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="191"/>
+      <c r="I3" s="191"/>
+      <c r="J3" s="191"/>
       <c r="K3" s="52"/>
-      <c r="L3" s="198" t="s">
+      <c r="L3" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
       <c r="O3" s="53"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="48"/>
@@ -3143,11 +3012,11 @@
       <c r="I4" s="51"/>
       <c r="J4" s="52"/>
       <c r="K4" s="52"/>
-      <c r="L4" s="117" t="s">
+      <c r="L4" s="276" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
+      <c r="M4" s="276"/>
+      <c r="N4" s="276"/>
       <c r="O4" s="53"/>
       <c r="P4" s="52"/>
       <c r="Q4" s="48"/>
@@ -3158,19 +3027,19 @@
       <c r="C5" s="48"/>
       <c r="D5" s="49"/>
       <c r="E5" s="48"/>
-      <c r="F5" s="166" t="s">
+      <c r="F5" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="167"/>
-      <c r="H5" s="168" t="s">
+      <c r="G5" s="281"/>
+      <c r="H5" s="253" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="169"/>
-      <c r="J5" s="169"/>
+      <c r="I5" s="254"/>
+      <c r="J5" s="254"/>
       <c r="K5" s="52"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
-      <c r="N5" s="117"/>
+      <c r="L5" s="276"/>
+      <c r="M5" s="276"/>
+      <c r="N5" s="276"/>
       <c r="O5" s="53"/>
       <c r="P5" s="52"/>
       <c r="Q5" s="48"/>
@@ -3182,23 +3051,23 @@
       <c r="C6" s="48"/>
       <c r="D6" s="49"/>
       <c r="E6" s="48"/>
-      <c r="F6" s="197" t="s">
+      <c r="F6" s="236" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="182"/>
-      <c r="H6" s="168" t="s">
+      <c r="G6" s="191"/>
+      <c r="H6" s="253" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="169"/>
-      <c r="J6" s="169"/>
+      <c r="I6" s="254"/>
+      <c r="J6" s="254"/>
       <c r="K6" s="52"/>
-      <c r="L6" s="181" t="s">
+      <c r="L6" s="286" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="187" t="s">
+      <c r="M6" s="287" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="188"/>
+      <c r="N6" s="288"/>
       <c r="O6" s="53"/>
       <c r="P6" s="52"/>
       <c r="Q6" s="48"/>
@@ -3215,9 +3084,9 @@
       <c r="I7" s="57"/>
       <c r="J7" s="58"/>
       <c r="K7" s="52"/>
-      <c r="L7" s="182"/>
-      <c r="M7" s="189"/>
-      <c r="N7" s="189"/>
+      <c r="L7" s="191"/>
+      <c r="M7" s="289"/>
+      <c r="N7" s="289"/>
       <c r="O7" s="53"/>
       <c r="P7" s="52"/>
       <c r="Q7" s="48"/>
@@ -3228,19 +3097,19 @@
       <c r="C8" s="48"/>
       <c r="D8" s="49"/>
       <c r="E8" s="48"/>
-      <c r="F8" s="213" t="s">
+      <c r="F8" s="250" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="182"/>
-      <c r="H8" s="214" t="s">
+      <c r="G8" s="191"/>
+      <c r="H8" s="251" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="215"/>
-      <c r="J8" s="215"/>
+      <c r="I8" s="252"/>
+      <c r="J8" s="252"/>
       <c r="K8" s="52"/>
-      <c r="L8" s="182"/>
-      <c r="M8" s="190"/>
-      <c r="N8" s="190"/>
+      <c r="L8" s="191"/>
+      <c r="M8" s="290"/>
+      <c r="N8" s="290"/>
       <c r="O8" s="52"/>
       <c r="P8" s="52"/>
       <c r="Q8" s="48"/>
@@ -3307,24 +3176,24 @@
     <row r="12" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="59"/>
       <c r="C12" s="59"/>
-      <c r="D12" s="174" t="s">
+      <c r="D12" s="284" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="175"/>
-      <c r="F12" s="172" t="s">
+      <c r="E12" s="285"/>
+      <c r="F12" s="282" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="173"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="173"/>
-      <c r="J12" s="173"/>
+      <c r="G12" s="283"/>
+      <c r="H12" s="283"/>
+      <c r="I12" s="283"/>
+      <c r="J12" s="283"/>
       <c r="K12" s="65"/>
-      <c r="L12" s="194" t="s">
+      <c r="L12" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="182"/>
-      <c r="N12" s="182"/>
-      <c r="O12" s="195"/>
+      <c r="M12" s="191"/>
+      <c r="N12" s="191"/>
+      <c r="O12" s="233"/>
       <c r="P12" s="98" t="s">
         <v>14</v>
       </c>
@@ -3334,24 +3203,24 @@
     <row r="13" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
-      <c r="D13" s="153" t="s">
+      <c r="D13" s="237" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="154"/>
-      <c r="F13" s="170" t="s">
+      <c r="E13" s="238"/>
+      <c r="F13" s="248" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="171"/>
-      <c r="H13" s="171"/>
-      <c r="I13" s="171"/>
-      <c r="J13" s="171"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="249"/>
+      <c r="J13" s="249"/>
       <c r="K13" s="66"/>
-      <c r="L13" s="127" t="s">
+      <c r="L13" s="278" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
+      <c r="M13" s="279"/>
+      <c r="N13" s="279"/>
+      <c r="O13" s="279"/>
       <c r="P13" s="6" t="s">
         <v>18</v>
       </c>
@@ -3361,24 +3230,24 @@
     <row r="14" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
-      <c r="D14" s="153" t="s">
+      <c r="D14" s="237" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="154"/>
-      <c r="F14" s="170" t="s">
+      <c r="E14" s="238"/>
+      <c r="F14" s="248" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="171"/>
-      <c r="H14" s="171"/>
-      <c r="I14" s="171"/>
-      <c r="J14" s="171"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
       <c r="K14" s="67"/>
-      <c r="L14" s="129" t="s">
+      <c r="L14" s="269" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
+      <c r="M14" s="270"/>
+      <c r="N14" s="270"/>
+      <c r="O14" s="270"/>
       <c r="P14" s="6" t="s">
         <v>22</v>
       </c>
@@ -3388,24 +3257,24 @@
     <row r="15" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
-      <c r="D15" s="153" t="s">
+      <c r="D15" s="237" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="154"/>
-      <c r="F15" s="170" t="s">
+      <c r="E15" s="238"/>
+      <c r="F15" s="248" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="171"/>
-      <c r="H15" s="171"/>
-      <c r="I15" s="171"/>
-      <c r="J15" s="171"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="249"/>
       <c r="K15" s="55"/>
-      <c r="L15" s="129" t="s">
+      <c r="L15" s="269" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
+      <c r="M15" s="270"/>
+      <c r="N15" s="270"/>
+      <c r="O15" s="270"/>
       <c r="P15" s="6" t="s">
         <v>26</v>
       </c>
@@ -3415,24 +3284,24 @@
     <row r="16" spans="2:21" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
-      <c r="D16" s="125" t="s">
+      <c r="D16" s="277" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="126"/>
-      <c r="F16" s="180" t="s">
+      <c r="E16" s="246"/>
+      <c r="F16" s="275" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="171"/>
-      <c r="H16" s="171"/>
-      <c r="I16" s="171"/>
-      <c r="J16" s="171"/>
+      <c r="G16" s="249"/>
+      <c r="H16" s="249"/>
+      <c r="I16" s="249"/>
+      <c r="J16" s="249"/>
       <c r="K16" s="65"/>
-      <c r="L16" s="129" t="s">
+      <c r="L16" s="269" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="130"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
+      <c r="M16" s="270"/>
+      <c r="N16" s="270"/>
+      <c r="O16" s="270"/>
       <c r="P16" s="6" t="s">
         <v>30</v>
       </c>
@@ -3446,8 +3315,8 @@
       <c r="E17" s="62"/>
       <c r="F17" s="63"/>
       <c r="G17" s="63"/>
-      <c r="H17" s="219"/>
-      <c r="I17" s="202"/>
+      <c r="H17" s="212"/>
+      <c r="I17" s="174"/>
       <c r="J17" s="64"/>
       <c r="K17" s="66"/>
       <c r="L17" s="55"/>
@@ -3460,23 +3329,23 @@
     <row r="18" spans="2:19" s="7" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="75"/>
       <c r="C18" s="75"/>
-      <c r="D18" s="179" t="s">
+      <c r="D18" s="274" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="123"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="123"/>
-      <c r="J18" s="124"/>
+      <c r="E18" s="205"/>
+      <c r="F18" s="205"/>
+      <c r="G18" s="205"/>
+      <c r="H18" s="205"/>
+      <c r="I18" s="205"/>
+      <c r="J18" s="206"/>
       <c r="K18" s="73"/>
-      <c r="L18" s="131" t="s">
+      <c r="L18" s="231" t="s">
         <v>32</v>
       </c>
-      <c r="M18" s="123"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="124"/>
+      <c r="M18" s="205"/>
+      <c r="N18" s="205"/>
+      <c r="O18" s="205"/>
+      <c r="P18" s="206"/>
       <c r="Q18" s="55"/>
       <c r="R18" s="55"/>
       <c r="S18" s="1"/>
@@ -3484,24 +3353,24 @@
     <row r="19" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="74"/>
       <c r="C19" s="74"/>
-      <c r="D19" s="119" t="s">
+      <c r="D19" s="192" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="120"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="203" t="s">
+      <c r="E19" s="193"/>
+      <c r="F19" s="193"/>
+      <c r="G19" s="193"/>
+      <c r="H19" s="194"/>
+      <c r="I19" s="200" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="120"/>
+      <c r="J19" s="193"/>
       <c r="K19" s="55"/>
-      <c r="L19" s="122" t="s">
+      <c r="L19" s="204" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="123"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="124"/>
+      <c r="M19" s="205"/>
+      <c r="N19" s="205"/>
+      <c r="O19" s="206"/>
       <c r="P19" s="84" t="s">
         <v>35</v>
       </c>
@@ -3511,24 +3380,24 @@
     <row r="20" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
-      <c r="D20" s="178" t="s">
+      <c r="D20" s="211" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="121"/>
-      <c r="I20" s="184" t="s">
+      <c r="E20" s="193"/>
+      <c r="F20" s="193"/>
+      <c r="G20" s="193"/>
+      <c r="H20" s="194"/>
+      <c r="I20" s="215" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="120"/>
+      <c r="J20" s="193"/>
       <c r="K20" s="55"/>
       <c r="L20" s="229" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="123"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="124"/>
+      <c r="M20" s="205"/>
+      <c r="N20" s="205"/>
+      <c r="O20" s="206"/>
       <c r="P20" s="85" t="s">
         <v>37</v>
       </c>
@@ -3538,24 +3407,24 @@
     <row r="21" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
-      <c r="D21" s="119" t="s">
+      <c r="D21" s="192" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="120"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="121"/>
-      <c r="I21" s="203" t="s">
+      <c r="E21" s="193"/>
+      <c r="F21" s="193"/>
+      <c r="G21" s="193"/>
+      <c r="H21" s="194"/>
+      <c r="I21" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="120"/>
+      <c r="J21" s="193"/>
       <c r="K21" s="55"/>
-      <c r="L21" s="122" t="s">
+      <c r="L21" s="204" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="123"/>
-      <c r="N21" s="123"/>
-      <c r="O21" s="124"/>
+      <c r="M21" s="205"/>
+      <c r="N21" s="205"/>
+      <c r="O21" s="206"/>
       <c r="P21" s="84" t="s">
         <v>37</v>
       </c>
@@ -3565,24 +3434,24 @@
     <row r="22" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
-      <c r="D22" s="178" t="s">
+      <c r="D22" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="120"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="121"/>
-      <c r="I22" s="184" t="s">
+      <c r="E22" s="193"/>
+      <c r="F22" s="193"/>
+      <c r="G22" s="193"/>
+      <c r="H22" s="194"/>
+      <c r="I22" s="215" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="120"/>
+      <c r="J22" s="193"/>
       <c r="K22" s="55"/>
-      <c r="L22" s="209" t="s">
+      <c r="L22" s="242" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="210"/>
-      <c r="N22" s="210"/>
-      <c r="O22" s="211"/>
+      <c r="M22" s="243"/>
+      <c r="N22" s="243"/>
+      <c r="O22" s="244"/>
       <c r="P22" s="86" t="s">
         <v>41</v>
       </c>
@@ -3592,17 +3461,17 @@
     <row r="23" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
-      <c r="D23" s="119" t="s">
+      <c r="D23" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="120"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="203" t="s">
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="193"/>
+      <c r="H23" s="194"/>
+      <c r="I23" s="200" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="120"/>
+      <c r="J23" s="193"/>
       <c r="K23" s="55"/>
       <c r="L23" s="82"/>
       <c r="M23" s="82"/>
@@ -3615,49 +3484,49 @@
     <row r="24" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
-      <c r="D24" s="178" t="s">
+      <c r="D24" s="211" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="120"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="120"/>
-      <c r="H24" s="121"/>
-      <c r="I24" s="184" t="s">
+      <c r="E24" s="193"/>
+      <c r="F24" s="193"/>
+      <c r="G24" s="193"/>
+      <c r="H24" s="194"/>
+      <c r="I24" s="215" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="120"/>
+      <c r="J24" s="193"/>
       <c r="K24" s="55"/>
-      <c r="L24" s="131" t="s">
+      <c r="L24" s="231" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="123"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="123"/>
-      <c r="P24" s="124"/>
+      <c r="M24" s="205"/>
+      <c r="N24" s="205"/>
+      <c r="O24" s="205"/>
+      <c r="P24" s="206"/>
       <c r="Q24" s="55"/>
       <c r="R24" s="55"/>
     </row>
     <row r="25" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="119" t="s">
+      <c r="D25" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="121"/>
-      <c r="I25" s="203" t="s">
+      <c r="E25" s="193"/>
+      <c r="F25" s="193"/>
+      <c r="G25" s="193"/>
+      <c r="H25" s="194"/>
+      <c r="I25" s="200" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="120"/>
+      <c r="J25" s="193"/>
       <c r="K25" s="55"/>
-      <c r="L25" s="122" t="s">
+      <c r="L25" s="204" t="s">
         <v>48</v>
       </c>
-      <c r="M25" s="123"/>
-      <c r="N25" s="123"/>
-      <c r="O25" s="124"/>
+      <c r="M25" s="205"/>
+      <c r="N25" s="205"/>
+      <c r="O25" s="206"/>
       <c r="P25" s="84" t="s">
         <v>49</v>
       </c>
@@ -3667,22 +3536,22 @@
     <row r="26" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
-      <c r="D26" s="244" t="s">
+      <c r="D26" s="210" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="123"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="123"/>
+      <c r="E26" s="205"/>
+      <c r="F26" s="205"/>
+      <c r="G26" s="205"/>
+      <c r="H26" s="205"/>
+      <c r="I26" s="205"/>
+      <c r="J26" s="205"/>
       <c r="K26" s="55"/>
       <c r="L26" s="229" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="123"/>
-      <c r="N26" s="123"/>
-      <c r="O26" s="124"/>
+      <c r="M26" s="205"/>
+      <c r="N26" s="205"/>
+      <c r="O26" s="206"/>
       <c r="P26" s="85" t="s">
         <v>52</v>
       </c>
@@ -3692,20 +3561,20 @@
     <row r="27" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
-      <c r="D27" s="223"/>
-      <c r="E27" s="224"/>
-      <c r="F27" s="224"/>
-      <c r="G27" s="224"/>
-      <c r="H27" s="224"/>
-      <c r="I27" s="224"/>
-      <c r="J27" s="224"/>
+      <c r="D27" s="222"/>
+      <c r="E27" s="223"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="223"/>
+      <c r="H27" s="223"/>
+      <c r="I27" s="223"/>
+      <c r="J27" s="223"/>
       <c r="K27" s="55"/>
-      <c r="L27" s="122" t="s">
+      <c r="L27" s="204" t="s">
         <v>53</v>
       </c>
-      <c r="M27" s="123"/>
-      <c r="N27" s="123"/>
-      <c r="O27" s="124"/>
+      <c r="M27" s="205"/>
+      <c r="N27" s="205"/>
+      <c r="O27" s="206"/>
       <c r="P27" s="84" t="s">
         <v>49</v>
       </c>
@@ -3734,49 +3603,49 @@
     <row r="29" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
-      <c r="D29" s="183" t="s">
+      <c r="D29" s="247" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="182"/>
-      <c r="F29" s="182"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="182"/>
-      <c r="I29" s="182"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="191"/>
+      <c r="G29" s="191"/>
+      <c r="H29" s="191"/>
+      <c r="I29" s="191"/>
       <c r="J29" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K29" s="55"/>
-      <c r="L29" s="212" t="s">
+      <c r="L29" s="245" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="126"/>
-      <c r="N29" s="126"/>
-      <c r="O29" s="126"/>
-      <c r="P29" s="126"/>
+      <c r="M29" s="246"/>
+      <c r="N29" s="246"/>
+      <c r="O29" s="246"/>
+      <c r="P29" s="246"/>
       <c r="Q29" s="55"/>
       <c r="R29" s="55"/>
     </row>
     <row r="30" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
-      <c r="D30" s="191" t="s">
+      <c r="D30" s="219" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="192"/>
-      <c r="F30" s="192"/>
-      <c r="G30" s="192"/>
-      <c r="H30" s="192"/>
-      <c r="I30" s="193"/>
+      <c r="E30" s="220"/>
+      <c r="F30" s="220"/>
+      <c r="G30" s="220"/>
+      <c r="H30" s="220"/>
+      <c r="I30" s="221"/>
       <c r="J30" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K30" s="55"/>
-      <c r="L30" s="199" t="s">
+      <c r="L30" s="224" t="s">
         <v>59</v>
       </c>
-      <c r="M30" s="120"/>
-      <c r="N30" s="120"/>
-      <c r="O30" s="200"/>
+      <c r="M30" s="193"/>
+      <c r="N30" s="193"/>
+      <c r="O30" s="196"/>
       <c r="P30" s="9" t="s">
         <v>60</v>
       </c>
@@ -3786,24 +3655,24 @@
     <row r="31" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
-      <c r="D31" s="155" t="s">
+      <c r="D31" s="187" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="156"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="157"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="188"/>
+      <c r="G31" s="188"/>
+      <c r="H31" s="188"/>
+      <c r="I31" s="189"/>
       <c r="J31" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K31" s="55"/>
-      <c r="L31" s="236" t="s">
+      <c r="L31" s="195" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="120"/>
-      <c r="N31" s="120"/>
-      <c r="O31" s="200"/>
+      <c r="M31" s="193"/>
+      <c r="N31" s="193"/>
+      <c r="O31" s="196"/>
       <c r="P31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3813,24 +3682,24 @@
     <row r="32" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
-      <c r="D32" s="165" t="s">
+      <c r="D32" s="213" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="156"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="156"/>
-      <c r="I32" s="157"/>
+      <c r="E32" s="188"/>
+      <c r="F32" s="188"/>
+      <c r="G32" s="188"/>
+      <c r="H32" s="188"/>
+      <c r="I32" s="189"/>
       <c r="J32" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K32" s="55"/>
-      <c r="L32" s="199" t="s">
+      <c r="L32" s="224" t="s">
         <v>65</v>
       </c>
-      <c r="M32" s="120"/>
-      <c r="N32" s="120"/>
-      <c r="O32" s="200"/>
+      <c r="M32" s="193"/>
+      <c r="N32" s="193"/>
+      <c r="O32" s="196"/>
       <c r="P32" s="9" t="s">
         <v>66</v>
       </c>
@@ -3840,24 +3709,24 @@
     <row r="33" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74"/>
       <c r="C33" s="74"/>
-      <c r="D33" s="155" t="s">
+      <c r="D33" s="187" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="156"/>
-      <c r="H33" s="156"/>
-      <c r="I33" s="157"/>
+      <c r="E33" s="188"/>
+      <c r="F33" s="188"/>
+      <c r="G33" s="188"/>
+      <c r="H33" s="188"/>
+      <c r="I33" s="189"/>
       <c r="J33" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K33" s="55"/>
-      <c r="L33" s="206" t="s">
+      <c r="L33" s="241" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="207"/>
-      <c r="N33" s="207"/>
-      <c r="O33" s="208"/>
+      <c r="M33" s="198"/>
+      <c r="N33" s="198"/>
+      <c r="O33" s="199"/>
       <c r="P33" s="11" t="s">
         <v>63</v>
       </c>
@@ -3867,14 +3736,14 @@
     <row r="34" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
-      <c r="D34" s="165" t="s">
+      <c r="D34" s="213" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="156"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="156"/>
-      <c r="H34" s="156"/>
-      <c r="I34" s="157"/>
+      <c r="E34" s="188"/>
+      <c r="F34" s="188"/>
+      <c r="G34" s="188"/>
+      <c r="H34" s="188"/>
+      <c r="I34" s="189"/>
       <c r="J34" s="14" t="s">
         <v>58</v>
       </c>
@@ -3890,7 +3759,7 @@
     <row r="35" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="222" t="s">
+      <c r="D35" s="216" t="s">
         <v>70</v>
       </c>
       <c r="E35" s="217"/>
@@ -3905,10 +3774,10 @@
       <c r="L35" s="228" t="s">
         <v>71</v>
       </c>
-      <c r="M35" s="182"/>
-      <c r="N35" s="182"/>
-      <c r="O35" s="182"/>
-      <c r="P35" s="182"/>
+      <c r="M35" s="191"/>
+      <c r="N35" s="191"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="191"/>
       <c r="Q35" s="55"/>
       <c r="R35" s="55"/>
     </row>
@@ -3923,12 +3792,12 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="55"/>
-      <c r="L36" s="241" t="s">
+      <c r="L36" s="207" t="s">
         <v>72</v>
       </c>
-      <c r="M36" s="242"/>
-      <c r="N36" s="242"/>
-      <c r="O36" s="243"/>
+      <c r="M36" s="208"/>
+      <c r="N36" s="208"/>
+      <c r="O36" s="209"/>
       <c r="P36" s="20" t="s">
         <v>73</v>
       </c>
@@ -3938,24 +3807,24 @@
     <row r="37" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="74"/>
       <c r="C37" s="74"/>
-      <c r="D37" s="183" t="s">
+      <c r="D37" s="247" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="182"/>
-      <c r="F37" s="182"/>
-      <c r="G37" s="182"/>
-      <c r="H37" s="182"/>
-      <c r="I37" s="182"/>
+      <c r="E37" s="191"/>
+      <c r="F37" s="191"/>
+      <c r="G37" s="191"/>
+      <c r="H37" s="191"/>
+      <c r="I37" s="191"/>
       <c r="J37" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="55"/>
-      <c r="L37" s="178" t="s">
+      <c r="L37" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="M37" s="120"/>
-      <c r="N37" s="120"/>
-      <c r="O37" s="121"/>
+      <c r="M37" s="193"/>
+      <c r="N37" s="193"/>
+      <c r="O37" s="194"/>
       <c r="P37" s="10" t="s">
         <v>73</v>
       </c>
@@ -3965,24 +3834,24 @@
     <row r="38" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
-      <c r="D38" s="191" t="s">
+      <c r="D38" s="219" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="192"/>
-      <c r="F38" s="192"/>
-      <c r="G38" s="192"/>
-      <c r="H38" s="192"/>
-      <c r="I38" s="193"/>
+      <c r="E38" s="220"/>
+      <c r="F38" s="220"/>
+      <c r="G38" s="220"/>
+      <c r="H38" s="220"/>
+      <c r="I38" s="221"/>
       <c r="J38" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="55"/>
-      <c r="L38" s="119" t="s">
+      <c r="L38" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="120"/>
-      <c r="N38" s="120"/>
-      <c r="O38" s="121"/>
+      <c r="M38" s="193"/>
+      <c r="N38" s="193"/>
+      <c r="O38" s="194"/>
       <c r="P38" s="9" t="s">
         <v>73</v>
       </c>
@@ -3992,24 +3861,24 @@
     <row r="39" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
-      <c r="D39" s="155" t="s">
+      <c r="D39" s="187" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="156"/>
-      <c r="F39" s="156"/>
-      <c r="G39" s="156"/>
-      <c r="H39" s="156"/>
-      <c r="I39" s="157"/>
+      <c r="E39" s="188"/>
+      <c r="F39" s="188"/>
+      <c r="G39" s="188"/>
+      <c r="H39" s="188"/>
+      <c r="I39" s="189"/>
       <c r="J39" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K39" s="55"/>
-      <c r="L39" s="178" t="s">
+      <c r="L39" s="211" t="s">
         <v>79</v>
       </c>
-      <c r="M39" s="120"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="121"/>
+      <c r="M39" s="193"/>
+      <c r="N39" s="193"/>
+      <c r="O39" s="194"/>
       <c r="P39" s="10" t="s">
         <v>73</v>
       </c>
@@ -4019,24 +3888,24 @@
     <row r="40" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
-      <c r="D40" s="165" t="s">
+      <c r="D40" s="213" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="156"/>
-      <c r="F40" s="156"/>
-      <c r="G40" s="156"/>
-      <c r="H40" s="156"/>
-      <c r="I40" s="157"/>
+      <c r="E40" s="188"/>
+      <c r="F40" s="188"/>
+      <c r="G40" s="188"/>
+      <c r="H40" s="188"/>
+      <c r="I40" s="189"/>
       <c r="J40" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K40" s="55"/>
-      <c r="L40" s="237" t="s">
+      <c r="L40" s="197" t="s">
         <v>81</v>
       </c>
-      <c r="M40" s="207"/>
-      <c r="N40" s="207"/>
-      <c r="O40" s="208"/>
+      <c r="M40" s="198"/>
+      <c r="N40" s="198"/>
+      <c r="O40" s="199"/>
       <c r="P40" s="21" t="s">
         <v>73</v>
       </c>
@@ -4046,14 +3915,14 @@
     <row r="41" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
-      <c r="D41" s="155" t="s">
+      <c r="D41" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="156"/>
-      <c r="F41" s="156"/>
-      <c r="G41" s="156"/>
-      <c r="H41" s="156"/>
-      <c r="I41" s="157"/>
+      <c r="E41" s="188"/>
+      <c r="F41" s="188"/>
+      <c r="G41" s="188"/>
+      <c r="H41" s="188"/>
+      <c r="I41" s="189"/>
       <c r="J41" s="13" t="s">
         <v>58</v>
       </c>
@@ -4069,14 +3938,14 @@
     <row r="42" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
-      <c r="D42" s="165" t="s">
+      <c r="D42" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="156"/>
-      <c r="F42" s="156"/>
-      <c r="G42" s="156"/>
-      <c r="H42" s="156"/>
-      <c r="I42" s="157"/>
+      <c r="E42" s="188"/>
+      <c r="F42" s="188"/>
+      <c r="G42" s="188"/>
+      <c r="H42" s="188"/>
+      <c r="I42" s="189"/>
       <c r="J42" s="14" t="s">
         <v>58</v>
       </c>
@@ -4092,14 +3961,14 @@
     <row r="43" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
-      <c r="D43" s="155" t="s">
+      <c r="D43" s="187" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="156"/>
-      <c r="F43" s="156"/>
-      <c r="G43" s="156"/>
-      <c r="H43" s="156"/>
-      <c r="I43" s="157"/>
+      <c r="E43" s="188"/>
+      <c r="F43" s="188"/>
+      <c r="G43" s="188"/>
+      <c r="H43" s="188"/>
+      <c r="I43" s="189"/>
       <c r="J43" s="13" t="s">
         <v>58</v>
       </c>
@@ -4115,14 +3984,14 @@
     <row r="44" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
-      <c r="D44" s="191" t="s">
+      <c r="D44" s="219" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="192"/>
-      <c r="F44" s="192"/>
-      <c r="G44" s="192"/>
-      <c r="H44" s="192"/>
-      <c r="I44" s="193"/>
+      <c r="E44" s="220"/>
+      <c r="F44" s="220"/>
+      <c r="G44" s="220"/>
+      <c r="H44" s="220"/>
+      <c r="I44" s="221"/>
       <c r="J44" s="12" t="s">
         <v>58</v>
       </c>
@@ -4138,14 +4007,14 @@
     <row r="45" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
-      <c r="D45" s="155" t="s">
+      <c r="D45" s="187" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="156"/>
-      <c r="F45" s="156"/>
-      <c r="G45" s="156"/>
-      <c r="H45" s="156"/>
-      <c r="I45" s="157"/>
+      <c r="E45" s="188"/>
+      <c r="F45" s="188"/>
+      <c r="G45" s="188"/>
+      <c r="H45" s="188"/>
+      <c r="I45" s="189"/>
       <c r="J45" s="13" t="s">
         <v>58</v>
       </c>
@@ -4161,7 +4030,7 @@
     <row r="46" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
-      <c r="D46" s="216" t="s">
+      <c r="D46" s="255" t="s">
         <v>87</v>
       </c>
       <c r="E46" s="217"/>
@@ -4173,13 +4042,13 @@
         <v>58</v>
       </c>
       <c r="K46" s="55"/>
-      <c r="L46" s="235" t="s">
+      <c r="L46" s="190" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="182"/>
-      <c r="N46" s="182"/>
-      <c r="O46" s="182"/>
-      <c r="P46" s="182"/>
+      <c r="M46" s="191"/>
+      <c r="N46" s="191"/>
+      <c r="O46" s="191"/>
+      <c r="P46" s="191"/>
       <c r="Q46" s="55"/>
       <c r="R46" s="55"/>
     </row>
@@ -4232,14 +4101,14 @@
       <c r="D49" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="162" t="s">
+      <c r="E49" s="136" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="163"/>
-      <c r="G49" s="163"/>
-      <c r="H49" s="163"/>
-      <c r="I49" s="163"/>
-      <c r="J49" s="163"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="137"/>
+      <c r="J49" s="137"/>
       <c r="K49" s="91" t="s">
         <v>93</v>
       </c>
@@ -4249,10 +4118,10 @@
       <c r="M49" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="N49" s="162" t="s">
+      <c r="N49" s="136" t="s">
         <v>96</v>
       </c>
-      <c r="O49" s="163"/>
+      <c r="O49" s="137"/>
       <c r="P49" s="91" t="s">
         <v>97</v>
       </c>
@@ -4264,101 +4133,101 @@
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
       <c r="D50" s="25"/>
-      <c r="E50" s="185"/>
-      <c r="F50" s="118"/>
-      <c r="G50" s="118"/>
-      <c r="H50" s="118"/>
-      <c r="I50" s="118"/>
-      <c r="J50" s="186"/>
+      <c r="E50" s="234"/>
+      <c r="F50" s="147"/>
+      <c r="G50" s="147"/>
+      <c r="H50" s="147"/>
+      <c r="I50" s="147"/>
+      <c r="J50" s="139"/>
       <c r="K50" s="26"/>
       <c r="L50" s="27"/>
       <c r="M50" s="28"/>
-      <c r="N50" s="238"/>
-      <c r="O50" s="186"/>
+      <c r="N50" s="138"/>
+      <c r="O50" s="139"/>
       <c r="P50" s="29"/>
     </row>
     <row r="51" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8"/>
       <c r="C51" s="23"/>
       <c r="D51" s="30"/>
-      <c r="E51" s="204"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="118"/>
-      <c r="H51" s="118"/>
-      <c r="I51" s="118"/>
-      <c r="J51" s="186"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="147"/>
+      <c r="G51" s="147"/>
+      <c r="H51" s="147"/>
+      <c r="I51" s="147"/>
+      <c r="J51" s="139"/>
       <c r="K51" s="31"/>
       <c r="L51" s="32"/>
       <c r="M51" s="33"/>
-      <c r="N51" s="231"/>
-      <c r="O51" s="186"/>
+      <c r="N51" s="170"/>
+      <c r="O51" s="139"/>
       <c r="P51" s="34"/>
     </row>
     <row r="52" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
       <c r="D52" s="25"/>
-      <c r="E52" s="185"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
-      <c r="H52" s="118"/>
-      <c r="I52" s="118"/>
-      <c r="J52" s="186"/>
+      <c r="E52" s="234"/>
+      <c r="F52" s="147"/>
+      <c r="G52" s="147"/>
+      <c r="H52" s="147"/>
+      <c r="I52" s="147"/>
+      <c r="J52" s="139"/>
       <c r="K52" s="26"/>
       <c r="L52" s="27"/>
       <c r="M52" s="28"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="186"/>
+      <c r="N52" s="138"/>
+      <c r="O52" s="139"/>
       <c r="P52" s="29"/>
     </row>
     <row r="53" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
       <c r="D53" s="30"/>
-      <c r="E53" s="204"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
-      <c r="I53" s="118"/>
-      <c r="J53" s="186"/>
+      <c r="E53" s="146"/>
+      <c r="F53" s="147"/>
+      <c r="G53" s="147"/>
+      <c r="H53" s="147"/>
+      <c r="I53" s="147"/>
+      <c r="J53" s="139"/>
       <c r="K53" s="31"/>
       <c r="L53" s="32"/>
       <c r="M53" s="33"/>
-      <c r="N53" s="231"/>
-      <c r="O53" s="186"/>
+      <c r="N53" s="170"/>
+      <c r="O53" s="139"/>
       <c r="P53" s="34"/>
     </row>
     <row r="54" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="D54" s="25"/>
-      <c r="E54" s="185"/>
-      <c r="F54" s="118"/>
-      <c r="G54" s="118"/>
-      <c r="H54" s="118"/>
-      <c r="I54" s="118"/>
-      <c r="J54" s="186"/>
+      <c r="E54" s="234"/>
+      <c r="F54" s="147"/>
+      <c r="G54" s="147"/>
+      <c r="H54" s="147"/>
+      <c r="I54" s="147"/>
+      <c r="J54" s="139"/>
       <c r="K54" s="26"/>
       <c r="L54" s="27"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="186"/>
+      <c r="N54" s="138"/>
+      <c r="O54" s="139"/>
       <c r="P54" s="29"/>
     </row>
     <row r="55" spans="2:23" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8"/>
       <c r="C55" s="23"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="204"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="118"/>
-      <c r="H55" s="118"/>
-      <c r="I55" s="118"/>
-      <c r="J55" s="186"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="147"/>
+      <c r="G55" s="147"/>
+      <c r="H55" s="147"/>
+      <c r="I55" s="147"/>
+      <c r="J55" s="139"/>
       <c r="K55" s="31"/>
       <c r="L55" s="32"/>
       <c r="M55" s="33"/>
-      <c r="N55" s="231"/>
-      <c r="O55" s="186"/>
+      <c r="N55" s="170"/>
+      <c r="O55" s="139"/>
       <c r="P55" s="34"/>
     </row>
     <row r="56" spans="2:23" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4376,11 +4245,11 @@
       <c r="M56" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="N56" s="280">
+      <c r="N56" s="144">
         <f>SUM(N50:N55)</f>
         <v>0</v>
       </c>
-      <c r="O56" s="281"/>
+      <c r="O56" s="145"/>
       <c r="P56" s="3"/>
     </row>
     <row r="57" spans="2:23" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4398,11 +4267,11 @@
       <c r="M57" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="N57" s="254">
+      <c r="N57" s="178">
         <f>+N56*0.12</f>
         <v>0</v>
       </c>
-      <c r="O57" s="255"/>
+      <c r="O57" s="179"/>
       <c r="P57" s="3"/>
     </row>
     <row r="58" spans="2:23" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -4420,11 +4289,11 @@
       <c r="M58" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="N58" s="161">
+      <c r="N58" s="272">
         <f>+N57+N56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="118"/>
+      <c r="O58" s="147"/>
       <c r="P58" s="3"/>
     </row>
     <row r="59" spans="2:23" s="3" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4449,21 +4318,21 @@
     <row r="60" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
-      <c r="D60" s="256" t="s">
+      <c r="D60" s="180" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="256"/>
-      <c r="F60" s="256"/>
-      <c r="G60" s="256"/>
-      <c r="H60" s="256"/>
-      <c r="I60" s="256"/>
-      <c r="J60" s="256"/>
-      <c r="K60" s="256"/>
-      <c r="L60" s="256"/>
-      <c r="M60" s="256"/>
-      <c r="N60" s="256"/>
-      <c r="O60" s="256"/>
-      <c r="P60" s="256"/>
+      <c r="E60" s="180"/>
+      <c r="F60" s="180"/>
+      <c r="G60" s="180"/>
+      <c r="H60" s="180"/>
+      <c r="I60" s="180"/>
+      <c r="J60" s="180"/>
+      <c r="K60" s="180"/>
+      <c r="L60" s="180"/>
+      <c r="M60" s="180"/>
+      <c r="N60" s="180"/>
+      <c r="O60" s="180"/>
+      <c r="P60" s="180"/>
       <c r="Q60" s="56"/>
       <c r="R60" s="56"/>
     </row>
@@ -4475,24 +4344,24 @@
       </c>
       <c r="E61" s="230"/>
       <c r="F61" s="230"/>
-      <c r="G61" s="294" t="s">
+      <c r="G61" s="153" t="s">
         <v>103</v>
       </c>
-      <c r="H61" s="295"/>
-      <c r="I61" s="305" t="s">
+      <c r="H61" s="154"/>
+      <c r="I61" s="161" t="s">
         <v>105</v>
       </c>
-      <c r="J61" s="305"/>
-      <c r="K61" s="158" t="s">
+      <c r="J61" s="161"/>
+      <c r="K61" s="119" t="s">
         <v>132</v>
       </c>
-      <c r="L61" s="160"/>
-      <c r="M61" s="158" t="s">
+      <c r="L61" s="120"/>
+      <c r="M61" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="N61" s="159"/>
-      <c r="O61" s="159"/>
-      <c r="P61" s="160"/>
+      <c r="N61" s="271"/>
+      <c r="O61" s="271"/>
+      <c r="P61" s="120"/>
       <c r="Q61" s="56"/>
       <c r="R61" s="56"/>
       <c r="U61" s="35"/>
@@ -4502,21 +4371,21 @@
     <row r="62" spans="2:23" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
-      <c r="D62" s="275" t="s">
+      <c r="D62" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="275"/>
-      <c r="F62" s="275"/>
-      <c r="G62" s="296"/>
-      <c r="H62" s="297"/>
-      <c r="I62" s="312"/>
-      <c r="J62" s="313"/>
-      <c r="K62" s="306"/>
-      <c r="L62" s="307"/>
-      <c r="M62" s="304"/>
-      <c r="N62" s="276"/>
-      <c r="O62" s="276"/>
-      <c r="P62" s="276"/>
+      <c r="E62" s="140"/>
+      <c r="F62" s="140"/>
+      <c r="G62" s="155"/>
+      <c r="H62" s="156"/>
+      <c r="I62" s="162"/>
+      <c r="J62" s="163"/>
+      <c r="K62" s="121"/>
+      <c r="L62" s="122"/>
+      <c r="M62" s="141"/>
+      <c r="N62" s="142"/>
+      <c r="O62" s="142"/>
+      <c r="P62" s="142"/>
       <c r="Q62" s="56"/>
       <c r="R62" s="56"/>
       <c r="S62"/>
@@ -4528,19 +4397,19 @@
     <row r="63" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
-      <c r="D63" s="277"/>
-      <c r="E63" s="277"/>
-      <c r="F63" s="277"/>
-      <c r="G63" s="257"/>
-      <c r="H63" s="258"/>
-      <c r="I63" s="298"/>
-      <c r="J63" s="299"/>
-      <c r="K63" s="308"/>
-      <c r="L63" s="309"/>
-      <c r="M63" s="259"/>
-      <c r="N63" s="245"/>
-      <c r="O63" s="245"/>
-      <c r="P63" s="245"/>
+      <c r="D63" s="143"/>
+      <c r="E63" s="143"/>
+      <c r="F63" s="143"/>
+      <c r="G63" s="157"/>
+      <c r="H63" s="158"/>
+      <c r="I63" s="127"/>
+      <c r="J63" s="128"/>
+      <c r="K63" s="123"/>
+      <c r="L63" s="124"/>
+      <c r="M63" s="181"/>
+      <c r="N63" s="149"/>
+      <c r="O63" s="149"/>
+      <c r="P63" s="149"/>
       <c r="Q63" s="103"/>
       <c r="R63" s="103"/>
       <c r="S63"/>
@@ -4552,19 +4421,19 @@
     <row r="64" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
-      <c r="D64" s="246"/>
-      <c r="E64" s="246"/>
-      <c r="F64" s="246"/>
-      <c r="G64" s="291"/>
-      <c r="H64" s="292"/>
-      <c r="I64" s="300"/>
-      <c r="J64" s="301"/>
-      <c r="K64" s="310"/>
-      <c r="L64" s="311"/>
-      <c r="M64" s="293"/>
-      <c r="N64" s="164"/>
-      <c r="O64" s="164"/>
-      <c r="P64" s="164"/>
+      <c r="D64" s="166"/>
+      <c r="E64" s="166"/>
+      <c r="F64" s="166"/>
+      <c r="G64" s="159"/>
+      <c r="H64" s="160"/>
+      <c r="I64" s="164"/>
+      <c r="J64" s="165"/>
+      <c r="K64" s="125"/>
+      <c r="L64" s="126"/>
+      <c r="M64" s="151"/>
+      <c r="N64" s="148"/>
+      <c r="O64" s="148"/>
+      <c r="P64" s="148"/>
       <c r="Q64" s="56"/>
       <c r="R64" s="56"/>
       <c r="S64"/>
@@ -4576,19 +4445,19 @@
     <row r="65" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="74"/>
       <c r="C65" s="74"/>
-      <c r="D65" s="257"/>
-      <c r="E65" s="258"/>
-      <c r="F65" s="259"/>
-      <c r="G65" s="257"/>
-      <c r="H65" s="258"/>
-      <c r="I65" s="298"/>
-      <c r="J65" s="299"/>
-      <c r="K65" s="298"/>
-      <c r="L65" s="299"/>
-      <c r="M65" s="258"/>
-      <c r="N65" s="258"/>
-      <c r="O65" s="258"/>
-      <c r="P65" s="259"/>
+      <c r="D65" s="157"/>
+      <c r="E65" s="158"/>
+      <c r="F65" s="181"/>
+      <c r="G65" s="157"/>
+      <c r="H65" s="158"/>
+      <c r="I65" s="127"/>
+      <c r="J65" s="128"/>
+      <c r="K65" s="127"/>
+      <c r="L65" s="128"/>
+      <c r="M65" s="158"/>
+      <c r="N65" s="158"/>
+      <c r="O65" s="158"/>
+      <c r="P65" s="181"/>
       <c r="Q65" s="56"/>
       <c r="R65" s="56"/>
       <c r="S65"/>
@@ -4597,19 +4466,19 @@
     <row r="66" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="74"/>
       <c r="C66" s="74"/>
-      <c r="D66" s="164"/>
-      <c r="E66" s="164"/>
-      <c r="F66" s="164"/>
-      <c r="G66" s="291"/>
-      <c r="H66" s="292"/>
-      <c r="I66" s="302"/>
-      <c r="J66" s="303"/>
-      <c r="K66" s="302"/>
-      <c r="L66" s="303"/>
-      <c r="M66" s="293"/>
-      <c r="N66" s="164"/>
-      <c r="O66" s="164"/>
-      <c r="P66" s="164"/>
+      <c r="D66" s="148"/>
+      <c r="E66" s="148"/>
+      <c r="F66" s="148"/>
+      <c r="G66" s="159"/>
+      <c r="H66" s="160"/>
+      <c r="I66" s="117"/>
+      <c r="J66" s="118"/>
+      <c r="K66" s="117"/>
+      <c r="L66" s="118"/>
+      <c r="M66" s="151"/>
+      <c r="N66" s="148"/>
+      <c r="O66" s="148"/>
+      <c r="P66" s="148"/>
       <c r="Q66" s="56"/>
       <c r="R66" s="56"/>
     </row>
@@ -4638,20 +4507,20 @@
       <c r="D68" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="E68" s="140" t="s">
+      <c r="E68" s="256" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="141"/>
-      <c r="G68" s="141"/>
-      <c r="H68" s="141"/>
-      <c r="I68" s="141"/>
-      <c r="J68" s="141"/>
-      <c r="K68" s="141"/>
-      <c r="L68" s="141"/>
-      <c r="M68" s="141"/>
-      <c r="N68" s="141"/>
-      <c r="O68" s="141"/>
-      <c r="P68" s="142"/>
+      <c r="F68" s="257"/>
+      <c r="G68" s="257"/>
+      <c r="H68" s="257"/>
+      <c r="I68" s="257"/>
+      <c r="J68" s="257"/>
+      <c r="K68" s="257"/>
+      <c r="L68" s="257"/>
+      <c r="M68" s="257"/>
+      <c r="N68" s="257"/>
+      <c r="O68" s="257"/>
+      <c r="P68" s="258"/>
       <c r="Q68" s="55"/>
       <c r="R68" s="55"/>
     </row>
@@ -4661,20 +4530,20 @@
       <c r="D69" s="110">
         <v>1</v>
       </c>
-      <c r="E69" s="143" t="s">
+      <c r="E69" s="259" t="s">
         <v>108</v>
       </c>
-      <c r="F69" s="144"/>
-      <c r="G69" s="144"/>
-      <c r="H69" s="144"/>
-      <c r="I69" s="144"/>
-      <c r="J69" s="144"/>
-      <c r="K69" s="144"/>
-      <c r="L69" s="144"/>
-      <c r="M69" s="144"/>
-      <c r="N69" s="144"/>
-      <c r="O69" s="144"/>
-      <c r="P69" s="145"/>
+      <c r="F69" s="260"/>
+      <c r="G69" s="260"/>
+      <c r="H69" s="260"/>
+      <c r="I69" s="260"/>
+      <c r="J69" s="260"/>
+      <c r="K69" s="260"/>
+      <c r="L69" s="260"/>
+      <c r="M69" s="260"/>
+      <c r="N69" s="260"/>
+      <c r="O69" s="260"/>
+      <c r="P69" s="261"/>
       <c r="Q69" s="99"/>
       <c r="R69" s="99"/>
     </row>
@@ -4684,18 +4553,18 @@
       <c r="D70" s="112">
         <v>2</v>
       </c>
-      <c r="E70" s="232"/>
-      <c r="F70" s="233"/>
-      <c r="G70" s="233"/>
-      <c r="H70" s="233"/>
-      <c r="I70" s="233"/>
-      <c r="J70" s="233"/>
-      <c r="K70" s="233"/>
-      <c r="L70" s="233"/>
-      <c r="M70" s="233"/>
-      <c r="N70" s="233"/>
-      <c r="O70" s="233"/>
-      <c r="P70" s="233"/>
+      <c r="E70" s="184"/>
+      <c r="F70" s="185"/>
+      <c r="G70" s="185"/>
+      <c r="H70" s="185"/>
+      <c r="I70" s="185"/>
+      <c r="J70" s="185"/>
+      <c r="K70" s="185"/>
+      <c r="L70" s="185"/>
+      <c r="M70" s="185"/>
+      <c r="N70" s="185"/>
+      <c r="O70" s="185"/>
+      <c r="P70" s="185"/>
       <c r="Q70" s="55"/>
       <c r="R70" s="55"/>
     </row>
@@ -4705,18 +4574,18 @@
       <c r="D71" s="110">
         <v>3</v>
       </c>
-      <c r="E71" s="196"/>
-      <c r="F71" s="177"/>
-      <c r="G71" s="177"/>
-      <c r="H71" s="177"/>
-      <c r="I71" s="177"/>
-      <c r="J71" s="177"/>
-      <c r="K71" s="177"/>
-      <c r="L71" s="177"/>
-      <c r="M71" s="177"/>
-      <c r="N71" s="177"/>
-      <c r="O71" s="177"/>
-      <c r="P71" s="177"/>
+      <c r="E71" s="235"/>
+      <c r="F71" s="172"/>
+      <c r="G71" s="172"/>
+      <c r="H71" s="172"/>
+      <c r="I71" s="172"/>
+      <c r="J71" s="172"/>
+      <c r="K71" s="172"/>
+      <c r="L71" s="172"/>
+      <c r="M71" s="172"/>
+      <c r="N71" s="172"/>
+      <c r="O71" s="172"/>
+      <c r="P71" s="172"/>
     </row>
     <row r="72" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="8"/>
@@ -4724,18 +4593,18 @@
       <c r="D72" s="112">
         <v>4</v>
       </c>
-      <c r="E72" s="220"/>
-      <c r="F72" s="221"/>
-      <c r="G72" s="221"/>
-      <c r="H72" s="221"/>
-      <c r="I72" s="221"/>
-      <c r="J72" s="221"/>
-      <c r="K72" s="221"/>
-      <c r="L72" s="221"/>
-      <c r="M72" s="221"/>
-      <c r="N72" s="221"/>
-      <c r="O72" s="221"/>
-      <c r="P72" s="221"/>
+      <c r="E72" s="214"/>
+      <c r="F72" s="203"/>
+      <c r="G72" s="203"/>
+      <c r="H72" s="203"/>
+      <c r="I72" s="203"/>
+      <c r="J72" s="203"/>
+      <c r="K72" s="203"/>
+      <c r="L72" s="203"/>
+      <c r="M72" s="203"/>
+      <c r="N72" s="203"/>
+      <c r="O72" s="203"/>
+      <c r="P72" s="203"/>
     </row>
     <row r="73" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="8"/>
@@ -4743,18 +4612,18 @@
       <c r="D73" s="110">
         <v>5</v>
       </c>
-      <c r="E73" s="176"/>
-      <c r="F73" s="177"/>
-      <c r="G73" s="177"/>
-      <c r="H73" s="177"/>
-      <c r="I73" s="177"/>
-      <c r="J73" s="177"/>
-      <c r="K73" s="177"/>
-      <c r="L73" s="177"/>
-      <c r="M73" s="177"/>
-      <c r="N73" s="177"/>
-      <c r="O73" s="177"/>
-      <c r="P73" s="177"/>
+      <c r="E73" s="273"/>
+      <c r="F73" s="172"/>
+      <c r="G73" s="172"/>
+      <c r="H73" s="172"/>
+      <c r="I73" s="172"/>
+      <c r="J73" s="172"/>
+      <c r="K73" s="172"/>
+      <c r="L73" s="172"/>
+      <c r="M73" s="172"/>
+      <c r="N73" s="172"/>
+      <c r="O73" s="172"/>
+      <c r="P73" s="172"/>
     </row>
     <row r="74" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="8"/>
@@ -4779,20 +4648,20 @@
       <c r="D75" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E75" s="252" t="s">
+      <c r="E75" s="176" t="s">
         <v>109</v>
       </c>
-      <c r="F75" s="253"/>
-      <c r="G75" s="253"/>
-      <c r="H75" s="253"/>
-      <c r="I75" s="253"/>
-      <c r="J75" s="253"/>
-      <c r="K75" s="253"/>
-      <c r="L75" s="253"/>
-      <c r="M75" s="253"/>
-      <c r="N75" s="253"/>
-      <c r="O75" s="253"/>
-      <c r="P75" s="253"/>
+      <c r="F75" s="177"/>
+      <c r="G75" s="177"/>
+      <c r="H75" s="177"/>
+      <c r="I75" s="177"/>
+      <c r="J75" s="177"/>
+      <c r="K75" s="177"/>
+      <c r="L75" s="177"/>
+      <c r="M75" s="177"/>
+      <c r="N75" s="177"/>
+      <c r="O75" s="177"/>
+      <c r="P75" s="177"/>
       <c r="Q75" s="55"/>
       <c r="R75" s="55"/>
     </row>
@@ -4802,20 +4671,20 @@
       <c r="D76" s="110">
         <v>1</v>
       </c>
-      <c r="E76" s="146" t="s">
+      <c r="E76" s="262" t="s">
         <v>110</v>
       </c>
-      <c r="F76" s="146"/>
-      <c r="G76" s="146"/>
-      <c r="H76" s="146"/>
-      <c r="I76" s="146"/>
-      <c r="J76" s="146"/>
-      <c r="K76" s="146"/>
-      <c r="L76" s="146"/>
-      <c r="M76" s="146"/>
-      <c r="N76" s="146"/>
-      <c r="O76" s="146"/>
-      <c r="P76" s="146"/>
+      <c r="F76" s="262"/>
+      <c r="G76" s="262"/>
+      <c r="H76" s="262"/>
+      <c r="I76" s="262"/>
+      <c r="J76" s="262"/>
+      <c r="K76" s="262"/>
+      <c r="L76" s="262"/>
+      <c r="M76" s="262"/>
+      <c r="N76" s="262"/>
+      <c r="O76" s="262"/>
+      <c r="P76" s="262"/>
       <c r="Q76" s="55"/>
       <c r="R76" s="55"/>
     </row>
@@ -4825,18 +4694,18 @@
       <c r="D77" s="112">
         <v>2</v>
       </c>
-      <c r="E77" s="147"/>
-      <c r="F77" s="148"/>
-      <c r="G77" s="148"/>
-      <c r="H77" s="148"/>
-      <c r="I77" s="148"/>
-      <c r="J77" s="148"/>
-      <c r="K77" s="148"/>
-      <c r="L77" s="148"/>
-      <c r="M77" s="148"/>
-      <c r="N77" s="148"/>
-      <c r="O77" s="148"/>
-      <c r="P77" s="149"/>
+      <c r="E77" s="263"/>
+      <c r="F77" s="264"/>
+      <c r="G77" s="264"/>
+      <c r="H77" s="264"/>
+      <c r="I77" s="264"/>
+      <c r="J77" s="264"/>
+      <c r="K77" s="264"/>
+      <c r="L77" s="264"/>
+      <c r="M77" s="264"/>
+      <c r="N77" s="264"/>
+      <c r="O77" s="264"/>
+      <c r="P77" s="265"/>
       <c r="Q77" s="55"/>
       <c r="R77" s="55"/>
     </row>
@@ -4846,18 +4715,18 @@
       <c r="D78" s="110">
         <v>3</v>
       </c>
-      <c r="E78" s="150"/>
-      <c r="F78" s="151"/>
-      <c r="G78" s="151"/>
-      <c r="H78" s="151"/>
-      <c r="I78" s="151"/>
-      <c r="J78" s="151"/>
-      <c r="K78" s="151"/>
-      <c r="L78" s="151"/>
-      <c r="M78" s="151"/>
-      <c r="N78" s="151"/>
-      <c r="O78" s="151"/>
-      <c r="P78" s="152"/>
+      <c r="E78" s="266"/>
+      <c r="F78" s="267"/>
+      <c r="G78" s="267"/>
+      <c r="H78" s="267"/>
+      <c r="I78" s="267"/>
+      <c r="J78" s="267"/>
+      <c r="K78" s="267"/>
+      <c r="L78" s="267"/>
+      <c r="M78" s="267"/>
+      <c r="N78" s="267"/>
+      <c r="O78" s="267"/>
+      <c r="P78" s="268"/>
       <c r="Q78" s="55"/>
       <c r="R78" s="55"/>
     </row>
@@ -4867,18 +4736,18 @@
       <c r="D79" s="112">
         <v>4</v>
       </c>
-      <c r="E79" s="240"/>
-      <c r="F79" s="221"/>
-      <c r="G79" s="221"/>
-      <c r="H79" s="221"/>
-      <c r="I79" s="221"/>
-      <c r="J79" s="221"/>
-      <c r="K79" s="221"/>
-      <c r="L79" s="221"/>
-      <c r="M79" s="221"/>
-      <c r="N79" s="221"/>
-      <c r="O79" s="221"/>
-      <c r="P79" s="221"/>
+      <c r="E79" s="202"/>
+      <c r="F79" s="203"/>
+      <c r="G79" s="203"/>
+      <c r="H79" s="203"/>
+      <c r="I79" s="203"/>
+      <c r="J79" s="203"/>
+      <c r="K79" s="203"/>
+      <c r="L79" s="203"/>
+      <c r="M79" s="203"/>
+      <c r="N79" s="203"/>
+      <c r="O79" s="203"/>
+      <c r="P79" s="203"/>
     </row>
     <row r="80" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="8"/>
@@ -4886,35 +4755,35 @@
       <c r="D80" s="110">
         <v>5</v>
       </c>
-      <c r="E80" s="249"/>
-      <c r="F80" s="177"/>
-      <c r="G80" s="177"/>
-      <c r="H80" s="177"/>
-      <c r="I80" s="177"/>
-      <c r="J80" s="177"/>
-      <c r="K80" s="177"/>
-      <c r="L80" s="177"/>
-      <c r="M80" s="177"/>
-      <c r="N80" s="177"/>
-      <c r="O80" s="177"/>
-      <c r="P80" s="177"/>
+      <c r="E80" s="171"/>
+      <c r="F80" s="172"/>
+      <c r="G80" s="172"/>
+      <c r="H80" s="172"/>
+      <c r="I80" s="172"/>
+      <c r="J80" s="172"/>
+      <c r="K80" s="172"/>
+      <c r="L80" s="172"/>
+      <c r="M80" s="172"/>
+      <c r="N80" s="172"/>
+      <c r="O80" s="172"/>
+      <c r="P80" s="172"/>
     </row>
     <row r="81" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="101"/>
-      <c r="E81" s="251"/>
-      <c r="F81" s="118"/>
-      <c r="G81" s="118"/>
-      <c r="H81" s="118"/>
-      <c r="I81" s="118"/>
-      <c r="J81" s="118"/>
-      <c r="K81" s="118"/>
-      <c r="L81" s="118"/>
-      <c r="M81" s="118"/>
-      <c r="N81" s="118"/>
-      <c r="O81" s="118"/>
-      <c r="P81" s="118"/>
+      <c r="E81" s="175"/>
+      <c r="F81" s="147"/>
+      <c r="G81" s="147"/>
+      <c r="H81" s="147"/>
+      <c r="I81" s="147"/>
+      <c r="J81" s="147"/>
+      <c r="K81" s="147"/>
+      <c r="L81" s="147"/>
+      <c r="M81" s="147"/>
+      <c r="N81" s="147"/>
+      <c r="O81" s="147"/>
+      <c r="P81" s="147"/>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B82" s="74"/>
@@ -4941,40 +4810,40 @@
       <c r="D83" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="E83" s="260" t="s">
+      <c r="E83" s="182" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="260"/>
-      <c r="G83" s="260"/>
-      <c r="H83" s="260"/>
-      <c r="I83" s="260"/>
-      <c r="J83" s="260"/>
-      <c r="K83" s="260"/>
-      <c r="L83" s="260"/>
-      <c r="M83" s="260"/>
-      <c r="N83" s="260"/>
-      <c r="O83" s="260"/>
-      <c r="P83" s="260"/>
+      <c r="F83" s="182"/>
+      <c r="G83" s="182"/>
+      <c r="H83" s="182"/>
+      <c r="I83" s="182"/>
+      <c r="J83" s="182"/>
+      <c r="K83" s="182"/>
+      <c r="L83" s="182"/>
+      <c r="M83" s="182"/>
+      <c r="N83" s="182"/>
+      <c r="O83" s="182"/>
+      <c r="P83" s="182"/>
       <c r="Q83" s="72"/>
       <c r="R83" s="72"/>
     </row>
     <row r="84" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="138">
+      <c r="D84" s="292">
         <v>1</v>
       </c>
-      <c r="E84" s="132" t="s">
+      <c r="E84" s="293" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="133"/>
-      <c r="G84" s="133"/>
-      <c r="H84" s="133"/>
-      <c r="I84" s="133"/>
-      <c r="J84" s="133"/>
-      <c r="K84" s="133"/>
-      <c r="L84" s="133"/>
-      <c r="M84" s="134"/>
+      <c r="F84" s="293"/>
+      <c r="G84" s="293"/>
+      <c r="H84" s="293"/>
+      <c r="I84" s="293"/>
+      <c r="J84" s="293"/>
+      <c r="K84" s="293"/>
+      <c r="L84" s="293"/>
+      <c r="M84" s="293"/>
       <c r="N84" s="47"/>
       <c r="O84" s="47"/>
       <c r="P84" s="47"/>
@@ -4984,44 +4853,46 @@
     <row r="85" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="139"/>
-      <c r="E85" s="135"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="136"/>
-      <c r="H85" s="136"/>
-      <c r="I85" s="136"/>
-      <c r="J85" s="136"/>
-      <c r="K85" s="136"/>
-      <c r="L85" s="136"/>
-      <c r="M85" s="137"/>
+      <c r="D85" s="296">
+        <v>2</v>
+      </c>
+      <c r="E85" s="297"/>
+      <c r="F85" s="297"/>
+      <c r="G85" s="297"/>
+      <c r="H85" s="297"/>
+      <c r="I85" s="297"/>
+      <c r="J85" s="297"/>
+      <c r="K85" s="297"/>
+      <c r="L85" s="297"/>
+      <c r="M85" s="297"/>
       <c r="N85" s="46"/>
-      <c r="O85" s="162" t="s">
+      <c r="O85" s="136" t="s">
         <v>113</v>
       </c>
-      <c r="P85" s="162"/>
+      <c r="P85" s="136"/>
       <c r="Q85" s="72"/>
       <c r="R85" s="72"/>
     </row>
     <row r="86" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="278">
-        <v>2</v>
-      </c>
-      <c r="E86" s="262"/>
-      <c r="F86" s="263"/>
-      <c r="G86" s="263"/>
-      <c r="H86" s="263"/>
-      <c r="I86" s="263"/>
-      <c r="J86" s="263"/>
-      <c r="K86" s="263"/>
-      <c r="L86" s="263"/>
-      <c r="M86" s="264"/>
+      <c r="D86" s="292">
+        <v>3</v>
+      </c>
+      <c r="E86" s="295"/>
+      <c r="F86" s="295"/>
+      <c r="G86" s="295"/>
+      <c r="H86" s="295"/>
+      <c r="I86" s="295"/>
+      <c r="J86" s="295"/>
+      <c r="K86" s="295"/>
+      <c r="L86" s="295"/>
+      <c r="M86" s="295"/>
       <c r="N86" s="4"/>
-      <c r="O86" s="289" t="s">
+      <c r="O86" s="134" t="s">
         <v>115</v>
       </c>
-      <c r="P86" s="289"/>
+      <c r="P86" s="134"/>
       <c r="Q86" s="44"/>
       <c r="R86" s="44"/>
       <c r="T86" s="97" t="s">
@@ -5031,77 +4902,81 @@
     <row r="87" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="279"/>
-      <c r="E87" s="265"/>
-      <c r="F87" s="266"/>
-      <c r="G87" s="266"/>
-      <c r="H87" s="266"/>
-      <c r="I87" s="266"/>
-      <c r="J87" s="266"/>
-      <c r="K87" s="266"/>
-      <c r="L87" s="266"/>
-      <c r="M87" s="267"/>
+      <c r="D87" s="296">
+        <v>4</v>
+      </c>
+      <c r="E87" s="294"/>
+      <c r="F87" s="294"/>
+      <c r="G87" s="294"/>
+      <c r="H87" s="294"/>
+      <c r="I87" s="294"/>
+      <c r="J87" s="294"/>
+      <c r="K87" s="294"/>
+      <c r="L87" s="294"/>
+      <c r="M87" s="294"/>
       <c r="N87" s="5"/>
-      <c r="O87" s="289"/>
-      <c r="P87" s="289"/>
+      <c r="O87" s="134"/>
+      <c r="P87" s="134"/>
       <c r="Q87" s="44"/>
       <c r="R87" s="44"/>
     </row>
     <row r="88" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="138">
-        <v>3</v>
-      </c>
-      <c r="E88" s="269"/>
-      <c r="F88" s="270"/>
-      <c r="G88" s="270"/>
-      <c r="H88" s="270"/>
-      <c r="I88" s="270"/>
-      <c r="J88" s="270"/>
-      <c r="K88" s="270"/>
-      <c r="L88" s="270"/>
-      <c r="M88" s="271"/>
+      <c r="D88" s="292">
+        <v>5</v>
+      </c>
+      <c r="E88" s="295"/>
+      <c r="F88" s="295"/>
+      <c r="G88" s="295"/>
+      <c r="H88" s="295"/>
+      <c r="I88" s="295"/>
+      <c r="J88" s="295"/>
+      <c r="K88" s="295"/>
+      <c r="L88" s="295"/>
+      <c r="M88" s="295"/>
       <c r="N88" s="5"/>
-      <c r="O88" s="289"/>
-      <c r="P88" s="289"/>
+      <c r="O88" s="134"/>
+      <c r="P88" s="134"/>
       <c r="Q88" s="44"/>
       <c r="R88" s="44"/>
     </row>
     <row r="89" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="139"/>
-      <c r="E89" s="272"/>
-      <c r="F89" s="273"/>
-      <c r="G89" s="273"/>
-      <c r="H89" s="273"/>
-      <c r="I89" s="273"/>
-      <c r="J89" s="273"/>
-      <c r="K89" s="273"/>
-      <c r="L89" s="273"/>
-      <c r="M89" s="274"/>
+      <c r="D89" s="296">
+        <v>6</v>
+      </c>
+      <c r="E89" s="294"/>
+      <c r="F89" s="294"/>
+      <c r="G89" s="294"/>
+      <c r="H89" s="294"/>
+      <c r="I89" s="294"/>
+      <c r="J89" s="294"/>
+      <c r="K89" s="294"/>
+      <c r="L89" s="294"/>
+      <c r="M89" s="294"/>
       <c r="N89" s="5"/>
-      <c r="O89" s="290"/>
-      <c r="P89" s="290"/>
+      <c r="O89" s="135"/>
+      <c r="P89" s="135"/>
       <c r="Q89" s="44"/>
       <c r="R89" s="44"/>
     </row>
     <row r="90" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="278">
-        <v>4</v>
-      </c>
-      <c r="E90" s="262"/>
-      <c r="F90" s="263"/>
-      <c r="G90" s="263"/>
-      <c r="H90" s="263"/>
-      <c r="I90" s="263"/>
-      <c r="J90" s="263"/>
-      <c r="K90" s="263"/>
-      <c r="L90" s="263"/>
-      <c r="M90" s="264"/>
+      <c r="D90" s="292">
+        <v>7</v>
+      </c>
+      <c r="E90" s="295"/>
+      <c r="F90" s="295"/>
+      <c r="G90" s="295"/>
+      <c r="H90" s="295"/>
+      <c r="I90" s="295"/>
+      <c r="J90" s="295"/>
+      <c r="K90" s="295"/>
+      <c r="L90" s="295"/>
+      <c r="M90" s="295"/>
       <c r="N90" s="5"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -5111,39 +4986,41 @@
     <row r="91" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="279"/>
-      <c r="E91" s="265"/>
-      <c r="F91" s="266"/>
-      <c r="G91" s="266"/>
-      <c r="H91" s="266"/>
-      <c r="I91" s="266"/>
-      <c r="J91" s="266"/>
-      <c r="K91" s="266"/>
-      <c r="L91" s="266"/>
-      <c r="M91" s="267"/>
+      <c r="D91" s="296">
+        <v>8</v>
+      </c>
+      <c r="E91" s="294"/>
+      <c r="F91" s="294"/>
+      <c r="G91" s="294"/>
+      <c r="H91" s="294"/>
+      <c r="I91" s="294"/>
+      <c r="J91" s="294"/>
+      <c r="K91" s="294"/>
+      <c r="L91" s="294"/>
+      <c r="M91" s="294"/>
       <c r="N91" s="5"/>
-      <c r="O91" s="162" t="s">
+      <c r="O91" s="136" t="s">
         <v>116</v>
       </c>
-      <c r="P91" s="162"/>
+      <c r="P91" s="136"/>
       <c r="Q91" s="44"/>
       <c r="R91" s="44"/>
     </row>
     <row r="92" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="138">
-        <v>5</v>
-      </c>
-      <c r="E92" s="269"/>
-      <c r="F92" s="270"/>
-      <c r="G92" s="270"/>
-      <c r="H92" s="270"/>
-      <c r="I92" s="270"/>
-      <c r="J92" s="270"/>
-      <c r="K92" s="270"/>
-      <c r="L92" s="270"/>
-      <c r="M92" s="271"/>
+      <c r="D92" s="292">
+        <v>9</v>
+      </c>
+      <c r="E92" s="295"/>
+      <c r="F92" s="295"/>
+      <c r="G92" s="295"/>
+      <c r="H92" s="295"/>
+      <c r="I92" s="295"/>
+      <c r="J92" s="295"/>
+      <c r="K92" s="295"/>
+      <c r="L92" s="295"/>
+      <c r="M92" s="295"/>
       <c r="N92" s="5"/>
       <c r="O92" s="91"/>
       <c r="P92" s="91"/>
@@ -5153,119 +5030,125 @@
     <row r="93" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="139"/>
-      <c r="E93" s="272"/>
-      <c r="F93" s="273"/>
-      <c r="G93" s="273"/>
-      <c r="H93" s="273"/>
-      <c r="I93" s="273"/>
-      <c r="J93" s="273"/>
-      <c r="K93" s="273"/>
-      <c r="L93" s="273"/>
-      <c r="M93" s="274"/>
+      <c r="D93" s="296">
+        <v>10</v>
+      </c>
+      <c r="E93" s="294"/>
+      <c r="F93" s="294"/>
+      <c r="G93" s="294"/>
+      <c r="H93" s="294"/>
+      <c r="I93" s="294"/>
+      <c r="J93" s="294"/>
+      <c r="K93" s="294"/>
+      <c r="L93" s="294"/>
+      <c r="M93" s="294"/>
       <c r="N93" s="5"/>
-      <c r="O93" s="289" t="s">
+      <c r="O93" s="134" t="s">
         <v>117</v>
       </c>
-      <c r="P93" s="289"/>
+      <c r="P93" s="134"/>
       <c r="Q93" s="44"/>
       <c r="R93" s="44"/>
     </row>
     <row r="94" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="278">
-        <v>6</v>
-      </c>
-      <c r="E94" s="262"/>
-      <c r="F94" s="263"/>
-      <c r="G94" s="263"/>
-      <c r="H94" s="263"/>
-      <c r="I94" s="263"/>
-      <c r="J94" s="263"/>
-      <c r="K94" s="263"/>
-      <c r="L94" s="263"/>
-      <c r="M94" s="264"/>
+      <c r="D94" s="292">
+        <v>11</v>
+      </c>
+      <c r="E94" s="295"/>
+      <c r="F94" s="295"/>
+      <c r="G94" s="295"/>
+      <c r="H94" s="295"/>
+      <c r="I94" s="295"/>
+      <c r="J94" s="295"/>
+      <c r="K94" s="295"/>
+      <c r="L94" s="295"/>
+      <c r="M94" s="295"/>
       <c r="N94" s="5"/>
-      <c r="O94" s="289"/>
-      <c r="P94" s="289"/>
+      <c r="O94" s="134"/>
+      <c r="P94" s="134"/>
       <c r="Q94" s="44"/>
       <c r="R94" s="44"/>
     </row>
     <row r="95" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="279"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="266"/>
-      <c r="G95" s="266"/>
-      <c r="H95" s="266"/>
-      <c r="I95" s="266"/>
-      <c r="J95" s="266"/>
-      <c r="K95" s="266"/>
-      <c r="L95" s="266"/>
-      <c r="M95" s="267"/>
+      <c r="D95" s="296">
+        <v>12</v>
+      </c>
+      <c r="E95" s="294"/>
+      <c r="F95" s="294"/>
+      <c r="G95" s="294"/>
+      <c r="H95" s="294"/>
+      <c r="I95" s="294"/>
+      <c r="J95" s="294"/>
+      <c r="K95" s="294"/>
+      <c r="L95" s="294"/>
+      <c r="M95" s="294"/>
       <c r="N95" s="5"/>
-      <c r="O95" s="289"/>
-      <c r="P95" s="289"/>
+      <c r="O95" s="134"/>
+      <c r="P95" s="134"/>
       <c r="Q95" s="44"/>
       <c r="R95" s="44"/>
     </row>
     <row r="96" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="138">
-        <v>7</v>
-      </c>
-      <c r="E96" s="269"/>
-      <c r="F96" s="270"/>
-      <c r="G96" s="270"/>
-      <c r="H96" s="270"/>
-      <c r="I96" s="270"/>
-      <c r="J96" s="270"/>
-      <c r="K96" s="270"/>
-      <c r="L96" s="270"/>
-      <c r="M96" s="271"/>
+      <c r="D96" s="292">
+        <v>13</v>
+      </c>
+      <c r="E96" s="295"/>
+      <c r="F96" s="295"/>
+      <c r="G96" s="295"/>
+      <c r="H96" s="295"/>
+      <c r="I96" s="295"/>
+      <c r="J96" s="295"/>
+      <c r="K96" s="295"/>
+      <c r="L96" s="295"/>
+      <c r="M96" s="295"/>
       <c r="N96" s="5"/>
-      <c r="O96" s="289"/>
-      <c r="P96" s="289"/>
+      <c r="O96" s="134"/>
+      <c r="P96" s="134"/>
       <c r="Q96" s="44"/>
       <c r="R96" s="44"/>
     </row>
     <row r="97" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="139"/>
-      <c r="E97" s="272"/>
-      <c r="F97" s="273"/>
-      <c r="G97" s="273"/>
-      <c r="H97" s="273"/>
-      <c r="I97" s="273"/>
-      <c r="J97" s="273"/>
-      <c r="K97" s="273"/>
-      <c r="L97" s="273"/>
-      <c r="M97" s="274"/>
+      <c r="D97" s="296">
+        <v>14</v>
+      </c>
+      <c r="E97" s="294"/>
+      <c r="F97" s="294"/>
+      <c r="G97" s="294"/>
+      <c r="H97" s="294"/>
+      <c r="I97" s="294"/>
+      <c r="J97" s="294"/>
+      <c r="K97" s="294"/>
+      <c r="L97" s="294"/>
+      <c r="M97" s="294"/>
       <c r="N97" s="5"/>
-      <c r="O97" s="290"/>
-      <c r="P97" s="290"/>
+      <c r="O97" s="135"/>
+      <c r="P97" s="135"/>
       <c r="Q97" s="44"/>
       <c r="R97" s="44"/>
     </row>
     <row r="98" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="278">
-        <v>8</v>
-      </c>
-      <c r="E98" s="262"/>
-      <c r="F98" s="263"/>
-      <c r="G98" s="263"/>
-      <c r="H98" s="263"/>
-      <c r="I98" s="263"/>
-      <c r="J98" s="263"/>
-      <c r="K98" s="263"/>
-      <c r="L98" s="263"/>
-      <c r="M98" s="264"/>
+      <c r="D98" s="292">
+        <v>15</v>
+      </c>
+      <c r="E98" s="295"/>
+      <c r="F98" s="295"/>
+      <c r="G98" s="295"/>
+      <c r="H98" s="295"/>
+      <c r="I98" s="295"/>
+      <c r="J98" s="295"/>
+      <c r="K98" s="295"/>
+      <c r="L98" s="295"/>
+      <c r="M98" s="295"/>
       <c r="N98" s="5"/>
       <c r="O98" s="114"/>
       <c r="P98" s="114"/>
@@ -5275,263 +5158,277 @@
     <row r="99" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="279"/>
-      <c r="E99" s="265"/>
-      <c r="F99" s="266"/>
-      <c r="G99" s="266"/>
-      <c r="H99" s="266"/>
-      <c r="I99" s="266"/>
-      <c r="J99" s="266"/>
-      <c r="K99" s="266"/>
-      <c r="L99" s="266"/>
-      <c r="M99" s="267"/>
+      <c r="D99" s="296">
+        <v>16</v>
+      </c>
+      <c r="E99" s="294"/>
+      <c r="F99" s="294"/>
+      <c r="G99" s="294"/>
+      <c r="H99" s="294"/>
+      <c r="I99" s="294"/>
+      <c r="J99" s="294"/>
+      <c r="K99" s="294"/>
+      <c r="L99" s="294"/>
+      <c r="M99" s="294"/>
       <c r="N99" s="5"/>
-      <c r="O99" s="162" t="s">
+      <c r="O99" s="136" t="s">
         <v>118</v>
       </c>
-      <c r="P99" s="162"/>
+      <c r="P99" s="136"/>
       <c r="Q99" s="44"/>
       <c r="R99" s="44"/>
     </row>
     <row r="100" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="138">
-        <v>9</v>
-      </c>
-      <c r="E100" s="269"/>
-      <c r="F100" s="270"/>
-      <c r="G100" s="270"/>
-      <c r="H100" s="270"/>
-      <c r="I100" s="270"/>
-      <c r="J100" s="270"/>
-      <c r="K100" s="270"/>
-      <c r="L100" s="270"/>
-      <c r="M100" s="271"/>
+      <c r="D100" s="292">
+        <v>17</v>
+      </c>
+      <c r="E100" s="295"/>
+      <c r="F100" s="295"/>
+      <c r="G100" s="295"/>
+      <c r="H100" s="295"/>
+      <c r="I100" s="295"/>
+      <c r="J100" s="295"/>
+      <c r="K100" s="295"/>
+      <c r="L100" s="295"/>
+      <c r="M100" s="295"/>
       <c r="N100" s="5"/>
-      <c r="O100" s="289" t="s">
+      <c r="O100" s="134" t="s">
         <v>119</v>
       </c>
-      <c r="P100" s="289"/>
+      <c r="P100" s="134"/>
       <c r="Q100" s="44"/>
       <c r="R100" s="44"/>
     </row>
     <row r="101" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="139"/>
-      <c r="E101" s="272"/>
-      <c r="F101" s="273"/>
-      <c r="G101" s="273"/>
-      <c r="H101" s="273"/>
-      <c r="I101" s="273"/>
-      <c r="J101" s="273"/>
-      <c r="K101" s="273"/>
-      <c r="L101" s="273"/>
-      <c r="M101" s="274"/>
+      <c r="D101" s="296">
+        <v>18</v>
+      </c>
+      <c r="E101" s="294"/>
+      <c r="F101" s="294"/>
+      <c r="G101" s="294"/>
+      <c r="H101" s="294"/>
+      <c r="I101" s="294"/>
+      <c r="J101" s="294"/>
+      <c r="K101" s="294"/>
+      <c r="L101" s="294"/>
+      <c r="M101" s="294"/>
       <c r="N101" s="5"/>
-      <c r="O101" s="289"/>
-      <c r="P101" s="289"/>
+      <c r="O101" s="134"/>
+      <c r="P101" s="134"/>
       <c r="Q101" s="44"/>
       <c r="R101" s="44"/>
     </row>
     <row r="102" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
-      <c r="D102" s="278">
-        <v>10</v>
-      </c>
-      <c r="E102" s="262"/>
-      <c r="F102" s="263"/>
-      <c r="G102" s="263"/>
-      <c r="H102" s="263"/>
-      <c r="I102" s="263"/>
-      <c r="J102" s="263"/>
-      <c r="K102" s="263"/>
-      <c r="L102" s="263"/>
-      <c r="M102" s="264"/>
+      <c r="D102" s="292">
+        <v>19</v>
+      </c>
+      <c r="E102" s="295"/>
+      <c r="F102" s="295"/>
+      <c r="G102" s="295"/>
+      <c r="H102" s="295"/>
+      <c r="I102" s="295"/>
+      <c r="J102" s="295"/>
+      <c r="K102" s="295"/>
+      <c r="L102" s="295"/>
+      <c r="M102" s="295"/>
       <c r="N102" s="5"/>
-      <c r="O102" s="289"/>
-      <c r="P102" s="289"/>
+      <c r="O102" s="134"/>
+      <c r="P102" s="134"/>
       <c r="Q102" s="44"/>
       <c r="R102" s="44"/>
     </row>
     <row r="103" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="279"/>
-      <c r="E103" s="265"/>
-      <c r="F103" s="266"/>
-      <c r="G103" s="266"/>
-      <c r="H103" s="266"/>
-      <c r="I103" s="266"/>
-      <c r="J103" s="266"/>
-      <c r="K103" s="266"/>
-      <c r="L103" s="266"/>
-      <c r="M103" s="267"/>
+      <c r="D103" s="296">
+        <v>20</v>
+      </c>
+      <c r="E103" s="294"/>
+      <c r="F103" s="294"/>
+      <c r="G103" s="294"/>
+      <c r="H103" s="294"/>
+      <c r="I103" s="294"/>
+      <c r="J103" s="294"/>
+      <c r="K103" s="294"/>
+      <c r="L103" s="294"/>
+      <c r="M103" s="294"/>
       <c r="N103" s="5"/>
-      <c r="O103" s="289"/>
-      <c r="P103" s="289"/>
+      <c r="O103" s="134"/>
+      <c r="P103" s="134"/>
       <c r="Q103" s="44"/>
       <c r="R103" s="44"/>
     </row>
     <row r="104" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="138">
-        <v>11</v>
-      </c>
-      <c r="E104" s="269"/>
-      <c r="F104" s="270"/>
-      <c r="G104" s="270"/>
-      <c r="H104" s="270"/>
-      <c r="I104" s="270"/>
-      <c r="J104" s="270"/>
-      <c r="K104" s="270"/>
-      <c r="L104" s="270"/>
-      <c r="M104" s="271"/>
+      <c r="D104" s="292">
+        <v>21</v>
+      </c>
+      <c r="E104" s="295"/>
+      <c r="F104" s="295"/>
+      <c r="G104" s="295"/>
+      <c r="H104" s="295"/>
+      <c r="I104" s="295"/>
+      <c r="J104" s="295"/>
+      <c r="K104" s="295"/>
+      <c r="L104" s="295"/>
+      <c r="M104" s="295"/>
       <c r="N104" s="5"/>
-      <c r="O104" s="289"/>
-      <c r="P104" s="289"/>
+      <c r="O104" s="134"/>
+      <c r="P104" s="134"/>
       <c r="Q104" s="44"/>
       <c r="R104" s="44"/>
     </row>
     <row r="105" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="139"/>
-      <c r="E105" s="272"/>
-      <c r="F105" s="273"/>
-      <c r="G105" s="273"/>
-      <c r="H105" s="273"/>
-      <c r="I105" s="273"/>
-      <c r="J105" s="273"/>
-      <c r="K105" s="273"/>
-      <c r="L105" s="273"/>
-      <c r="M105" s="274"/>
+      <c r="D105" s="296">
+        <v>22</v>
+      </c>
+      <c r="E105" s="294"/>
+      <c r="F105" s="294"/>
+      <c r="G105" s="294"/>
+      <c r="H105" s="294"/>
+      <c r="I105" s="294"/>
+      <c r="J105" s="294"/>
+      <c r="K105" s="294"/>
+      <c r="L105" s="294"/>
+      <c r="M105" s="294"/>
       <c r="N105" s="5"/>
-      <c r="O105" s="290"/>
-      <c r="P105" s="290"/>
+      <c r="O105" s="135"/>
+      <c r="P105" s="135"/>
       <c r="Q105" s="44"/>
       <c r="R105" s="44"/>
     </row>
     <row r="106" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="278">
-        <v>12</v>
-      </c>
-      <c r="E106" s="262"/>
-      <c r="F106" s="263"/>
-      <c r="G106" s="263"/>
-      <c r="H106" s="263"/>
-      <c r="I106" s="263"/>
-      <c r="J106" s="263"/>
-      <c r="K106" s="263"/>
-      <c r="L106" s="263"/>
-      <c r="M106" s="264"/>
+      <c r="D106" s="292">
+        <v>23</v>
+      </c>
+      <c r="E106" s="295"/>
+      <c r="F106" s="295"/>
+      <c r="G106" s="295"/>
+      <c r="H106" s="295"/>
+      <c r="I106" s="295"/>
+      <c r="J106" s="295"/>
+      <c r="K106" s="295"/>
+      <c r="L106" s="295"/>
+      <c r="M106" s="295"/>
       <c r="N106" s="5"/>
-      <c r="O106" s="283"/>
-      <c r="P106" s="283"/>
+      <c r="O106" s="129"/>
+      <c r="P106" s="129"/>
       <c r="Q106" s="44"/>
       <c r="R106" s="44"/>
     </row>
     <row r="107" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="279"/>
-      <c r="E107" s="265"/>
-      <c r="F107" s="266"/>
-      <c r="G107" s="266"/>
-      <c r="H107" s="266"/>
-      <c r="I107" s="266"/>
-      <c r="J107" s="266"/>
-      <c r="K107" s="266"/>
-      <c r="L107" s="266"/>
-      <c r="M107" s="267"/>
+      <c r="D107" s="296">
+        <v>24</v>
+      </c>
+      <c r="E107" s="294"/>
+      <c r="F107" s="294"/>
+      <c r="G107" s="294"/>
+      <c r="H107" s="294"/>
+      <c r="I107" s="294"/>
+      <c r="J107" s="294"/>
+      <c r="K107" s="294"/>
+      <c r="L107" s="294"/>
+      <c r="M107" s="294"/>
       <c r="N107" s="5"/>
-      <c r="O107" s="284"/>
-      <c r="P107" s="284"/>
+      <c r="O107" s="291"/>
+      <c r="P107" s="291"/>
       <c r="Q107" s="44"/>
       <c r="R107" s="44"/>
     </row>
     <row r="108" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="138">
-        <v>13</v>
-      </c>
-      <c r="E108" s="269"/>
-      <c r="F108" s="270"/>
-      <c r="G108" s="270"/>
-      <c r="H108" s="270"/>
-      <c r="I108" s="270"/>
-      <c r="J108" s="270"/>
-      <c r="K108" s="270"/>
-      <c r="L108" s="270"/>
-      <c r="M108" s="271"/>
+      <c r="D108" s="292">
+        <v>25</v>
+      </c>
+      <c r="E108" s="295"/>
+      <c r="F108" s="295"/>
+      <c r="G108" s="295"/>
+      <c r="H108" s="295"/>
+      <c r="I108" s="295"/>
+      <c r="J108" s="295"/>
+      <c r="K108" s="295"/>
+      <c r="L108" s="295"/>
+      <c r="M108" s="295"/>
       <c r="N108" s="5"/>
-      <c r="O108" s="284"/>
-      <c r="P108" s="284"/>
+      <c r="O108" s="291"/>
+      <c r="P108" s="291"/>
       <c r="Q108" s="44"/>
       <c r="R108" s="44"/>
     </row>
     <row r="109" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="139"/>
-      <c r="E109" s="272"/>
-      <c r="F109" s="273"/>
-      <c r="G109" s="273"/>
-      <c r="H109" s="273"/>
-      <c r="I109" s="273"/>
-      <c r="J109" s="273"/>
-      <c r="K109" s="273"/>
-      <c r="L109" s="273"/>
-      <c r="M109" s="274"/>
+      <c r="D109" s="296">
+        <v>26</v>
+      </c>
+      <c r="E109" s="294"/>
+      <c r="F109" s="294"/>
+      <c r="G109" s="294"/>
+      <c r="H109" s="294"/>
+      <c r="I109" s="294"/>
+      <c r="J109" s="294"/>
+      <c r="K109" s="294"/>
+      <c r="L109" s="294"/>
+      <c r="M109" s="294"/>
       <c r="N109" s="5"/>
-      <c r="O109" s="284"/>
-      <c r="P109" s="284"/>
+      <c r="O109" s="291"/>
+      <c r="P109" s="291"/>
       <c r="Q109" s="44"/>
       <c r="R109" s="44"/>
     </row>
     <row r="110" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
-      <c r="D110" s="278">
-        <v>14</v>
-      </c>
-      <c r="E110" s="262"/>
-      <c r="F110" s="263"/>
-      <c r="G110" s="263"/>
-      <c r="H110" s="263"/>
-      <c r="I110" s="263"/>
-      <c r="J110" s="263"/>
-      <c r="K110" s="263"/>
-      <c r="L110" s="263"/>
-      <c r="M110" s="264"/>
+      <c r="D110" s="292">
+        <v>27</v>
+      </c>
+      <c r="E110" s="295"/>
+      <c r="F110" s="295"/>
+      <c r="G110" s="295"/>
+      <c r="H110" s="295"/>
+      <c r="I110" s="295"/>
+      <c r="J110" s="295"/>
+      <c r="K110" s="295"/>
+      <c r="L110" s="295"/>
+      <c r="M110" s="295"/>
       <c r="N110" s="5"/>
-      <c r="O110" s="284"/>
-      <c r="P110" s="284"/>
+      <c r="O110" s="291"/>
+      <c r="P110" s="291"/>
       <c r="Q110" s="44"/>
       <c r="R110" s="44"/>
     </row>
     <row r="111" spans="2:18" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="279"/>
-      <c r="E111" s="265"/>
-      <c r="F111" s="266"/>
-      <c r="G111" s="266"/>
-      <c r="H111" s="266"/>
-      <c r="I111" s="266"/>
-      <c r="J111" s="266"/>
-      <c r="K111" s="266"/>
-      <c r="L111" s="266"/>
-      <c r="M111" s="267"/>
+      <c r="D111" s="296">
+        <v>28</v>
+      </c>
+      <c r="E111" s="294"/>
+      <c r="F111" s="294"/>
+      <c r="G111" s="294"/>
+      <c r="H111" s="294"/>
+      <c r="I111" s="294"/>
+      <c r="J111" s="294"/>
+      <c r="K111" s="294"/>
+      <c r="L111" s="294"/>
+      <c r="M111" s="294"/>
       <c r="N111" s="5"/>
-      <c r="O111" s="285"/>
-      <c r="P111" s="285"/>
+      <c r="O111" s="130"/>
+      <c r="P111" s="130"/>
       <c r="Q111" s="46"/>
       <c r="R111" s="46"/>
     </row>
@@ -5549,10 +5446,10 @@
       <c r="L112" s="116"/>
       <c r="M112" s="116"/>
       <c r="N112" s="5"/>
-      <c r="O112" s="282" t="s">
+      <c r="O112" s="152" t="s">
         <v>88</v>
       </c>
-      <c r="P112" s="282"/>
+      <c r="P112" s="152"/>
       <c r="Q112" s="46"/>
       <c r="R112" s="46"/>
     </row>
@@ -5581,20 +5478,20 @@
       <c r="D114" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="E114" s="286" t="s">
+      <c r="E114" s="131" t="s">
         <v>129</v>
       </c>
-      <c r="F114" s="287"/>
-      <c r="G114" s="287"/>
-      <c r="H114" s="287"/>
-      <c r="I114" s="287"/>
-      <c r="J114" s="287"/>
-      <c r="K114" s="287"/>
-      <c r="L114" s="287"/>
-      <c r="M114" s="287"/>
-      <c r="N114" s="287"/>
-      <c r="O114" s="287"/>
-      <c r="P114" s="287"/>
+      <c r="F114" s="132"/>
+      <c r="G114" s="132"/>
+      <c r="H114" s="132"/>
+      <c r="I114" s="132"/>
+      <c r="J114" s="132"/>
+      <c r="K114" s="132"/>
+      <c r="L114" s="132"/>
+      <c r="M114" s="132"/>
+      <c r="N114" s="132"/>
+      <c r="O114" s="132"/>
+      <c r="P114" s="132"/>
       <c r="Q114" s="44"/>
       <c r="R114" s="44"/>
     </row>
@@ -5604,20 +5501,20 @@
       <c r="D115" s="108">
         <v>1</v>
       </c>
-      <c r="E115" s="288" t="s">
+      <c r="E115" s="133" t="s">
         <v>120</v>
       </c>
-      <c r="F115" s="288"/>
-      <c r="G115" s="288"/>
-      <c r="H115" s="288"/>
-      <c r="I115" s="288"/>
-      <c r="J115" s="288"/>
-      <c r="K115" s="288"/>
-      <c r="L115" s="288"/>
-      <c r="M115" s="288"/>
-      <c r="N115" s="288"/>
-      <c r="O115" s="288"/>
-      <c r="P115" s="288"/>
+      <c r="F115" s="133"/>
+      <c r="G115" s="133"/>
+      <c r="H115" s="133"/>
+      <c r="I115" s="133"/>
+      <c r="J115" s="133"/>
+      <c r="K115" s="133"/>
+      <c r="L115" s="133"/>
+      <c r="M115" s="133"/>
+      <c r="N115" s="133"/>
+      <c r="O115" s="133"/>
+      <c r="P115" s="133"/>
       <c r="Q115" s="55"/>
       <c r="R115" s="55"/>
     </row>
@@ -5627,18 +5524,18 @@
       <c r="D116" s="113">
         <v>2</v>
       </c>
-      <c r="E116" s="245"/>
-      <c r="F116" s="245"/>
-      <c r="G116" s="245"/>
-      <c r="H116" s="245"/>
-      <c r="I116" s="245"/>
-      <c r="J116" s="245"/>
-      <c r="K116" s="245"/>
-      <c r="L116" s="245"/>
-      <c r="M116" s="245"/>
-      <c r="N116" s="245"/>
-      <c r="O116" s="245"/>
-      <c r="P116" s="245"/>
+      <c r="E116" s="149"/>
+      <c r="F116" s="149"/>
+      <c r="G116" s="149"/>
+      <c r="H116" s="149"/>
+      <c r="I116" s="149"/>
+      <c r="J116" s="149"/>
+      <c r="K116" s="149"/>
+      <c r="L116" s="149"/>
+      <c r="M116" s="149"/>
+      <c r="N116" s="149"/>
+      <c r="O116" s="149"/>
+      <c r="P116" s="149"/>
       <c r="Q116" s="55"/>
       <c r="R116" s="55"/>
     </row>
@@ -5648,18 +5545,18 @@
       <c r="D117" s="108">
         <v>3</v>
       </c>
-      <c r="E117" s="164"/>
-      <c r="F117" s="164"/>
-      <c r="G117" s="164"/>
-      <c r="H117" s="164"/>
-      <c r="I117" s="164"/>
-      <c r="J117" s="164"/>
-      <c r="K117" s="164"/>
-      <c r="L117" s="164"/>
-      <c r="M117" s="164"/>
-      <c r="N117" s="164"/>
-      <c r="O117" s="164"/>
-      <c r="P117" s="164"/>
+      <c r="E117" s="148"/>
+      <c r="F117" s="148"/>
+      <c r="G117" s="148"/>
+      <c r="H117" s="148"/>
+      <c r="I117" s="148"/>
+      <c r="J117" s="148"/>
+      <c r="K117" s="148"/>
+      <c r="L117" s="148"/>
+      <c r="M117" s="148"/>
+      <c r="N117" s="148"/>
+      <c r="O117" s="148"/>
+      <c r="P117" s="148"/>
       <c r="Q117" s="55"/>
       <c r="R117" s="55"/>
     </row>
@@ -5669,18 +5566,18 @@
       <c r="D118" s="113">
         <v>4</v>
       </c>
-      <c r="E118" s="245"/>
-      <c r="F118" s="245"/>
-      <c r="G118" s="245"/>
-      <c r="H118" s="245"/>
-      <c r="I118" s="245"/>
-      <c r="J118" s="245"/>
-      <c r="K118" s="245"/>
-      <c r="L118" s="245"/>
-      <c r="M118" s="245"/>
-      <c r="N118" s="245"/>
-      <c r="O118" s="245"/>
-      <c r="P118" s="245"/>
+      <c r="E118" s="149"/>
+      <c r="F118" s="149"/>
+      <c r="G118" s="149"/>
+      <c r="H118" s="149"/>
+      <c r="I118" s="149"/>
+      <c r="J118" s="149"/>
+      <c r="K118" s="149"/>
+      <c r="L118" s="149"/>
+      <c r="M118" s="149"/>
+      <c r="N118" s="149"/>
+      <c r="O118" s="149"/>
+      <c r="P118" s="149"/>
     </row>
     <row r="119" spans="2:18" ht="24" x14ac:dyDescent="0.3">
       <c r="B119" s="3"/>
@@ -5688,18 +5585,18 @@
       <c r="D119" s="108">
         <v>5</v>
       </c>
-      <c r="E119" s="268"/>
-      <c r="F119" s="268"/>
-      <c r="G119" s="268"/>
-      <c r="H119" s="268"/>
-      <c r="I119" s="268"/>
-      <c r="J119" s="268"/>
-      <c r="K119" s="268"/>
-      <c r="L119" s="268"/>
-      <c r="M119" s="268"/>
-      <c r="N119" s="268"/>
-      <c r="O119" s="268"/>
-      <c r="P119" s="268"/>
+      <c r="E119" s="150"/>
+      <c r="F119" s="150"/>
+      <c r="G119" s="150"/>
+      <c r="H119" s="150"/>
+      <c r="I119" s="150"/>
+      <c r="J119" s="150"/>
+      <c r="K119" s="150"/>
+      <c r="L119" s="150"/>
+      <c r="M119" s="150"/>
+      <c r="N119" s="150"/>
+      <c r="O119" s="150"/>
+      <c r="P119" s="150"/>
     </row>
     <row r="120" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="8"/>
@@ -5707,18 +5604,18 @@
       <c r="D120" s="113">
         <v>6</v>
       </c>
-      <c r="E120" s="245"/>
-      <c r="F120" s="245"/>
-      <c r="G120" s="245"/>
-      <c r="H120" s="245"/>
-      <c r="I120" s="245"/>
-      <c r="J120" s="245"/>
-      <c r="K120" s="245"/>
-      <c r="L120" s="245"/>
-      <c r="M120" s="245"/>
-      <c r="N120" s="245"/>
-      <c r="O120" s="245"/>
-      <c r="P120" s="245"/>
+      <c r="E120" s="149"/>
+      <c r="F120" s="149"/>
+      <c r="G120" s="149"/>
+      <c r="H120" s="149"/>
+      <c r="I120" s="149"/>
+      <c r="J120" s="149"/>
+      <c r="K120" s="149"/>
+      <c r="L120" s="149"/>
+      <c r="M120" s="149"/>
+      <c r="N120" s="149"/>
+      <c r="O120" s="149"/>
+      <c r="P120" s="149"/>
       <c r="Q120" s="55"/>
       <c r="R120" s="55"/>
     </row>
@@ -5728,18 +5625,18 @@
       <c r="D121" s="108">
         <v>7</v>
       </c>
-      <c r="E121" s="164"/>
-      <c r="F121" s="164"/>
-      <c r="G121" s="164"/>
-      <c r="H121" s="164"/>
-      <c r="I121" s="164"/>
-      <c r="J121" s="164"/>
-      <c r="K121" s="164"/>
-      <c r="L121" s="164"/>
-      <c r="M121" s="164"/>
-      <c r="N121" s="164"/>
-      <c r="O121" s="164"/>
-      <c r="P121" s="164"/>
+      <c r="E121" s="148"/>
+      <c r="F121" s="148"/>
+      <c r="G121" s="148"/>
+      <c r="H121" s="148"/>
+      <c r="I121" s="148"/>
+      <c r="J121" s="148"/>
+      <c r="K121" s="148"/>
+      <c r="L121" s="148"/>
+      <c r="M121" s="148"/>
+      <c r="N121" s="148"/>
+      <c r="O121" s="148"/>
+      <c r="P121" s="148"/>
       <c r="Q121" s="55"/>
       <c r="R121" s="55"/>
     </row>
@@ -5749,58 +5646,58 @@
       <c r="D122" s="113">
         <v>8</v>
       </c>
-      <c r="E122" s="245"/>
-      <c r="F122" s="245"/>
-      <c r="G122" s="245"/>
-      <c r="H122" s="245"/>
-      <c r="I122" s="245"/>
-      <c r="J122" s="245"/>
-      <c r="K122" s="245"/>
-      <c r="L122" s="245"/>
-      <c r="M122" s="245"/>
-      <c r="N122" s="245"/>
-      <c r="O122" s="245"/>
-      <c r="P122" s="245"/>
+      <c r="E122" s="149"/>
+      <c r="F122" s="149"/>
+      <c r="G122" s="149"/>
+      <c r="H122" s="149"/>
+      <c r="I122" s="149"/>
+      <c r="J122" s="149"/>
+      <c r="K122" s="149"/>
+      <c r="L122" s="149"/>
+      <c r="M122" s="149"/>
+      <c r="N122" s="149"/>
+      <c r="O122" s="149"/>
+      <c r="P122" s="149"/>
       <c r="Q122" s="55"/>
       <c r="R122" s="55"/>
     </row>
     <row r="123" spans="2:18" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="74"/>
       <c r="C123" s="74"/>
-      <c r="D123" s="261"/>
-      <c r="E123" s="261"/>
-      <c r="F123" s="261"/>
-      <c r="G123" s="261"/>
-      <c r="H123" s="261"/>
-      <c r="I123" s="261"/>
-      <c r="J123" s="261"/>
-      <c r="K123" s="261"/>
-      <c r="L123" s="261"/>
-      <c r="M123" s="261"/>
-      <c r="N123" s="261"/>
-      <c r="O123" s="261"/>
-      <c r="P123" s="261"/>
+      <c r="D123" s="183"/>
+      <c r="E123" s="183"/>
+      <c r="F123" s="183"/>
+      <c r="G123" s="183"/>
+      <c r="H123" s="183"/>
+      <c r="I123" s="183"/>
+      <c r="J123" s="183"/>
+      <c r="K123" s="183"/>
+      <c r="L123" s="183"/>
+      <c r="M123" s="183"/>
+      <c r="N123" s="183"/>
+      <c r="O123" s="183"/>
+      <c r="P123" s="183"/>
       <c r="Q123" s="55"/>
       <c r="R123" s="55"/>
     </row>
     <row r="124" spans="2:18" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="74"/>
       <c r="C124" s="74"/>
-      <c r="D124" s="239" t="s">
+      <c r="D124" s="201" t="s">
         <v>121</v>
       </c>
-      <c r="E124" s="239"/>
-      <c r="F124" s="239"/>
-      <c r="G124" s="239"/>
-      <c r="H124" s="239"/>
-      <c r="I124" s="239"/>
-      <c r="J124" s="239"/>
-      <c r="K124" s="239"/>
-      <c r="L124" s="239"/>
-      <c r="M124" s="239"/>
-      <c r="N124" s="239"/>
-      <c r="O124" s="239"/>
-      <c r="P124" s="239"/>
+      <c r="E124" s="201"/>
+      <c r="F124" s="201"/>
+      <c r="G124" s="201"/>
+      <c r="H124" s="201"/>
+      <c r="I124" s="201"/>
+      <c r="J124" s="201"/>
+      <c r="K124" s="201"/>
+      <c r="L124" s="201"/>
+      <c r="M124" s="201"/>
+      <c r="N124" s="201"/>
+      <c r="O124" s="201"/>
+      <c r="P124" s="201"/>
       <c r="Q124" s="55"/>
       <c r="R124" s="55"/>
     </row>
@@ -5826,27 +5723,27 @@
     <row r="126" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="74"/>
       <c r="C126" s="74"/>
-      <c r="D126" s="205" t="s">
+      <c r="D126" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="E126" s="205"/>
-      <c r="F126" s="205"/>
+      <c r="E126" s="169"/>
+      <c r="F126" s="169"/>
       <c r="G126" s="55"/>
-      <c r="H126" s="205" t="s">
+      <c r="H126" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="I126" s="205"/>
-      <c r="J126" s="205"/>
+      <c r="I126" s="169"/>
+      <c r="J126" s="169"/>
       <c r="K126" s="55"/>
-      <c r="L126" s="205" t="s">
+      <c r="L126" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="M126" s="205"/>
+      <c r="M126" s="169"/>
       <c r="N126" s="55"/>
-      <c r="O126" s="205" t="s">
+      <c r="O126" s="169" t="s">
         <v>123</v>
       </c>
-      <c r="P126" s="205"/>
+      <c r="P126" s="169"/>
       <c r="Q126" s="55"/>
       <c r="R126" s="55"/>
     </row>
@@ -5948,54 +5845,54 @@
     <row r="132" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="74"/>
       <c r="C132" s="74"/>
-      <c r="D132" s="201" t="s">
+      <c r="D132" s="240" t="s">
         <v>124</v>
       </c>
-      <c r="E132" s="202"/>
-      <c r="F132" s="202"/>
+      <c r="E132" s="174"/>
+      <c r="F132" s="174"/>
       <c r="G132" s="94"/>
-      <c r="H132" s="250" t="s">
+      <c r="H132" s="173" t="s">
         <v>125</v>
       </c>
-      <c r="I132" s="202"/>
-      <c r="J132" s="202"/>
+      <c r="I132" s="174"/>
+      <c r="J132" s="174"/>
       <c r="K132" s="94"/>
-      <c r="L132" s="247" t="s">
+      <c r="L132" s="167" t="s">
         <v>126</v>
       </c>
-      <c r="M132" s="248"/>
+      <c r="M132" s="168"/>
       <c r="N132" s="94"/>
-      <c r="O132" s="247" t="s">
+      <c r="O132" s="167" t="s">
         <v>127</v>
       </c>
-      <c r="P132" s="248"/>
+      <c r="P132" s="168"/>
       <c r="Q132" s="55"/>
       <c r="R132" s="55"/>
     </row>
     <row r="133" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B133" s="74"/>
       <c r="C133" s="74"/>
-      <c r="D133" s="234" t="s">
+      <c r="D133" s="186" t="s">
         <v>130</v>
       </c>
-      <c r="E133" s="234"/>
-      <c r="F133" s="234"/>
+      <c r="E133" s="186"/>
+      <c r="F133" s="186"/>
       <c r="G133" s="90"/>
-      <c r="H133" s="234" t="s">
+      <c r="H133" s="186" t="s">
         <v>131</v>
       </c>
-      <c r="I133" s="118"/>
-      <c r="J133" s="118"/>
+      <c r="I133" s="147"/>
+      <c r="J133" s="147"/>
       <c r="K133" s="94"/>
-      <c r="L133" s="235" t="s">
+      <c r="L133" s="190" t="s">
         <v>128</v>
       </c>
-      <c r="M133" s="202"/>
+      <c r="M133" s="174"/>
       <c r="N133" s="94"/>
-      <c r="O133" s="234" t="s">
+      <c r="O133" s="186" t="s">
         <v>16</v>
       </c>
-      <c r="P133" s="234"/>
+      <c r="P133" s="186"/>
       <c r="Q133" s="55"/>
       <c r="R133" s="55"/>
     </row>
@@ -6043,95 +5940,116 @@
     </row>
   </sheetData>
   <mergeCells count="204">
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="D108:D109"/>
-    <mergeCell ref="E108:M109"/>
-    <mergeCell ref="D110:D111"/>
-    <mergeCell ref="E110:M111"/>
-    <mergeCell ref="E98:M99"/>
-    <mergeCell ref="O106:P111"/>
-    <mergeCell ref="E114:P114"/>
-    <mergeCell ref="E115:P115"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:M105"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="E106:M107"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="O100:P105"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="E100:M101"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="E102:M103"/>
-    <mergeCell ref="E49:J49"/>
-    <mergeCell ref="E96:M97"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="M62:P62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="E86:M87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="E88:M89"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="O85:P85"/>
-    <mergeCell ref="O86:P89"/>
-    <mergeCell ref="O91:P91"/>
-    <mergeCell ref="E94:M95"/>
-    <mergeCell ref="E121:P121"/>
-    <mergeCell ref="E122:P122"/>
-    <mergeCell ref="E116:P116"/>
-    <mergeCell ref="E117:P117"/>
-    <mergeCell ref="E118:P118"/>
-    <mergeCell ref="E119:P119"/>
-    <mergeCell ref="E120:P120"/>
-    <mergeCell ref="M64:P64"/>
-    <mergeCell ref="O112:P112"/>
-    <mergeCell ref="O93:P97"/>
-    <mergeCell ref="E92:M93"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="L132:M132"/>
-    <mergeCell ref="O126:P126"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="L126:M126"/>
-    <mergeCell ref="E80:P80"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="H132:J132"/>
-    <mergeCell ref="O132:P132"/>
-    <mergeCell ref="E81:P81"/>
-    <mergeCell ref="E75:P75"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="D60:P60"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="M66:P66"/>
-    <mergeCell ref="M65:P65"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="E83:P83"/>
-    <mergeCell ref="D123:P123"/>
-    <mergeCell ref="E90:M91"/>
-    <mergeCell ref="E70:P70"/>
+    <mergeCell ref="E102:M102"/>
+    <mergeCell ref="E103:M103"/>
+    <mergeCell ref="E104:M104"/>
+    <mergeCell ref="E105:M105"/>
+    <mergeCell ref="E106:M106"/>
+    <mergeCell ref="E107:M107"/>
+    <mergeCell ref="E108:M108"/>
+    <mergeCell ref="E109:M109"/>
+    <mergeCell ref="E84:M84"/>
+    <mergeCell ref="E85:M85"/>
+    <mergeCell ref="E86:M86"/>
+    <mergeCell ref="E87:M87"/>
+    <mergeCell ref="E88:M88"/>
+    <mergeCell ref="E89:M89"/>
+    <mergeCell ref="E90:M90"/>
+    <mergeCell ref="E91:M91"/>
+    <mergeCell ref="E92:M92"/>
+    <mergeCell ref="E93:M93"/>
+    <mergeCell ref="E94:M94"/>
+    <mergeCell ref="E95:M95"/>
+    <mergeCell ref="E96:M96"/>
+    <mergeCell ref="E97:M97"/>
+    <mergeCell ref="E98:M98"/>
+    <mergeCell ref="E99:M99"/>
+    <mergeCell ref="E100:M100"/>
+    <mergeCell ref="E101:M101"/>
+    <mergeCell ref="L4:N5"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:N8"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="M61:P61"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D37:I37"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E54:J54"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D39:I39"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="E52:J52"/>
+    <mergeCell ref="E71:P71"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="E53:J53"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="E50:J50"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="L29:P29"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="E72:P72"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="D48:P48"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="L35:P35"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="E68:P68"/>
     <mergeCell ref="H133:J133"/>
     <mergeCell ref="D31:I31"/>
     <mergeCell ref="L46:P46"/>
@@ -6156,97 +6074,76 @@
     <mergeCell ref="O133:P133"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="D24:H24"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D42:I42"/>
-    <mergeCell ref="E72:P72"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D44:I44"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L39:O39"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="D48:P48"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="L35:P35"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="E52:J52"/>
-    <mergeCell ref="E71:P71"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="D38:I38"/>
-    <mergeCell ref="E53:J53"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="E50:J50"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="L29:P29"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="E84:M85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E68:P68"/>
+    <mergeCell ref="L132:M132"/>
+    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="L126:M126"/>
+    <mergeCell ref="E80:P80"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="H132:J132"/>
+    <mergeCell ref="O132:P132"/>
+    <mergeCell ref="E81:P81"/>
+    <mergeCell ref="E75:P75"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="D60:P60"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="M66:P66"/>
+    <mergeCell ref="M65:P65"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="E83:P83"/>
+    <mergeCell ref="D123:P123"/>
+    <mergeCell ref="E70:P70"/>
     <mergeCell ref="E69:P69"/>
     <mergeCell ref="E76:P76"/>
+    <mergeCell ref="E121:P121"/>
+    <mergeCell ref="E122:P122"/>
+    <mergeCell ref="E116:P116"/>
+    <mergeCell ref="E117:P117"/>
+    <mergeCell ref="E118:P118"/>
+    <mergeCell ref="E119:P119"/>
+    <mergeCell ref="E120:P120"/>
+    <mergeCell ref="M64:P64"/>
+    <mergeCell ref="O112:P112"/>
+    <mergeCell ref="O93:P97"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="D64:F64"/>
     <mergeCell ref="E77:P77"/>
     <mergeCell ref="E78:P78"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="M61:P61"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="L25:O25"/>
     <mergeCell ref="E73:P73"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="L18:P18"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="D37:I37"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="E54:J54"/>
-    <mergeCell ref="M6:N8"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D39:I39"/>
-    <mergeCell ref="L37:O37"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="E111:M111"/>
+    <mergeCell ref="E110:M110"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="M62:P62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="O86:P89"/>
+    <mergeCell ref="O91:P91"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="O106:P111"/>
+    <mergeCell ref="E114:P114"/>
+    <mergeCell ref="E115:P115"/>
+    <mergeCell ref="O100:P105"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="I63:J63"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -5472,7 +5472,7 @@
       <c r="Q113" s="44"/>
       <c r="R113" s="44"/>
     </row>
-    <row r="114" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" hidden="1" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
       <c r="D114" s="107" t="s">
@@ -5495,7 +5495,7 @@
       <c r="Q114" s="44"/>
       <c r="R114" s="44"/>
     </row>
-    <row r="115" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" hidden="1" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
       <c r="D115" s="108">
@@ -5518,7 +5518,7 @@
       <c r="Q115" s="55"/>
       <c r="R115" s="55"/>
     </row>
-    <row r="116" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" hidden="1" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
       <c r="D116" s="113">
@@ -5539,7 +5539,7 @@
       <c r="Q116" s="55"/>
       <c r="R116" s="55"/>
     </row>
-    <row r="117" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" hidden="1" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="108">
@@ -5560,7 +5560,7 @@
       <c r="Q117" s="55"/>
       <c r="R117" s="55"/>
     </row>
-    <row r="118" spans="2:18" ht="24" x14ac:dyDescent="0.3">
+    <row r="118" hidden="1" spans="2:18" ht="24" x14ac:dyDescent="0.3">
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="113">
@@ -5579,7 +5579,7 @@
       <c r="O118" s="149"/>
       <c r="P118" s="149"/>
     </row>
-    <row r="119" spans="2:18" ht="24" x14ac:dyDescent="0.3">
+    <row r="119" hidden="1" spans="2:18" ht="24" x14ac:dyDescent="0.3">
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="108">
@@ -5598,7 +5598,7 @@
       <c r="O119" s="150"/>
       <c r="P119" s="150"/>
     </row>
-    <row r="120" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" hidden="1" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
       <c r="D120" s="113">
@@ -5619,7 +5619,7 @@
       <c r="Q120" s="55"/>
       <c r="R120" s="55"/>
     </row>
-    <row r="121" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" hidden="1" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
       <c r="D121" s="108">
@@ -5640,7 +5640,7 @@
       <c r="Q121" s="55"/>
       <c r="R121" s="55"/>
     </row>
-    <row r="122" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" hidden="1" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
       <c r="D122" s="113">

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -5858,9 +5858,11 @@
       <c r="E128" s="92" t="n"/>
       <c r="F128" s="92" t="n"/>
       <c r="G128" s="55" t="n"/>
-      <c r="H128" s="92" t="n"/>
-      <c r="I128" s="92" t="n"/>
-      <c r="J128" s="92" t="n"/>
+      <c r="H128" s="93" t="inlineStr">
+        <is>
+          <t>{{FIRMA_GERENTE}}</t>
+        </is>
+      </c>
       <c r="K128" s="55" t="n"/>
       <c r="L128" s="93" t="inlineStr">
         <is>
@@ -5880,9 +5882,6 @@
       <c r="E129" s="92" t="n"/>
       <c r="F129" s="92" t="n"/>
       <c r="G129" s="55" t="n"/>
-      <c r="H129" s="92" t="n"/>
-      <c r="I129" s="92" t="n"/>
-      <c r="J129" s="92" t="n"/>
       <c r="K129" s="55" t="n"/>
       <c r="N129" s="55" t="n"/>
       <c r="O129" s="92" t="n"/>
@@ -5897,9 +5896,6 @@
       <c r="E130" s="92" t="n"/>
       <c r="F130" s="92" t="n"/>
       <c r="G130" s="55" t="n"/>
-      <c r="H130" s="92" t="n"/>
-      <c r="I130" s="92" t="n"/>
-      <c r="J130" s="92" t="n"/>
       <c r="K130" s="55" t="n"/>
       <c r="N130" s="55" t="n"/>
       <c r="O130" s="92" t="n"/>
@@ -5914,9 +5910,9 @@
       <c r="E131" s="93" t="n"/>
       <c r="F131" s="93" t="n"/>
       <c r="G131" s="55" t="n"/>
-      <c r="H131" s="93" t="n"/>
-      <c r="I131" s="93" t="n"/>
-      <c r="J131" s="93" t="n"/>
+      <c r="H131" s="329" t="n"/>
+      <c r="I131" s="329" t="n"/>
+      <c r="J131" s="329" t="n"/>
       <c r="K131" s="55" t="n"/>
       <c r="L131" s="329" t="n"/>
       <c r="M131" s="329" t="n"/>
@@ -6034,7 +6030,7 @@
       <c r="R136" s="55" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="205">
+  <mergeCells count="206">
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="D32:I32"/>
     <mergeCell ref="H132:J132"/>
@@ -6078,6 +6074,7 @@
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="D31:I31"/>
     <mergeCell ref="L46:P46"/>
+    <mergeCell ref="H128:J131"/>
     <mergeCell ref="D45:I45"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="L38:O38"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5760" yWindow="348" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="C-9-12" sheetId="1" state="visible" r:id="rId1"/>
@@ -79,9 +79,9 @@
     <definedName name="DUCELEC" localSheetId="0">#REF!</definedName>
     <definedName name="ESPECIALES" localSheetId="0">#REF!</definedName>
     <definedName name="EXP" localSheetId="0">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$135</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$125</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -252,13 +252,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Calibri Light"/>
       <family val="2"/>
       <b val="1"/>
@@ -273,40 +266,39 @@
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="16"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="16"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Open Sans"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="0"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Open Sans"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Open Sans"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Open Sans"/>
+      <b val="1"/>
+      <color rgb="FFE05900"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Open Sans"/>
+      <color theme="0" tint="-0.0499893185216834"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Open Sans"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -366,7 +358,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="89">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -972,19 +964,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
@@ -998,19 +977,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
@@ -1039,35 +1005,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
       <bottom style="thin">
         <color theme="2" tint="-0.249977111117893"/>
       </bottom>
@@ -1107,26 +1049,6 @@
       <top style="thin">
         <color theme="0" tint="-0.499984740745262"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
       <bottom style="thin">
         <color theme="0" tint="-0.499984740745262"/>
       </bottom>
@@ -1143,104 +1065,6 @@
       <bottom style="thin">
         <color theme="0" tint="-0.499984740745262"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
-        <color theme="1" tint="0.0499893185216834"/>
-      </right>
-      <top style="medium">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="0"/>
-      </right>
-      <top style="medium">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="dotted">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
-        <color theme="1" tint="0.0499893185216834"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
-        <color theme="1" tint="0.0499893185216834"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1260,17 +1084,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color theme="1" tint="0.499984740745262"/>
@@ -1311,15 +1124,6 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color theme="0"/>
       </right>
       <top style="thin">
@@ -1347,10 +1151,148 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color theme="1" tint="0.0499893185216834"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color theme="1" tint="0.0499893185216834"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
       </right>
       <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color theme="1" tint="0.0499893185216834"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
         <color theme="0"/>
       </top>
       <bottom/>
@@ -1361,7 +1303,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="333">
+  <cellXfs count="296">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1718,20 +1660,13 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1742,16 +1677,12 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="32" fillId="4" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="27" fillId="4" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1762,307 +1693,77 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="56" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="56" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="50" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="50" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="63" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2083,23 +1784,201 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="66" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2111,6 +1990,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="21" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
@@ -2130,310 +2012,311 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="33" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="69" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="48" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="29" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="48" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="7" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="31" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="31" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="65" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="65" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="87" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="83" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2825,29 +2708,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:W136"/>
+  <dimension ref="B2:W126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.4"/>
   <cols>
-    <col width="3.109375" customWidth="1" style="191" min="1" max="1"/>
-    <col width="2.33203125" customWidth="1" style="191" min="2" max="2"/>
-    <col width="4.88671875" customWidth="1" style="191" min="3" max="3"/>
+    <col width="3.109375" customWidth="1" style="148" min="1" max="1"/>
+    <col width="2.33203125" customWidth="1" style="148" min="2" max="2"/>
+    <col width="4.88671875" customWidth="1" style="148" min="3" max="3"/>
     <col width="11.44140625" bestFit="1" customWidth="1" style="45" min="4" max="4"/>
-    <col width="16.33203125" customWidth="1" style="191" min="5" max="5"/>
-    <col width="13.6640625" customWidth="1" style="191" min="6" max="6"/>
-    <col width="11.44140625" customWidth="1" style="191" min="7" max="7"/>
-    <col width="16.44140625" bestFit="1" customWidth="1" style="191" min="8" max="8"/>
-    <col width="13.33203125" customWidth="1" style="191" min="9" max="10"/>
-    <col width="10.44140625" customWidth="1" style="191" min="11" max="11"/>
-    <col width="19" customWidth="1" style="191" min="12" max="12"/>
-    <col width="16.6640625" bestFit="1" customWidth="1" style="191" min="13" max="13"/>
-    <col width="6.88671875" customWidth="1" style="191" min="14" max="14"/>
-    <col width="16.33203125" customWidth="1" style="191" min="15" max="15"/>
-    <col width="24.109375" bestFit="1" customWidth="1" style="191" min="16" max="16"/>
-    <col width="4.88671875" customWidth="1" style="174" min="17" max="17"/>
-    <col width="2.109375" customWidth="1" style="174" min="18" max="18"/>
-    <col width="2.33203125" customWidth="1" style="191" min="19" max="19"/>
-    <col width="11.44140625" customWidth="1" style="191" min="20" max="20"/>
-    <col width="11.44140625" customWidth="1" style="191" min="21" max="16384"/>
+    <col width="16.33203125" customWidth="1" style="148" min="5" max="5"/>
+    <col width="13.6640625" customWidth="1" style="148" min="6" max="6"/>
+    <col width="11.44140625" customWidth="1" style="148" min="7" max="7"/>
+    <col width="16.44140625" bestFit="1" customWidth="1" style="148" min="8" max="8"/>
+    <col width="13.33203125" customWidth="1" style="148" min="9" max="10"/>
+    <col width="10.44140625" customWidth="1" style="148" min="11" max="11"/>
+    <col width="19" customWidth="1" style="148" min="12" max="12"/>
+    <col width="16.6640625" bestFit="1" customWidth="1" style="148" min="13" max="13"/>
+    <col width="6.88671875" customWidth="1" style="148" min="14" max="14"/>
+    <col width="16.33203125" customWidth="1" style="148" min="15" max="15"/>
+    <col width="24.109375" bestFit="1" customWidth="1" style="148" min="16" max="16"/>
+    <col width="4.88671875" customWidth="1" style="123" min="17" max="17"/>
+    <col width="2.109375" customWidth="1" style="123" min="18" max="18"/>
+    <col width="2.33203125" customWidth="1" style="148" min="19" max="19"/>
+    <col width="11.44140625" customWidth="1" style="148" min="20" max="21"/>
+    <col width="11.44140625" customWidth="1" style="148" min="22" max="16384"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -2874,13 +2757,13 @@
       <c r="C3" s="48" t="n"/>
       <c r="D3" s="49" t="n"/>
       <c r="E3" s="48" t="n"/>
-      <c r="F3" s="239" t="inlineStr">
+      <c r="F3" s="235" t="inlineStr">
         <is>
           <t>PUNTO DE ACTA DE CONTRATO</t>
         </is>
       </c>
       <c r="K3" s="52" t="n"/>
-      <c r="L3" s="239" t="inlineStr">
+      <c r="L3" s="235" t="inlineStr">
         <is>
           <t>PROYECTO</t>
         </is>
@@ -2901,13 +2784,13 @@
       <c r="I4" s="51" t="n"/>
       <c r="J4" s="52" t="n"/>
       <c r="K4" s="52" t="n"/>
-      <c r="L4" s="276" t="inlineStr">
+      <c r="L4" s="169" t="inlineStr">
         <is>
           <t>{{PROYECTO}}</t>
         </is>
       </c>
-      <c r="M4" s="147" t="n"/>
-      <c r="N4" s="147" t="n"/>
+      <c r="M4" s="161" t="n"/>
+      <c r="N4" s="161" t="n"/>
       <c r="O4" s="53" t="n"/>
       <c r="P4" s="52" t="n"/>
       <c r="Q4" s="48" t="n"/>
@@ -2918,23 +2801,23 @@
       <c r="C5" s="48" t="n"/>
       <c r="D5" s="49" t="n"/>
       <c r="E5" s="48" t="n"/>
-      <c r="F5" s="280" t="inlineStr">
+      <c r="F5" s="200" t="inlineStr">
         <is>
           <t>RUBRO</t>
         </is>
       </c>
-      <c r="G5" s="281" t="n"/>
-      <c r="H5" s="253" t="inlineStr">
+      <c r="G5" s="201" t="n"/>
+      <c r="H5" s="165" t="inlineStr">
         <is>
           <t>{{RUBRO}}</t>
         </is>
       </c>
-      <c r="I5" s="254" t="n"/>
-      <c r="J5" s="254" t="n"/>
+      <c r="I5" s="166" t="n"/>
+      <c r="J5" s="166" t="n"/>
       <c r="K5" s="52" t="n"/>
-      <c r="L5" s="147" t="n"/>
-      <c r="M5" s="147" t="n"/>
-      <c r="N5" s="147" t="n"/>
+      <c r="L5" s="161" t="n"/>
+      <c r="M5" s="161" t="n"/>
+      <c r="N5" s="161" t="n"/>
       <c r="O5" s="53" t="n"/>
       <c r="P5" s="52" t="n"/>
       <c r="Q5" s="48" t="n"/>
@@ -2946,30 +2829,30 @@
       <c r="C6" s="48" t="n"/>
       <c r="D6" s="49" t="n"/>
       <c r="E6" s="48" t="n"/>
-      <c r="F6" s="236" t="inlineStr">
+      <c r="F6" s="185" t="inlineStr">
         <is>
           <t>No. CONTRATO</t>
         </is>
       </c>
-      <c r="H6" s="253" t="inlineStr">
+      <c r="H6" s="165" t="inlineStr">
         <is>
           <t>{{NO_CONTRATO}}</t>
         </is>
       </c>
-      <c r="I6" s="254" t="n"/>
-      <c r="J6" s="254" t="n"/>
+      <c r="I6" s="166" t="n"/>
+      <c r="J6" s="166" t="n"/>
       <c r="K6" s="52" t="n"/>
-      <c r="L6" s="286" t="inlineStr">
+      <c r="L6" s="261" t="inlineStr">
         <is>
           <t>TIPO DE CONTRATO</t>
         </is>
       </c>
-      <c r="M6" s="287" t="inlineStr">
+      <c r="M6" s="281" t="inlineStr">
         <is>
           <t>{{TIPO_CONTRATO}}</t>
         </is>
       </c>
-      <c r="N6" s="298" t="n"/>
+      <c r="N6" s="265" t="n"/>
       <c r="O6" s="53" t="n"/>
       <c r="P6" s="52" t="n"/>
       <c r="Q6" s="48" t="n"/>
@@ -2986,8 +2869,8 @@
       <c r="I7" s="57" t="n"/>
       <c r="J7" s="58" t="n"/>
       <c r="K7" s="52" t="n"/>
-      <c r="M7" s="147" t="n"/>
-      <c r="N7" s="147" t="n"/>
+      <c r="M7" s="161" t="n"/>
+      <c r="N7" s="161" t="n"/>
       <c r="O7" s="53" t="n"/>
       <c r="P7" s="52" t="n"/>
       <c r="Q7" s="48" t="n"/>
@@ -2998,21 +2881,21 @@
       <c r="C8" s="48" t="n"/>
       <c r="D8" s="49" t="n"/>
       <c r="E8" s="48" t="n"/>
-      <c r="F8" s="250" t="inlineStr">
+      <c r="F8" s="241" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="H8" s="251" t="inlineStr">
+      <c r="H8" s="245" t="inlineStr">
         <is>
           <t>{{FECHA_ACTA}}</t>
         </is>
       </c>
-      <c r="I8" s="252" t="n"/>
-      <c r="J8" s="252" t="n"/>
+      <c r="I8" s="246" t="n"/>
+      <c r="J8" s="246" t="n"/>
       <c r="K8" s="52" t="n"/>
-      <c r="M8" s="299" t="n"/>
-      <c r="N8" s="299" t="n"/>
+      <c r="M8" s="266" t="n"/>
+      <c r="N8" s="266" t="n"/>
       <c r="O8" s="52" t="n"/>
       <c r="P8" s="52" t="n"/>
       <c r="Q8" s="48" t="n"/>
@@ -3079,28 +2962,28 @@
     <row r="12" ht="21.9" customHeight="1">
       <c r="B12" s="59" t="n"/>
       <c r="C12" s="59" t="n"/>
-      <c r="D12" s="284" t="inlineStr">
+      <c r="D12" s="249" t="inlineStr">
         <is>
           <t>EMPRESA:</t>
         </is>
       </c>
-      <c r="E12" s="285" t="n"/>
-      <c r="F12" s="282" t="inlineStr">
+      <c r="E12" s="250" t="n"/>
+      <c r="F12" s="236" t="inlineStr">
         <is>
           <t>{{EMPRESA}}</t>
         </is>
       </c>
-      <c r="G12" s="283" t="n"/>
-      <c r="H12" s="283" t="n"/>
-      <c r="I12" s="283" t="n"/>
-      <c r="J12" s="283" t="n"/>
+      <c r="G12" s="237" t="n"/>
+      <c r="H12" s="237" t="n"/>
+      <c r="I12" s="237" t="n"/>
+      <c r="J12" s="237" t="n"/>
       <c r="K12" s="65" t="n"/>
-      <c r="L12" s="232" t="inlineStr">
+      <c r="L12" s="167" t="inlineStr">
         <is>
           <t xml:space="preserve">FORMA DE PAGO  </t>
         </is>
       </c>
-      <c r="O12" s="233" t="n"/>
+      <c r="O12" s="168" t="n"/>
       <c r="P12" s="98" t="inlineStr">
         <is>
           <t>PORCENTAJE:</t>
@@ -3112,30 +2995,30 @@
     <row r="13" ht="21.9" customHeight="1">
       <c r="B13" s="59" t="n"/>
       <c r="C13" s="59" t="n"/>
-      <c r="D13" s="237" t="inlineStr">
+      <c r="D13" s="144" t="inlineStr">
         <is>
           <t>CONTACTO:</t>
         </is>
       </c>
-      <c r="E13" s="238" t="n"/>
-      <c r="F13" s="248" t="inlineStr">
+      <c r="E13" s="145" t="n"/>
+      <c r="F13" s="227" t="inlineStr">
         <is>
           <t>{{CONTACTO}}</t>
         </is>
       </c>
-      <c r="G13" s="249" t="n"/>
-      <c r="H13" s="249" t="n"/>
-      <c r="I13" s="249" t="n"/>
-      <c r="J13" s="249" t="n"/>
+      <c r="G13" s="228" t="n"/>
+      <c r="H13" s="228" t="n"/>
+      <c r="I13" s="228" t="n"/>
+      <c r="J13" s="228" t="n"/>
       <c r="K13" s="66" t="n"/>
-      <c r="L13" s="278" t="inlineStr">
+      <c r="L13" s="270" t="inlineStr">
         <is>
           <t>Anticipo</t>
         </is>
       </c>
-      <c r="M13" s="279" t="n"/>
-      <c r="N13" s="279" t="n"/>
-      <c r="O13" s="279" t="n"/>
+      <c r="M13" s="271" t="n"/>
+      <c r="N13" s="271" t="n"/>
+      <c r="O13" s="271" t="n"/>
       <c r="P13" s="6" t="inlineStr">
         <is>
           <t>{{ANTICIPO}}</t>
@@ -3147,30 +3030,30 @@
     <row r="14" ht="21.9" customHeight="1">
       <c r="B14" s="59" t="n"/>
       <c r="C14" s="59" t="n"/>
-      <c r="D14" s="237" t="inlineStr">
+      <c r="D14" s="144" t="inlineStr">
         <is>
           <t>NO. TELEFONO:</t>
         </is>
       </c>
-      <c r="E14" s="238" t="n"/>
-      <c r="F14" s="248" t="inlineStr">
+      <c r="E14" s="145" t="n"/>
+      <c r="F14" s="227" t="inlineStr">
         <is>
           <t>{{TELEFONO}}</t>
         </is>
       </c>
-      <c r="G14" s="249" t="n"/>
-      <c r="H14" s="249" t="n"/>
-      <c r="I14" s="249" t="n"/>
-      <c r="J14" s="249" t="n"/>
+      <c r="G14" s="228" t="n"/>
+      <c r="H14" s="228" t="n"/>
+      <c r="I14" s="228" t="n"/>
+      <c r="J14" s="228" t="n"/>
       <c r="K14" s="67" t="n"/>
-      <c r="L14" s="269" t="inlineStr">
+      <c r="L14" s="170" t="inlineStr">
         <is>
           <t>Estimaciones mensuales / quincenales</t>
         </is>
       </c>
-      <c r="M14" s="270" t="n"/>
-      <c r="N14" s="270" t="n"/>
-      <c r="O14" s="270" t="n"/>
+      <c r="M14" s="171" t="n"/>
+      <c r="N14" s="171" t="n"/>
+      <c r="O14" s="171" t="n"/>
       <c r="P14" s="6" t="inlineStr">
         <is>
           <t>{{ESTIMACIONES}}</t>
@@ -3182,30 +3065,30 @@
     <row r="15" ht="21.9" customHeight="1">
       <c r="B15" s="59" t="n"/>
       <c r="C15" s="59" t="n"/>
-      <c r="D15" s="237" t="inlineStr">
+      <c r="D15" s="144" t="inlineStr">
         <is>
           <t>NO. NIT</t>
         </is>
       </c>
-      <c r="E15" s="238" t="n"/>
-      <c r="F15" s="248" t="inlineStr">
+      <c r="E15" s="145" t="n"/>
+      <c r="F15" s="227" t="inlineStr">
         <is>
           <t>{{NIT}}</t>
         </is>
       </c>
-      <c r="G15" s="249" t="n"/>
-      <c r="H15" s="249" t="n"/>
-      <c r="I15" s="249" t="n"/>
-      <c r="J15" s="249" t="n"/>
+      <c r="G15" s="228" t="n"/>
+      <c r="H15" s="228" t="n"/>
+      <c r="I15" s="228" t="n"/>
+      <c r="J15" s="228" t="n"/>
       <c r="K15" s="55" t="n"/>
-      <c r="L15" s="269" t="inlineStr">
+      <c r="L15" s="170" t="inlineStr">
         <is>
           <t>Contra entrega</t>
         </is>
       </c>
-      <c r="M15" s="270" t="n"/>
-      <c r="N15" s="270" t="n"/>
-      <c r="O15" s="270" t="n"/>
+      <c r="M15" s="171" t="n"/>
+      <c r="N15" s="171" t="n"/>
+      <c r="O15" s="171" t="n"/>
       <c r="P15" s="6" t="inlineStr">
         <is>
           <t>{{CONTRA_ENTREGA}}</t>
@@ -3217,30 +3100,30 @@
     <row r="16" ht="21.9" customHeight="1" thickBot="1">
       <c r="B16" s="59" t="n"/>
       <c r="C16" s="59" t="n"/>
-      <c r="D16" s="277" t="inlineStr">
+      <c r="D16" s="268" t="inlineStr">
         <is>
           <t>NO. COTIZACION</t>
         </is>
       </c>
-      <c r="E16" s="246" t="n"/>
-      <c r="F16" s="275" t="inlineStr">
+      <c r="E16" s="269" t="n"/>
+      <c r="F16" s="260" t="inlineStr">
         <is>
           <t>{{NO_COTIZACION}}</t>
         </is>
       </c>
-      <c r="G16" s="249" t="n"/>
-      <c r="H16" s="249" t="n"/>
-      <c r="I16" s="249" t="n"/>
-      <c r="J16" s="249" t="n"/>
+      <c r="G16" s="228" t="n"/>
+      <c r="H16" s="228" t="n"/>
+      <c r="I16" s="228" t="n"/>
+      <c r="J16" s="228" t="n"/>
       <c r="K16" s="65" t="n"/>
-      <c r="L16" s="269" t="inlineStr">
+      <c r="L16" s="170" t="inlineStr">
         <is>
           <t>Retenido</t>
         </is>
       </c>
-      <c r="M16" s="270" t="n"/>
-      <c r="N16" s="270" t="n"/>
-      <c r="O16" s="270" t="n"/>
+      <c r="M16" s="171" t="n"/>
+      <c r="N16" s="171" t="n"/>
+      <c r="O16" s="171" t="n"/>
       <c r="P16" s="6" t="inlineStr">
         <is>
           <t>{{RETENIDO}}</t>
@@ -3249,14 +3132,14 @@
       <c r="Q16" s="55" t="n"/>
       <c r="R16" s="55" t="n"/>
     </row>
-    <row r="17" ht="18" customFormat="1" customHeight="1" s="174" thickBot="1">
+    <row r="17" ht="18" customFormat="1" customHeight="1" s="123" thickBot="1">
       <c r="B17" s="60" t="n"/>
       <c r="C17" s="60" t="n"/>
       <c r="D17" s="61" t="n"/>
       <c r="E17" s="62" t="n"/>
       <c r="F17" s="63" t="n"/>
       <c r="G17" s="63" t="n"/>
-      <c r="H17" s="212" t="n"/>
+      <c r="H17" s="206" t="n"/>
       <c r="J17" s="64" t="n"/>
       <c r="K17" s="66" t="n"/>
       <c r="L17" s="55" t="n"/>
@@ -3269,58 +3152,58 @@
     <row r="18" ht="21.9" customFormat="1" customHeight="1" s="7" thickBot="1">
       <c r="B18" s="75" t="n"/>
       <c r="C18" s="75" t="n"/>
-      <c r="D18" s="274" t="inlineStr">
+      <c r="D18" s="256" t="inlineStr">
         <is>
           <t>DOCUMENTOS PARA INGRESO DE FACTURA OBLIGATORIOS</t>
         </is>
       </c>
-      <c r="E18" s="205" t="n"/>
-      <c r="F18" s="205" t="n"/>
-      <c r="G18" s="205" t="n"/>
-      <c r="H18" s="205" t="n"/>
-      <c r="I18" s="205" t="n"/>
-      <c r="J18" s="206" t="n"/>
+      <c r="E18" s="138" t="n"/>
+      <c r="F18" s="138" t="n"/>
+      <c r="G18" s="138" t="n"/>
+      <c r="H18" s="138" t="n"/>
+      <c r="I18" s="138" t="n"/>
+      <c r="J18" s="139" t="n"/>
       <c r="K18" s="73" t="n"/>
-      <c r="L18" s="231" t="inlineStr">
+      <c r="L18" s="203" t="inlineStr">
         <is>
           <t>TIEMPOS DE PAGO CON RECEPCION DE FACTURA</t>
         </is>
       </c>
-      <c r="M18" s="205" t="n"/>
-      <c r="N18" s="205" t="n"/>
-      <c r="O18" s="205" t="n"/>
-      <c r="P18" s="206" t="n"/>
+      <c r="M18" s="138" t="n"/>
+      <c r="N18" s="138" t="n"/>
+      <c r="O18" s="138" t="n"/>
+      <c r="P18" s="139" t="n"/>
       <c r="Q18" s="55" t="n"/>
       <c r="R18" s="55" t="n"/>
-      <c r="S18" s="191" t="n"/>
+      <c r="S18" s="148" t="n"/>
     </row>
     <row r="19" ht="21.9" customHeight="1" thickBot="1">
       <c r="B19" s="74" t="n"/>
       <c r="C19" s="74" t="n"/>
-      <c r="D19" s="192" t="inlineStr">
+      <c r="D19" s="125" t="inlineStr">
         <is>
           <t>Contrato firmado por contratista</t>
         </is>
       </c>
-      <c r="E19" s="193" t="n"/>
-      <c r="F19" s="193" t="n"/>
-      <c r="G19" s="193" t="n"/>
-      <c r="H19" s="194" t="n"/>
-      <c r="I19" s="200" t="inlineStr">
+      <c r="E19" s="126" t="n"/>
+      <c r="F19" s="126" t="n"/>
+      <c r="G19" s="126" t="n"/>
+      <c r="H19" s="127" t="n"/>
+      <c r="I19" s="146" t="inlineStr">
         <is>
           <t>para anticipo</t>
         </is>
       </c>
-      <c r="J19" s="193" t="n"/>
+      <c r="J19" s="126" t="n"/>
       <c r="K19" s="55" t="n"/>
-      <c r="L19" s="204" t="inlineStr">
+      <c r="L19" s="137" t="inlineStr">
         <is>
           <t>Anticipo</t>
         </is>
       </c>
-      <c r="M19" s="205" t="n"/>
-      <c r="N19" s="205" t="n"/>
-      <c r="O19" s="206" t="n"/>
+      <c r="M19" s="138" t="n"/>
+      <c r="N19" s="138" t="n"/>
+      <c r="O19" s="139" t="n"/>
       <c r="P19" s="84" t="inlineStr">
         <is>
           <t>15 DIAS</t>
@@ -3332,30 +3215,30 @@
     <row r="20" ht="21.9" customHeight="1" thickBot="1">
       <c r="B20" s="74" t="n"/>
       <c r="C20" s="74" t="n"/>
-      <c r="D20" s="211" t="inlineStr">
+      <c r="D20" s="221" t="inlineStr">
         <is>
           <t>Punto de acta firmado por contratista, genrete E4, lider E4</t>
         </is>
       </c>
-      <c r="E20" s="193" t="n"/>
-      <c r="F20" s="193" t="n"/>
-      <c r="G20" s="193" t="n"/>
-      <c r="H20" s="194" t="n"/>
-      <c r="I20" s="215" t="inlineStr">
+      <c r="E20" s="126" t="n"/>
+      <c r="F20" s="126" t="n"/>
+      <c r="G20" s="126" t="n"/>
+      <c r="H20" s="127" t="n"/>
+      <c r="I20" s="173" t="inlineStr">
         <is>
           <t>para anticipo</t>
         </is>
       </c>
-      <c r="J20" s="193" t="n"/>
+      <c r="J20" s="126" t="n"/>
       <c r="K20" s="55" t="n"/>
-      <c r="L20" s="229" t="inlineStr">
+      <c r="L20" s="226" t="inlineStr">
         <is>
           <t>Estimaciones mensuales / quincenales</t>
         </is>
       </c>
-      <c r="M20" s="205" t="n"/>
-      <c r="N20" s="205" t="n"/>
-      <c r="O20" s="206" t="n"/>
+      <c r="M20" s="138" t="n"/>
+      <c r="N20" s="138" t="n"/>
+      <c r="O20" s="139" t="n"/>
       <c r="P20" s="85" t="inlineStr">
         <is>
           <t>30 DIAS</t>
@@ -3367,30 +3250,30 @@
     <row r="21" ht="21.9" customHeight="1" thickBot="1">
       <c r="B21" s="74" t="n"/>
       <c r="C21" s="74" t="n"/>
-      <c r="D21" s="192" t="inlineStr">
+      <c r="D21" s="125" t="inlineStr">
         <is>
           <t>Factura</t>
         </is>
       </c>
-      <c r="E21" s="193" t="n"/>
-      <c r="F21" s="193" t="n"/>
-      <c r="G21" s="193" t="n"/>
-      <c r="H21" s="194" t="n"/>
-      <c r="I21" s="200" t="inlineStr">
+      <c r="E21" s="126" t="n"/>
+      <c r="F21" s="126" t="n"/>
+      <c r="G21" s="126" t="n"/>
+      <c r="H21" s="127" t="n"/>
+      <c r="I21" s="146" t="inlineStr">
         <is>
           <t>anticipo / estimacion</t>
         </is>
       </c>
-      <c r="J21" s="193" t="n"/>
+      <c r="J21" s="126" t="n"/>
       <c r="K21" s="55" t="n"/>
-      <c r="L21" s="204" t="inlineStr">
+      <c r="L21" s="137" t="inlineStr">
         <is>
           <t>Contra entrega</t>
         </is>
       </c>
-      <c r="M21" s="205" t="n"/>
-      <c r="N21" s="205" t="n"/>
-      <c r="O21" s="206" t="n"/>
+      <c r="M21" s="138" t="n"/>
+      <c r="N21" s="138" t="n"/>
+      <c r="O21" s="139" t="n"/>
       <c r="P21" s="84" t="inlineStr">
         <is>
           <t>30 DIAS</t>
@@ -3402,30 +3285,30 @@
     <row r="22" ht="21.9" customHeight="1" thickBot="1">
       <c r="B22" s="74" t="n"/>
       <c r="C22" s="74" t="n"/>
-      <c r="D22" s="211" t="inlineStr">
+      <c r="D22" s="221" t="inlineStr">
         <is>
           <t>Documento adelanto de pago</t>
         </is>
       </c>
-      <c r="E22" s="193" t="n"/>
-      <c r="F22" s="193" t="n"/>
-      <c r="G22" s="193" t="n"/>
-      <c r="H22" s="194" t="n"/>
-      <c r="I22" s="215" t="inlineStr">
+      <c r="E22" s="126" t="n"/>
+      <c r="F22" s="126" t="n"/>
+      <c r="G22" s="126" t="n"/>
+      <c r="H22" s="127" t="n"/>
+      <c r="I22" s="173" t="inlineStr">
         <is>
           <t>para anticipo</t>
         </is>
       </c>
-      <c r="J22" s="193" t="n"/>
+      <c r="J22" s="126" t="n"/>
       <c r="K22" s="55" t="n"/>
-      <c r="L22" s="242" t="inlineStr">
+      <c r="L22" s="229" t="inlineStr">
         <is>
           <t>Retenido</t>
         </is>
       </c>
-      <c r="M22" s="243" t="n"/>
-      <c r="N22" s="243" t="n"/>
-      <c r="O22" s="244" t="n"/>
+      <c r="M22" s="230" t="n"/>
+      <c r="N22" s="230" t="n"/>
+      <c r="O22" s="231" t="n"/>
       <c r="P22" s="86" t="inlineStr">
         <is>
           <t>3 MESES</t>
@@ -3437,21 +3320,21 @@
     <row r="23" ht="21.9" customHeight="1" thickBot="1">
       <c r="B23" s="74" t="n"/>
       <c r="C23" s="74" t="n"/>
-      <c r="D23" s="192" t="inlineStr">
+      <c r="D23" s="125" t="inlineStr">
         <is>
           <t>Documento de estado de pago</t>
         </is>
       </c>
-      <c r="E23" s="193" t="n"/>
-      <c r="F23" s="193" t="n"/>
-      <c r="G23" s="193" t="n"/>
-      <c r="H23" s="194" t="n"/>
-      <c r="I23" s="200" t="inlineStr">
+      <c r="E23" s="126" t="n"/>
+      <c r="F23" s="126" t="n"/>
+      <c r="G23" s="126" t="n"/>
+      <c r="H23" s="127" t="n"/>
+      <c r="I23" s="146" t="inlineStr">
         <is>
           <t>para estimacion</t>
         </is>
       </c>
-      <c r="J23" s="193" t="n"/>
+      <c r="J23" s="126" t="n"/>
       <c r="K23" s="55" t="n"/>
       <c r="L23" s="82" t="n"/>
       <c r="M23" s="82" t="n"/>
@@ -3464,61 +3347,61 @@
     <row r="24" ht="21.9" customHeight="1" thickBot="1">
       <c r="B24" s="74" t="n"/>
       <c r="C24" s="74" t="n"/>
-      <c r="D24" s="211" t="inlineStr">
+      <c r="D24" s="221" t="inlineStr">
         <is>
           <t>Carta de garantia</t>
         </is>
       </c>
-      <c r="E24" s="193" t="n"/>
-      <c r="F24" s="193" t="n"/>
-      <c r="G24" s="193" t="n"/>
-      <c r="H24" s="194" t="n"/>
-      <c r="I24" s="215" t="inlineStr">
+      <c r="E24" s="126" t="n"/>
+      <c r="F24" s="126" t="n"/>
+      <c r="G24" s="126" t="n"/>
+      <c r="H24" s="127" t="n"/>
+      <c r="I24" s="173" t="inlineStr">
         <is>
           <t>para pago final</t>
         </is>
       </c>
-      <c r="J24" s="193" t="n"/>
+      <c r="J24" s="126" t="n"/>
       <c r="K24" s="55" t="n"/>
-      <c r="L24" s="231" t="inlineStr">
+      <c r="L24" s="203" t="inlineStr">
         <is>
           <t>DÍAS DE INGRESO DE FACTURA</t>
         </is>
       </c>
-      <c r="M24" s="205" t="n"/>
-      <c r="N24" s="205" t="n"/>
-      <c r="O24" s="205" t="n"/>
-      <c r="P24" s="206" t="n"/>
+      <c r="M24" s="138" t="n"/>
+      <c r="N24" s="138" t="n"/>
+      <c r="O24" s="138" t="n"/>
+      <c r="P24" s="139" t="n"/>
       <c r="Q24" s="55" t="n"/>
       <c r="R24" s="55" t="n"/>
     </row>
     <row r="25" ht="39" customHeight="1" thickBot="1">
       <c r="B25" s="74" t="n"/>
       <c r="C25" s="74" t="n"/>
-      <c r="D25" s="192" t="inlineStr">
+      <c r="D25" s="125" t="inlineStr">
         <is>
           <t>Manual de mantenimiento</t>
         </is>
       </c>
-      <c r="E25" s="193" t="n"/>
-      <c r="F25" s="193" t="n"/>
-      <c r="G25" s="193" t="n"/>
-      <c r="H25" s="194" t="n"/>
-      <c r="I25" s="200" t="inlineStr">
+      <c r="E25" s="126" t="n"/>
+      <c r="F25" s="126" t="n"/>
+      <c r="G25" s="126" t="n"/>
+      <c r="H25" s="127" t="n"/>
+      <c r="I25" s="146" t="inlineStr">
         <is>
           <t>para pago final</t>
         </is>
       </c>
-      <c r="J25" s="193" t="n"/>
+      <c r="J25" s="126" t="n"/>
       <c r="K25" s="55" t="n"/>
-      <c r="L25" s="204" t="inlineStr">
+      <c r="L25" s="137" t="inlineStr">
         <is>
           <t>Anticipo / Adelanto de pago</t>
         </is>
       </c>
-      <c r="M25" s="205" t="n"/>
-      <c r="N25" s="205" t="n"/>
-      <c r="O25" s="206" t="n"/>
+      <c r="M25" s="138" t="n"/>
+      <c r="N25" s="138" t="n"/>
+      <c r="O25" s="139" t="n"/>
       <c r="P25" s="84" t="inlineStr">
         <is>
           <t>Lunes de               8:00 AM- 4:00 PM</t>
@@ -3530,26 +3413,26 @@
     <row r="26" ht="39" customHeight="1" thickBot="1">
       <c r="B26" s="74" t="n"/>
       <c r="C26" s="74" t="n"/>
-      <c r="D26" s="210" t="inlineStr">
+      <c r="D26" s="143" t="inlineStr">
         <is>
           <t>TODO DOCUMENTO DE ESTIMACION Y ADELANTO DEBE IR FIRMADO POR EL CONTRATISTA</t>
         </is>
       </c>
-      <c r="E26" s="205" t="n"/>
-      <c r="F26" s="205" t="n"/>
-      <c r="G26" s="205" t="n"/>
-      <c r="H26" s="205" t="n"/>
-      <c r="I26" s="205" t="n"/>
-      <c r="J26" s="205" t="n"/>
+      <c r="E26" s="138" t="n"/>
+      <c r="F26" s="138" t="n"/>
+      <c r="G26" s="138" t="n"/>
+      <c r="H26" s="138" t="n"/>
+      <c r="I26" s="138" t="n"/>
+      <c r="J26" s="138" t="n"/>
       <c r="K26" s="55" t="n"/>
-      <c r="L26" s="229" t="inlineStr">
+      <c r="L26" s="226" t="inlineStr">
         <is>
           <t>Estados de pago / Estimación de avances</t>
         </is>
       </c>
-      <c r="M26" s="205" t="n"/>
-      <c r="N26" s="205" t="n"/>
-      <c r="O26" s="206" t="n"/>
+      <c r="M26" s="138" t="n"/>
+      <c r="N26" s="138" t="n"/>
+      <c r="O26" s="139" t="n"/>
       <c r="P26" s="85" t="inlineStr">
         <is>
           <t>Lunes y Martes de 8:00 AM- 4:00 PM</t>
@@ -3561,22 +3444,22 @@
     <row r="27" ht="39" customHeight="1" thickBot="1">
       <c r="B27" s="74" t="n"/>
       <c r="C27" s="74" t="n"/>
-      <c r="D27" s="222" t="n"/>
-      <c r="E27" s="223" t="n"/>
-      <c r="F27" s="223" t="n"/>
-      <c r="G27" s="223" t="n"/>
-      <c r="H27" s="223" t="n"/>
-      <c r="I27" s="223" t="n"/>
-      <c r="J27" s="223" t="n"/>
+      <c r="D27" s="218" t="n"/>
+      <c r="E27" s="219" t="n"/>
+      <c r="F27" s="219" t="n"/>
+      <c r="G27" s="219" t="n"/>
+      <c r="H27" s="219" t="n"/>
+      <c r="I27" s="219" t="n"/>
+      <c r="J27" s="219" t="n"/>
       <c r="K27" s="55" t="n"/>
-      <c r="L27" s="204" t="inlineStr">
+      <c r="L27" s="137" t="inlineStr">
         <is>
           <t>Pagos de mano de obra</t>
         </is>
       </c>
-      <c r="M27" s="205" t="n"/>
-      <c r="N27" s="205" t="n"/>
-      <c r="O27" s="206" t="n"/>
+      <c r="M27" s="138" t="n"/>
+      <c r="N27" s="138" t="n"/>
+      <c r="O27" s="139" t="n"/>
       <c r="P27" s="84" t="inlineStr">
         <is>
           <t>Lunes de               8:00 AM- 4:00 PM</t>
@@ -3607,56 +3490,56 @@
     <row r="29" ht="21.9" customHeight="1" thickBot="1">
       <c r="B29" s="74" t="n"/>
       <c r="C29" s="74" t="n"/>
-      <c r="D29" s="247" t="inlineStr">
+      <c r="D29" s="262" t="inlineStr">
         <is>
           <t>PUNTOS GENERALES A CUMPLIR EN OBRA</t>
         </is>
       </c>
-      <c r="J29" s="247" t="inlineStr">
+      <c r="J29" s="262" t="inlineStr">
         <is>
           <t>SI / NO</t>
         </is>
       </c>
       <c r="K29" s="55" t="n"/>
-      <c r="L29" s="245" t="inlineStr">
+      <c r="L29" s="272" t="inlineStr">
         <is>
           <t xml:space="preserve">MULTAS A APLICAR </t>
         </is>
       </c>
-      <c r="M29" s="246" t="n"/>
-      <c r="N29" s="246" t="n"/>
-      <c r="O29" s="246" t="n"/>
-      <c r="P29" s="246" t="n"/>
+      <c r="M29" s="269" t="n"/>
+      <c r="N29" s="269" t="n"/>
+      <c r="O29" s="269" t="n"/>
+      <c r="P29" s="269" t="n"/>
       <c r="Q29" s="55" t="n"/>
       <c r="R29" s="55" t="n"/>
     </row>
     <row r="30" ht="21.9" customHeight="1" thickBot="1">
       <c r="B30" s="74" t="n"/>
       <c r="C30" s="74" t="n"/>
-      <c r="D30" s="219" t="inlineStr">
+      <c r="D30" s="215" t="inlineStr">
         <is>
           <t>Llevar bitácora diaria</t>
         </is>
       </c>
-      <c r="E30" s="220" t="n"/>
-      <c r="F30" s="220" t="n"/>
-      <c r="G30" s="220" t="n"/>
-      <c r="H30" s="220" t="n"/>
-      <c r="I30" s="221" t="n"/>
+      <c r="E30" s="216" t="n"/>
+      <c r="F30" s="216" t="n"/>
+      <c r="G30" s="216" t="n"/>
+      <c r="H30" s="216" t="n"/>
+      <c r="I30" s="217" t="n"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K30" s="55" t="n"/>
-      <c r="L30" s="224" t="inlineStr">
+      <c r="L30" s="220" t="inlineStr">
         <is>
           <t>Por atraso de entrega</t>
         </is>
       </c>
-      <c r="M30" s="193" t="n"/>
-      <c r="N30" s="193" t="n"/>
-      <c r="O30" s="196" t="n"/>
+      <c r="M30" s="126" t="n"/>
+      <c r="N30" s="126" t="n"/>
+      <c r="O30" s="180" t="n"/>
       <c r="P30" s="9" t="inlineStr">
         <is>
           <t>1% POR DIA</t>
@@ -3668,30 +3551,30 @@
     <row r="31" ht="21.9" customHeight="1" thickBot="1">
       <c r="B31" s="74" t="n"/>
       <c r="C31" s="74" t="n"/>
-      <c r="D31" s="187" t="inlineStr">
+      <c r="D31" s="124" t="inlineStr">
         <is>
           <t>Encargado de seguridad industrial</t>
         </is>
       </c>
-      <c r="E31" s="188" t="n"/>
-      <c r="F31" s="188" t="n"/>
-      <c r="G31" s="188" t="n"/>
-      <c r="H31" s="188" t="n"/>
-      <c r="I31" s="189" t="n"/>
+      <c r="E31" s="120" t="n"/>
+      <c r="F31" s="120" t="n"/>
+      <c r="G31" s="120" t="n"/>
+      <c r="H31" s="120" t="n"/>
+      <c r="I31" s="121" t="n"/>
       <c r="J31" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K31" s="55" t="n"/>
-      <c r="L31" s="195" t="inlineStr">
+      <c r="L31" s="179" t="inlineStr">
         <is>
           <t>Por orden y limpieza</t>
         </is>
       </c>
-      <c r="M31" s="193" t="n"/>
-      <c r="N31" s="193" t="n"/>
-      <c r="O31" s="196" t="n"/>
+      <c r="M31" s="126" t="n"/>
+      <c r="N31" s="126" t="n"/>
+      <c r="O31" s="180" t="n"/>
       <c r="P31" s="10" t="inlineStr">
         <is>
           <t>Q.25 POR EVENTO</t>
@@ -3703,30 +3586,30 @@
     <row r="32" ht="21.9" customHeight="1" thickBot="1">
       <c r="B32" s="74" t="n"/>
       <c r="C32" s="74" t="n"/>
-      <c r="D32" s="213" t="inlineStr">
+      <c r="D32" s="119" t="inlineStr">
         <is>
           <t>Protocolo de seguridad</t>
         </is>
       </c>
-      <c r="E32" s="188" t="n"/>
-      <c r="F32" s="188" t="n"/>
-      <c r="G32" s="188" t="n"/>
-      <c r="H32" s="188" t="n"/>
-      <c r="I32" s="189" t="n"/>
+      <c r="E32" s="120" t="n"/>
+      <c r="F32" s="120" t="n"/>
+      <c r="G32" s="120" t="n"/>
+      <c r="H32" s="120" t="n"/>
+      <c r="I32" s="121" t="n"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K32" s="55" t="n"/>
-      <c r="L32" s="224" t="inlineStr">
+      <c r="L32" s="220" t="inlineStr">
         <is>
           <t>Por no cumplir con Seguridad Industrial</t>
         </is>
       </c>
-      <c r="M32" s="193" t="n"/>
-      <c r="N32" s="193" t="n"/>
-      <c r="O32" s="196" t="n"/>
+      <c r="M32" s="126" t="n"/>
+      <c r="N32" s="126" t="n"/>
+      <c r="O32" s="180" t="n"/>
       <c r="P32" s="9" t="inlineStr">
         <is>
           <t>Q.50 POR PERSONA</t>
@@ -3738,30 +3621,30 @@
     <row r="33" ht="36.75" customHeight="1">
       <c r="B33" s="74" t="n"/>
       <c r="C33" s="74" t="n"/>
-      <c r="D33" s="187" t="inlineStr">
+      <c r="D33" s="124" t="inlineStr">
         <is>
           <t>Reunión semanal con LIDER DE PROYECTO</t>
         </is>
       </c>
-      <c r="E33" s="188" t="n"/>
-      <c r="F33" s="188" t="n"/>
-      <c r="G33" s="188" t="n"/>
-      <c r="H33" s="188" t="n"/>
-      <c r="I33" s="189" t="n"/>
+      <c r="E33" s="120" t="n"/>
+      <c r="F33" s="120" t="n"/>
+      <c r="G33" s="120" t="n"/>
+      <c r="H33" s="120" t="n"/>
+      <c r="I33" s="121" t="n"/>
       <c r="J33" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K33" s="55" t="n"/>
-      <c r="L33" s="241" t="inlineStr">
+      <c r="L33" s="248" t="inlineStr">
         <is>
           <t>Por no cumplir con documentos de reporteria semanal</t>
         </is>
       </c>
-      <c r="M33" s="198" t="n"/>
-      <c r="N33" s="198" t="n"/>
-      <c r="O33" s="199" t="n"/>
+      <c r="M33" s="182" t="n"/>
+      <c r="N33" s="182" t="n"/>
+      <c r="O33" s="183" t="n"/>
       <c r="P33" s="11" t="inlineStr">
         <is>
           <t>Q.25 POR EVENTO</t>
@@ -3773,16 +3656,16 @@
     <row r="34" ht="21.9" customHeight="1">
       <c r="B34" s="74" t="n"/>
       <c r="C34" s="74" t="n"/>
-      <c r="D34" s="213" t="inlineStr">
+      <c r="D34" s="119" t="inlineStr">
         <is>
           <t>Arq / Ing para supervisar</t>
         </is>
       </c>
-      <c r="E34" s="188" t="n"/>
-      <c r="F34" s="188" t="n"/>
-      <c r="G34" s="188" t="n"/>
-      <c r="H34" s="188" t="n"/>
-      <c r="I34" s="189" t="n"/>
+      <c r="E34" s="120" t="n"/>
+      <c r="F34" s="120" t="n"/>
+      <c r="G34" s="120" t="n"/>
+      <c r="H34" s="120" t="n"/>
+      <c r="I34" s="121" t="n"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
           <t>SI</t>
@@ -3800,23 +3683,23 @@
     <row r="35" ht="21.9" customHeight="1">
       <c r="B35" s="74" t="n"/>
       <c r="C35" s="74" t="n"/>
-      <c r="D35" s="216" t="inlineStr">
+      <c r="D35" s="211" t="inlineStr">
         <is>
           <t>Encargado técnico de supervisión (maestro de obras, etc)</t>
         </is>
       </c>
-      <c r="E35" s="217" t="n"/>
-      <c r="F35" s="217" t="n"/>
-      <c r="G35" s="217" t="n"/>
-      <c r="H35" s="217" t="n"/>
-      <c r="I35" s="218" t="n"/>
+      <c r="E35" s="212" t="n"/>
+      <c r="F35" s="212" t="n"/>
+      <c r="G35" s="212" t="n"/>
+      <c r="H35" s="212" t="n"/>
+      <c r="I35" s="213" t="n"/>
       <c r="J35" s="18" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K35" s="55" t="n"/>
-      <c r="L35" s="228" t="inlineStr">
+      <c r="L35" s="159" t="inlineStr">
         <is>
           <t>DOCUMENTO ENTREGADOS A CONTRATISTA POR PARTE DE E4</t>
         </is>
@@ -3835,14 +3718,14 @@
       <c r="I36" s="19" t="n"/>
       <c r="J36" s="19" t="n"/>
       <c r="K36" s="55" t="n"/>
-      <c r="L36" s="207" t="inlineStr">
+      <c r="L36" s="140" t="inlineStr">
         <is>
           <t>Cronograma de obra</t>
         </is>
       </c>
-      <c r="M36" s="208" t="n"/>
-      <c r="N36" s="208" t="n"/>
-      <c r="O36" s="209" t="n"/>
+      <c r="M36" s="141" t="n"/>
+      <c r="N36" s="141" t="n"/>
+      <c r="O36" s="142" t="n"/>
       <c r="P36" s="20" t="inlineStr">
         <is>
           <t>X</t>
@@ -3854,25 +3737,25 @@
     <row r="37" ht="21.9" customHeight="1" thickBot="1">
       <c r="B37" s="74" t="n"/>
       <c r="C37" s="74" t="n"/>
-      <c r="D37" s="247" t="inlineStr">
+      <c r="D37" s="262" t="inlineStr">
         <is>
           <t>PLANOS ENTREGADOS A CONTRATISTA</t>
         </is>
       </c>
-      <c r="J37" s="247" t="inlineStr">
+      <c r="J37" s="262" t="inlineStr">
         <is>
           <t>SI / NO</t>
         </is>
       </c>
       <c r="K37" s="55" t="n"/>
-      <c r="L37" s="211" t="inlineStr">
+      <c r="L37" s="221" t="inlineStr">
         <is>
           <t>Politica de recepcion de facturas y pagos</t>
         </is>
       </c>
-      <c r="M37" s="193" t="n"/>
-      <c r="N37" s="193" t="n"/>
-      <c r="O37" s="194" t="n"/>
+      <c r="M37" s="126" t="n"/>
+      <c r="N37" s="126" t="n"/>
+      <c r="O37" s="127" t="n"/>
       <c r="P37" s="10" t="inlineStr">
         <is>
           <t>X</t>
@@ -3884,30 +3767,30 @@
     <row r="38" ht="21.9" customHeight="1" thickBot="1">
       <c r="B38" s="74" t="n"/>
       <c r="C38" s="74" t="n"/>
-      <c r="D38" s="219" t="inlineStr">
+      <c r="D38" s="215" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
-      <c r="E38" s="220" t="n"/>
-      <c r="F38" s="220" t="n"/>
-      <c r="G38" s="220" t="n"/>
-      <c r="H38" s="220" t="n"/>
-      <c r="I38" s="221" t="n"/>
+      <c r="E38" s="216" t="n"/>
+      <c r="F38" s="216" t="n"/>
+      <c r="G38" s="216" t="n"/>
+      <c r="H38" s="216" t="n"/>
+      <c r="I38" s="217" t="n"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K38" s="55" t="n"/>
-      <c r="L38" s="192" t="inlineStr">
+      <c r="L38" s="125" t="inlineStr">
         <is>
           <t>Politica de SSO en obra</t>
         </is>
       </c>
-      <c r="M38" s="193" t="n"/>
-      <c r="N38" s="193" t="n"/>
-      <c r="O38" s="194" t="n"/>
+      <c r="M38" s="126" t="n"/>
+      <c r="N38" s="126" t="n"/>
+      <c r="O38" s="127" t="n"/>
       <c r="P38" s="9" t="inlineStr">
         <is>
           <t>X</t>
@@ -3919,30 +3802,30 @@
     <row r="39" ht="21.9" customHeight="1" thickBot="1">
       <c r="B39" s="74" t="n"/>
       <c r="C39" s="74" t="n"/>
-      <c r="D39" s="187" t="inlineStr">
+      <c r="D39" s="124" t="inlineStr">
         <is>
           <t>Cotas</t>
         </is>
       </c>
-      <c r="E39" s="188" t="n"/>
-      <c r="F39" s="188" t="n"/>
-      <c r="G39" s="188" t="n"/>
-      <c r="H39" s="188" t="n"/>
-      <c r="I39" s="189" t="n"/>
+      <c r="E39" s="120" t="n"/>
+      <c r="F39" s="120" t="n"/>
+      <c r="G39" s="120" t="n"/>
+      <c r="H39" s="120" t="n"/>
+      <c r="I39" s="121" t="n"/>
       <c r="J39" s="13" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K39" s="55" t="n"/>
-      <c r="L39" s="211" t="inlineStr">
+      <c r="L39" s="221" t="inlineStr">
         <is>
           <t>Plan de pagos</t>
         </is>
       </c>
-      <c r="M39" s="193" t="n"/>
-      <c r="N39" s="193" t="n"/>
-      <c r="O39" s="194" t="n"/>
+      <c r="M39" s="126" t="n"/>
+      <c r="N39" s="126" t="n"/>
+      <c r="O39" s="127" t="n"/>
       <c r="P39" s="10" t="inlineStr">
         <is>
           <t>X</t>
@@ -3954,30 +3837,30 @@
     <row r="40" ht="21.9" customHeight="1">
       <c r="B40" s="74" t="n"/>
       <c r="C40" s="74" t="n"/>
-      <c r="D40" s="213" t="inlineStr">
+      <c r="D40" s="119" t="inlineStr">
         <is>
           <t>Elevaciones y secciones</t>
         </is>
       </c>
-      <c r="E40" s="188" t="n"/>
-      <c r="F40" s="188" t="n"/>
-      <c r="G40" s="188" t="n"/>
-      <c r="H40" s="188" t="n"/>
-      <c r="I40" s="189" t="n"/>
+      <c r="E40" s="120" t="n"/>
+      <c r="F40" s="120" t="n"/>
+      <c r="G40" s="120" t="n"/>
+      <c r="H40" s="120" t="n"/>
+      <c r="I40" s="121" t="n"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K40" s="55" t="n"/>
-      <c r="L40" s="197" t="inlineStr">
+      <c r="L40" s="181" t="inlineStr">
         <is>
           <t>Planos actualizados</t>
         </is>
       </c>
-      <c r="M40" s="198" t="n"/>
-      <c r="N40" s="198" t="n"/>
-      <c r="O40" s="199" t="n"/>
+      <c r="M40" s="182" t="n"/>
+      <c r="N40" s="182" t="n"/>
+      <c r="O40" s="183" t="n"/>
       <c r="P40" s="21" t="inlineStr">
         <is>
           <t>X</t>
@@ -3989,16 +3872,16 @@
     <row r="41" ht="21.9" customHeight="1">
       <c r="B41" s="74" t="n"/>
       <c r="C41" s="74" t="n"/>
-      <c r="D41" s="187" t="inlineStr">
+      <c r="D41" s="124" t="inlineStr">
         <is>
           <t>Hidrosanitarias</t>
         </is>
       </c>
-      <c r="E41" s="188" t="n"/>
-      <c r="F41" s="188" t="n"/>
-      <c r="G41" s="188" t="n"/>
-      <c r="H41" s="188" t="n"/>
-      <c r="I41" s="189" t="n"/>
+      <c r="E41" s="120" t="n"/>
+      <c r="F41" s="120" t="n"/>
+      <c r="G41" s="120" t="n"/>
+      <c r="H41" s="120" t="n"/>
+      <c r="I41" s="121" t="n"/>
       <c r="J41" s="13" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4016,16 +3899,16 @@
     <row r="42" ht="21.9" customHeight="1">
       <c r="B42" s="74" t="n"/>
       <c r="C42" s="74" t="n"/>
-      <c r="D42" s="213" t="inlineStr">
+      <c r="D42" s="119" t="inlineStr">
         <is>
           <t>Electricidad</t>
         </is>
       </c>
-      <c r="E42" s="188" t="n"/>
-      <c r="F42" s="188" t="n"/>
-      <c r="G42" s="188" t="n"/>
-      <c r="H42" s="188" t="n"/>
-      <c r="I42" s="189" t="n"/>
+      <c r="E42" s="120" t="n"/>
+      <c r="F42" s="120" t="n"/>
+      <c r="G42" s="120" t="n"/>
+      <c r="H42" s="120" t="n"/>
+      <c r="I42" s="121" t="n"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4043,16 +3926,16 @@
     <row r="43" ht="21.9" customHeight="1">
       <c r="B43" s="74" t="n"/>
       <c r="C43" s="74" t="n"/>
-      <c r="D43" s="187" t="inlineStr">
+      <c r="D43" s="124" t="inlineStr">
         <is>
           <t>Acabados</t>
         </is>
       </c>
-      <c r="E43" s="188" t="n"/>
-      <c r="F43" s="188" t="n"/>
-      <c r="G43" s="188" t="n"/>
-      <c r="H43" s="188" t="n"/>
-      <c r="I43" s="189" t="n"/>
+      <c r="E43" s="120" t="n"/>
+      <c r="F43" s="120" t="n"/>
+      <c r="G43" s="120" t="n"/>
+      <c r="H43" s="120" t="n"/>
+      <c r="I43" s="121" t="n"/>
       <c r="J43" s="13" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4070,16 +3953,16 @@
     <row r="44" ht="21.9" customHeight="1">
       <c r="B44" s="74" t="n"/>
       <c r="C44" s="74" t="n"/>
-      <c r="D44" s="219" t="inlineStr">
+      <c r="D44" s="215" t="inlineStr">
         <is>
           <t>Estructura principal</t>
         </is>
       </c>
-      <c r="E44" s="220" t="n"/>
-      <c r="F44" s="220" t="n"/>
-      <c r="G44" s="220" t="n"/>
-      <c r="H44" s="220" t="n"/>
-      <c r="I44" s="221" t="n"/>
+      <c r="E44" s="216" t="n"/>
+      <c r="F44" s="216" t="n"/>
+      <c r="G44" s="216" t="n"/>
+      <c r="H44" s="216" t="n"/>
+      <c r="I44" s="217" t="n"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4097,16 +3980,16 @@
     <row r="45" ht="21.9" customHeight="1">
       <c r="B45" s="74" t="n"/>
       <c r="C45" s="74" t="n"/>
-      <c r="D45" s="187" t="inlineStr">
+      <c r="D45" s="124" t="inlineStr">
         <is>
           <t>Estructura secundaria</t>
         </is>
       </c>
-      <c r="E45" s="188" t="n"/>
-      <c r="F45" s="188" t="n"/>
-      <c r="G45" s="188" t="n"/>
-      <c r="H45" s="188" t="n"/>
-      <c r="I45" s="189" t="n"/>
+      <c r="E45" s="120" t="n"/>
+      <c r="F45" s="120" t="n"/>
+      <c r="G45" s="120" t="n"/>
+      <c r="H45" s="120" t="n"/>
+      <c r="I45" s="121" t="n"/>
       <c r="J45" s="13" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4124,23 +4007,23 @@
     <row r="46" ht="21.9" customHeight="1">
       <c r="B46" s="74" t="n"/>
       <c r="C46" s="74" t="n"/>
-      <c r="D46" s="255" t="inlineStr">
+      <c r="D46" s="278" t="inlineStr">
         <is>
           <t>Obras secundarias</t>
         </is>
       </c>
-      <c r="E46" s="217" t="n"/>
-      <c r="F46" s="217" t="n"/>
-      <c r="G46" s="217" t="n"/>
-      <c r="H46" s="217" t="n"/>
-      <c r="I46" s="218" t="n"/>
+      <c r="E46" s="212" t="n"/>
+      <c r="F46" s="212" t="n"/>
+      <c r="G46" s="212" t="n"/>
+      <c r="H46" s="212" t="n"/>
+      <c r="I46" s="213" t="n"/>
       <c r="J46" s="22" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="K46" s="55" t="n"/>
-      <c r="L46" s="190" t="inlineStr">
+      <c r="L46" s="174" t="inlineStr">
         <is>
           <t>FIRMA - Proveedor o contratista</t>
         </is>
@@ -4148,7 +4031,7 @@
       <c r="Q46" s="55" t="n"/>
       <c r="R46" s="55" t="n"/>
     </row>
-    <row r="47" ht="23.1" customFormat="1" customHeight="1" s="174" thickBot="1">
+    <row r="47" ht="23.1" customFormat="1" customHeight="1" s="123" thickBot="1">
       <c r="B47" s="74" t="n"/>
       <c r="C47" s="74" t="n"/>
       <c r="D47" s="55" t="n"/>
@@ -4170,23 +4053,23 @@
     <row r="48" ht="21.9" customHeight="1" thickTop="1">
       <c r="B48" s="74" t="n"/>
       <c r="C48" s="76" t="n"/>
-      <c r="D48" s="225" t="inlineStr">
+      <c r="D48" s="223" t="inlineStr">
         <is>
           <t xml:space="preserve">ALCANCES COTIZACIÓN DEL PROVEEDOR </t>
         </is>
       </c>
-      <c r="E48" s="226" t="n"/>
-      <c r="F48" s="226" t="n"/>
-      <c r="G48" s="226" t="n"/>
-      <c r="H48" s="226" t="n"/>
-      <c r="I48" s="226" t="n"/>
-      <c r="J48" s="226" t="n"/>
-      <c r="K48" s="226" t="n"/>
-      <c r="L48" s="226" t="n"/>
-      <c r="M48" s="226" t="n"/>
-      <c r="N48" s="226" t="n"/>
-      <c r="O48" s="226" t="n"/>
-      <c r="P48" s="227" t="n"/>
+      <c r="E48" s="224" t="n"/>
+      <c r="F48" s="224" t="n"/>
+      <c r="G48" s="224" t="n"/>
+      <c r="H48" s="224" t="n"/>
+      <c r="I48" s="224" t="n"/>
+      <c r="J48" s="224" t="n"/>
+      <c r="K48" s="224" t="n"/>
+      <c r="L48" s="224" t="n"/>
+      <c r="M48" s="224" t="n"/>
+      <c r="N48" s="224" t="n"/>
+      <c r="O48" s="224" t="n"/>
+      <c r="P48" s="225" t="n"/>
       <c r="Q48" s="55" t="n"/>
       <c r="R48" s="55" t="n"/>
       <c r="T48" s="97" t="inlineStr">
@@ -4195,222 +4078,222 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="21.9" customFormat="1" customHeight="1" s="137">
+    <row r="49" ht="21.9" customFormat="1" customHeight="1" s="198">
       <c r="B49" s="76" t="n"/>
       <c r="C49" s="76" t="n"/>
-      <c r="D49" s="136" t="inlineStr">
+      <c r="D49" s="154" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E49" s="136" t="inlineStr">
+      <c r="E49" s="154" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="K49" s="136" t="inlineStr">
+      <c r="K49" s="154" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="L49" s="136" t="inlineStr">
+      <c r="L49" s="154" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="M49" s="136" t="inlineStr">
+      <c r="M49" s="154" t="inlineStr">
         <is>
           <t>P. Unitario</t>
         </is>
       </c>
-      <c r="N49" s="136" t="inlineStr">
+      <c r="N49" s="154" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="P49" s="136" t="inlineStr">
+      <c r="P49" s="154" t="inlineStr">
         <is>
           <t>COMENTARIOS</t>
         </is>
       </c>
       <c r="Q49" s="71" t="n"/>
       <c r="R49" s="71" t="n"/>
-      <c r="T49" s="191" t="n"/>
+      <c r="T49" s="148" t="n"/>
     </row>
     <row r="50" ht="69.90000000000001" customHeight="1">
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="23" t="n"/>
-      <c r="D50" s="25" t="n"/>
-      <c r="E50" s="234" t="n"/>
-      <c r="F50" s="147" t="n"/>
-      <c r="G50" s="147" t="n"/>
-      <c r="H50" s="147" t="n"/>
-      <c r="I50" s="147" t="n"/>
-      <c r="J50" s="139" t="n"/>
+      <c r="D50" s="293" t="n"/>
+      <c r="E50" s="247" t="n"/>
+      <c r="F50" s="161" t="n"/>
+      <c r="G50" s="161" t="n"/>
+      <c r="H50" s="161" t="n"/>
+      <c r="I50" s="161" t="n"/>
+      <c r="J50" s="133" t="n"/>
       <c r="K50" s="26" t="n"/>
       <c r="L50" s="27" t="n"/>
       <c r="M50" s="28" t="n"/>
-      <c r="N50" s="138" t="n"/>
-      <c r="O50" s="139" t="n"/>
+      <c r="N50" s="184" t="n"/>
+      <c r="O50" s="133" t="n"/>
       <c r="P50" s="29" t="n"/>
     </row>
     <row r="51" ht="68.09999999999999" customHeight="1">
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="23" t="n"/>
-      <c r="D51" s="30" t="n"/>
-      <c r="E51" s="146" t="n"/>
-      <c r="F51" s="147" t="n"/>
-      <c r="G51" s="147" t="n"/>
-      <c r="H51" s="147" t="n"/>
-      <c r="I51" s="147" t="n"/>
-      <c r="J51" s="139" t="n"/>
+      <c r="D51" s="294" t="n"/>
+      <c r="E51" s="178" t="n"/>
+      <c r="F51" s="161" t="n"/>
+      <c r="G51" s="161" t="n"/>
+      <c r="H51" s="161" t="n"/>
+      <c r="I51" s="161" t="n"/>
+      <c r="J51" s="133" t="n"/>
       <c r="K51" s="31" t="n"/>
       <c r="L51" s="32" t="n"/>
       <c r="M51" s="33" t="n"/>
-      <c r="N51" s="170" t="n"/>
-      <c r="O51" s="139" t="n"/>
+      <c r="N51" s="132" t="n"/>
+      <c r="O51" s="133" t="n"/>
       <c r="P51" s="34" t="n"/>
     </row>
     <row r="52" ht="68.09999999999999" customHeight="1">
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="23" t="n"/>
-      <c r="D52" s="25" t="n"/>
-      <c r="E52" s="234" t="n"/>
-      <c r="F52" s="147" t="n"/>
-      <c r="G52" s="147" t="n"/>
-      <c r="H52" s="147" t="n"/>
-      <c r="I52" s="147" t="n"/>
-      <c r="J52" s="139" t="n"/>
+      <c r="D52" s="293" t="n"/>
+      <c r="E52" s="247" t="n"/>
+      <c r="F52" s="161" t="n"/>
+      <c r="G52" s="161" t="n"/>
+      <c r="H52" s="161" t="n"/>
+      <c r="I52" s="161" t="n"/>
+      <c r="J52" s="133" t="n"/>
       <c r="K52" s="26" t="n"/>
       <c r="L52" s="27" t="n"/>
       <c r="M52" s="28" t="n"/>
-      <c r="N52" s="138" t="n"/>
-      <c r="O52" s="139" t="n"/>
+      <c r="N52" s="184" t="n"/>
+      <c r="O52" s="133" t="n"/>
       <c r="P52" s="29" t="n"/>
     </row>
     <row r="53" ht="69.90000000000001" customHeight="1">
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="23" t="n"/>
-      <c r="D53" s="30" t="n"/>
-      <c r="E53" s="146" t="n"/>
-      <c r="F53" s="147" t="n"/>
-      <c r="G53" s="147" t="n"/>
-      <c r="H53" s="147" t="n"/>
-      <c r="I53" s="147" t="n"/>
-      <c r="J53" s="139" t="n"/>
+      <c r="D53" s="294" t="n"/>
+      <c r="E53" s="178" t="n"/>
+      <c r="F53" s="161" t="n"/>
+      <c r="G53" s="161" t="n"/>
+      <c r="H53" s="161" t="n"/>
+      <c r="I53" s="161" t="n"/>
+      <c r="J53" s="133" t="n"/>
       <c r="K53" s="31" t="n"/>
       <c r="L53" s="32" t="n"/>
       <c r="M53" s="33" t="n"/>
-      <c r="N53" s="170" t="n"/>
-      <c r="O53" s="139" t="n"/>
+      <c r="N53" s="132" t="n"/>
+      <c r="O53" s="133" t="n"/>
       <c r="P53" s="34" t="n"/>
     </row>
     <row r="54" ht="69.90000000000001" customHeight="1">
       <c r="B54" s="23" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="234" t="n"/>
-      <c r="F54" s="147" t="n"/>
-      <c r="G54" s="147" t="n"/>
-      <c r="H54" s="147" t="n"/>
-      <c r="I54" s="147" t="n"/>
-      <c r="J54" s="139" t="n"/>
+      <c r="D54" s="293" t="n"/>
+      <c r="E54" s="247" t="n"/>
+      <c r="F54" s="161" t="n"/>
+      <c r="G54" s="161" t="n"/>
+      <c r="H54" s="161" t="n"/>
+      <c r="I54" s="161" t="n"/>
+      <c r="J54" s="133" t="n"/>
       <c r="K54" s="26" t="n"/>
       <c r="L54" s="27" t="n"/>
       <c r="M54" s="28" t="n"/>
-      <c r="N54" s="138" t="n"/>
-      <c r="O54" s="139" t="n"/>
+      <c r="N54" s="184" t="n"/>
+      <c r="O54" s="133" t="n"/>
       <c r="P54" s="29" t="n"/>
     </row>
     <row r="55" ht="66.90000000000001" customHeight="1">
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="23" t="n"/>
-      <c r="D55" s="30" t="n"/>
-      <c r="E55" s="146" t="n"/>
-      <c r="F55" s="147" t="n"/>
-      <c r="G55" s="147" t="n"/>
-      <c r="H55" s="147" t="n"/>
-      <c r="I55" s="147" t="n"/>
-      <c r="J55" s="139" t="n"/>
+      <c r="D55" s="294" t="n"/>
+      <c r="E55" s="178" t="n"/>
+      <c r="F55" s="161" t="n"/>
+      <c r="G55" s="161" t="n"/>
+      <c r="H55" s="161" t="n"/>
+      <c r="I55" s="161" t="n"/>
+      <c r="J55" s="133" t="n"/>
       <c r="K55" s="31" t="n"/>
       <c r="L55" s="32" t="n"/>
       <c r="M55" s="33" t="n"/>
-      <c r="N55" s="170" t="n"/>
-      <c r="O55" s="139" t="n"/>
+      <c r="N55" s="132" t="n"/>
+      <c r="O55" s="133" t="n"/>
       <c r="P55" s="34" t="n"/>
     </row>
     <row r="56" ht="21.9" customHeight="1">
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="23" t="n"/>
-      <c r="D56" s="174" t="n"/>
-      <c r="E56" s="174" t="n"/>
-      <c r="F56" s="174" t="n"/>
-      <c r="G56" s="174" t="n"/>
-      <c r="H56" s="174" t="n"/>
-      <c r="I56" s="174" t="n"/>
-      <c r="J56" s="174" t="n"/>
-      <c r="K56" s="174" t="n"/>
-      <c r="L56" s="174" t="n"/>
+      <c r="D56" s="123" t="n"/>
+      <c r="E56" s="123" t="n"/>
+      <c r="F56" s="123" t="n"/>
+      <c r="G56" s="123" t="n"/>
+      <c r="H56" s="123" t="n"/>
+      <c r="I56" s="123" t="n"/>
+      <c r="J56" s="123" t="n"/>
+      <c r="K56" s="123" t="n"/>
+      <c r="L56" s="123" t="n"/>
       <c r="M56" s="95" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="N56" s="144">
+      <c r="N56" s="233">
         <f>SUM(N50:N55)</f>
         <v/>
       </c>
-      <c r="O56" s="145" t="n"/>
-      <c r="P56" s="174" t="n"/>
+      <c r="O56" s="234" t="n"/>
+      <c r="P56" s="123" t="n"/>
     </row>
     <row r="57" ht="21.9" customHeight="1" thickBot="1">
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="23" t="n"/>
-      <c r="D57" s="174" t="n"/>
-      <c r="E57" s="174" t="n"/>
-      <c r="F57" s="174" t="n"/>
-      <c r="G57" s="174" t="n"/>
-      <c r="H57" s="174" t="n"/>
-      <c r="I57" s="174" t="n"/>
-      <c r="J57" s="174" t="n"/>
-      <c r="K57" s="174" t="n"/>
-      <c r="L57" s="174" t="n"/>
+      <c r="D57" s="123" t="n"/>
+      <c r="E57" s="123" t="n"/>
+      <c r="F57" s="123" t="n"/>
+      <c r="G57" s="123" t="n"/>
+      <c r="H57" s="123" t="n"/>
+      <c r="I57" s="123" t="n"/>
+      <c r="J57" s="123" t="n"/>
+      <c r="K57" s="123" t="n"/>
+      <c r="L57" s="123" t="n"/>
       <c r="M57" s="96" t="inlineStr">
         <is>
           <t>IVA</t>
         </is>
       </c>
-      <c r="N57" s="178">
+      <c r="N57" s="274">
         <f>+N56*0.12</f>
         <v/>
       </c>
-      <c r="O57" s="179" t="n"/>
-      <c r="P57" s="174" t="n"/>
+      <c r="O57" s="275" t="n"/>
+      <c r="P57" s="123" t="n"/>
     </row>
     <row r="58" ht="21.9" customHeight="1" thickTop="1">
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="23" t="n"/>
-      <c r="D58" s="174" t="n"/>
-      <c r="E58" s="174" t="n"/>
-      <c r="F58" s="174" t="n"/>
-      <c r="G58" s="174" t="n"/>
-      <c r="H58" s="174" t="n"/>
-      <c r="I58" s="174" t="n"/>
-      <c r="J58" s="174" t="n"/>
-      <c r="K58" s="174" t="n"/>
-      <c r="L58" s="174" t="n"/>
+      <c r="D58" s="123" t="n"/>
+      <c r="E58" s="123" t="n"/>
+      <c r="F58" s="123" t="n"/>
+      <c r="G58" s="123" t="n"/>
+      <c r="H58" s="123" t="n"/>
+      <c r="I58" s="123" t="n"/>
+      <c r="J58" s="123" t="n"/>
+      <c r="K58" s="123" t="n"/>
+      <c r="L58" s="123" t="n"/>
       <c r="M58" s="95" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="N58" s="272">
+      <c r="N58" s="240">
         <f>+N57+N56</f>
         <v/>
       </c>
-      <c r="O58" s="147" t="n"/>
-      <c r="P58" s="174" t="n"/>
-    </row>
-    <row r="59" ht="11.1" customFormat="1" customHeight="1" s="174">
+      <c r="O58" s="161" t="n"/>
+      <c r="P58" s="123" t="n"/>
+    </row>
+    <row r="59" ht="11.1" customFormat="1" customHeight="1" s="123">
       <c r="B59" s="74" t="n"/>
       <c r="C59" s="74" t="n"/>
       <c r="D59" s="55" t="n"/>
@@ -4432,7 +4315,7 @@
     <row r="60" ht="21" customHeight="1">
       <c r="B60" s="74" t="n"/>
       <c r="C60" s="74" t="n"/>
-      <c r="D60" s="180" t="inlineStr">
+      <c r="D60" s="282" t="inlineStr">
         <is>
           <t>PROGRAMACIÓN DE FECHAS</t>
         </is>
@@ -4440,42 +4323,42 @@
       <c r="Q60" s="56" t="n"/>
       <c r="R60" s="56" t="n"/>
     </row>
-    <row r="61" customFormat="1" s="174">
+    <row r="61" customFormat="1" s="123">
       <c r="B61" s="74" t="n"/>
       <c r="C61" s="74" t="n"/>
-      <c r="D61" s="230" t="inlineStr">
+      <c r="D61" s="283" t="inlineStr">
         <is>
           <t>ÁREA</t>
         </is>
       </c>
-      <c r="E61" s="300" t="n"/>
-      <c r="F61" s="301" t="n"/>
-      <c r="G61" s="153" t="inlineStr">
+      <c r="E61" s="258" t="n"/>
+      <c r="F61" s="259" t="n"/>
+      <c r="G61" s="284" t="inlineStr">
         <is>
           <t>INICIO</t>
         </is>
       </c>
-      <c r="H61" s="302" t="n"/>
-      <c r="I61" s="161" t="inlineStr">
+      <c r="H61" s="191" t="n"/>
+      <c r="I61" s="285" t="inlineStr">
         <is>
           <t>TERMINA</t>
         </is>
       </c>
-      <c r="J61" s="303" t="n"/>
-      <c r="K61" s="304" t="inlineStr">
+      <c r="J61" s="194" t="n"/>
+      <c r="K61" s="286" t="inlineStr">
         <is>
           <t>DIAS</t>
         </is>
       </c>
-      <c r="L61" s="305" t="n"/>
-      <c r="M61" s="304" t="inlineStr">
+      <c r="L61" s="118" t="n"/>
+      <c r="M61" s="286" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="N61" s="306" t="n"/>
-      <c r="O61" s="306" t="n"/>
-      <c r="P61" s="305" t="n"/>
+      <c r="N61" s="117" t="n"/>
+      <c r="O61" s="117" t="n"/>
+      <c r="P61" s="118" t="n"/>
       <c r="Q61" s="56" t="n"/>
       <c r="R61" s="56" t="n"/>
       <c r="U61" s="35" t="n"/>
@@ -4485,23 +4368,23 @@
     <row r="62" ht="21.6" customHeight="1">
       <c r="B62" s="74" t="n"/>
       <c r="C62" s="74" t="n"/>
-      <c r="D62" s="140" t="inlineStr">
+      <c r="D62" s="263" t="inlineStr">
         <is>
           <t>{{PROGRAMACION}}</t>
         </is>
       </c>
-      <c r="E62" s="307" t="n"/>
-      <c r="F62" s="308" t="n"/>
-      <c r="G62" s="155" t="n"/>
-      <c r="H62" s="309" t="n"/>
-      <c r="I62" s="310" t="n"/>
-      <c r="J62" s="311" t="n"/>
-      <c r="K62" s="312" t="n"/>
-      <c r="L62" s="313" t="n"/>
-      <c r="M62" s="141" t="n"/>
-      <c r="N62" s="307" t="n"/>
-      <c r="O62" s="307" t="n"/>
-      <c r="P62" s="308" t="n"/>
+      <c r="E62" s="187" t="n"/>
+      <c r="F62" s="188" t="n"/>
+      <c r="G62" s="204" t="n"/>
+      <c r="H62" s="129" t="n"/>
+      <c r="I62" s="243" t="n"/>
+      <c r="J62" s="244" t="n"/>
+      <c r="K62" s="279" t="n"/>
+      <c r="L62" s="280" t="n"/>
+      <c r="M62" s="189" t="n"/>
+      <c r="N62" s="187" t="n"/>
+      <c r="O62" s="187" t="n"/>
+      <c r="P62" s="188" t="n"/>
       <c r="Q62" s="56" t="n"/>
       <c r="R62" s="56" t="n"/>
       <c r="U62" s="35" t="n"/>
@@ -4511,19 +4394,19 @@
     <row r="63" ht="21" customHeight="1">
       <c r="B63" s="74" t="n"/>
       <c r="C63" s="74" t="n"/>
-      <c r="D63" s="143" t="n"/>
-      <c r="E63" s="309" t="n"/>
-      <c r="F63" s="314" t="n"/>
-      <c r="G63" s="157" t="n"/>
-      <c r="H63" s="309" t="n"/>
-      <c r="I63" s="315" t="n"/>
-      <c r="J63" s="316" t="n"/>
-      <c r="K63" s="317" t="n"/>
-      <c r="L63" s="316" t="n"/>
-      <c r="M63" s="181" t="n"/>
-      <c r="N63" s="309" t="n"/>
-      <c r="O63" s="309" t="n"/>
-      <c r="P63" s="314" t="n"/>
+      <c r="D63" s="276" t="n"/>
+      <c r="E63" s="129" t="n"/>
+      <c r="F63" s="130" t="n"/>
+      <c r="G63" s="210" t="n"/>
+      <c r="H63" s="129" t="n"/>
+      <c r="I63" s="253" t="n"/>
+      <c r="J63" s="196" t="n"/>
+      <c r="K63" s="202" t="n"/>
+      <c r="L63" s="196" t="n"/>
+      <c r="M63" s="222" t="n"/>
+      <c r="N63" s="129" t="n"/>
+      <c r="O63" s="129" t="n"/>
+      <c r="P63" s="130" t="n"/>
       <c r="Q63" s="103" t="n"/>
       <c r="R63" s="103" t="n"/>
       <c r="U63" s="35" t="n"/>
@@ -4533,64 +4416,64 @@
     <row r="64" ht="21" customHeight="1">
       <c r="B64" s="74" t="n"/>
       <c r="C64" s="74" t="n"/>
-      <c r="D64" s="166" t="n"/>
-      <c r="E64" s="309" t="n"/>
-      <c r="F64" s="314" t="n"/>
-      <c r="G64" s="159" t="n"/>
-      <c r="H64" s="309" t="n"/>
-      <c r="I64" s="318" t="n"/>
-      <c r="J64" s="316" t="n"/>
-      <c r="K64" s="319" t="n"/>
-      <c r="L64" s="316" t="n"/>
-      <c r="M64" s="151" t="n"/>
-      <c r="N64" s="309" t="n"/>
-      <c r="O64" s="309" t="n"/>
-      <c r="P64" s="314" t="n"/>
+      <c r="D64" s="267" t="n"/>
+      <c r="E64" s="129" t="n"/>
+      <c r="F64" s="130" t="n"/>
+      <c r="G64" s="149" t="n"/>
+      <c r="H64" s="129" t="n"/>
+      <c r="I64" s="251" t="n"/>
+      <c r="J64" s="196" t="n"/>
+      <c r="K64" s="195" t="n"/>
+      <c r="L64" s="196" t="n"/>
+      <c r="M64" s="209" t="n"/>
+      <c r="N64" s="129" t="n"/>
+      <c r="O64" s="129" t="n"/>
+      <c r="P64" s="130" t="n"/>
       <c r="Q64" s="56" t="n"/>
       <c r="R64" s="56" t="n"/>
       <c r="U64" s="35" t="n"/>
       <c r="V64" s="35" t="n"/>
       <c r="W64" s="35" t="n"/>
     </row>
-    <row r="65" ht="20.4" customFormat="1" customHeight="1" s="174">
+    <row r="65" ht="20.4" customFormat="1" customHeight="1" s="123">
       <c r="B65" s="74" t="n"/>
       <c r="C65" s="74" t="n"/>
-      <c r="D65" s="149" t="n"/>
-      <c r="E65" s="309" t="n"/>
-      <c r="F65" s="314" t="n"/>
-      <c r="G65" s="157" t="n"/>
-      <c r="H65" s="309" t="n"/>
-      <c r="I65" s="315" t="n"/>
-      <c r="J65" s="316" t="n"/>
-      <c r="K65" s="315" t="n"/>
-      <c r="L65" s="316" t="n"/>
-      <c r="M65" s="181" t="n"/>
-      <c r="N65" s="309" t="n"/>
-      <c r="O65" s="309" t="n"/>
-      <c r="P65" s="314" t="n"/>
+      <c r="D65" s="131" t="n"/>
+      <c r="E65" s="129" t="n"/>
+      <c r="F65" s="130" t="n"/>
+      <c r="G65" s="210" t="n"/>
+      <c r="H65" s="129" t="n"/>
+      <c r="I65" s="253" t="n"/>
+      <c r="J65" s="196" t="n"/>
+      <c r="K65" s="253" t="n"/>
+      <c r="L65" s="196" t="n"/>
+      <c r="M65" s="222" t="n"/>
+      <c r="N65" s="129" t="n"/>
+      <c r="O65" s="129" t="n"/>
+      <c r="P65" s="130" t="n"/>
       <c r="Q65" s="56" t="n"/>
       <c r="R65" s="56" t="n"/>
     </row>
-    <row r="66" ht="20.4" customFormat="1" customHeight="1" s="174">
+    <row r="66" ht="20.4" customFormat="1" customHeight="1" s="123">
       <c r="B66" s="74" t="n"/>
       <c r="C66" s="74" t="n"/>
-      <c r="D66" s="148" t="n"/>
-      <c r="E66" s="309" t="n"/>
-      <c r="F66" s="314" t="n"/>
-      <c r="G66" s="159" t="n"/>
-      <c r="H66" s="309" t="n"/>
-      <c r="I66" s="320" t="n"/>
-      <c r="J66" s="321" t="n"/>
-      <c r="K66" s="320" t="n"/>
-      <c r="L66" s="321" t="n"/>
-      <c r="M66" s="151" t="n"/>
-      <c r="N66" s="309" t="n"/>
-      <c r="O66" s="309" t="n"/>
-      <c r="P66" s="314" t="n"/>
+      <c r="D66" s="128" t="n"/>
+      <c r="E66" s="129" t="n"/>
+      <c r="F66" s="130" t="n"/>
+      <c r="G66" s="149" t="n"/>
+      <c r="H66" s="129" t="n"/>
+      <c r="I66" s="150" t="n"/>
+      <c r="J66" s="151" t="n"/>
+      <c r="K66" s="150" t="n"/>
+      <c r="L66" s="151" t="n"/>
+      <c r="M66" s="209" t="n"/>
+      <c r="N66" s="129" t="n"/>
+      <c r="O66" s="129" t="n"/>
+      <c r="P66" s="130" t="n"/>
       <c r="Q66" s="56" t="n"/>
       <c r="R66" s="56" t="n"/>
     </row>
-    <row r="67" ht="25.8" customFormat="1" customHeight="1" s="174">
+    <row r="67" ht="25.8" customFormat="1" customHeight="1" s="123">
       <c r="B67" s="74" t="n"/>
       <c r="C67" s="74" t="n"/>
       <c r="D67" s="56" t="n"/>
@@ -4612,132 +4495,132 @@
     <row r="68" ht="24.9" customHeight="1">
       <c r="B68" s="74" t="n"/>
       <c r="C68" s="74" t="n"/>
-      <c r="D68" s="109" t="inlineStr">
+      <c r="D68" s="283" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E68" s="322" t="inlineStr">
+      <c r="E68" s="287" t="inlineStr">
         <is>
           <t>TRABAJOS PREVIOS A INICIAR</t>
         </is>
       </c>
-      <c r="F68" s="306" t="n"/>
-      <c r="G68" s="306" t="n"/>
-      <c r="H68" s="306" t="n"/>
-      <c r="I68" s="306" t="n"/>
-      <c r="J68" s="306" t="n"/>
-      <c r="K68" s="306" t="n"/>
-      <c r="L68" s="306" t="n"/>
-      <c r="M68" s="306" t="n"/>
-      <c r="N68" s="306" t="n"/>
-      <c r="O68" s="306" t="n"/>
-      <c r="P68" s="305" t="n"/>
+      <c r="F68" s="117" t="n"/>
+      <c r="G68" s="117" t="n"/>
+      <c r="H68" s="117" t="n"/>
+      <c r="I68" s="117" t="n"/>
+      <c r="J68" s="117" t="n"/>
+      <c r="K68" s="117" t="n"/>
+      <c r="L68" s="117" t="n"/>
+      <c r="M68" s="117" t="n"/>
+      <c r="N68" s="117" t="n"/>
+      <c r="O68" s="117" t="n"/>
+      <c r="P68" s="118" t="n"/>
       <c r="Q68" s="55" t="n"/>
       <c r="R68" s="55" t="n"/>
     </row>
     <row r="69" ht="24.9" customHeight="1">
       <c r="B69" s="74" t="n"/>
       <c r="C69" s="99" t="n"/>
-      <c r="D69" s="110" t="n">
+      <c r="D69" s="108" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="323" t="inlineStr">
+      <c r="E69" s="186" t="inlineStr">
         <is>
           <t>{{TRABAJOS_PREVIOS}}</t>
         </is>
       </c>
-      <c r="F69" s="307" t="n"/>
-      <c r="G69" s="307" t="n"/>
-      <c r="H69" s="307" t="n"/>
-      <c r="I69" s="307" t="n"/>
-      <c r="J69" s="307" t="n"/>
-      <c r="K69" s="307" t="n"/>
-      <c r="L69" s="307" t="n"/>
-      <c r="M69" s="307" t="n"/>
-      <c r="N69" s="307" t="n"/>
-      <c r="O69" s="307" t="n"/>
-      <c r="P69" s="308" t="n"/>
+      <c r="F69" s="187" t="n"/>
+      <c r="G69" s="187" t="n"/>
+      <c r="H69" s="187" t="n"/>
+      <c r="I69" s="187" t="n"/>
+      <c r="J69" s="187" t="n"/>
+      <c r="K69" s="187" t="n"/>
+      <c r="L69" s="187" t="n"/>
+      <c r="M69" s="187" t="n"/>
+      <c r="N69" s="187" t="n"/>
+      <c r="O69" s="187" t="n"/>
+      <c r="P69" s="188" t="n"/>
       <c r="Q69" s="99" t="n"/>
       <c r="R69" s="99" t="n"/>
     </row>
     <row r="70" ht="25.8" customHeight="1">
       <c r="B70" s="74" t="n"/>
       <c r="C70" s="74" t="n"/>
-      <c r="D70" s="112" t="n">
+      <c r="D70" s="110" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="184" t="n"/>
-      <c r="F70" s="307" t="n"/>
-      <c r="G70" s="307" t="n"/>
-      <c r="H70" s="307" t="n"/>
-      <c r="I70" s="307" t="n"/>
-      <c r="J70" s="307" t="n"/>
-      <c r="K70" s="307" t="n"/>
-      <c r="L70" s="307" t="n"/>
-      <c r="M70" s="307" t="n"/>
-      <c r="N70" s="307" t="n"/>
-      <c r="O70" s="307" t="n"/>
-      <c r="P70" s="308" t="n"/>
+      <c r="E70" s="295" t="n"/>
+      <c r="F70" s="187" t="n"/>
+      <c r="G70" s="187" t="n"/>
+      <c r="H70" s="187" t="n"/>
+      <c r="I70" s="187" t="n"/>
+      <c r="J70" s="187" t="n"/>
+      <c r="K70" s="187" t="n"/>
+      <c r="L70" s="187" t="n"/>
+      <c r="M70" s="187" t="n"/>
+      <c r="N70" s="187" t="n"/>
+      <c r="O70" s="187" t="n"/>
+      <c r="P70" s="188" t="n"/>
       <c r="Q70" s="55" t="n"/>
       <c r="R70" s="55" t="n"/>
     </row>
     <row r="71" ht="24.9" customHeight="1">
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
-      <c r="D71" s="110" t="n">
+      <c r="D71" s="108" t="n">
         <v>3</v>
       </c>
-      <c r="E71" s="235" t="n"/>
-      <c r="F71" s="309" t="n"/>
-      <c r="G71" s="309" t="n"/>
-      <c r="H71" s="309" t="n"/>
-      <c r="I71" s="309" t="n"/>
-      <c r="J71" s="309" t="n"/>
-      <c r="K71" s="309" t="n"/>
-      <c r="L71" s="309" t="n"/>
-      <c r="M71" s="309" t="n"/>
-      <c r="N71" s="309" t="n"/>
-      <c r="O71" s="309" t="n"/>
-      <c r="P71" s="314" t="n"/>
+      <c r="E71" s="252" t="n"/>
+      <c r="F71" s="129" t="n"/>
+      <c r="G71" s="129" t="n"/>
+      <c r="H71" s="129" t="n"/>
+      <c r="I71" s="129" t="n"/>
+      <c r="J71" s="129" t="n"/>
+      <c r="K71" s="129" t="n"/>
+      <c r="L71" s="129" t="n"/>
+      <c r="M71" s="129" t="n"/>
+      <c r="N71" s="129" t="n"/>
+      <c r="O71" s="129" t="n"/>
+      <c r="P71" s="130" t="n"/>
     </row>
     <row r="72" ht="24.9" customHeight="1">
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="112" t="n">
+      <c r="D72" s="110" t="n">
         <v>4</v>
       </c>
-      <c r="E72" s="214" t="n"/>
-      <c r="F72" s="309" t="n"/>
-      <c r="G72" s="309" t="n"/>
-      <c r="H72" s="309" t="n"/>
-      <c r="I72" s="309" t="n"/>
-      <c r="J72" s="309" t="n"/>
-      <c r="K72" s="309" t="n"/>
-      <c r="L72" s="309" t="n"/>
-      <c r="M72" s="309" t="n"/>
-      <c r="N72" s="309" t="n"/>
-      <c r="O72" s="309" t="n"/>
-      <c r="P72" s="314" t="n"/>
+      <c r="E72" s="207" t="n"/>
+      <c r="F72" s="129" t="n"/>
+      <c r="G72" s="129" t="n"/>
+      <c r="H72" s="129" t="n"/>
+      <c r="I72" s="129" t="n"/>
+      <c r="J72" s="129" t="n"/>
+      <c r="K72" s="129" t="n"/>
+      <c r="L72" s="129" t="n"/>
+      <c r="M72" s="129" t="n"/>
+      <c r="N72" s="129" t="n"/>
+      <c r="O72" s="129" t="n"/>
+      <c r="P72" s="130" t="n"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="B73" s="8" t="n"/>
       <c r="C73" s="8" t="n"/>
-      <c r="D73" s="110" t="n">
+      <c r="D73" s="108" t="n">
         <v>5</v>
       </c>
-      <c r="E73" s="273" t="n"/>
-      <c r="F73" s="309" t="n"/>
-      <c r="G73" s="309" t="n"/>
-      <c r="H73" s="309" t="n"/>
-      <c r="I73" s="309" t="n"/>
-      <c r="J73" s="309" t="n"/>
-      <c r="K73" s="309" t="n"/>
-      <c r="L73" s="309" t="n"/>
-      <c r="M73" s="309" t="n"/>
-      <c r="N73" s="309" t="n"/>
-      <c r="O73" s="309" t="n"/>
-      <c r="P73" s="314" t="n"/>
+      <c r="E73" s="255" t="n"/>
+      <c r="F73" s="129" t="n"/>
+      <c r="G73" s="129" t="n"/>
+      <c r="H73" s="129" t="n"/>
+      <c r="I73" s="129" t="n"/>
+      <c r="J73" s="129" t="n"/>
+      <c r="K73" s="129" t="n"/>
+      <c r="L73" s="129" t="n"/>
+      <c r="M73" s="129" t="n"/>
+      <c r="N73" s="129" t="n"/>
+      <c r="O73" s="129" t="n"/>
+      <c r="P73" s="130" t="n"/>
     </row>
     <row r="74" ht="24.9" customHeight="1">
       <c r="B74" s="8" t="n"/>
@@ -4759,151 +4642,151 @@
     <row r="75" ht="24.9" customHeight="1">
       <c r="B75" s="74" t="n"/>
       <c r="C75" s="74" t="n"/>
-      <c r="D75" s="111" t="inlineStr">
+      <c r="D75" s="288" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E75" s="176" t="inlineStr">
+      <c r="E75" s="289" t="inlineStr">
         <is>
           <t>SERVICIOS BASICOS NECESARIOS PARA TRABAJAR</t>
         </is>
       </c>
-      <c r="F75" s="306" t="n"/>
-      <c r="G75" s="306" t="n"/>
-      <c r="H75" s="306" t="n"/>
-      <c r="I75" s="306" t="n"/>
-      <c r="J75" s="306" t="n"/>
-      <c r="K75" s="306" t="n"/>
-      <c r="L75" s="306" t="n"/>
-      <c r="M75" s="306" t="n"/>
-      <c r="N75" s="306" t="n"/>
-      <c r="O75" s="306" t="n"/>
-      <c r="P75" s="306" t="n"/>
+      <c r="F75" s="117" t="n"/>
+      <c r="G75" s="117" t="n"/>
+      <c r="H75" s="117" t="n"/>
+      <c r="I75" s="117" t="n"/>
+      <c r="J75" s="117" t="n"/>
+      <c r="K75" s="117" t="n"/>
+      <c r="L75" s="117" t="n"/>
+      <c r="M75" s="117" t="n"/>
+      <c r="N75" s="117" t="n"/>
+      <c r="O75" s="117" t="n"/>
+      <c r="P75" s="117" t="n"/>
       <c r="Q75" s="55" t="n"/>
       <c r="R75" s="55" t="n"/>
     </row>
     <row r="76" ht="24.9" customHeight="1">
       <c r="B76" s="74" t="n"/>
       <c r="C76" s="74" t="n"/>
-      <c r="D76" s="110" t="n">
+      <c r="D76" s="108" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="262" t="inlineStr">
+      <c r="E76" s="192" t="inlineStr">
         <is>
           <t>{{SERVICIOS_BASICOS}}</t>
         </is>
       </c>
-      <c r="F76" s="307" t="n"/>
-      <c r="G76" s="307" t="n"/>
-      <c r="H76" s="307" t="n"/>
-      <c r="I76" s="307" t="n"/>
-      <c r="J76" s="307" t="n"/>
-      <c r="K76" s="307" t="n"/>
-      <c r="L76" s="307" t="n"/>
-      <c r="M76" s="307" t="n"/>
-      <c r="N76" s="307" t="n"/>
-      <c r="O76" s="307" t="n"/>
-      <c r="P76" s="308" t="n"/>
+      <c r="F76" s="187" t="n"/>
+      <c r="G76" s="187" t="n"/>
+      <c r="H76" s="187" t="n"/>
+      <c r="I76" s="187" t="n"/>
+      <c r="J76" s="187" t="n"/>
+      <c r="K76" s="187" t="n"/>
+      <c r="L76" s="187" t="n"/>
+      <c r="M76" s="187" t="n"/>
+      <c r="N76" s="187" t="n"/>
+      <c r="O76" s="187" t="n"/>
+      <c r="P76" s="188" t="n"/>
       <c r="Q76" s="55" t="n"/>
       <c r="R76" s="55" t="n"/>
     </row>
     <row r="77" ht="24.9" customHeight="1">
       <c r="B77" s="74" t="n"/>
       <c r="C77" s="74" t="n"/>
-      <c r="D77" s="112" t="n">
+      <c r="D77" s="110" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="324" t="n"/>
-      <c r="F77" s="307" t="n"/>
-      <c r="G77" s="307" t="n"/>
-      <c r="H77" s="307" t="n"/>
-      <c r="I77" s="307" t="n"/>
-      <c r="J77" s="307" t="n"/>
-      <c r="K77" s="307" t="n"/>
-      <c r="L77" s="307" t="n"/>
-      <c r="M77" s="307" t="n"/>
-      <c r="N77" s="307" t="n"/>
-      <c r="O77" s="307" t="n"/>
-      <c r="P77" s="308" t="n"/>
+      <c r="E77" s="197" t="n"/>
+      <c r="F77" s="187" t="n"/>
+      <c r="G77" s="187" t="n"/>
+      <c r="H77" s="187" t="n"/>
+      <c r="I77" s="187" t="n"/>
+      <c r="J77" s="187" t="n"/>
+      <c r="K77" s="187" t="n"/>
+      <c r="L77" s="187" t="n"/>
+      <c r="M77" s="187" t="n"/>
+      <c r="N77" s="187" t="n"/>
+      <c r="O77" s="187" t="n"/>
+      <c r="P77" s="188" t="n"/>
       <c r="Q77" s="55" t="n"/>
       <c r="R77" s="55" t="n"/>
     </row>
     <row r="78" ht="24.9" customHeight="1">
       <c r="B78" s="74" t="n"/>
       <c r="C78" s="74" t="n"/>
-      <c r="D78" s="110" t="n">
+      <c r="D78" s="108" t="n">
         <v>3</v>
       </c>
-      <c r="E78" s="262" t="n"/>
-      <c r="F78" s="307" t="n"/>
-      <c r="G78" s="307" t="n"/>
-      <c r="H78" s="307" t="n"/>
-      <c r="I78" s="307" t="n"/>
-      <c r="J78" s="307" t="n"/>
-      <c r="K78" s="307" t="n"/>
-      <c r="L78" s="307" t="n"/>
-      <c r="M78" s="307" t="n"/>
-      <c r="N78" s="307" t="n"/>
-      <c r="O78" s="307" t="n"/>
-      <c r="P78" s="308" t="n"/>
+      <c r="E78" s="192" t="n"/>
+      <c r="F78" s="187" t="n"/>
+      <c r="G78" s="187" t="n"/>
+      <c r="H78" s="187" t="n"/>
+      <c r="I78" s="187" t="n"/>
+      <c r="J78" s="187" t="n"/>
+      <c r="K78" s="187" t="n"/>
+      <c r="L78" s="187" t="n"/>
+      <c r="M78" s="187" t="n"/>
+      <c r="N78" s="187" t="n"/>
+      <c r="O78" s="187" t="n"/>
+      <c r="P78" s="188" t="n"/>
       <c r="Q78" s="55" t="n"/>
       <c r="R78" s="55" t="n"/>
     </row>
     <row r="79" ht="27" customHeight="1">
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="112" t="n">
+      <c r="D79" s="110" t="n">
         <v>4</v>
       </c>
-      <c r="E79" s="202" t="n"/>
-      <c r="F79" s="309" t="n"/>
-      <c r="G79" s="309" t="n"/>
-      <c r="H79" s="309" t="n"/>
-      <c r="I79" s="309" t="n"/>
-      <c r="J79" s="309" t="n"/>
-      <c r="K79" s="309" t="n"/>
-      <c r="L79" s="309" t="n"/>
-      <c r="M79" s="309" t="n"/>
-      <c r="N79" s="309" t="n"/>
-      <c r="O79" s="309" t="n"/>
-      <c r="P79" s="314" t="n"/>
+      <c r="E79" s="254" t="n"/>
+      <c r="F79" s="129" t="n"/>
+      <c r="G79" s="129" t="n"/>
+      <c r="H79" s="129" t="n"/>
+      <c r="I79" s="129" t="n"/>
+      <c r="J79" s="129" t="n"/>
+      <c r="K79" s="129" t="n"/>
+      <c r="L79" s="129" t="n"/>
+      <c r="M79" s="129" t="n"/>
+      <c r="N79" s="129" t="n"/>
+      <c r="O79" s="129" t="n"/>
+      <c r="P79" s="130" t="n"/>
     </row>
     <row r="80" ht="24.9" customHeight="1">
       <c r="B80" s="8" t="n"/>
       <c r="C80" s="8" t="n"/>
-      <c r="D80" s="110" t="n">
+      <c r="D80" s="108" t="n">
         <v>5</v>
       </c>
-      <c r="E80" s="171" t="n"/>
-      <c r="F80" s="309" t="n"/>
-      <c r="G80" s="309" t="n"/>
-      <c r="H80" s="309" t="n"/>
-      <c r="I80" s="309" t="n"/>
-      <c r="J80" s="309" t="n"/>
-      <c r="K80" s="309" t="n"/>
-      <c r="L80" s="309" t="n"/>
-      <c r="M80" s="309" t="n"/>
-      <c r="N80" s="309" t="n"/>
-      <c r="O80" s="309" t="n"/>
-      <c r="P80" s="314" t="n"/>
+      <c r="E80" s="199" t="n"/>
+      <c r="F80" s="129" t="n"/>
+      <c r="G80" s="129" t="n"/>
+      <c r="H80" s="129" t="n"/>
+      <c r="I80" s="129" t="n"/>
+      <c r="J80" s="129" t="n"/>
+      <c r="K80" s="129" t="n"/>
+      <c r="L80" s="129" t="n"/>
+      <c r="M80" s="129" t="n"/>
+      <c r="N80" s="129" t="n"/>
+      <c r="O80" s="129" t="n"/>
+      <c r="P80" s="130" t="n"/>
     </row>
     <row r="81" ht="24.9" customHeight="1">
       <c r="B81" s="8" t="n"/>
       <c r="C81" s="8" t="n"/>
       <c r="D81" s="101" t="n"/>
-      <c r="E81" s="175" t="n"/>
-      <c r="F81" s="147" t="n"/>
-      <c r="G81" s="147" t="n"/>
-      <c r="H81" s="147" t="n"/>
-      <c r="I81" s="147" t="n"/>
-      <c r="J81" s="147" t="n"/>
-      <c r="K81" s="147" t="n"/>
-      <c r="L81" s="147" t="n"/>
-      <c r="M81" s="147" t="n"/>
-      <c r="N81" s="147" t="n"/>
-      <c r="O81" s="147" t="n"/>
-      <c r="P81" s="147" t="n"/>
+      <c r="E81" s="162" t="n"/>
+      <c r="F81" s="161" t="n"/>
+      <c r="G81" s="161" t="n"/>
+      <c r="H81" s="161" t="n"/>
+      <c r="I81" s="161" t="n"/>
+      <c r="J81" s="161" t="n"/>
+      <c r="K81" s="161" t="n"/>
+      <c r="L81" s="161" t="n"/>
+      <c r="M81" s="161" t="n"/>
+      <c r="N81" s="161" t="n"/>
+      <c r="O81" s="161" t="n"/>
+      <c r="P81" s="161" t="n"/>
     </row>
     <row r="82">
       <c r="B82" s="74" t="n"/>
@@ -4927,12 +4810,12 @@
     <row r="83" ht="24.9" customHeight="1">
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="106" t="inlineStr">
+      <c r="D83" s="290" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E83" s="182" t="inlineStr">
+      <c r="E83" s="291" t="inlineStr">
         <is>
           <t>PUNTOS DE REVISIÓN ESPECÍFICA PARA RECEPCIÓN DE TRABAJOS</t>
         </is>
@@ -4943,22 +4826,22 @@
     <row r="84" ht="26.4" customHeight="1">
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
-      <c r="D84" s="293" t="n">
+      <c r="D84" s="232" t="n">
         <v>1</v>
       </c>
-      <c r="E84" s="293" t="inlineStr">
+      <c r="E84" s="232" t="inlineStr">
         <is>
           <t>{{PUNTOS_REVISION}}</t>
         </is>
       </c>
-      <c r="F84" s="325" t="n"/>
-      <c r="G84" s="325" t="n"/>
-      <c r="H84" s="325" t="n"/>
-      <c r="I84" s="325" t="n"/>
-      <c r="J84" s="325" t="n"/>
-      <c r="K84" s="325" t="n"/>
-      <c r="L84" s="325" t="n"/>
-      <c r="M84" s="326" t="n"/>
+      <c r="F84" s="156" t="n"/>
+      <c r="G84" s="156" t="n"/>
+      <c r="H84" s="156" t="n"/>
+      <c r="I84" s="156" t="n"/>
+      <c r="J84" s="156" t="n"/>
+      <c r="K84" s="156" t="n"/>
+      <c r="L84" s="156" t="n"/>
+      <c r="M84" s="157" t="n"/>
       <c r="N84" s="47" t="n"/>
       <c r="O84" s="47" t="n"/>
       <c r="P84" s="47" t="n"/>
@@ -4968,20 +4851,20 @@
     <row r="85" ht="26.4" customHeight="1">
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="297" t="n">
+      <c r="D85" s="155" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="297" t="n"/>
-      <c r="F85" s="325" t="n"/>
-      <c r="G85" s="325" t="n"/>
-      <c r="H85" s="325" t="n"/>
-      <c r="I85" s="325" t="n"/>
-      <c r="J85" s="325" t="n"/>
-      <c r="K85" s="325" t="n"/>
-      <c r="L85" s="325" t="n"/>
-      <c r="M85" s="326" t="n"/>
+      <c r="E85" s="155" t="n"/>
+      <c r="F85" s="156" t="n"/>
+      <c r="G85" s="156" t="n"/>
+      <c r="H85" s="156" t="n"/>
+      <c r="I85" s="156" t="n"/>
+      <c r="J85" s="156" t="n"/>
+      <c r="K85" s="156" t="n"/>
+      <c r="L85" s="156" t="n"/>
+      <c r="M85" s="157" t="n"/>
       <c r="N85" s="46" t="n"/>
-      <c r="O85" s="136" t="inlineStr">
+      <c r="O85" s="154" t="inlineStr">
         <is>
           <t>RECEPCIONES EN CAMPO</t>
         </is>
@@ -4992,20 +4875,20 @@
     <row r="86" ht="27" customHeight="1">
       <c r="B86" s="8" t="n"/>
       <c r="C86" s="8" t="n"/>
-      <c r="D86" s="293" t="n">
+      <c r="D86" s="232" t="n">
         <v>3</v>
       </c>
-      <c r="E86" s="295" t="n"/>
-      <c r="F86" s="327" t="n"/>
-      <c r="G86" s="327" t="n"/>
-      <c r="H86" s="327" t="n"/>
-      <c r="I86" s="327" t="n"/>
-      <c r="J86" s="327" t="n"/>
-      <c r="K86" s="327" t="n"/>
-      <c r="L86" s="327" t="n"/>
-      <c r="M86" s="328" t="n"/>
+      <c r="E86" s="158" t="n"/>
+      <c r="F86" s="135" t="n"/>
+      <c r="G86" s="135" t="n"/>
+      <c r="H86" s="135" t="n"/>
+      <c r="I86" s="135" t="n"/>
+      <c r="J86" s="135" t="n"/>
+      <c r="K86" s="135" t="n"/>
+      <c r="L86" s="135" t="n"/>
+      <c r="M86" s="136" t="n"/>
       <c r="N86" s="4" t="n"/>
-      <c r="O86" s="135" t="inlineStr">
+      <c r="O86" s="242" t="inlineStr">
         <is>
           <t>Cartas firmadas por Lider de Proyecto y Maestro de obras, con fotografias de avance, cuadro de cantidades y renglones</t>
         </is>
@@ -5021,18 +4904,18 @@
     <row r="87" ht="26.4" customHeight="1">
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="297" t="n">
+      <c r="D87" s="155" t="n">
         <v>4</v>
       </c>
-      <c r="E87" s="294" t="n"/>
-      <c r="F87" s="327" t="n"/>
-      <c r="G87" s="327" t="n"/>
-      <c r="H87" s="327" t="n"/>
-      <c r="I87" s="327" t="n"/>
-      <c r="J87" s="327" t="n"/>
-      <c r="K87" s="327" t="n"/>
-      <c r="L87" s="327" t="n"/>
-      <c r="M87" s="328" t="n"/>
+      <c r="E87" s="134" t="n"/>
+      <c r="F87" s="135" t="n"/>
+      <c r="G87" s="135" t="n"/>
+      <c r="H87" s="135" t="n"/>
+      <c r="I87" s="135" t="n"/>
+      <c r="J87" s="135" t="n"/>
+      <c r="K87" s="135" t="n"/>
+      <c r="L87" s="135" t="n"/>
+      <c r="M87" s="136" t="n"/>
       <c r="N87" s="5" t="n"/>
       <c r="Q87" s="44" t="n"/>
       <c r="R87" s="44" t="n"/>
@@ -5040,18 +4923,18 @@
     <row r="88" ht="27.6" customHeight="1">
       <c r="B88" s="8" t="n"/>
       <c r="C88" s="8" t="n"/>
-      <c r="D88" s="293" t="n">
+      <c r="D88" s="232" t="n">
         <v>5</v>
       </c>
-      <c r="E88" s="295" t="n"/>
-      <c r="F88" s="327" t="n"/>
-      <c r="G88" s="327" t="n"/>
-      <c r="H88" s="327" t="n"/>
-      <c r="I88" s="327" t="n"/>
-      <c r="J88" s="327" t="n"/>
-      <c r="K88" s="327" t="n"/>
-      <c r="L88" s="327" t="n"/>
-      <c r="M88" s="328" t="n"/>
+      <c r="E88" s="158" t="n"/>
+      <c r="F88" s="135" t="n"/>
+      <c r="G88" s="135" t="n"/>
+      <c r="H88" s="135" t="n"/>
+      <c r="I88" s="135" t="n"/>
+      <c r="J88" s="135" t="n"/>
+      <c r="K88" s="135" t="n"/>
+      <c r="L88" s="135" t="n"/>
+      <c r="M88" s="136" t="n"/>
       <c r="N88" s="5" t="n"/>
       <c r="Q88" s="44" t="n"/>
       <c r="R88" s="44" t="n"/>
@@ -5059,62 +4942,62 @@
     <row r="89" ht="27.6" customHeight="1">
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
-      <c r="D89" s="297" t="n">
+      <c r="D89" s="155" t="n">
         <v>6</v>
       </c>
-      <c r="E89" s="294" t="n"/>
-      <c r="F89" s="327" t="n"/>
-      <c r="G89" s="327" t="n"/>
-      <c r="H89" s="327" t="n"/>
-      <c r="I89" s="327" t="n"/>
-      <c r="J89" s="327" t="n"/>
-      <c r="K89" s="327" t="n"/>
-      <c r="L89" s="327" t="n"/>
-      <c r="M89" s="328" t="n"/>
+      <c r="E89" s="134" t="n"/>
+      <c r="F89" s="135" t="n"/>
+      <c r="G89" s="135" t="n"/>
+      <c r="H89" s="135" t="n"/>
+      <c r="I89" s="135" t="n"/>
+      <c r="J89" s="135" t="n"/>
+      <c r="K89" s="135" t="n"/>
+      <c r="L89" s="135" t="n"/>
+      <c r="M89" s="136" t="n"/>
       <c r="N89" s="5" t="n"/>
-      <c r="O89" s="329" t="n"/>
-      <c r="P89" s="329" t="n"/>
+      <c r="O89" s="176" t="n"/>
+      <c r="P89" s="176" t="n"/>
       <c r="Q89" s="44" t="n"/>
       <c r="R89" s="44" t="n"/>
     </row>
     <row r="90" ht="27.6" customHeight="1">
       <c r="B90" s="8" t="n"/>
       <c r="C90" s="8" t="n"/>
-      <c r="D90" s="293" t="n">
+      <c r="D90" s="232" t="n">
         <v>7</v>
       </c>
-      <c r="E90" s="295" t="n"/>
-      <c r="F90" s="327" t="n"/>
-      <c r="G90" s="327" t="n"/>
-      <c r="H90" s="327" t="n"/>
-      <c r="I90" s="327" t="n"/>
-      <c r="J90" s="327" t="n"/>
-      <c r="K90" s="327" t="n"/>
-      <c r="L90" s="327" t="n"/>
-      <c r="M90" s="328" t="n"/>
+      <c r="E90" s="158" t="n"/>
+      <c r="F90" s="135" t="n"/>
+      <c r="G90" s="135" t="n"/>
+      <c r="H90" s="135" t="n"/>
+      <c r="I90" s="135" t="n"/>
+      <c r="J90" s="135" t="n"/>
+      <c r="K90" s="135" t="n"/>
+      <c r="L90" s="135" t="n"/>
+      <c r="M90" s="136" t="n"/>
       <c r="N90" s="5" t="n"/>
-      <c r="O90" s="174" t="n"/>
-      <c r="P90" s="174" t="n"/>
+      <c r="O90" s="123" t="n"/>
+      <c r="P90" s="123" t="n"/>
       <c r="Q90" s="44" t="n"/>
       <c r="R90" s="44" t="n"/>
     </row>
     <row r="91" ht="27.6" customHeight="1">
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="297" t="n">
+      <c r="D91" s="155" t="n">
         <v>8</v>
       </c>
-      <c r="E91" s="294" t="n"/>
-      <c r="F91" s="327" t="n"/>
-      <c r="G91" s="327" t="n"/>
-      <c r="H91" s="327" t="n"/>
-      <c r="I91" s="327" t="n"/>
-      <c r="J91" s="327" t="n"/>
-      <c r="K91" s="327" t="n"/>
-      <c r="L91" s="327" t="n"/>
-      <c r="M91" s="328" t="n"/>
+      <c r="E91" s="134" t="n"/>
+      <c r="F91" s="135" t="n"/>
+      <c r="G91" s="135" t="n"/>
+      <c r="H91" s="135" t="n"/>
+      <c r="I91" s="135" t="n"/>
+      <c r="J91" s="135" t="n"/>
+      <c r="K91" s="135" t="n"/>
+      <c r="L91" s="135" t="n"/>
+      <c r="M91" s="136" t="n"/>
       <c r="N91" s="5" t="n"/>
-      <c r="O91" s="136" t="inlineStr">
+      <c r="O91" s="154" t="inlineStr">
         <is>
           <t>RESPONSABILIDADES</t>
         </is>
@@ -5125,41 +5008,41 @@
     <row r="92" ht="27.6" customHeight="1">
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="8" t="n"/>
-      <c r="D92" s="293" t="n">
+      <c r="D92" s="232" t="n">
         <v>9</v>
       </c>
-      <c r="E92" s="295" t="n"/>
-      <c r="F92" s="327" t="n"/>
-      <c r="G92" s="327" t="n"/>
-      <c r="H92" s="327" t="n"/>
-      <c r="I92" s="327" t="n"/>
-      <c r="J92" s="327" t="n"/>
-      <c r="K92" s="327" t="n"/>
-      <c r="L92" s="327" t="n"/>
-      <c r="M92" s="328" t="n"/>
+      <c r="E92" s="158" t="n"/>
+      <c r="F92" s="135" t="n"/>
+      <c r="G92" s="135" t="n"/>
+      <c r="H92" s="135" t="n"/>
+      <c r="I92" s="135" t="n"/>
+      <c r="J92" s="135" t="n"/>
+      <c r="K92" s="135" t="n"/>
+      <c r="L92" s="135" t="n"/>
+      <c r="M92" s="136" t="n"/>
       <c r="N92" s="5" t="n"/>
-      <c r="O92" s="136" t="n"/>
-      <c r="P92" s="136" t="n"/>
+      <c r="O92" s="154" t="n"/>
+      <c r="P92" s="154" t="n"/>
       <c r="Q92" s="44" t="n"/>
       <c r="R92" s="44" t="n"/>
     </row>
     <row r="93" ht="27.6" customHeight="1">
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="297" t="n">
+      <c r="D93" s="155" t="n">
         <v>10</v>
       </c>
-      <c r="E93" s="294" t="n"/>
-      <c r="F93" s="327" t="n"/>
-      <c r="G93" s="327" t="n"/>
-      <c r="H93" s="327" t="n"/>
-      <c r="I93" s="327" t="n"/>
-      <c r="J93" s="327" t="n"/>
-      <c r="K93" s="327" t="n"/>
-      <c r="L93" s="327" t="n"/>
-      <c r="M93" s="328" t="n"/>
+      <c r="E93" s="134" t="n"/>
+      <c r="F93" s="135" t="n"/>
+      <c r="G93" s="135" t="n"/>
+      <c r="H93" s="135" t="n"/>
+      <c r="I93" s="135" t="n"/>
+      <c r="J93" s="135" t="n"/>
+      <c r="K93" s="135" t="n"/>
+      <c r="L93" s="135" t="n"/>
+      <c r="M93" s="136" t="n"/>
       <c r="N93" s="5" t="n"/>
-      <c r="O93" s="135" t="inlineStr">
+      <c r="O93" s="242" t="inlineStr">
         <is>
           <t>Contratista es el unico responsable de cumplir con los pagos directo a su personal en obra, tanto salario pactado como prestaciones en dado apliquen, quitando responsabilidad a E4 ante cualquier inconveniente</t>
         </is>
@@ -5170,18 +5053,18 @@
     <row r="94" ht="27.6" customHeight="1">
       <c r="B94" s="8" t="n"/>
       <c r="C94" s="8" t="n"/>
-      <c r="D94" s="293" t="n">
+      <c r="D94" s="232" t="n">
         <v>11</v>
       </c>
-      <c r="E94" s="295" t="n"/>
-      <c r="F94" s="327" t="n"/>
-      <c r="G94" s="327" t="n"/>
-      <c r="H94" s="327" t="n"/>
-      <c r="I94" s="327" t="n"/>
-      <c r="J94" s="327" t="n"/>
-      <c r="K94" s="327" t="n"/>
-      <c r="L94" s="327" t="n"/>
-      <c r="M94" s="328" t="n"/>
+      <c r="E94" s="158" t="n"/>
+      <c r="F94" s="135" t="n"/>
+      <c r="G94" s="135" t="n"/>
+      <c r="H94" s="135" t="n"/>
+      <c r="I94" s="135" t="n"/>
+      <c r="J94" s="135" t="n"/>
+      <c r="K94" s="135" t="n"/>
+      <c r="L94" s="135" t="n"/>
+      <c r="M94" s="136" t="n"/>
       <c r="N94" s="5" t="n"/>
       <c r="Q94" s="44" t="n"/>
       <c r="R94" s="44" t="n"/>
@@ -5189,18 +5072,18 @@
     <row r="95" ht="27.6" customHeight="1">
       <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="297" t="n">
+      <c r="D95" s="155" t="n">
         <v>12</v>
       </c>
-      <c r="E95" s="294" t="n"/>
-      <c r="F95" s="327" t="n"/>
-      <c r="G95" s="327" t="n"/>
-      <c r="H95" s="327" t="n"/>
-      <c r="I95" s="327" t="n"/>
-      <c r="J95" s="327" t="n"/>
-      <c r="K95" s="327" t="n"/>
-      <c r="L95" s="327" t="n"/>
-      <c r="M95" s="328" t="n"/>
+      <c r="E95" s="134" t="n"/>
+      <c r="F95" s="135" t="n"/>
+      <c r="G95" s="135" t="n"/>
+      <c r="H95" s="135" t="n"/>
+      <c r="I95" s="135" t="n"/>
+      <c r="J95" s="135" t="n"/>
+      <c r="K95" s="135" t="n"/>
+      <c r="L95" s="135" t="n"/>
+      <c r="M95" s="136" t="n"/>
       <c r="N95" s="5" t="n"/>
       <c r="Q95" s="44" t="n"/>
       <c r="R95" s="44" t="n"/>
@@ -5208,18 +5091,18 @@
     <row r="96" ht="27.6" customHeight="1">
       <c r="B96" s="8" t="n"/>
       <c r="C96" s="8" t="n"/>
-      <c r="D96" s="293" t="n">
+      <c r="D96" s="232" t="n">
         <v>13</v>
       </c>
-      <c r="E96" s="295" t="n"/>
-      <c r="F96" s="327" t="n"/>
-      <c r="G96" s="327" t="n"/>
-      <c r="H96" s="327" t="n"/>
-      <c r="I96" s="327" t="n"/>
-      <c r="J96" s="327" t="n"/>
-      <c r="K96" s="327" t="n"/>
-      <c r="L96" s="327" t="n"/>
-      <c r="M96" s="328" t="n"/>
+      <c r="E96" s="158" t="n"/>
+      <c r="F96" s="135" t="n"/>
+      <c r="G96" s="135" t="n"/>
+      <c r="H96" s="135" t="n"/>
+      <c r="I96" s="135" t="n"/>
+      <c r="J96" s="135" t="n"/>
+      <c r="K96" s="135" t="n"/>
+      <c r="L96" s="135" t="n"/>
+      <c r="M96" s="136" t="n"/>
       <c r="N96" s="5" t="n"/>
       <c r="Q96" s="44" t="n"/>
       <c r="R96" s="44" t="n"/>
@@ -5227,62 +5110,62 @@
     <row r="97" ht="27.6" customHeight="1">
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="297" t="n">
+      <c r="D97" s="155" t="n">
         <v>14</v>
       </c>
-      <c r="E97" s="294" t="n"/>
-      <c r="F97" s="327" t="n"/>
-      <c r="G97" s="327" t="n"/>
-      <c r="H97" s="327" t="n"/>
-      <c r="I97" s="327" t="n"/>
-      <c r="J97" s="327" t="n"/>
-      <c r="K97" s="327" t="n"/>
-      <c r="L97" s="327" t="n"/>
-      <c r="M97" s="328" t="n"/>
+      <c r="E97" s="134" t="n"/>
+      <c r="F97" s="135" t="n"/>
+      <c r="G97" s="135" t="n"/>
+      <c r="H97" s="135" t="n"/>
+      <c r="I97" s="135" t="n"/>
+      <c r="J97" s="135" t="n"/>
+      <c r="K97" s="135" t="n"/>
+      <c r="L97" s="135" t="n"/>
+      <c r="M97" s="136" t="n"/>
       <c r="N97" s="5" t="n"/>
-      <c r="O97" s="329" t="n"/>
-      <c r="P97" s="329" t="n"/>
+      <c r="O97" s="176" t="n"/>
+      <c r="P97" s="176" t="n"/>
       <c r="Q97" s="44" t="n"/>
       <c r="R97" s="44" t="n"/>
     </row>
     <row r="98" ht="27.6" customHeight="1">
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
-      <c r="D98" s="293" t="n">
+      <c r="D98" s="232" t="n">
         <v>15</v>
       </c>
-      <c r="E98" s="295" t="n"/>
-      <c r="F98" s="327" t="n"/>
-      <c r="G98" s="327" t="n"/>
-      <c r="H98" s="327" t="n"/>
-      <c r="I98" s="327" t="n"/>
-      <c r="J98" s="327" t="n"/>
-      <c r="K98" s="327" t="n"/>
-      <c r="L98" s="327" t="n"/>
-      <c r="M98" s="328" t="n"/>
+      <c r="E98" s="158" t="n"/>
+      <c r="F98" s="135" t="n"/>
+      <c r="G98" s="135" t="n"/>
+      <c r="H98" s="135" t="n"/>
+      <c r="I98" s="135" t="n"/>
+      <c r="J98" s="135" t="n"/>
+      <c r="K98" s="135" t="n"/>
+      <c r="L98" s="135" t="n"/>
+      <c r="M98" s="136" t="n"/>
       <c r="N98" s="5" t="n"/>
-      <c r="O98" s="134" t="n"/>
-      <c r="P98" s="134" t="n"/>
+      <c r="O98" s="111" t="n"/>
+      <c r="P98" s="111" t="n"/>
       <c r="Q98" s="44" t="n"/>
       <c r="R98" s="44" t="n"/>
     </row>
     <row r="99" ht="27.6" customHeight="1">
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="297" t="n">
+      <c r="D99" s="155" t="n">
         <v>16</v>
       </c>
-      <c r="E99" s="294" t="n"/>
-      <c r="F99" s="327" t="n"/>
-      <c r="G99" s="327" t="n"/>
-      <c r="H99" s="327" t="n"/>
-      <c r="I99" s="327" t="n"/>
-      <c r="J99" s="327" t="n"/>
-      <c r="K99" s="327" t="n"/>
-      <c r="L99" s="327" t="n"/>
-      <c r="M99" s="328" t="n"/>
+      <c r="E99" s="134" t="n"/>
+      <c r="F99" s="135" t="n"/>
+      <c r="G99" s="135" t="n"/>
+      <c r="H99" s="135" t="n"/>
+      <c r="I99" s="135" t="n"/>
+      <c r="J99" s="135" t="n"/>
+      <c r="K99" s="135" t="n"/>
+      <c r="L99" s="135" t="n"/>
+      <c r="M99" s="136" t="n"/>
       <c r="N99" s="5" t="n"/>
-      <c r="O99" s="136" t="inlineStr">
+      <c r="O99" s="154" t="inlineStr">
         <is>
           <t>CIERRE DEL PROYECTO</t>
         </is>
@@ -5293,20 +5176,20 @@
     <row r="100" ht="27.6" customHeight="1">
       <c r="B100" s="8" t="n"/>
       <c r="C100" s="8" t="n"/>
-      <c r="D100" s="293" t="n">
+      <c r="D100" s="232" t="n">
         <v>17</v>
       </c>
-      <c r="E100" s="295" t="n"/>
-      <c r="F100" s="327" t="n"/>
-      <c r="G100" s="327" t="n"/>
-      <c r="H100" s="327" t="n"/>
-      <c r="I100" s="327" t="n"/>
-      <c r="J100" s="327" t="n"/>
-      <c r="K100" s="327" t="n"/>
-      <c r="L100" s="327" t="n"/>
-      <c r="M100" s="328" t="n"/>
+      <c r="E100" s="158" t="n"/>
+      <c r="F100" s="135" t="n"/>
+      <c r="G100" s="135" t="n"/>
+      <c r="H100" s="135" t="n"/>
+      <c r="I100" s="135" t="n"/>
+      <c r="J100" s="135" t="n"/>
+      <c r="K100" s="135" t="n"/>
+      <c r="L100" s="135" t="n"/>
+      <c r="M100" s="136" t="n"/>
       <c r="N100" s="5" t="n"/>
-      <c r="O100" s="135" t="inlineStr">
+      <c r="O100" s="242" t="inlineStr">
         <is>
           <t>Si existen facturas pendientes de pago al finalizar el proyecto será notificado. De no recibir respuesta dentro de los próximos 15 días calendario se considerará como aceptado, se cancelará el monto pendiente y se emitirá el finiquito por el cierre del proyecto</t>
         </is>
@@ -5317,18 +5200,18 @@
     <row r="101" ht="27.6" customHeight="1">
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="297" t="n">
+      <c r="D101" s="155" t="n">
         <v>18</v>
       </c>
-      <c r="E101" s="294" t="n"/>
-      <c r="F101" s="327" t="n"/>
-      <c r="G101" s="327" t="n"/>
-      <c r="H101" s="327" t="n"/>
-      <c r="I101" s="327" t="n"/>
-      <c r="J101" s="327" t="n"/>
-      <c r="K101" s="327" t="n"/>
-      <c r="L101" s="327" t="n"/>
-      <c r="M101" s="328" t="n"/>
+      <c r="E101" s="134" t="n"/>
+      <c r="F101" s="135" t="n"/>
+      <c r="G101" s="135" t="n"/>
+      <c r="H101" s="135" t="n"/>
+      <c r="I101" s="135" t="n"/>
+      <c r="J101" s="135" t="n"/>
+      <c r="K101" s="135" t="n"/>
+      <c r="L101" s="135" t="n"/>
+      <c r="M101" s="136" t="n"/>
       <c r="N101" s="5" t="n"/>
       <c r="Q101" s="44" t="n"/>
       <c r="R101" s="44" t="n"/>
@@ -5336,18 +5219,18 @@
     <row r="102" ht="27.6" customHeight="1">
       <c r="B102" s="8" t="n"/>
       <c r="C102" s="8" t="n"/>
-      <c r="D102" s="293" t="n">
+      <c r="D102" s="232" t="n">
         <v>19</v>
       </c>
-      <c r="E102" s="295" t="n"/>
-      <c r="F102" s="327" t="n"/>
-      <c r="G102" s="327" t="n"/>
-      <c r="H102" s="327" t="n"/>
-      <c r="I102" s="327" t="n"/>
-      <c r="J102" s="327" t="n"/>
-      <c r="K102" s="327" t="n"/>
-      <c r="L102" s="327" t="n"/>
-      <c r="M102" s="328" t="n"/>
+      <c r="E102" s="158" t="n"/>
+      <c r="F102" s="135" t="n"/>
+      <c r="G102" s="135" t="n"/>
+      <c r="H102" s="135" t="n"/>
+      <c r="I102" s="135" t="n"/>
+      <c r="J102" s="135" t="n"/>
+      <c r="K102" s="135" t="n"/>
+      <c r="L102" s="135" t="n"/>
+      <c r="M102" s="136" t="n"/>
       <c r="N102" s="5" t="n"/>
       <c r="Q102" s="44" t="n"/>
       <c r="R102" s="44" t="n"/>
@@ -5355,18 +5238,18 @@
     <row r="103" ht="27.6" customHeight="1">
       <c r="B103" s="8" t="n"/>
       <c r="C103" s="8" t="n"/>
-      <c r="D103" s="297" t="n">
+      <c r="D103" s="155" t="n">
         <v>20</v>
       </c>
-      <c r="E103" s="294" t="n"/>
-      <c r="F103" s="327" t="n"/>
-      <c r="G103" s="327" t="n"/>
-      <c r="H103" s="327" t="n"/>
-      <c r="I103" s="327" t="n"/>
-      <c r="J103" s="327" t="n"/>
-      <c r="K103" s="327" t="n"/>
-      <c r="L103" s="327" t="n"/>
-      <c r="M103" s="328" t="n"/>
+      <c r="E103" s="134" t="n"/>
+      <c r="F103" s="135" t="n"/>
+      <c r="G103" s="135" t="n"/>
+      <c r="H103" s="135" t="n"/>
+      <c r="I103" s="135" t="n"/>
+      <c r="J103" s="135" t="n"/>
+      <c r="K103" s="135" t="n"/>
+      <c r="L103" s="135" t="n"/>
+      <c r="M103" s="136" t="n"/>
       <c r="N103" s="5" t="n"/>
       <c r="Q103" s="44" t="n"/>
       <c r="R103" s="44" t="n"/>
@@ -5374,18 +5257,18 @@
     <row r="104" ht="27.6" customHeight="1">
       <c r="B104" s="8" t="n"/>
       <c r="C104" s="8" t="n"/>
-      <c r="D104" s="293" t="n">
+      <c r="D104" s="232" t="n">
         <v>21</v>
       </c>
-      <c r="E104" s="295" t="n"/>
-      <c r="F104" s="327" t="n"/>
-      <c r="G104" s="327" t="n"/>
-      <c r="H104" s="327" t="n"/>
-      <c r="I104" s="327" t="n"/>
-      <c r="J104" s="327" t="n"/>
-      <c r="K104" s="327" t="n"/>
-      <c r="L104" s="327" t="n"/>
-      <c r="M104" s="328" t="n"/>
+      <c r="E104" s="158" t="n"/>
+      <c r="F104" s="135" t="n"/>
+      <c r="G104" s="135" t="n"/>
+      <c r="H104" s="135" t="n"/>
+      <c r="I104" s="135" t="n"/>
+      <c r="J104" s="135" t="n"/>
+      <c r="K104" s="135" t="n"/>
+      <c r="L104" s="135" t="n"/>
+      <c r="M104" s="136" t="n"/>
       <c r="N104" s="5" t="n"/>
       <c r="Q104" s="44" t="n"/>
       <c r="R104" s="44" t="n"/>
@@ -5393,60 +5276,60 @@
     <row r="105" ht="27.6" customHeight="1">
       <c r="B105" s="8" t="n"/>
       <c r="C105" s="8" t="n"/>
-      <c r="D105" s="297" t="n">
+      <c r="D105" s="155" t="n">
         <v>22</v>
       </c>
-      <c r="E105" s="294" t="n"/>
-      <c r="F105" s="327" t="n"/>
-      <c r="G105" s="327" t="n"/>
-      <c r="H105" s="327" t="n"/>
-      <c r="I105" s="327" t="n"/>
-      <c r="J105" s="327" t="n"/>
-      <c r="K105" s="327" t="n"/>
-      <c r="L105" s="327" t="n"/>
-      <c r="M105" s="328" t="n"/>
+      <c r="E105" s="134" t="n"/>
+      <c r="F105" s="135" t="n"/>
+      <c r="G105" s="135" t="n"/>
+      <c r="H105" s="135" t="n"/>
+      <c r="I105" s="135" t="n"/>
+      <c r="J105" s="135" t="n"/>
+      <c r="K105" s="135" t="n"/>
+      <c r="L105" s="135" t="n"/>
+      <c r="M105" s="136" t="n"/>
       <c r="N105" s="5" t="n"/>
-      <c r="O105" s="329" t="n"/>
-      <c r="P105" s="329" t="n"/>
+      <c r="O105" s="176" t="n"/>
+      <c r="P105" s="176" t="n"/>
       <c r="Q105" s="44" t="n"/>
       <c r="R105" s="44" t="n"/>
     </row>
     <row r="106" ht="27.6" customHeight="1">
       <c r="B106" s="8" t="n"/>
       <c r="C106" s="8" t="n"/>
-      <c r="D106" s="293" t="n">
+      <c r="D106" s="232" t="n">
         <v>23</v>
       </c>
-      <c r="E106" s="295" t="n"/>
-      <c r="F106" s="327" t="n"/>
-      <c r="G106" s="327" t="n"/>
-      <c r="H106" s="327" t="n"/>
-      <c r="I106" s="327" t="n"/>
-      <c r="J106" s="327" t="n"/>
-      <c r="K106" s="327" t="n"/>
-      <c r="L106" s="327" t="n"/>
-      <c r="M106" s="328" t="n"/>
+      <c r="E106" s="158" t="n"/>
+      <c r="F106" s="135" t="n"/>
+      <c r="G106" s="135" t="n"/>
+      <c r="H106" s="135" t="n"/>
+      <c r="I106" s="135" t="n"/>
+      <c r="J106" s="135" t="n"/>
+      <c r="K106" s="135" t="n"/>
+      <c r="L106" s="135" t="n"/>
+      <c r="M106" s="136" t="n"/>
       <c r="N106" s="5" t="n"/>
-      <c r="O106" s="330" t="n"/>
-      <c r="P106" s="168" t="n"/>
+      <c r="O106" s="163" t="n"/>
+      <c r="P106" s="153" t="n"/>
       <c r="Q106" s="44" t="n"/>
       <c r="R106" s="44" t="n"/>
     </row>
     <row r="107" ht="27.6" customHeight="1">
       <c r="B107" s="8" t="n"/>
       <c r="C107" s="8" t="n"/>
-      <c r="D107" s="297" t="n">
+      <c r="D107" s="155" t="n">
         <v>24</v>
       </c>
-      <c r="E107" s="294" t="n"/>
-      <c r="F107" s="327" t="n"/>
-      <c r="G107" s="327" t="n"/>
-      <c r="H107" s="327" t="n"/>
-      <c r="I107" s="327" t="n"/>
-      <c r="J107" s="327" t="n"/>
-      <c r="K107" s="327" t="n"/>
-      <c r="L107" s="327" t="n"/>
-      <c r="M107" s="328" t="n"/>
+      <c r="E107" s="134" t="n"/>
+      <c r="F107" s="135" t="n"/>
+      <c r="G107" s="135" t="n"/>
+      <c r="H107" s="135" t="n"/>
+      <c r="I107" s="135" t="n"/>
+      <c r="J107" s="135" t="n"/>
+      <c r="K107" s="135" t="n"/>
+      <c r="L107" s="135" t="n"/>
+      <c r="M107" s="136" t="n"/>
       <c r="N107" s="5" t="n"/>
       <c r="Q107" s="44" t="n"/>
       <c r="R107" s="44" t="n"/>
@@ -5454,18 +5337,18 @@
     <row r="108" ht="27.6" customHeight="1">
       <c r="B108" s="8" t="n"/>
       <c r="C108" s="8" t="n"/>
-      <c r="D108" s="293" t="n">
+      <c r="D108" s="232" t="n">
         <v>25</v>
       </c>
-      <c r="E108" s="295" t="n"/>
-      <c r="F108" s="327" t="n"/>
-      <c r="G108" s="327" t="n"/>
-      <c r="H108" s="327" t="n"/>
-      <c r="I108" s="327" t="n"/>
-      <c r="J108" s="327" t="n"/>
-      <c r="K108" s="327" t="n"/>
-      <c r="L108" s="327" t="n"/>
-      <c r="M108" s="328" t="n"/>
+      <c r="E108" s="158" t="n"/>
+      <c r="F108" s="135" t="n"/>
+      <c r="G108" s="135" t="n"/>
+      <c r="H108" s="135" t="n"/>
+      <c r="I108" s="135" t="n"/>
+      <c r="J108" s="135" t="n"/>
+      <c r="K108" s="135" t="n"/>
+      <c r="L108" s="135" t="n"/>
+      <c r="M108" s="136" t="n"/>
       <c r="N108" s="5" t="n"/>
       <c r="Q108" s="44" t="n"/>
       <c r="R108" s="44" t="n"/>
@@ -5473,18 +5356,18 @@
     <row r="109" ht="27.6" customHeight="1">
       <c r="B109" s="8" t="n"/>
       <c r="C109" s="8" t="n"/>
-      <c r="D109" s="297" t="n">
+      <c r="D109" s="155" t="n">
         <v>26</v>
       </c>
-      <c r="E109" s="294" t="n"/>
-      <c r="F109" s="327" t="n"/>
-      <c r="G109" s="327" t="n"/>
-      <c r="H109" s="327" t="n"/>
-      <c r="I109" s="327" t="n"/>
-      <c r="J109" s="327" t="n"/>
-      <c r="K109" s="327" t="n"/>
-      <c r="L109" s="327" t="n"/>
-      <c r="M109" s="328" t="n"/>
+      <c r="E109" s="134" t="n"/>
+      <c r="F109" s="135" t="n"/>
+      <c r="G109" s="135" t="n"/>
+      <c r="H109" s="135" t="n"/>
+      <c r="I109" s="135" t="n"/>
+      <c r="J109" s="135" t="n"/>
+      <c r="K109" s="135" t="n"/>
+      <c r="L109" s="135" t="n"/>
+      <c r="M109" s="136" t="n"/>
       <c r="N109" s="5" t="n"/>
       <c r="Q109" s="44" t="n"/>
       <c r="R109" s="44" t="n"/>
@@ -5492,18 +5375,18 @@
     <row r="110" ht="27.6" customHeight="1">
       <c r="B110" s="8" t="n"/>
       <c r="C110" s="8" t="n"/>
-      <c r="D110" s="293" t="n">
+      <c r="D110" s="232" t="n">
         <v>27</v>
       </c>
-      <c r="E110" s="295" t="n"/>
-      <c r="F110" s="327" t="n"/>
-      <c r="G110" s="327" t="n"/>
-      <c r="H110" s="327" t="n"/>
-      <c r="I110" s="327" t="n"/>
-      <c r="J110" s="327" t="n"/>
-      <c r="K110" s="327" t="n"/>
-      <c r="L110" s="327" t="n"/>
-      <c r="M110" s="328" t="n"/>
+      <c r="E110" s="158" t="n"/>
+      <c r="F110" s="135" t="n"/>
+      <c r="G110" s="135" t="n"/>
+      <c r="H110" s="135" t="n"/>
+      <c r="I110" s="135" t="n"/>
+      <c r="J110" s="135" t="n"/>
+      <c r="K110" s="135" t="n"/>
+      <c r="L110" s="135" t="n"/>
+      <c r="M110" s="136" t="n"/>
       <c r="N110" s="5" t="n"/>
       <c r="Q110" s="44" t="n"/>
       <c r="R110" s="44" t="n"/>
@@ -5511,44 +5394,44 @@
     <row r="111" ht="27.6" customHeight="1" thickBot="1">
       <c r="B111" s="8" t="n"/>
       <c r="C111" s="8" t="n"/>
-      <c r="D111" s="297" t="n">
+      <c r="D111" s="155" t="n">
         <v>28</v>
       </c>
-      <c r="E111" s="294" t="n"/>
-      <c r="F111" s="327" t="n"/>
-      <c r="G111" s="327" t="n"/>
-      <c r="H111" s="327" t="n"/>
-      <c r="I111" s="327" t="n"/>
-      <c r="J111" s="327" t="n"/>
-      <c r="K111" s="327" t="n"/>
-      <c r="L111" s="327" t="n"/>
-      <c r="M111" s="328" t="n"/>
+      <c r="E111" s="134" t="n"/>
+      <c r="F111" s="135" t="n"/>
+      <c r="G111" s="135" t="n"/>
+      <c r="H111" s="135" t="n"/>
+      <c r="I111" s="135" t="n"/>
+      <c r="J111" s="135" t="n"/>
+      <c r="K111" s="135" t="n"/>
+      <c r="L111" s="135" t="n"/>
+      <c r="M111" s="136" t="n"/>
       <c r="N111" s="5" t="n"/>
-      <c r="O111" s="331" t="n"/>
-      <c r="P111" s="331" t="n"/>
+      <c r="O111" s="164" t="n"/>
+      <c r="P111" s="164" t="n"/>
       <c r="Q111" s="46" t="n"/>
       <c r="R111" s="46" t="n"/>
     </row>
     <row r="112" ht="27.6" customHeight="1">
       <c r="B112" s="8" t="n"/>
       <c r="C112" s="8" t="n"/>
-      <c r="D112" s="115" t="n"/>
-      <c r="E112" s="116" t="n"/>
-      <c r="F112" s="116" t="n"/>
-      <c r="G112" s="116" t="n"/>
-      <c r="H112" s="116" t="n"/>
-      <c r="I112" s="116" t="n"/>
-      <c r="J112" s="116" t="n"/>
-      <c r="K112" s="116" t="n"/>
-      <c r="L112" s="116" t="n"/>
-      <c r="M112" s="116" t="n"/>
+      <c r="D112" s="112" t="n"/>
+      <c r="E112" s="113" t="n"/>
+      <c r="F112" s="113" t="n"/>
+      <c r="G112" s="113" t="n"/>
+      <c r="H112" s="113" t="n"/>
+      <c r="I112" s="113" t="n"/>
+      <c r="J112" s="113" t="n"/>
+      <c r="K112" s="113" t="n"/>
+      <c r="L112" s="113" t="n"/>
+      <c r="M112" s="113" t="n"/>
       <c r="N112" s="5" t="n"/>
-      <c r="O112" s="152" t="inlineStr">
+      <c r="O112" s="238" t="inlineStr">
         <is>
           <t>FIRMA - Proveedor o contratista</t>
         </is>
       </c>
-      <c r="P112" s="332" t="n"/>
+      <c r="P112" s="239" t="n"/>
       <c r="Q112" s="46" t="n"/>
       <c r="R112" s="46" t="n"/>
     </row>
@@ -5556,7 +5439,7 @@
       <c r="B113" s="8" t="n"/>
       <c r="C113" s="8" t="n"/>
       <c r="D113" s="104" t="n"/>
-      <c r="E113" s="175" t="n"/>
+      <c r="E113" s="162" t="n"/>
       <c r="F113" s="105" t="n"/>
       <c r="G113" s="105" t="n"/>
       <c r="H113" s="105" t="n"/>
@@ -5566,485 +5449,279 @@
       <c r="L113" s="105" t="n"/>
       <c r="M113" s="105" t="n"/>
       <c r="N113" s="5" t="n"/>
-      <c r="O113" s="174" t="n"/>
-      <c r="P113" s="174" t="n"/>
+      <c r="O113" s="123" t="n"/>
+      <c r="P113" s="123" t="n"/>
       <c r="Q113" s="44" t="n"/>
       <c r="R113" s="44" t="n"/>
     </row>
-    <row r="114" hidden="1" ht="30" customHeight="1">
-      <c r="B114" s="8" t="n"/>
-      <c r="C114" s="8" t="n"/>
-      <c r="D114" s="107" t="inlineStr">
-        <is>
-          <t>NO.</t>
-        </is>
-      </c>
-      <c r="E114" s="131" t="inlineStr">
-        <is>
-          <t>CONDICIONES ESPECIALES</t>
-        </is>
-      </c>
-      <c r="F114" s="147" t="n"/>
-      <c r="G114" s="147" t="n"/>
-      <c r="H114" s="147" t="n"/>
-      <c r="I114" s="147" t="n"/>
-      <c r="J114" s="147" t="n"/>
-      <c r="K114" s="147" t="n"/>
-      <c r="L114" s="147" t="n"/>
-      <c r="M114" s="147" t="n"/>
-      <c r="N114" s="147" t="n"/>
-      <c r="O114" s="147" t="n"/>
-      <c r="P114" s="147" t="n"/>
-      <c r="Q114" s="44" t="n"/>
-      <c r="R114" s="44" t="n"/>
-    </row>
-    <row r="115" hidden="1" ht="21" customFormat="1" customHeight="1" s="174">
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="133" t="inlineStr">
-        <is>
-          <t>{{CONDICIONES_ESPECIALES}}</t>
-        </is>
-      </c>
-      <c r="F115" s="309" t="n"/>
-      <c r="G115" s="309" t="n"/>
-      <c r="H115" s="309" t="n"/>
-      <c r="I115" s="309" t="n"/>
-      <c r="J115" s="309" t="n"/>
-      <c r="K115" s="309" t="n"/>
-      <c r="L115" s="309" t="n"/>
-      <c r="M115" s="309" t="n"/>
-      <c r="N115" s="309" t="n"/>
-      <c r="O115" s="309" t="n"/>
-      <c r="P115" s="314" t="n"/>
+    <row r="114" ht="28.8" customHeight="1">
+      <c r="B114" s="74" t="n"/>
+      <c r="C114" s="74" t="n"/>
+      <c r="D114" s="214" t="inlineStr">
+        <is>
+          <t>AREA DE FIRMAS</t>
+        </is>
+      </c>
+      <c r="Q114" s="55" t="n"/>
+      <c r="R114" s="55" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="74" t="n"/>
+      <c r="C115" s="74" t="n"/>
+      <c r="D115" s="56" t="n"/>
+      <c r="E115" s="55" t="n"/>
+      <c r="F115" s="55" t="n"/>
+      <c r="G115" s="55" t="n"/>
+      <c r="H115" s="55" t="n"/>
+      <c r="I115" s="55" t="n"/>
+      <c r="J115" s="55" t="n"/>
+      <c r="K115" s="55" t="n"/>
+      <c r="L115" s="55" t="n"/>
+      <c r="M115" s="55" t="n"/>
+      <c r="N115" s="55" t="n"/>
+      <c r="O115" s="55" t="n"/>
+      <c r="P115" s="55" t="n"/>
       <c r="Q115" s="55" t="n"/>
       <c r="R115" s="55" t="n"/>
     </row>
-    <row r="116" hidden="1" ht="21" customFormat="1" customHeight="1" s="174">
-      <c r="B116" s="8" t="n"/>
-      <c r="C116" s="8" t="n"/>
-      <c r="D116" s="113" t="n">
-        <v>2</v>
-      </c>
-      <c r="E116" s="149" t="n"/>
-      <c r="F116" s="309" t="n"/>
-      <c r="G116" s="309" t="n"/>
-      <c r="H116" s="309" t="n"/>
-      <c r="I116" s="309" t="n"/>
-      <c r="J116" s="309" t="n"/>
-      <c r="K116" s="309" t="n"/>
-      <c r="L116" s="309" t="n"/>
-      <c r="M116" s="309" t="n"/>
-      <c r="N116" s="309" t="n"/>
-      <c r="O116" s="309" t="n"/>
-      <c r="P116" s="314" t="n"/>
+    <row r="116" ht="24" customHeight="1">
+      <c r="B116" s="74" t="n"/>
+      <c r="C116" s="74" t="n"/>
+      <c r="D116" s="172" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA E4</t>
+        </is>
+      </c>
+      <c r="G116" s="55" t="n"/>
+      <c r="H116" s="172" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA E4</t>
+        </is>
+      </c>
+      <c r="K116" s="55" t="n"/>
+      <c r="L116" s="172" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA E4</t>
+        </is>
+      </c>
+      <c r="N116" s="55" t="n"/>
+      <c r="O116" s="172" t="inlineStr">
+        <is>
+          <t>PROVEEDOR O CONTRATISTA</t>
+        </is>
+      </c>
       <c r="Q116" s="55" t="n"/>
       <c r="R116" s="55" t="n"/>
     </row>
-    <row r="117" hidden="1" ht="21" customFormat="1" customHeight="1" s="174">
-      <c r="B117" s="8" t="n"/>
-      <c r="C117" s="8" t="n"/>
-      <c r="D117" s="108" t="n">
-        <v>3</v>
-      </c>
-      <c r="E117" s="148" t="n"/>
-      <c r="F117" s="309" t="n"/>
-      <c r="G117" s="309" t="n"/>
-      <c r="H117" s="309" t="n"/>
-      <c r="I117" s="309" t="n"/>
-      <c r="J117" s="309" t="n"/>
-      <c r="K117" s="309" t="n"/>
-      <c r="L117" s="309" t="n"/>
-      <c r="M117" s="309" t="n"/>
-      <c r="N117" s="309" t="n"/>
-      <c r="O117" s="309" t="n"/>
-      <c r="P117" s="314" t="n"/>
+    <row r="117" ht="24" customFormat="1" customHeight="1" s="123">
+      <c r="B117" s="74" t="n"/>
+      <c r="C117" s="74" t="n"/>
+      <c r="D117" s="55" t="n"/>
+      <c r="E117" s="55" t="n"/>
+      <c r="F117" s="55" t="n"/>
+      <c r="G117" s="55" t="n"/>
+      <c r="H117" s="55" t="n"/>
+      <c r="I117" s="55" t="n"/>
+      <c r="J117" s="55" t="n"/>
+      <c r="K117" s="55" t="n"/>
+      <c r="L117" s="55" t="n"/>
+      <c r="M117" s="55" t="n"/>
+      <c r="N117" s="55" t="n"/>
+      <c r="O117" s="55" t="n"/>
+      <c r="P117" s="55" t="n"/>
       <c r="Q117" s="55" t="n"/>
       <c r="R117" s="55" t="n"/>
     </row>
-    <row r="118" hidden="1" ht="24" customHeight="1">
-      <c r="B118" s="174" t="n"/>
-      <c r="C118" s="174" t="n"/>
-      <c r="D118" s="113" t="n">
-        <v>4</v>
-      </c>
-      <c r="E118" s="149" t="n"/>
-      <c r="F118" s="309" t="n"/>
-      <c r="G118" s="309" t="n"/>
-      <c r="H118" s="309" t="n"/>
-      <c r="I118" s="309" t="n"/>
-      <c r="J118" s="309" t="n"/>
-      <c r="K118" s="309" t="n"/>
-      <c r="L118" s="309" t="n"/>
-      <c r="M118" s="309" t="n"/>
-      <c r="N118" s="309" t="n"/>
-      <c r="O118" s="309" t="n"/>
-      <c r="P118" s="314" t="n"/>
-    </row>
-    <row r="119" hidden="1" ht="24" customHeight="1">
-      <c r="B119" s="174" t="n"/>
-      <c r="C119" s="174" t="n"/>
-      <c r="D119" s="108" t="n">
-        <v>5</v>
-      </c>
-      <c r="E119" s="150" t="n"/>
-      <c r="F119" s="309" t="n"/>
-      <c r="G119" s="309" t="n"/>
-      <c r="H119" s="309" t="n"/>
-      <c r="I119" s="309" t="n"/>
-      <c r="J119" s="309" t="n"/>
-      <c r="K119" s="309" t="n"/>
-      <c r="L119" s="309" t="n"/>
-      <c r="M119" s="309" t="n"/>
-      <c r="N119" s="309" t="n"/>
-      <c r="O119" s="309" t="n"/>
-      <c r="P119" s="314" t="n"/>
-    </row>
-    <row r="120" hidden="1" ht="21" customFormat="1" customHeight="1" s="174">
-      <c r="B120" s="8" t="n"/>
-      <c r="C120" s="8" t="n"/>
-      <c r="D120" s="113" t="n">
-        <v>6</v>
-      </c>
-      <c r="E120" s="149" t="n"/>
-      <c r="F120" s="309" t="n"/>
-      <c r="G120" s="309" t="n"/>
-      <c r="H120" s="309" t="n"/>
-      <c r="I120" s="309" t="n"/>
-      <c r="J120" s="309" t="n"/>
-      <c r="K120" s="309" t="n"/>
-      <c r="L120" s="309" t="n"/>
-      <c r="M120" s="309" t="n"/>
-      <c r="N120" s="309" t="n"/>
-      <c r="O120" s="309" t="n"/>
-      <c r="P120" s="314" t="n"/>
+    <row r="118" ht="24" customHeight="1">
+      <c r="B118" s="74" t="n"/>
+      <c r="C118" s="74" t="n"/>
+      <c r="D118" s="292" t="inlineStr">
+        <is>
+          <t>{{FIRMA_LIDER}}</t>
+        </is>
+      </c>
+      <c r="G118" s="55" t="n"/>
+      <c r="H118" s="292" t="inlineStr">
+        <is>
+          <t>{{FIRMA_GERENTE}}</t>
+        </is>
+      </c>
+      <c r="K118" s="55" t="n"/>
+      <c r="L118" s="292" t="inlineStr">
+        <is>
+          <t>{{FIRMA_MELISSA}}</t>
+        </is>
+      </c>
+      <c r="N118" s="55" t="n"/>
+      <c r="O118" s="92" t="n"/>
+      <c r="P118" s="92" t="n"/>
+      <c r="Q118" s="55" t="n"/>
+      <c r="R118" s="55" t="n"/>
+    </row>
+    <row r="119" ht="24" customHeight="1">
+      <c r="B119" s="74" t="n"/>
+      <c r="C119" s="74" t="n"/>
+      <c r="G119" s="55" t="n"/>
+      <c r="K119" s="55" t="n"/>
+      <c r="N119" s="55" t="n"/>
+      <c r="O119" s="92" t="n"/>
+      <c r="P119" s="92" t="n"/>
+      <c r="Q119" s="55" t="n"/>
+      <c r="R119" s="55" t="n"/>
+    </row>
+    <row r="120" ht="24" customHeight="1">
+      <c r="B120" s="74" t="n"/>
+      <c r="C120" s="74" t="n"/>
+      <c r="G120" s="55" t="n"/>
+      <c r="K120" s="55" t="n"/>
+      <c r="N120" s="55" t="n"/>
+      <c r="O120" s="92" t="n"/>
+      <c r="P120" s="92" t="n"/>
       <c r="Q120" s="55" t="n"/>
       <c r="R120" s="55" t="n"/>
     </row>
-    <row r="121" hidden="1" ht="21" customFormat="1" customHeight="1" s="174">
-      <c r="B121" s="8" t="n"/>
-      <c r="C121" s="8" t="n"/>
-      <c r="D121" s="108" t="n">
-        <v>7</v>
-      </c>
-      <c r="E121" s="148" t="n"/>
-      <c r="F121" s="309" t="n"/>
-      <c r="G121" s="309" t="n"/>
-      <c r="H121" s="309" t="n"/>
-      <c r="I121" s="309" t="n"/>
-      <c r="J121" s="309" t="n"/>
-      <c r="K121" s="309" t="n"/>
-      <c r="L121" s="309" t="n"/>
-      <c r="M121" s="309" t="n"/>
-      <c r="N121" s="309" t="n"/>
-      <c r="O121" s="309" t="n"/>
-      <c r="P121" s="314" t="n"/>
+    <row r="121" ht="24" customHeight="1">
+      <c r="B121" s="74" t="n"/>
+      <c r="C121" s="74" t="n"/>
+      <c r="D121" s="176" t="n"/>
+      <c r="E121" s="176" t="n"/>
+      <c r="F121" s="176" t="n"/>
+      <c r="G121" s="55" t="n"/>
+      <c r="H121" s="176" t="n"/>
+      <c r="I121" s="176" t="n"/>
+      <c r="J121" s="176" t="n"/>
+      <c r="K121" s="55" t="n"/>
+      <c r="L121" s="176" t="n"/>
+      <c r="M121" s="176" t="n"/>
+      <c r="N121" s="55" t="n"/>
+      <c r="O121" s="175" t="n"/>
+      <c r="P121" s="175" t="n"/>
       <c r="Q121" s="55" t="n"/>
       <c r="R121" s="55" t="n"/>
     </row>
-    <row r="122" hidden="1" ht="21" customFormat="1" customHeight="1" s="174">
-      <c r="B122" s="8" t="n"/>
-      <c r="C122" s="8" t="n"/>
-      <c r="D122" s="113" t="n">
-        <v>8</v>
-      </c>
-      <c r="E122" s="149" t="n"/>
-      <c r="F122" s="309" t="n"/>
-      <c r="G122" s="309" t="n"/>
-      <c r="H122" s="309" t="n"/>
-      <c r="I122" s="309" t="n"/>
-      <c r="J122" s="309" t="n"/>
-      <c r="K122" s="309" t="n"/>
-      <c r="L122" s="309" t="n"/>
-      <c r="M122" s="309" t="n"/>
-      <c r="N122" s="309" t="n"/>
-      <c r="O122" s="309" t="n"/>
-      <c r="P122" s="314" t="n"/>
+    <row r="122" ht="24" customFormat="1" customHeight="1" s="123">
+      <c r="B122" s="74" t="n"/>
+      <c r="C122" s="74" t="n"/>
+      <c r="D122" s="208" t="inlineStr">
+        <is>
+          <t>FIRMA - Líder de proyecto</t>
+        </is>
+      </c>
+      <c r="G122" s="208" t="n"/>
+      <c r="H122" s="122" t="inlineStr">
+        <is>
+          <t>FIRMA - Gerente de proyecto</t>
+        </is>
+      </c>
+      <c r="K122" s="208" t="n"/>
+      <c r="L122" s="152" t="inlineStr">
+        <is>
+          <t>FIRMA - Gerente de procurement</t>
+        </is>
+      </c>
+      <c r="M122" s="153" t="n"/>
+      <c r="N122" s="208" t="n"/>
+      <c r="O122" s="152" t="inlineStr">
+        <is>
+          <t>FIRMA - Contratista</t>
+        </is>
+      </c>
+      <c r="P122" s="153" t="n"/>
       <c r="Q122" s="55" t="n"/>
       <c r="R122" s="55" t="n"/>
     </row>
-    <row r="123" ht="27" customFormat="1" customHeight="1" s="174">
+    <row r="123" ht="24.9" customFormat="1" customHeight="1" s="123">
       <c r="B123" s="74" t="n"/>
       <c r="C123" s="74" t="n"/>
-      <c r="D123" s="183" t="n"/>
+      <c r="D123" s="160" t="inlineStr">
+        <is>
+          <t>{{LIDER}}</t>
+        </is>
+      </c>
+      <c r="E123" s="161" t="n"/>
+      <c r="F123" s="161" t="n"/>
+      <c r="G123" s="174" t="n"/>
+      <c r="H123" s="160" t="inlineStr">
+        <is>
+          <t>{{GERENTE_PROYECTO}}</t>
+        </is>
+      </c>
+      <c r="I123" s="161" t="n"/>
+      <c r="J123" s="161" t="n"/>
+      <c r="K123" s="208" t="n"/>
+      <c r="L123" s="174" t="inlineStr">
+        <is>
+          <t>Arq. Melissa Alvarenga</t>
+        </is>
+      </c>
+      <c r="N123" s="208" t="n"/>
+      <c r="O123" s="160" t="inlineStr">
+        <is>
+          <t>{{CONTACTO}}</t>
+        </is>
+      </c>
+      <c r="P123" s="161" t="n"/>
       <c r="Q123" s="55" t="n"/>
       <c r="R123" s="55" t="n"/>
     </row>
-    <row r="124" ht="28.8" customHeight="1">
+    <row r="124" customFormat="1" s="123">
       <c r="B124" s="74" t="n"/>
       <c r="C124" s="74" t="n"/>
-      <c r="D124" s="201" t="inlineStr">
-        <is>
-          <t>AREA DE FIRMAS</t>
-        </is>
-      </c>
+      <c r="D124" s="55" t="n"/>
+      <c r="E124" s="55" t="n"/>
+      <c r="F124" s="55" t="n"/>
+      <c r="G124" s="55" t="n"/>
+      <c r="H124" s="55" t="n"/>
+      <c r="I124" s="55" t="n"/>
+      <c r="J124" s="55" t="n"/>
+      <c r="K124" s="55" t="n"/>
+      <c r="L124" s="77" t="n"/>
+      <c r="M124" s="77" t="n"/>
+      <c r="N124" s="55" t="n"/>
+      <c r="O124" s="77" t="n"/>
+      <c r="P124" s="78" t="n"/>
       <c r="Q124" s="55" t="n"/>
       <c r="R124" s="55" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="18" customFormat="1" customHeight="1" s="123" thickBot="1">
       <c r="B125" s="74" t="n"/>
       <c r="C125" s="74" t="n"/>
-      <c r="D125" s="56" t="n"/>
-      <c r="E125" s="55" t="n"/>
-      <c r="F125" s="55" t="n"/>
-      <c r="G125" s="55" t="n"/>
-      <c r="H125" s="55" t="n"/>
-      <c r="I125" s="55" t="n"/>
-      <c r="J125" s="55" t="n"/>
-      <c r="K125" s="55" t="n"/>
-      <c r="L125" s="55" t="n"/>
-      <c r="M125" s="55" t="n"/>
-      <c r="N125" s="55" t="n"/>
-      <c r="O125" s="55" t="n"/>
-      <c r="P125" s="55" t="n"/>
+      <c r="D125" s="79" t="n"/>
+      <c r="E125" s="80" t="n"/>
+      <c r="F125" s="80" t="n"/>
+      <c r="G125" s="80" t="n"/>
+      <c r="H125" s="80" t="n"/>
+      <c r="I125" s="80" t="n"/>
+      <c r="J125" s="80" t="n"/>
+      <c r="K125" s="80" t="n"/>
+      <c r="L125" s="80" t="n"/>
+      <c r="M125" s="80" t="n"/>
+      <c r="N125" s="80" t="n"/>
+      <c r="O125" s="80" t="n"/>
+      <c r="P125" s="80" t="n"/>
       <c r="Q125" s="55" t="n"/>
       <c r="R125" s="55" t="n"/>
     </row>
-    <row r="126" ht="24" customHeight="1">
-      <c r="B126" s="74" t="n"/>
-      <c r="C126" s="74" t="n"/>
-      <c r="D126" s="169" t="inlineStr">
-        <is>
-          <t>CONSTRUCTORA E4</t>
-        </is>
-      </c>
-      <c r="G126" s="55" t="n"/>
-      <c r="H126" s="169" t="inlineStr">
-        <is>
-          <t>CONSTRUCTORA E4</t>
-        </is>
-      </c>
-      <c r="K126" s="55" t="n"/>
-      <c r="L126" s="169" t="inlineStr">
-        <is>
-          <t>CONSTRUCTORA E4</t>
-        </is>
-      </c>
-      <c r="N126" s="55" t="n"/>
-      <c r="O126" s="169" t="inlineStr">
-        <is>
-          <t>PROVEEDOR O CONTRATISTA</t>
-        </is>
-      </c>
+    <row r="126">
       <c r="Q126" s="55" t="n"/>
       <c r="R126" s="55" t="n"/>
     </row>
-    <row r="127" ht="24" customFormat="1" customHeight="1" s="174">
-      <c r="B127" s="74" t="n"/>
-      <c r="C127" s="74" t="n"/>
-      <c r="D127" s="55" t="n"/>
-      <c r="E127" s="55" t="n"/>
-      <c r="F127" s="55" t="n"/>
-      <c r="G127" s="55" t="n"/>
-      <c r="H127" s="55" t="n"/>
-      <c r="I127" s="55" t="n"/>
-      <c r="J127" s="55" t="n"/>
-      <c r="K127" s="55" t="n"/>
-      <c r="L127" s="55" t="n"/>
-      <c r="M127" s="55" t="n"/>
-      <c r="N127" s="55" t="n"/>
-      <c r="O127" s="55" t="n"/>
-      <c r="P127" s="55" t="n"/>
-      <c r="Q127" s="55" t="n"/>
-      <c r="R127" s="55" t="n"/>
-    </row>
-    <row r="128" ht="24" customHeight="1">
-      <c r="B128" s="74" t="n"/>
-      <c r="C128" s="74" t="n"/>
-      <c r="D128" s="92" t="n"/>
-      <c r="E128" s="92" t="n"/>
-      <c r="F128" s="92" t="n"/>
-      <c r="G128" s="55" t="n"/>
-      <c r="H128" s="93" t="inlineStr">
-        <is>
-          <t>{{FIRMA_GERENTE}}</t>
-        </is>
-      </c>
-      <c r="K128" s="55" t="n"/>
-      <c r="L128" s="93" t="inlineStr">
-        <is>
-          <t>{{FIRMA_MELISSA}}</t>
-        </is>
-      </c>
-      <c r="N128" s="55" t="n"/>
-      <c r="O128" s="92" t="n"/>
-      <c r="P128" s="92" t="n"/>
-      <c r="Q128" s="55" t="n"/>
-      <c r="R128" s="55" t="n"/>
-    </row>
-    <row r="129" ht="24" customHeight="1">
-      <c r="B129" s="74" t="n"/>
-      <c r="C129" s="74" t="n"/>
-      <c r="D129" s="92" t="n"/>
-      <c r="E129" s="92" t="n"/>
-      <c r="F129" s="92" t="n"/>
-      <c r="G129" s="55" t="n"/>
-      <c r="K129" s="55" t="n"/>
-      <c r="N129" s="55" t="n"/>
-      <c r="O129" s="92" t="n"/>
-      <c r="P129" s="92" t="n"/>
-      <c r="Q129" s="55" t="n"/>
-      <c r="R129" s="55" t="n"/>
-    </row>
-    <row r="130" ht="24" customHeight="1">
-      <c r="B130" s="74" t="n"/>
-      <c r="C130" s="74" t="n"/>
-      <c r="D130" s="92" t="n"/>
-      <c r="E130" s="92" t="n"/>
-      <c r="F130" s="92" t="n"/>
-      <c r="G130" s="55" t="n"/>
-      <c r="K130" s="55" t="n"/>
-      <c r="N130" s="55" t="n"/>
-      <c r="O130" s="92" t="n"/>
-      <c r="P130" s="92" t="n"/>
-      <c r="Q130" s="55" t="n"/>
-      <c r="R130" s="55" t="n"/>
-    </row>
-    <row r="131" ht="24" customHeight="1">
-      <c r="B131" s="74" t="n"/>
-      <c r="C131" s="74" t="n"/>
-      <c r="D131" s="93" t="n"/>
-      <c r="E131" s="93" t="n"/>
-      <c r="F131" s="93" t="n"/>
-      <c r="G131" s="55" t="n"/>
-      <c r="H131" s="329" t="n"/>
-      <c r="I131" s="329" t="n"/>
-      <c r="J131" s="329" t="n"/>
-      <c r="K131" s="55" t="n"/>
-      <c r="L131" s="329" t="n"/>
-      <c r="M131" s="329" t="n"/>
-      <c r="N131" s="55" t="n"/>
-      <c r="O131" s="93" t="n"/>
-      <c r="P131" s="93" t="n"/>
-      <c r="Q131" s="55" t="n"/>
-      <c r="R131" s="55" t="n"/>
-    </row>
-    <row r="132" ht="24" customFormat="1" customHeight="1" s="174">
-      <c r="B132" s="74" t="n"/>
-      <c r="C132" s="74" t="n"/>
-      <c r="D132" s="240" t="inlineStr">
-        <is>
-          <t>FIRMA - Líder de proyecto</t>
-        </is>
-      </c>
-      <c r="G132" s="240" t="n"/>
-      <c r="H132" s="173" t="inlineStr">
-        <is>
-          <t>FIRMA - Gerente de proyecto</t>
-        </is>
-      </c>
-      <c r="K132" s="240" t="n"/>
-      <c r="L132" s="167" t="inlineStr">
-        <is>
-          <t>FIRMA - Gerente de procurement</t>
-        </is>
-      </c>
-      <c r="M132" s="168" t="n"/>
-      <c r="N132" s="240" t="n"/>
-      <c r="O132" s="167" t="inlineStr">
-        <is>
-          <t>FIRMA - Contratista</t>
-        </is>
-      </c>
-      <c r="P132" s="168" t="n"/>
-      <c r="Q132" s="55" t="n"/>
-      <c r="R132" s="55" t="n"/>
-    </row>
-    <row r="133" ht="24.9" customFormat="1" customHeight="1" s="174">
-      <c r="B133" s="74" t="n"/>
-      <c r="C133" s="74" t="n"/>
-      <c r="D133" s="186" t="inlineStr">
-        <is>
-          <t>{{LIDER}}</t>
-        </is>
-      </c>
-      <c r="E133" s="147" t="n"/>
-      <c r="F133" s="147" t="n"/>
-      <c r="G133" s="190" t="n"/>
-      <c r="H133" s="186" t="inlineStr">
-        <is>
-          <t>{{GERENTE_PROYECTO}}</t>
-        </is>
-      </c>
-      <c r="I133" s="147" t="n"/>
-      <c r="J133" s="147" t="n"/>
-      <c r="K133" s="240" t="n"/>
-      <c r="L133" s="190" t="inlineStr">
-        <is>
-          <t>Arq. Melissa Alvarenga</t>
-        </is>
-      </c>
-      <c r="N133" s="240" t="n"/>
-      <c r="O133" s="186" t="inlineStr">
-        <is>
-          <t>{{CONTACTO}}</t>
-        </is>
-      </c>
-      <c r="P133" s="147" t="n"/>
-      <c r="Q133" s="55" t="n"/>
-      <c r="R133" s="55" t="n"/>
-    </row>
-    <row r="134" customFormat="1" s="174">
-      <c r="B134" s="74" t="n"/>
-      <c r="C134" s="74" t="n"/>
-      <c r="D134" s="55" t="n"/>
-      <c r="E134" s="55" t="n"/>
-      <c r="F134" s="55" t="n"/>
-      <c r="G134" s="55" t="n"/>
-      <c r="H134" s="55" t="n"/>
-      <c r="I134" s="55" t="n"/>
-      <c r="J134" s="55" t="n"/>
-      <c r="K134" s="55" t="n"/>
-      <c r="L134" s="77" t="n"/>
-      <c r="M134" s="77" t="n"/>
-      <c r="N134" s="55" t="n"/>
-      <c r="O134" s="77" t="n"/>
-      <c r="P134" s="78" t="n"/>
-      <c r="Q134" s="55" t="n"/>
-      <c r="R134" s="55" t="n"/>
-    </row>
-    <row r="135" ht="18" customFormat="1" customHeight="1" s="174" thickBot="1">
-      <c r="B135" s="74" t="n"/>
-      <c r="C135" s="74" t="n"/>
-      <c r="D135" s="79" t="n"/>
-      <c r="E135" s="80" t="n"/>
-      <c r="F135" s="80" t="n"/>
-      <c r="G135" s="80" t="n"/>
-      <c r="H135" s="80" t="n"/>
-      <c r="I135" s="80" t="n"/>
-      <c r="J135" s="80" t="n"/>
-      <c r="K135" s="80" t="n"/>
-      <c r="L135" s="80" t="n"/>
-      <c r="M135" s="80" t="n"/>
-      <c r="N135" s="80" t="n"/>
-      <c r="O135" s="80" t="n"/>
-      <c r="P135" s="80" t="n"/>
-      <c r="Q135" s="55" t="n"/>
-      <c r="R135" s="55" t="n"/>
-    </row>
-    <row r="136">
-      <c r="Q136" s="55" t="n"/>
-      <c r="R136" s="55" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="206">
+  <mergeCells count="197">
     <mergeCell ref="M61:P61"/>
+    <mergeCell ref="H123:J123"/>
+    <mergeCell ref="D116:F116"/>
     <mergeCell ref="D32:I32"/>
-    <mergeCell ref="H132:J132"/>
     <mergeCell ref="D41:I41"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D66:F66"/>
-    <mergeCell ref="E118:P118"/>
     <mergeCell ref="N53:O53"/>
     <mergeCell ref="E105:M105"/>
+    <mergeCell ref="E99:M99"/>
     <mergeCell ref="L27:O27"/>
-    <mergeCell ref="E99:M99"/>
+    <mergeCell ref="L116:M116"/>
     <mergeCell ref="D43:I43"/>
     <mergeCell ref="L36:O36"/>
-    <mergeCell ref="D123:P123"/>
     <mergeCell ref="D26:J26"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="I25:J25"/>
@@ -6052,29 +5729,25 @@
     <mergeCell ref="D60:P60"/>
     <mergeCell ref="G66:H66"/>
     <mergeCell ref="I66:J66"/>
-    <mergeCell ref="L132:M132"/>
     <mergeCell ref="O99:P99"/>
     <mergeCell ref="E91:M91"/>
     <mergeCell ref="E85:M85"/>
     <mergeCell ref="E100:M100"/>
     <mergeCell ref="L19:O19"/>
     <mergeCell ref="L35:P35"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="E120:P120"/>
     <mergeCell ref="E81:P81"/>
     <mergeCell ref="O106:P111"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="E93:M93"/>
     <mergeCell ref="L12:O12"/>
+    <mergeCell ref="L122:M122"/>
     <mergeCell ref="E102:M102"/>
     <mergeCell ref="L4:N5"/>
-    <mergeCell ref="E121:P121"/>
     <mergeCell ref="L14:O14"/>
-    <mergeCell ref="O126:P126"/>
     <mergeCell ref="I20:J20"/>
+    <mergeCell ref="H122:J122"/>
     <mergeCell ref="D31:I31"/>
     <mergeCell ref="L46:P46"/>
-    <mergeCell ref="H128:J131"/>
     <mergeCell ref="D45:I45"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="L38:O38"/>
@@ -6091,7 +5764,6 @@
     <mergeCell ref="N51:O51"/>
     <mergeCell ref="E78:P78"/>
     <mergeCell ref="I61:J61"/>
-    <mergeCell ref="E114:P114"/>
     <mergeCell ref="K64:L64"/>
     <mergeCell ref="E90:M90"/>
     <mergeCell ref="E77:P77"/>
@@ -6111,14 +5783,12 @@
     <mergeCell ref="D33:I33"/>
     <mergeCell ref="D42:I42"/>
     <mergeCell ref="E72:P72"/>
-    <mergeCell ref="D132:F132"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="M64:P64"/>
-    <mergeCell ref="H126:J126"/>
     <mergeCell ref="G65:H65"/>
     <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D124:P124"/>
     <mergeCell ref="D44:I44"/>
+    <mergeCell ref="O123:P123"/>
     <mergeCell ref="D27:J27"/>
     <mergeCell ref="D34:I34"/>
     <mergeCell ref="D25:H25"/>
@@ -6135,40 +5805,43 @@
     <mergeCell ref="L20:O20"/>
     <mergeCell ref="F14:J14"/>
     <mergeCell ref="N55:O55"/>
+    <mergeCell ref="L118:M121"/>
     <mergeCell ref="E107:M107"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="E103:M103"/>
     <mergeCell ref="E94:M94"/>
     <mergeCell ref="L22:O22"/>
+    <mergeCell ref="D118:F121"/>
     <mergeCell ref="N54:O54"/>
     <mergeCell ref="E84:M84"/>
-    <mergeCell ref="O132:P132"/>
+    <mergeCell ref="D114:P114"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="N56:O56"/>
     <mergeCell ref="E108:M108"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="E86:M86"/>
     <mergeCell ref="F3:J3"/>
     <mergeCell ref="F15:J15"/>
+    <mergeCell ref="E86:M86"/>
     <mergeCell ref="E95:M95"/>
     <mergeCell ref="F12:J12"/>
+    <mergeCell ref="D122:F122"/>
     <mergeCell ref="E89:M89"/>
-    <mergeCell ref="L128:M131"/>
-    <mergeCell ref="E116:P116"/>
     <mergeCell ref="O112:P112"/>
     <mergeCell ref="N58:O58"/>
     <mergeCell ref="L32:O32"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="L126:M126"/>
     <mergeCell ref="O100:P105"/>
     <mergeCell ref="D38:I38"/>
     <mergeCell ref="I62:J62"/>
+    <mergeCell ref="H116:J116"/>
+    <mergeCell ref="L123:M123"/>
     <mergeCell ref="O86:P89"/>
+    <mergeCell ref="D123:F123"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="E53:J53"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="E96:M96"/>
-    <mergeCell ref="I23:J23"/>
     <mergeCell ref="E50:J50"/>
     <mergeCell ref="L33:O33"/>
     <mergeCell ref="G64:H64"/>
@@ -6190,20 +5863,18 @@
     <mergeCell ref="L25:O25"/>
     <mergeCell ref="E73:P73"/>
     <mergeCell ref="I65:J65"/>
-    <mergeCell ref="H133:J133"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D18:J18"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="F16:J16"/>
-    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="O116:P116"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="M66:P66"/>
     <mergeCell ref="L6:L8"/>
     <mergeCell ref="D37:I37"/>
     <mergeCell ref="D62:F62"/>
-    <mergeCell ref="L133:M133"/>
-    <mergeCell ref="E119:P119"/>
     <mergeCell ref="I22:J22"/>
+    <mergeCell ref="H118:J121"/>
     <mergeCell ref="M6:N8"/>
     <mergeCell ref="E54:J54"/>
     <mergeCell ref="D30:I30"/>
@@ -6216,24 +5887,21 @@
     <mergeCell ref="L29:P29"/>
     <mergeCell ref="D29:I29"/>
     <mergeCell ref="E97:M97"/>
-    <mergeCell ref="O133:P133"/>
     <mergeCell ref="E75:P75"/>
-    <mergeCell ref="E115:P115"/>
     <mergeCell ref="N57:O57"/>
+    <mergeCell ref="O93:P97"/>
     <mergeCell ref="E109:M109"/>
-    <mergeCell ref="O93:P97"/>
     <mergeCell ref="K61:L61"/>
+    <mergeCell ref="F13:J13"/>
     <mergeCell ref="L15:O15"/>
-    <mergeCell ref="F13:J13"/>
     <mergeCell ref="D63:F63"/>
     <mergeCell ref="E68:P68"/>
-    <mergeCell ref="E117:P117"/>
+    <mergeCell ref="O122:P122"/>
     <mergeCell ref="D46:I46"/>
     <mergeCell ref="D24:H24"/>
-    <mergeCell ref="E122:P122"/>
+    <mergeCell ref="E111:M111"/>
     <mergeCell ref="D40:I40"/>
     <mergeCell ref="D65:F65"/>
-    <mergeCell ref="E111:M111"/>
     <mergeCell ref="N49:O49"/>
     <mergeCell ref="K62:L62"/>
     <mergeCell ref="E87:M87"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -1303,7 +1303,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2242,6 +2242,12 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4379,9 +4385,9 @@
       <c r="H62" s="129" t="n"/>
       <c r="I62" s="243" t="n"/>
       <c r="J62" s="244" t="n"/>
-      <c r="K62" s="279" t="n"/>
+      <c r="K62" s="296" t="n"/>
       <c r="L62" s="280" t="n"/>
-      <c r="M62" s="189" t="n"/>
+      <c r="M62" s="297" t="n"/>
       <c r="N62" s="187" t="n"/>
       <c r="O62" s="187" t="n"/>
       <c r="P62" s="188" t="n"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -1303,7 +1303,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2248,6 +2248,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="4" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4648,12 +4654,12 @@
     <row r="75" ht="24.9" customHeight="1">
       <c r="B75" s="74" t="n"/>
       <c r="C75" s="74" t="n"/>
-      <c r="D75" s="288" t="inlineStr">
+      <c r="D75" s="298" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E75" s="289" t="inlineStr">
+      <c r="E75" s="299" t="inlineStr">
         <is>
           <t>SERVICIOS BASICOS NECESARIOS PARA TRABAJAR</t>
         </is>
@@ -5757,7 +5763,6 @@
     <mergeCell ref="D45:I45"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="L38:O38"/>
-    <mergeCell ref="E83:P83"/>
     <mergeCell ref="E51:J51"/>
     <mergeCell ref="L31:O31"/>
     <mergeCell ref="L40:O40"/>
@@ -5807,6 +5812,7 @@
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="D48:P48"/>
     <mergeCell ref="K66:L66"/>
+    <mergeCell ref="E83:M83"/>
     <mergeCell ref="E92:M92"/>
     <mergeCell ref="L20:O20"/>
     <mergeCell ref="F14:J14"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -1303,7 +1303,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="306">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2253,6 +2253,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4537,7 +4555,7 @@
       <c r="D69" s="108" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="186" t="inlineStr">
+      <c r="E69" s="302" t="inlineStr">
         <is>
           <t>{{TRABAJOS_PREVIOS}}</t>
         </is>
@@ -4562,7 +4580,7 @@
       <c r="D70" s="110" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="295" t="n"/>
+      <c r="E70" s="303" t="n"/>
       <c r="F70" s="187" t="n"/>
       <c r="G70" s="187" t="n"/>
       <c r="H70" s="187" t="n"/>
@@ -4684,7 +4702,7 @@
       <c r="D76" s="108" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="192" t="inlineStr">
+      <c r="E76" s="304" t="inlineStr">
         <is>
           <t>{{SERVICIOS_BASICOS}}</t>
         </is>
@@ -4709,7 +4727,7 @@
       <c r="D77" s="110" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="197" t="n"/>
+      <c r="E77" s="305" t="n"/>
       <c r="F77" s="187" t="n"/>
       <c r="G77" s="187" t="n"/>
       <c r="H77" s="187" t="n"/>
@@ -4730,7 +4748,7 @@
       <c r="D78" s="108" t="n">
         <v>3</v>
       </c>
-      <c r="E78" s="192" t="n"/>
+      <c r="E78" s="304" t="n"/>
       <c r="F78" s="187" t="n"/>
       <c r="G78" s="187" t="n"/>
       <c r="H78" s="187" t="n"/>
@@ -4841,7 +4859,7 @@
       <c r="D84" s="232" t="n">
         <v>1</v>
       </c>
-      <c r="E84" s="232" t="inlineStr">
+      <c r="E84" s="300" t="inlineStr">
         <is>
           <t>{{PUNTOS_REVISION}}</t>
         </is>
@@ -4866,7 +4884,7 @@
       <c r="D85" s="155" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="155" t="n"/>
+      <c r="E85" s="301" t="n"/>
       <c r="F85" s="156" t="n"/>
       <c r="G85" s="156" t="n"/>
       <c r="H85" s="156" t="n"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5760" yWindow="348" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="C-9-12" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-9-12" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="ACOMETIDA">#REF!</definedName>
@@ -2351,7 +2351,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
@@ -2369,24 +2369,24 @@
       <nvPicPr>
         <cNvPr id="6" name="Imagen 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="555189" y="327972"/>
           <a:ext cx="1806529" cy="1723429"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2410,24 +2410,24 @@
       <nvPicPr>
         <cNvPr id="7" name="Picture 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="12628684" y="363359"/>
           <a:ext cx="2670669" cy="1876779"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5681,7 +5681,7 @@
       <c r="K123" s="208" t="n"/>
       <c r="L123" s="174" t="inlineStr">
         <is>
-          <t>Arq. Melissa Alvarenga</t>
+          <t>ARQ. MELISSA ALVARENGA</t>
         </is>
       </c>
       <c r="N123" s="208" t="n"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -4431,7 +4431,7 @@
       <c r="H63" s="129" t="n"/>
       <c r="I63" s="253" t="n"/>
       <c r="J63" s="196" t="n"/>
-      <c r="K63" s="202" t="n"/>
+      <c r="K63" s="253" t="n"/>
       <c r="L63" s="196" t="n"/>
       <c r="M63" s="222" t="n"/>
       <c r="N63" s="129" t="n"/>
@@ -4453,7 +4453,7 @@
       <c r="H64" s="129" t="n"/>
       <c r="I64" s="251" t="n"/>
       <c r="J64" s="196" t="n"/>
-      <c r="K64" s="195" t="n"/>
+      <c r="K64" s="251" t="n"/>
       <c r="L64" s="196" t="n"/>
       <c r="M64" s="209" t="n"/>
       <c r="N64" s="129" t="n"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -90,7 +90,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;Q&quot;* #,##0.00_-;\-&quot;Q&quot;* #,##0.00_-;_-&quot;Q&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -301,6 +301,11 @@
       <color theme="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Open Sans"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1303,7 +1308,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="306">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2271,6 +2276,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5694,22 +5702,14 @@
       <c r="Q123" s="55" t="n"/>
       <c r="R123" s="55" t="n"/>
     </row>
-    <row r="124" customFormat="1" s="123">
+    <row r="124" ht="27.6" customFormat="1" customHeight="1" s="123">
       <c r="B124" s="74" t="n"/>
       <c r="C124" s="74" t="n"/>
-      <c r="D124" s="55" t="n"/>
-      <c r="E124" s="55" t="n"/>
-      <c r="F124" s="55" t="n"/>
-      <c r="G124" s="55" t="n"/>
-      <c r="H124" s="55" t="n"/>
-      <c r="I124" s="55" t="n"/>
-      <c r="J124" s="55" t="n"/>
-      <c r="K124" s="55" t="n"/>
-      <c r="L124" s="77" t="n"/>
-      <c r="M124" s="77" t="n"/>
-      <c r="N124" s="55" t="n"/>
-      <c r="O124" s="77" t="n"/>
-      <c r="P124" s="78" t="n"/>
+      <c r="D124" s="306" t="inlineStr">
+        <is>
+          <t>{{TIPO_CONTRATO_MENSAJE}}</t>
+        </is>
+      </c>
       <c r="Q124" s="55" t="n"/>
       <c r="R124" s="55" t="n"/>
     </row>
@@ -5737,7 +5737,7 @@
       <c r="R126" s="55" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="197">
+  <mergeCells count="198">
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="H123:J123"/>
     <mergeCell ref="D116:F116"/>
@@ -5816,6 +5816,7 @@
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="G65:H65"/>
     <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D124:P124"/>
     <mergeCell ref="D44:I44"/>
     <mergeCell ref="O123:P123"/>
     <mergeCell ref="D27:J27"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -1308,7 +1308,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2279,6 +2279,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2746,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:W126"/>
+  <dimension ref="A1:W126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.4"/>
   <cols>
     <col width="3.109375" customWidth="1" style="148" min="1" max="1"/>
@@ -2771,6 +2774,7 @@
     <col width="11.44140625" customWidth="1" style="148" min="22" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="48" t="n"/>
       <c r="C2" s="48" t="n"/>
@@ -5705,7 +5709,7 @@
     <row r="124" ht="27.6" customFormat="1" customHeight="1" s="123">
       <c r="B124" s="74" t="n"/>
       <c r="C124" s="74" t="n"/>
-      <c r="D124" s="306" t="inlineStr">
+      <c r="D124" s="307" t="inlineStr">
         <is>
           <t>{{TIPO_CONTRATO_MENSAJE}}</t>
         </is>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -79,7 +79,7 @@
     <definedName name="DUCELEC" localSheetId="0">#REF!</definedName>
     <definedName name="ESPECIALES" localSheetId="0">#REF!</definedName>
     <definedName name="EXP" localSheetId="0">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$136</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -307,7 +307,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -362,8 +362,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC7828"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="85">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -1303,12 +1313,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="341">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2282,6 +2312,123 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="85" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="86" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="86" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="86" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="85" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="86" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="86" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="86" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="48" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="51" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="10" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="61" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2749,7 +2896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W126"/>
+  <dimension ref="A1:W135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.4"/>
   <cols>
     <col width="3.109375" customWidth="1" style="148" min="1" max="1"/>
@@ -3074,7 +3221,7 @@
       <c r="C14" s="59" t="n"/>
       <c r="D14" s="144" t="inlineStr">
         <is>
-          <t>NO. TELEFONO:</t>
+          <t>NO. TELÉFONO:</t>
         </is>
       </c>
       <c r="E14" s="145" t="n"/>
@@ -3144,7 +3291,7 @@
       <c r="C16" s="59" t="n"/>
       <c r="D16" s="268" t="inlineStr">
         <is>
-          <t>NO. COTIZACION</t>
+          <t>NO. COTIZACIÓN</t>
         </is>
       </c>
       <c r="E16" s="269" t="n"/>
@@ -3208,7 +3355,7 @@
       <c r="K18" s="73" t="n"/>
       <c r="L18" s="203" t="inlineStr">
         <is>
-          <t>TIEMPOS DE PAGO CON RECEPCION DE FACTURA</t>
+          <t>TIEMPOS DE PAGO CON RECEPCIÓN DE FACTURA</t>
         </is>
       </c>
       <c r="M18" s="138" t="n"/>
@@ -3248,7 +3395,7 @@
       <c r="O19" s="139" t="n"/>
       <c r="P19" s="84" t="inlineStr">
         <is>
-          <t>15 DIAS</t>
+          <t>15 DÍAS</t>
         </is>
       </c>
       <c r="Q19" s="55" t="n"/>
@@ -3259,7 +3406,7 @@
       <c r="C20" s="74" t="n"/>
       <c r="D20" s="221" t="inlineStr">
         <is>
-          <t>Punto de acta firmado por contratista, genrete E4, lider E4</t>
+          <t>Punto de acta firmado por contratista, gerente E4, líder E4</t>
         </is>
       </c>
       <c r="E20" s="126" t="n"/>
@@ -3283,7 +3430,7 @@
       <c r="O20" s="139" t="n"/>
       <c r="P20" s="85" t="inlineStr">
         <is>
-          <t>30 DIAS</t>
+          <t>30 DÍAS</t>
         </is>
       </c>
       <c r="Q20" s="55" t="n"/>
@@ -3303,7 +3450,7 @@
       <c r="H21" s="127" t="n"/>
       <c r="I21" s="146" t="inlineStr">
         <is>
-          <t>anticipo / estimacion</t>
+          <t>anticipo / estimación</t>
         </is>
       </c>
       <c r="J21" s="126" t="n"/>
@@ -3318,7 +3465,7 @@
       <c r="O21" s="139" t="n"/>
       <c r="P21" s="84" t="inlineStr">
         <is>
-          <t>30 DIAS</t>
+          <t>30 DÍAS</t>
         </is>
       </c>
       <c r="Q21" s="55" t="n"/>
@@ -3373,7 +3520,7 @@
       <c r="H23" s="127" t="n"/>
       <c r="I23" s="146" t="inlineStr">
         <is>
-          <t>para estimacion</t>
+          <t>para estimación</t>
         </is>
       </c>
       <c r="J23" s="126" t="n"/>
@@ -3391,7 +3538,7 @@
       <c r="C24" s="74" t="n"/>
       <c r="D24" s="221" t="inlineStr">
         <is>
-          <t>Carta de garantia</t>
+          <t>Carta de garantía</t>
         </is>
       </c>
       <c r="E24" s="126" t="n"/>
@@ -3446,7 +3593,8 @@
       <c r="O25" s="139" t="n"/>
       <c r="P25" s="84" t="inlineStr">
         <is>
-          <t>Lunes de               8:00 AM- 4:00 PM</t>
+          <t>Lunes de
+8:00 AM a 4:00 PM</t>
         </is>
       </c>
       <c r="Q25" s="55" t="n"/>
@@ -3457,7 +3605,7 @@
       <c r="C26" s="74" t="n"/>
       <c r="D26" s="143" t="inlineStr">
         <is>
-          <t>TODO DOCUMENTO DE ESTIMACION Y ADELANTO DEBE IR FIRMADO POR EL CONTRATISTA</t>
+          <t>TODO DOCUMENTO DE ESTIMACIÓN Y ADELANTO DEBE IR FIRMADO POR EL CONTRATISTA</t>
         </is>
       </c>
       <c r="E26" s="138" t="n"/>
@@ -3477,7 +3625,8 @@
       <c r="O26" s="139" t="n"/>
       <c r="P26" s="85" t="inlineStr">
         <is>
-          <t>Lunes y Martes de 8:00 AM- 4:00 PM</t>
+          <t>Lunes y Martes de
+8:00 AM a 4:00 PM</t>
         </is>
       </c>
       <c r="Q26" s="55" t="n"/>
@@ -3504,7 +3653,8 @@
       <c r="O27" s="139" t="n"/>
       <c r="P27" s="84" t="inlineStr">
         <is>
-          <t>Lunes de               8:00 AM- 4:00 PM</t>
+          <t>Lunes de
+8:00 AM a 4:00 PM</t>
         </is>
       </c>
       <c r="Q27" s="68" t="n"/>
@@ -3584,7 +3734,7 @@
       <c r="O30" s="180" t="n"/>
       <c r="P30" s="9" t="inlineStr">
         <is>
-          <t>1% POR DIA</t>
+          <t>1% POR DÍA</t>
         </is>
       </c>
       <c r="Q30" s="55" t="n"/>
@@ -3665,7 +3815,7 @@
       <c r="C33" s="74" t="n"/>
       <c r="D33" s="124" t="inlineStr">
         <is>
-          <t>Reunión semanal con LIDER DE PROYECTO</t>
+          <t>Reunión semanal con LÍDER DE PROYECTO</t>
         </is>
       </c>
       <c r="E33" s="120" t="n"/>
@@ -3681,7 +3831,7 @@
       <c r="K33" s="55" t="n"/>
       <c r="L33" s="248" t="inlineStr">
         <is>
-          <t>Por no cumplir con documentos de reporteria semanal</t>
+          <t>Por no cumplir con documentos de reportería semanal</t>
         </is>
       </c>
       <c r="M33" s="182" t="n"/>
@@ -3743,7 +3893,7 @@
       <c r="K35" s="55" t="n"/>
       <c r="L35" s="159" t="inlineStr">
         <is>
-          <t>DOCUMENTO ENTREGADOS A CONTRATISTA POR PARTE DE E4</t>
+          <t>DOCUMENTOS ENTREGADOS A CONTRATISTA POR PARTE DE E4</t>
         </is>
       </c>
       <c r="Q35" s="55" t="n"/>
@@ -3792,7 +3942,7 @@
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="221" t="inlineStr">
         <is>
-          <t>Politica de recepcion de facturas y pagos</t>
+          <t>Política de recepción de facturas y pagos</t>
         </is>
       </c>
       <c r="M37" s="126" t="n"/>
@@ -3827,7 +3977,7 @@
       <c r="K38" s="55" t="n"/>
       <c r="L38" s="125" t="inlineStr">
         <is>
-          <t>Politica de SSO en obra</t>
+          <t>Política de SSO en obra</t>
         </is>
       </c>
       <c r="M38" s="126" t="n"/>
@@ -4130,7 +4280,7 @@
       </c>
       <c r="E49" s="154" t="inlineStr">
         <is>
-          <t>DESCRIPCION</t>
+          <t>DESCRIPCIÓN</t>
         </is>
       </c>
       <c r="K49" s="154" t="inlineStr">
@@ -4165,102 +4315,102 @@
     <row r="50" ht="69.90000000000001" customHeight="1">
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="23" t="n"/>
-      <c r="D50" s="293" t="n"/>
-      <c r="E50" s="247" t="n"/>
+      <c r="D50" s="308" t="n"/>
+      <c r="E50" s="309" t="n"/>
       <c r="F50" s="161" t="n"/>
       <c r="G50" s="161" t="n"/>
       <c r="H50" s="161" t="n"/>
       <c r="I50" s="161" t="n"/>
-      <c r="J50" s="133" t="n"/>
+      <c r="J50" s="310" t="n"/>
       <c r="K50" s="26" t="n"/>
-      <c r="L50" s="27" t="n"/>
+      <c r="L50" s="311" t="n"/>
       <c r="M50" s="28" t="n"/>
-      <c r="N50" s="184" t="n"/>
-      <c r="O50" s="133" t="n"/>
+      <c r="N50" s="312" t="n"/>
+      <c r="O50" s="310" t="n"/>
       <c r="P50" s="29" t="n"/>
     </row>
     <row r="51" ht="68.09999999999999" customHeight="1">
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="23" t="n"/>
-      <c r="D51" s="294" t="n"/>
-      <c r="E51" s="178" t="n"/>
+      <c r="D51" s="313" t="n"/>
+      <c r="E51" s="314" t="n"/>
       <c r="F51" s="161" t="n"/>
       <c r="G51" s="161" t="n"/>
       <c r="H51" s="161" t="n"/>
       <c r="I51" s="161" t="n"/>
-      <c r="J51" s="133" t="n"/>
+      <c r="J51" s="310" t="n"/>
       <c r="K51" s="31" t="n"/>
-      <c r="L51" s="32" t="n"/>
+      <c r="L51" s="315" t="n"/>
       <c r="M51" s="33" t="n"/>
-      <c r="N51" s="132" t="n"/>
-      <c r="O51" s="133" t="n"/>
+      <c r="N51" s="316" t="n"/>
+      <c r="O51" s="310" t="n"/>
       <c r="P51" s="34" t="n"/>
     </row>
     <row r="52" ht="68.09999999999999" customHeight="1">
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="23" t="n"/>
-      <c r="D52" s="293" t="n"/>
-      <c r="E52" s="247" t="n"/>
+      <c r="D52" s="308" t="n"/>
+      <c r="E52" s="309" t="n"/>
       <c r="F52" s="161" t="n"/>
       <c r="G52" s="161" t="n"/>
       <c r="H52" s="161" t="n"/>
       <c r="I52" s="161" t="n"/>
-      <c r="J52" s="133" t="n"/>
+      <c r="J52" s="310" t="n"/>
       <c r="K52" s="26" t="n"/>
-      <c r="L52" s="27" t="n"/>
+      <c r="L52" s="311" t="n"/>
       <c r="M52" s="28" t="n"/>
-      <c r="N52" s="184" t="n"/>
-      <c r="O52" s="133" t="n"/>
+      <c r="N52" s="312" t="n"/>
+      <c r="O52" s="310" t="n"/>
       <c r="P52" s="29" t="n"/>
     </row>
     <row r="53" ht="69.90000000000001" customHeight="1">
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="23" t="n"/>
-      <c r="D53" s="294" t="n"/>
-      <c r="E53" s="178" t="n"/>
+      <c r="D53" s="313" t="n"/>
+      <c r="E53" s="314" t="n"/>
       <c r="F53" s="161" t="n"/>
       <c r="G53" s="161" t="n"/>
       <c r="H53" s="161" t="n"/>
       <c r="I53" s="161" t="n"/>
-      <c r="J53" s="133" t="n"/>
+      <c r="J53" s="310" t="n"/>
       <c r="K53" s="31" t="n"/>
-      <c r="L53" s="32" t="n"/>
+      <c r="L53" s="315" t="n"/>
       <c r="M53" s="33" t="n"/>
-      <c r="N53" s="132" t="n"/>
-      <c r="O53" s="133" t="n"/>
+      <c r="N53" s="316" t="n"/>
+      <c r="O53" s="310" t="n"/>
       <c r="P53" s="34" t="n"/>
     </row>
     <row r="54" ht="69.90000000000001" customHeight="1">
       <c r="B54" s="23" t="n"/>
-      <c r="D54" s="293" t="n"/>
-      <c r="E54" s="247" t="n"/>
+      <c r="D54" s="308" t="n"/>
+      <c r="E54" s="309" t="n"/>
       <c r="F54" s="161" t="n"/>
       <c r="G54" s="161" t="n"/>
       <c r="H54" s="161" t="n"/>
       <c r="I54" s="161" t="n"/>
-      <c r="J54" s="133" t="n"/>
+      <c r="J54" s="310" t="n"/>
       <c r="K54" s="26" t="n"/>
-      <c r="L54" s="27" t="n"/>
+      <c r="L54" s="311" t="n"/>
       <c r="M54" s="28" t="n"/>
-      <c r="N54" s="184" t="n"/>
-      <c r="O54" s="133" t="n"/>
+      <c r="N54" s="312" t="n"/>
+      <c r="O54" s="310" t="n"/>
       <c r="P54" s="29" t="n"/>
     </row>
     <row r="55" ht="66.90000000000001" customHeight="1">
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="23" t="n"/>
-      <c r="D55" s="294" t="n"/>
-      <c r="E55" s="178" t="n"/>
+      <c r="D55" s="313" t="n"/>
+      <c r="E55" s="314" t="n"/>
       <c r="F55" s="161" t="n"/>
       <c r="G55" s="161" t="n"/>
       <c r="H55" s="161" t="n"/>
       <c r="I55" s="161" t="n"/>
-      <c r="J55" s="133" t="n"/>
+      <c r="J55" s="310" t="n"/>
       <c r="K55" s="31" t="n"/>
-      <c r="L55" s="32" t="n"/>
+      <c r="L55" s="315" t="n"/>
       <c r="M55" s="33" t="n"/>
-      <c r="N55" s="132" t="n"/>
-      <c r="O55" s="133" t="n"/>
+      <c r="N55" s="316" t="n"/>
+      <c r="O55" s="310" t="n"/>
       <c r="P55" s="34" t="n"/>
     </row>
     <row r="56" ht="21.9" customHeight="1">
@@ -4357,7 +4507,7 @@
     <row r="60" ht="21" customHeight="1">
       <c r="B60" s="74" t="n"/>
       <c r="C60" s="74" t="n"/>
-      <c r="D60" s="282" t="inlineStr">
+      <c r="D60" s="317" t="inlineStr">
         <is>
           <t>PROGRAMACIÓN DE FECHAS</t>
         </is>
@@ -4368,32 +4518,32 @@
     <row r="61" customFormat="1" s="123">
       <c r="B61" s="74" t="n"/>
       <c r="C61" s="74" t="n"/>
-      <c r="D61" s="283" t="inlineStr">
+      <c r="D61" s="318" t="inlineStr">
         <is>
           <t>ÁREA</t>
         </is>
       </c>
       <c r="E61" s="258" t="n"/>
       <c r="F61" s="259" t="n"/>
-      <c r="G61" s="284" t="inlineStr">
+      <c r="G61" s="319" t="inlineStr">
         <is>
           <t>INICIO</t>
         </is>
       </c>
       <c r="H61" s="191" t="n"/>
-      <c r="I61" s="285" t="inlineStr">
+      <c r="I61" s="320" t="inlineStr">
         <is>
           <t>TERMINA</t>
         </is>
       </c>
       <c r="J61" s="194" t="n"/>
-      <c r="K61" s="286" t="inlineStr">
-        <is>
-          <t>DIAS</t>
+      <c r="K61" s="321" t="inlineStr">
+        <is>
+          <t>DÍAS</t>
         </is>
       </c>
       <c r="L61" s="118" t="n"/>
-      <c r="M61" s="286" t="inlineStr">
+      <c r="M61" s="321" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
@@ -4436,16 +4586,16 @@
     <row r="63" ht="21" customHeight="1">
       <c r="B63" s="74" t="n"/>
       <c r="C63" s="74" t="n"/>
-      <c r="D63" s="276" t="n"/>
+      <c r="D63" s="322" t="n"/>
       <c r="E63" s="129" t="n"/>
       <c r="F63" s="130" t="n"/>
-      <c r="G63" s="210" t="n"/>
+      <c r="G63" s="323" t="n"/>
       <c r="H63" s="129" t="n"/>
-      <c r="I63" s="253" t="n"/>
+      <c r="I63" s="324" t="n"/>
       <c r="J63" s="196" t="n"/>
-      <c r="K63" s="253" t="n"/>
+      <c r="K63" s="324" t="n"/>
       <c r="L63" s="196" t="n"/>
-      <c r="M63" s="222" t="n"/>
+      <c r="M63" s="325" t="n"/>
       <c r="N63" s="129" t="n"/>
       <c r="O63" s="129" t="n"/>
       <c r="P63" s="130" t="n"/>
@@ -4480,16 +4630,16 @@
     <row r="65" ht="20.4" customFormat="1" customHeight="1" s="123">
       <c r="B65" s="74" t="n"/>
       <c r="C65" s="74" t="n"/>
-      <c r="D65" s="131" t="n"/>
+      <c r="D65" s="326" t="n"/>
       <c r="E65" s="129" t="n"/>
       <c r="F65" s="130" t="n"/>
-      <c r="G65" s="210" t="n"/>
+      <c r="G65" s="323" t="n"/>
       <c r="H65" s="129" t="n"/>
-      <c r="I65" s="253" t="n"/>
+      <c r="I65" s="324" t="n"/>
       <c r="J65" s="196" t="n"/>
-      <c r="K65" s="253" t="n"/>
+      <c r="K65" s="324" t="n"/>
       <c r="L65" s="196" t="n"/>
-      <c r="M65" s="222" t="n"/>
+      <c r="M65" s="325" t="n"/>
       <c r="N65" s="129" t="n"/>
       <c r="O65" s="129" t="n"/>
       <c r="P65" s="130" t="n"/>
@@ -4537,12 +4687,12 @@
     <row r="68" ht="24.9" customHeight="1">
       <c r="B68" s="74" t="n"/>
       <c r="C68" s="74" t="n"/>
-      <c r="D68" s="283" t="inlineStr">
+      <c r="D68" s="318" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E68" s="287" t="inlineStr">
+      <c r="E68" s="327" t="inlineStr">
         <is>
           <t>TRABAJOS PREVIOS A INICIAR</t>
         </is>
@@ -4589,10 +4739,10 @@
     <row r="70" ht="25.8" customHeight="1">
       <c r="B70" s="74" t="n"/>
       <c r="C70" s="74" t="n"/>
-      <c r="D70" s="110" t="n">
+      <c r="D70" s="328" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="303" t="n"/>
+      <c r="E70" s="329" t="n"/>
       <c r="F70" s="187" t="n"/>
       <c r="G70" s="187" t="n"/>
       <c r="H70" s="187" t="n"/>
@@ -4629,10 +4779,10 @@
     <row r="72" ht="24.9" customHeight="1">
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="110" t="n">
+      <c r="D72" s="328" t="n">
         <v>4</v>
       </c>
-      <c r="E72" s="207" t="n"/>
+      <c r="E72" s="330" t="n"/>
       <c r="F72" s="129" t="n"/>
       <c r="G72" s="129" t="n"/>
       <c r="H72" s="129" t="n"/>
@@ -4684,14 +4834,14 @@
     <row r="75" ht="24.9" customHeight="1">
       <c r="B75" s="74" t="n"/>
       <c r="C75" s="74" t="n"/>
-      <c r="D75" s="298" t="inlineStr">
+      <c r="D75" s="331" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E75" s="299" t="inlineStr">
-        <is>
-          <t>SERVICIOS BASICOS NECESARIOS PARA TRABAJAR</t>
+      <c r="E75" s="332" t="inlineStr">
+        <is>
+          <t>SERVICIOS BÁSICOS NECESARIOS PARA TRABAJAR</t>
         </is>
       </c>
       <c r="F75" s="117" t="n"/>
@@ -4736,10 +4886,10 @@
     <row r="77" ht="24.9" customHeight="1">
       <c r="B77" s="74" t="n"/>
       <c r="C77" s="74" t="n"/>
-      <c r="D77" s="110" t="n">
+      <c r="D77" s="328" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="305" t="n"/>
+      <c r="E77" s="333" t="n"/>
       <c r="F77" s="187" t="n"/>
       <c r="G77" s="187" t="n"/>
       <c r="H77" s="187" t="n"/>
@@ -4778,10 +4928,10 @@
     <row r="79" ht="27" customHeight="1">
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="110" t="n">
+      <c r="D79" s="328" t="n">
         <v>4</v>
       </c>
-      <c r="E79" s="254" t="n"/>
+      <c r="E79" s="334" t="n"/>
       <c r="F79" s="129" t="n"/>
       <c r="G79" s="129" t="n"/>
       <c r="H79" s="129" t="n"/>
@@ -4852,12 +5002,12 @@
     <row r="83" ht="24.9" customHeight="1">
       <c r="B83" s="8" t="n"/>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="290" t="inlineStr">
+      <c r="D83" s="335" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="E83" s="291" t="inlineStr">
+      <c r="E83" s="336" t="inlineStr">
         <is>
           <t>PUNTOS DE REVISIÓN ESPECÍFICA PARA RECEPCIÓN DE TRABAJOS</t>
         </is>
@@ -4893,10 +5043,10 @@
     <row r="85" ht="26.4" customHeight="1">
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="155" t="n">
+      <c r="D85" s="337" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="301" t="n"/>
+      <c r="E85" s="338" t="n"/>
       <c r="F85" s="156" t="n"/>
       <c r="G85" s="156" t="n"/>
       <c r="H85" s="156" t="n"/>
@@ -4932,7 +5082,7 @@
       <c r="N86" s="4" t="n"/>
       <c r="O86" s="242" t="inlineStr">
         <is>
-          <t>Cartas firmadas por Lider de Proyecto y Maestro de obras, con fotografias de avance, cuadro de cantidades y renglones</t>
+          <t>Cartas firmadas por Líder de Proyecto y Maestro de obras, con fotografías de avance, cuadro de cantidades y renglones</t>
         </is>
       </c>
       <c r="Q86" s="44" t="n"/>
@@ -4946,10 +5096,10 @@
     <row r="87" ht="26.4" customHeight="1">
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="155" t="n">
+      <c r="D87" s="337" t="n">
         <v>4</v>
       </c>
-      <c r="E87" s="134" t="n"/>
+      <c r="E87" s="339" t="n"/>
       <c r="F87" s="135" t="n"/>
       <c r="G87" s="135" t="n"/>
       <c r="H87" s="135" t="n"/>
@@ -4984,10 +5134,10 @@
     <row r="89" ht="27.6" customHeight="1">
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
-      <c r="D89" s="155" t="n">
+      <c r="D89" s="337" t="n">
         <v>6</v>
       </c>
-      <c r="E89" s="134" t="n"/>
+      <c r="E89" s="339" t="n"/>
       <c r="F89" s="135" t="n"/>
       <c r="G89" s="135" t="n"/>
       <c r="H89" s="135" t="n"/>
@@ -5026,10 +5176,10 @@
     <row r="91" ht="27.6" customHeight="1">
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="155" t="n">
+      <c r="D91" s="337" t="n">
         <v>8</v>
       </c>
-      <c r="E91" s="134" t="n"/>
+      <c r="E91" s="339" t="n"/>
       <c r="F91" s="135" t="n"/>
       <c r="G91" s="135" t="n"/>
       <c r="H91" s="135" t="n"/>
@@ -5071,10 +5221,10 @@
     <row r="93" ht="27.6" customHeight="1">
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="155" t="n">
+      <c r="D93" s="337" t="n">
         <v>10</v>
       </c>
-      <c r="E93" s="134" t="n"/>
+      <c r="E93" s="339" t="n"/>
       <c r="F93" s="135" t="n"/>
       <c r="G93" s="135" t="n"/>
       <c r="H93" s="135" t="n"/>
@@ -5086,7 +5236,7 @@
       <c r="N93" s="5" t="n"/>
       <c r="O93" s="242" t="inlineStr">
         <is>
-          <t>Contratista es el unico responsable de cumplir con los pagos directo a su personal en obra, tanto salario pactado como prestaciones en dado apliquen, quitando responsabilidad a E4 ante cualquier inconveniente</t>
+          <t>Contratista es el único responsable de cumplir con los pagos directo a su personal en obra, tanto salario pactado como prestaciones en dado caso apliquen, quitando responsabilidad a E4 ante cualquier inconveniente</t>
         </is>
       </c>
       <c r="Q93" s="44" t="n"/>
@@ -5114,10 +5264,10 @@
     <row r="95" ht="27.6" customHeight="1">
       <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="155" t="n">
+      <c r="D95" s="337" t="n">
         <v>12</v>
       </c>
-      <c r="E95" s="134" t="n"/>
+      <c r="E95" s="339" t="n"/>
       <c r="F95" s="135" t="n"/>
       <c r="G95" s="135" t="n"/>
       <c r="H95" s="135" t="n"/>
@@ -5152,10 +5302,10 @@
     <row r="97" ht="27.6" customHeight="1">
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="155" t="n">
+      <c r="D97" s="337" t="n">
         <v>14</v>
       </c>
-      <c r="E97" s="134" t="n"/>
+      <c r="E97" s="339" t="n"/>
       <c r="F97" s="135" t="n"/>
       <c r="G97" s="135" t="n"/>
       <c r="H97" s="135" t="n"/>
@@ -5194,10 +5344,10 @@
     <row r="99" ht="27.6" customHeight="1">
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="155" t="n">
+      <c r="D99" s="337" t="n">
         <v>16</v>
       </c>
-      <c r="E99" s="134" t="n"/>
+      <c r="E99" s="339" t="n"/>
       <c r="F99" s="135" t="n"/>
       <c r="G99" s="135" t="n"/>
       <c r="H99" s="135" t="n"/>
@@ -5242,10 +5392,10 @@
     <row r="101" ht="27.6" customHeight="1">
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="155" t="n">
+      <c r="D101" s="337" t="n">
         <v>18</v>
       </c>
-      <c r="E101" s="134" t="n"/>
+      <c r="E101" s="339" t="n"/>
       <c r="F101" s="135" t="n"/>
       <c r="G101" s="135" t="n"/>
       <c r="H101" s="135" t="n"/>
@@ -5280,10 +5430,10 @@
     <row r="103" ht="27.6" customHeight="1">
       <c r="B103" s="8" t="n"/>
       <c r="C103" s="8" t="n"/>
-      <c r="D103" s="155" t="n">
+      <c r="D103" s="337" t="n">
         <v>20</v>
       </c>
-      <c r="E103" s="134" t="n"/>
+      <c r="E103" s="339" t="n"/>
       <c r="F103" s="135" t="n"/>
       <c r="G103" s="135" t="n"/>
       <c r="H103" s="135" t="n"/>
@@ -5318,10 +5468,10 @@
     <row r="105" ht="27.6" customHeight="1">
       <c r="B105" s="8" t="n"/>
       <c r="C105" s="8" t="n"/>
-      <c r="D105" s="155" t="n">
+      <c r="D105" s="337" t="n">
         <v>22</v>
       </c>
-      <c r="E105" s="134" t="n"/>
+      <c r="E105" s="339" t="n"/>
       <c r="F105" s="135" t="n"/>
       <c r="G105" s="135" t="n"/>
       <c r="H105" s="135" t="n"/>
@@ -5360,10 +5510,10 @@
     <row r="107" ht="27.6" customHeight="1">
       <c r="B107" s="8" t="n"/>
       <c r="C107" s="8" t="n"/>
-      <c r="D107" s="155" t="n">
+      <c r="D107" s="337" t="n">
         <v>24</v>
       </c>
-      <c r="E107" s="134" t="n"/>
+      <c r="E107" s="339" t="n"/>
       <c r="F107" s="135" t="n"/>
       <c r="G107" s="135" t="n"/>
       <c r="H107" s="135" t="n"/>
@@ -5398,10 +5548,10 @@
     <row r="109" ht="27.6" customHeight="1">
       <c r="B109" s="8" t="n"/>
       <c r="C109" s="8" t="n"/>
-      <c r="D109" s="155" t="n">
+      <c r="D109" s="337" t="n">
         <v>26</v>
       </c>
-      <c r="E109" s="134" t="n"/>
+      <c r="E109" s="339" t="n"/>
       <c r="F109" s="135" t="n"/>
       <c r="G109" s="135" t="n"/>
       <c r="H109" s="135" t="n"/>
@@ -5436,10 +5586,10 @@
     <row r="111" ht="27.6" customHeight="1" thickBot="1">
       <c r="B111" s="8" t="n"/>
       <c r="C111" s="8" t="n"/>
-      <c r="D111" s="155" t="n">
+      <c r="D111" s="337" t="n">
         <v>28</v>
       </c>
-      <c r="E111" s="134" t="n"/>
+      <c r="E111" s="339" t="n"/>
       <c r="F111" s="135" t="n"/>
       <c r="G111" s="135" t="n"/>
       <c r="H111" s="135" t="n"/>
@@ -5499,9 +5649,9 @@
     <row r="114" ht="28.8" customHeight="1">
       <c r="B114" s="74" t="n"/>
       <c r="C114" s="74" t="n"/>
-      <c r="D114" s="214" t="inlineStr">
-        <is>
-          <t>AREA DE FIRMAS</t>
+      <c r="D114" s="340" t="inlineStr">
+        <is>
+          <t>ÁREA DE FIRMAS</t>
         </is>
       </c>
       <c r="Q114" s="55" t="n"/>
@@ -5736,12 +5886,207 @@
       <c r="Q125" s="55" t="n"/>
       <c r="R125" s="55" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="18" customHeight="1">
       <c r="Q126" s="55" t="n"/>
       <c r="R126" s="55" t="n"/>
     </row>
+    <row r="127" ht="24.9" customHeight="1">
+      <c r="B127" s="74" t="n"/>
+      <c r="C127" s="74" t="n"/>
+      <c r="D127" s="318" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="E127" s="327" t="inlineStr">
+        <is>
+          <t>ANEXOS: DOCUMENTOS ADJUNTOS A LA SOLICITUD</t>
+        </is>
+      </c>
+      <c r="F127" s="117" t="n"/>
+      <c r="G127" s="117" t="n"/>
+      <c r="H127" s="117" t="n"/>
+      <c r="I127" s="117" t="n"/>
+      <c r="J127" s="117" t="n"/>
+      <c r="K127" s="117" t="n"/>
+      <c r="L127" s="117" t="n"/>
+      <c r="M127" s="117" t="n"/>
+      <c r="N127" s="117" t="n"/>
+      <c r="O127" s="117" t="n"/>
+      <c r="P127" s="118" t="n"/>
+      <c r="Q127" s="55" t="n"/>
+      <c r="R127" s="55" t="n"/>
+    </row>
+    <row r="128" ht="24.9" customHeight="1">
+      <c r="B128" s="74" t="n"/>
+      <c r="C128" s="99" t="n"/>
+      <c r="D128" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="302" t="n"/>
+      <c r="F128" s="187" t="n"/>
+      <c r="G128" s="187" t="n"/>
+      <c r="H128" s="187" t="n"/>
+      <c r="I128" s="187" t="n"/>
+      <c r="J128" s="187" t="n"/>
+      <c r="K128" s="187" t="n"/>
+      <c r="L128" s="187" t="n"/>
+      <c r="M128" s="187" t="n"/>
+      <c r="N128" s="187" t="n"/>
+      <c r="O128" s="187" t="n"/>
+      <c r="P128" s="188" t="n"/>
+      <c r="Q128" s="99" t="n"/>
+      <c r="R128" s="99" t="n"/>
+    </row>
+    <row r="129" ht="25.8" customHeight="1">
+      <c r="B129" s="74" t="n"/>
+      <c r="C129" s="74" t="n"/>
+      <c r="D129" s="328" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" s="329" t="n"/>
+      <c r="F129" s="187" t="n"/>
+      <c r="G129" s="187" t="n"/>
+      <c r="H129" s="187" t="n"/>
+      <c r="I129" s="187" t="n"/>
+      <c r="J129" s="187" t="n"/>
+      <c r="K129" s="187" t="n"/>
+      <c r="L129" s="187" t="n"/>
+      <c r="M129" s="187" t="n"/>
+      <c r="N129" s="187" t="n"/>
+      <c r="O129" s="187" t="n"/>
+      <c r="P129" s="188" t="n"/>
+      <c r="Q129" s="55" t="n"/>
+      <c r="R129" s="55" t="n"/>
+    </row>
+    <row r="130" ht="24.9" customHeight="1">
+      <c r="B130" s="74" t="n"/>
+      <c r="C130" s="99" t="n"/>
+      <c r="D130" s="108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" s="302" t="n"/>
+      <c r="F130" s="187" t="n"/>
+      <c r="G130" s="187" t="n"/>
+      <c r="H130" s="187" t="n"/>
+      <c r="I130" s="187" t="n"/>
+      <c r="J130" s="187" t="n"/>
+      <c r="K130" s="187" t="n"/>
+      <c r="L130" s="187" t="n"/>
+      <c r="M130" s="187" t="n"/>
+      <c r="N130" s="187" t="n"/>
+      <c r="O130" s="187" t="n"/>
+      <c r="P130" s="188" t="n"/>
+      <c r="Q130" s="99" t="n"/>
+      <c r="R130" s="99" t="n"/>
+    </row>
+    <row r="131" ht="25.8" customHeight="1">
+      <c r="B131" s="74" t="n"/>
+      <c r="C131" s="74" t="n"/>
+      <c r="D131" s="328" t="n">
+        <v>4</v>
+      </c>
+      <c r="E131" s="329" t="n"/>
+      <c r="F131" s="187" t="n"/>
+      <c r="G131" s="187" t="n"/>
+      <c r="H131" s="187" t="n"/>
+      <c r="I131" s="187" t="n"/>
+      <c r="J131" s="187" t="n"/>
+      <c r="K131" s="187" t="n"/>
+      <c r="L131" s="187" t="n"/>
+      <c r="M131" s="187" t="n"/>
+      <c r="N131" s="187" t="n"/>
+      <c r="O131" s="187" t="n"/>
+      <c r="P131" s="188" t="n"/>
+      <c r="Q131" s="55" t="n"/>
+      <c r="R131" s="55" t="n"/>
+    </row>
+    <row r="132" ht="24.9" customHeight="1">
+      <c r="B132" s="74" t="n"/>
+      <c r="C132" s="99" t="n"/>
+      <c r="D132" s="108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E132" s="302" t="n"/>
+      <c r="F132" s="187" t="n"/>
+      <c r="G132" s="187" t="n"/>
+      <c r="H132" s="187" t="n"/>
+      <c r="I132" s="187" t="n"/>
+      <c r="J132" s="187" t="n"/>
+      <c r="K132" s="187" t="n"/>
+      <c r="L132" s="187" t="n"/>
+      <c r="M132" s="187" t="n"/>
+      <c r="N132" s="187" t="n"/>
+      <c r="O132" s="187" t="n"/>
+      <c r="P132" s="188" t="n"/>
+      <c r="Q132" s="99" t="n"/>
+      <c r="R132" s="99" t="n"/>
+    </row>
+    <row r="133" ht="25.8" customHeight="1">
+      <c r="B133" s="74" t="n"/>
+      <c r="C133" s="74" t="n"/>
+      <c r="D133" s="328" t="n">
+        <v>6</v>
+      </c>
+      <c r="E133" s="329" t="n"/>
+      <c r="F133" s="187" t="n"/>
+      <c r="G133" s="187" t="n"/>
+      <c r="H133" s="187" t="n"/>
+      <c r="I133" s="187" t="n"/>
+      <c r="J133" s="187" t="n"/>
+      <c r="K133" s="187" t="n"/>
+      <c r="L133" s="187" t="n"/>
+      <c r="M133" s="187" t="n"/>
+      <c r="N133" s="187" t="n"/>
+      <c r="O133" s="187" t="n"/>
+      <c r="P133" s="188" t="n"/>
+      <c r="Q133" s="55" t="n"/>
+      <c r="R133" s="55" t="n"/>
+    </row>
+    <row r="134" ht="24.9" customHeight="1">
+      <c r="B134" s="74" t="n"/>
+      <c r="C134" s="99" t="n"/>
+      <c r="D134" s="108" t="n">
+        <v>7</v>
+      </c>
+      <c r="E134" s="302" t="n"/>
+      <c r="F134" s="187" t="n"/>
+      <c r="G134" s="187" t="n"/>
+      <c r="H134" s="187" t="n"/>
+      <c r="I134" s="187" t="n"/>
+      <c r="J134" s="187" t="n"/>
+      <c r="K134" s="187" t="n"/>
+      <c r="L134" s="187" t="n"/>
+      <c r="M134" s="187" t="n"/>
+      <c r="N134" s="187" t="n"/>
+      <c r="O134" s="187" t="n"/>
+      <c r="P134" s="188" t="n"/>
+      <c r="Q134" s="99" t="n"/>
+      <c r="R134" s="99" t="n"/>
+    </row>
+    <row r="135" ht="25.8" customHeight="1">
+      <c r="B135" s="74" t="n"/>
+      <c r="C135" s="74" t="n"/>
+      <c r="D135" s="328" t="n">
+        <v>8</v>
+      </c>
+      <c r="E135" s="329" t="n"/>
+      <c r="F135" s="187" t="n"/>
+      <c r="G135" s="187" t="n"/>
+      <c r="H135" s="187" t="n"/>
+      <c r="I135" s="187" t="n"/>
+      <c r="J135" s="187" t="n"/>
+      <c r="K135" s="187" t="n"/>
+      <c r="L135" s="187" t="n"/>
+      <c r="M135" s="187" t="n"/>
+      <c r="N135" s="187" t="n"/>
+      <c r="O135" s="187" t="n"/>
+      <c r="P135" s="188" t="n"/>
+      <c r="Q135" s="55" t="n"/>
+      <c r="R135" s="55" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="207">
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="H123:J123"/>
     <mergeCell ref="D116:F116"/>
@@ -5785,6 +6130,7 @@
     <mergeCell ref="D45:I45"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="L38:O38"/>
+    <mergeCell ref="E135:P135"/>
     <mergeCell ref="E51:J51"/>
     <mergeCell ref="L31:O31"/>
     <mergeCell ref="L40:O40"/>
@@ -5802,6 +6148,7 @@
     <mergeCell ref="E77:P77"/>
     <mergeCell ref="E104:M104"/>
     <mergeCell ref="E49:J49"/>
+    <mergeCell ref="E133:P133"/>
     <mergeCell ref="E80:P80"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="K63:L63"/>
@@ -5816,6 +6163,7 @@
     <mergeCell ref="D33:I33"/>
     <mergeCell ref="D42:I42"/>
     <mergeCell ref="E72:P72"/>
+    <mergeCell ref="E134:P134"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="G65:H65"/>
@@ -5891,17 +6239,21 @@
     <mergeCell ref="G63:H63"/>
     <mergeCell ref="K65:L65"/>
     <mergeCell ref="I63:J63"/>
+    <mergeCell ref="E127:P127"/>
     <mergeCell ref="D14:E14"/>
+    <mergeCell ref="E129:P129"/>
     <mergeCell ref="E88:M88"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="E79:P79"/>
     <mergeCell ref="L25:O25"/>
     <mergeCell ref="E73:P73"/>
     <mergeCell ref="I65:J65"/>
+    <mergeCell ref="E131:P131"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D18:J18"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="F16:J16"/>
+    <mergeCell ref="E128:P128"/>
     <mergeCell ref="O116:P116"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="M66:P66"/>
@@ -5930,6 +6282,7 @@
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="L15:O15"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="E130:P130"/>
     <mergeCell ref="E68:P68"/>
     <mergeCell ref="O122:P122"/>
     <mergeCell ref="D46:I46"/>
@@ -5937,6 +6290,7 @@
     <mergeCell ref="E111:M111"/>
     <mergeCell ref="D40:I40"/>
     <mergeCell ref="D65:F65"/>
+    <mergeCell ref="E132:P132"/>
     <mergeCell ref="N49:O49"/>
     <mergeCell ref="K62:L62"/>
     <mergeCell ref="E87:M87"/>
